--- a/premise/data/additional_inventories/lci-battery-capacity.xlsx
+++ b/premise/data/additional_inventories/lci-battery-capacity.xlsx
@@ -1792,8 +1792,10 @@
       <c r="A69" t="s">
         <v>1</v>
       </c>
-      <c r="B69" t="s">
-        <v>72</v>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Provides 1 kWh gross battery capacity using a Li-ion NMC955 pack. The complete-pack manufacturing recipe in lci-batteries-NMC955-LTO.xlsx contains 0.72591 kg cells per kg pack (72.591% cells, 27.409% other pack components). Use this manufactured cell fraction instead of the former generic 71% assumption. At the retained 2020 cell energy densities (minimum/mean/maximum) of 0.300/0.340/0.380 kWh per kg cell, pack mass is 1/(cell density * cell mass share): mean 4.051709537805285 kg/kWh, range 3.625213796983677 to 4.591937476179324 kg/kWh. Manufacturing and end of life use equal pack mass; signed disposal bounds mirror the manufacturing bounds. Source density/lifetime parameters: Hasselwander et al. (2023), https://doi.org/10.3390/batteries9070379. The source lifetime of 1000-1500 cycles and the existing future density trajectory remain modelling assumptions. Matching cell fraction is an allocation correction, not validation of practical cell performance. Rebuild scenario databases to apply.</t>
+        </is>
       </c>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.2">
@@ -1834,8 +1836,8 @@
         <v>48</v>
       </c>
       <c r="B74">
-        <f>1-0.29</f>
-        <v>0.71</v>
+        <f>0.72591</f>
+        <v>0.72591000000000006</v>
       </c>
     </row>
     <row r="75" spans="1:14" ht="16" x14ac:dyDescent="0.2">
@@ -1906,8 +1908,8 @@
         <v>63</v>
       </c>
       <c r="B78" s="3">
-        <f>1/(0.34*71%)</f>
-        <v>4.1425020712510356</v>
+        <f>1/(0.34*$B$74)</f>
+        <v>4.0517095378052854</v>
       </c>
       <c r="C78" t="s">
         <v>7</v>
@@ -1926,15 +1928,15 @@
       </c>
       <c r="H78" s="7">
         <f>B78</f>
-        <v>4.1425020712510356</v>
+        <v>4.0517095378052854</v>
       </c>
       <c r="I78" s="3">
-        <f>1/(0.38*71%)</f>
-        <v>3.7064492216456637</v>
+        <f>1/(0.38*$B$74)</f>
+        <v>3.6252137969836769</v>
       </c>
       <c r="J78" s="3">
-        <f>1/(0.3*71%)</f>
-        <v>4.694835680751174</v>
+        <f>1/(0.3*$B$74)</f>
+        <v>4.5919374761793241</v>
       </c>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.2">
@@ -1943,7 +1945,7 @@
       </c>
       <c r="B79" s="3">
         <f>-1*B78</f>
-        <v>-4.1425020712510356</v>
+        <v>-4.0517095378052854</v>
       </c>
       <c r="C79" t="s">
         <v>7</v>
@@ -1962,15 +1964,15 @@
       </c>
       <c r="H79" s="7">
         <f>B79</f>
-        <v>-4.1425020712510356</v>
+        <v>-4.0517095378052854</v>
       </c>
       <c r="I79" s="3">
-        <f>-1/(0.3*71%)</f>
-        <v>-4.694835680751174</v>
+        <f>-J78</f>
+        <v>-4.5919374761793241</v>
       </c>
       <c r="J79" s="3">
-        <f>-1/(0.38*71%)</f>
-        <v>-3.7064492216456637</v>
+        <f>-I78</f>
+        <v>-3.6252137969836769</v>
       </c>
       <c r="K79" t="b">
         <v>1</v>
@@ -5901,8 +5903,10 @@
       <c r="A67" t="s">
         <v>1</v>
       </c>
-      <c r="B67" t="s">
-        <v>72</v>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Provides 1 kWh gross battery capacity using a Li-ion NMC955 pack. The complete-pack manufacturing recipe in lci-batteries-NMC955-LTO.xlsx contains 0.72591 kg cells per kg pack (72.591% cells, 27.409% other pack components). Use this manufactured cell fraction instead of the former generic 71% assumption. At the retained 2020 cell energy densities (minimum/mean/maximum) of 0.300/0.340/0.380 kWh per kg cell, pack mass is 1/(cell density * cell mass share): mean 4.051709537805285 kg/kWh, range 3.625213796983677 to 4.591937476179324 kg/kWh. Manufacturing and end of life use equal pack mass; signed disposal bounds mirror the manufacturing bounds. Source density/lifetime parameters: Hasselwander et al. (2023), https://doi.org/10.3390/batteries9070379. The source lifetime of 1000-1500 cycles and the existing future density trajectory remain modelling assumptions. Matching cell fraction is an allocation correction, not validation of practical cell performance. Rebuild scenario databases to apply.</t>
+        </is>
       </c>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.2">
@@ -5943,8 +5947,8 @@
         <v>48</v>
       </c>
       <c r="B72">
-        <f>1-0.29</f>
-        <v>0.71</v>
+        <f>0.72591</f>
+        <v>0.72591000000000006</v>
       </c>
     </row>
     <row r="73" spans="1:14" ht="16" x14ac:dyDescent="0.2">
@@ -6015,8 +6019,8 @@
         <v>63</v>
       </c>
       <c r="B76" s="3">
-        <f>1/(0.34*71%)</f>
-        <v>4.1425020712510356</v>
+        <f>1/(0.34*$B$72)</f>
+        <v>4.0517095378052854</v>
       </c>
       <c r="C76" t="s">
         <v>7</v>
@@ -6035,15 +6039,15 @@
       </c>
       <c r="H76" s="7">
         <f>B76</f>
-        <v>4.1425020712510356</v>
+        <v>4.0517095378052854</v>
       </c>
       <c r="I76" s="3">
-        <f>1/(0.38*71%)</f>
-        <v>3.7064492216456637</v>
+        <f>1/(0.38*$B$72)</f>
+        <v>3.6252137969836769</v>
       </c>
       <c r="J76" s="3">
-        <f>1/(0.3*71%)</f>
-        <v>4.694835680751174</v>
+        <f>1/(0.3*$B$72)</f>
+        <v>4.5919374761793241</v>
       </c>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.2">
@@ -6052,7 +6056,7 @@
       </c>
       <c r="B77" s="3">
         <f>-1*B76</f>
-        <v>-4.1425020712510356</v>
+        <v>-4.0517095378052854</v>
       </c>
       <c r="C77" t="s">
         <v>7</v>
@@ -6071,15 +6075,15 @@
       </c>
       <c r="H77" s="7">
         <f>B77</f>
-        <v>-4.1425020712510356</v>
+        <v>-4.0517095378052854</v>
       </c>
       <c r="I77" s="3">
-        <f>-1/(0.3*71%)</f>
-        <v>-4.694835680751174</v>
+        <f>-J76</f>
+        <v>-4.5919374761793241</v>
       </c>
       <c r="J77" s="3">
-        <f>-1/(0.38*71%)</f>
-        <v>-3.7064492216456637</v>
+        <f>-I76</f>
+        <v>-3.6252137969836769</v>
       </c>
       <c r="K77" t="b">
         <v>1</v>

--- a/premise/data/additional_inventories/lci-battery-capacity.xlsx
+++ b/premise/data/additional_inventories/lci-battery-capacity.xlsx
@@ -770,16 +770,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:ns4="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N266"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" ns3:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="46.5" customWidth="1"/>
     <col min="2" max="2" width="24.1640625" customWidth="1"/>
     <col min="6" max="6" width="8.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:14" ns3:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>99</v>
       </c>
@@ -787,7 +787,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:14" ht="16" ns3:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
@@ -795,7 +795,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:14" ns3:dyDescent="0.2">
       <c r="A4" t="s">
         <v>1</v>
       </c>
@@ -803,7 +803,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" ns3:dyDescent="0.2">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -811,7 +811,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" ns3:dyDescent="0.2">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -819,7 +819,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" ns3:dyDescent="0.2">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -827,7 +827,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" ns3:dyDescent="0.2">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -836,7 +836,7 @@
       </c>
       <c r="F8" s="7"/>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:14" ns3:dyDescent="0.2">
       <c r="A9" t="s">
         <v>48</v>
       </c>
@@ -845,13 +845,13 @@
         <v>0.73</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:14" ht="16" ns3:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="7"/>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:14" ns3:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>10</v>
       </c>
@@ -886,7 +886,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:14" ht="16" ns3:dyDescent="0.2">
       <c r="A12" s="4" t="str">
         <f>B3</f>
         <v>market for battery capacity, Li-ion, LFP</v>
@@ -909,7 +909,7 @@
         <v>electricity storage capacity</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:14" ns3:dyDescent="0.2">
       <c r="A13" t="s">
         <v>17</v>
       </c>
@@ -945,7 +945,7 @@
         <v>9.7847358121330714</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:14" ns3:dyDescent="0.2">
       <c r="A14" t="s">
         <v>53</v>
       </c>
@@ -986,7 +986,7 @@
       <c r="M14" s="7"/>
       <c r="N14" s="7"/>
     </row>
-    <row r="16" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:14" ht="16" ns3:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>0</v>
       </c>
@@ -994,7 +994,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:14" ns3:dyDescent="0.2">
       <c r="A17" t="s">
         <v>1</v>
       </c>
@@ -1002,7 +1002,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:14" ns3:dyDescent="0.2">
       <c r="A18" t="s">
         <v>2</v>
       </c>
@@ -1010,7 +1010,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:14" ns3:dyDescent="0.2">
       <c r="A19" t="s">
         <v>4</v>
       </c>
@@ -1018,7 +1018,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:14" ns3:dyDescent="0.2">
       <c r="A20" t="s">
         <v>5</v>
       </c>
@@ -1026,7 +1026,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:14" ns3:dyDescent="0.2">
       <c r="A21" t="s">
         <v>6</v>
       </c>
@@ -1034,7 +1034,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:14" ns3:dyDescent="0.2">
       <c r="A22" t="s">
         <v>48</v>
       </c>
@@ -1043,13 +1043,13 @@
         <v>0.73</v>
       </c>
     </row>
-    <row r="23" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:14" ht="16" ns3:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B23" s="3"/>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:14" ns3:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>10</v>
       </c>
@@ -1084,7 +1084,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:14" ht="16" ns3:dyDescent="0.2">
       <c r="A25" s="4" t="str">
         <f>B16</f>
         <v>market for battery capacity, Li-ion, NMC111</v>
@@ -1107,7 +1107,7 @@
         <v>electricity storage capacity</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:14" ns3:dyDescent="0.2">
       <c r="A26" t="s">
         <v>20</v>
       </c>
@@ -1143,7 +1143,7 @@
         <v>9.7847358121330714</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:14" ns3:dyDescent="0.2">
       <c r="A27" t="s">
         <v>53</v>
       </c>
@@ -1184,7 +1184,7 @@
       <c r="M27" s="7"/>
       <c r="N27" s="7"/>
     </row>
-    <row r="29" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:14" ht="16" ns3:dyDescent="0.2">
       <c r="A29" s="2" t="s">
         <v>0</v>
       </c>
@@ -1192,7 +1192,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:14" ns3:dyDescent="0.2">
       <c r="A30" t="s">
         <v>1</v>
       </c>
@@ -1200,7 +1200,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:14" ns3:dyDescent="0.2">
       <c r="A31" t="s">
         <v>2</v>
       </c>
@@ -1208,7 +1208,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:14" ns3:dyDescent="0.2">
       <c r="A32" t="s">
         <v>4</v>
       </c>
@@ -1216,7 +1216,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:14" ns3:dyDescent="0.2">
       <c r="A33" t="s">
         <v>5</v>
       </c>
@@ -1224,7 +1224,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:14" ns3:dyDescent="0.2">
       <c r="A34" t="s">
         <v>6</v>
       </c>
@@ -1232,7 +1232,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:14" ns3:dyDescent="0.2">
       <c r="A35" t="s">
         <v>48</v>
       </c>
@@ -1241,13 +1241,13 @@
         <v>0.73</v>
       </c>
     </row>
-    <row r="36" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:14" ht="16" ns3:dyDescent="0.2">
       <c r="A36" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B36" s="3"/>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:14" ns3:dyDescent="0.2">
       <c r="A37" s="1" t="s">
         <v>10</v>
       </c>
@@ -1282,7 +1282,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="38" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:14" ht="16" ns3:dyDescent="0.2">
       <c r="A38" s="4" t="str">
         <f>B29</f>
         <v>market for battery capacity, Li-ion, NMC532</v>
@@ -1305,7 +1305,7 @@
         <v>electricity storage capacity</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:14" ns3:dyDescent="0.2">
       <c r="A39" t="s">
         <v>112</v>
       </c>
@@ -1341,7 +1341,7 @@
         <v>8.058017727639001</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:14" ns3:dyDescent="0.2">
       <c r="A40" t="s">
         <v>53</v>
       </c>
@@ -1382,7 +1382,7 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
     </row>
-    <row r="42" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:14" ht="16" ns3:dyDescent="0.2">
       <c r="A42" s="2" t="s">
         <v>0</v>
       </c>
@@ -1390,7 +1390,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:14" ns3:dyDescent="0.2">
       <c r="A43" t="s">
         <v>1</v>
       </c>
@@ -1398,7 +1398,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:14" ns3:dyDescent="0.2">
       <c r="A44" t="s">
         <v>2</v>
       </c>
@@ -1406,7 +1406,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:14" ns3:dyDescent="0.2">
       <c r="A45" t="s">
         <v>4</v>
       </c>
@@ -1414,7 +1414,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:14" ns3:dyDescent="0.2">
       <c r="A46" t="s">
         <v>5</v>
       </c>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="E46" s="3"/>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:14" ns3:dyDescent="0.2">
       <c r="A47" t="s">
         <v>6</v>
       </c>
@@ -1432,7 +1432,7 @@
       </c>
       <c r="E47" s="3"/>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:14" ns3:dyDescent="0.2">
       <c r="A48" t="s">
         <v>48</v>
       </c>
@@ -1441,13 +1441,13 @@
         <v>0.73</v>
       </c>
     </row>
-    <row r="49" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:14" ht="16" ns3:dyDescent="0.2">
       <c r="A49" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B49" s="3"/>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:14" ns3:dyDescent="0.2">
       <c r="A50" s="1" t="s">
         <v>10</v>
       </c>
@@ -1482,7 +1482,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="51" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:14" ht="16" ns3:dyDescent="0.2">
       <c r="A51" s="4" t="str">
         <f>B42</f>
         <v>market for battery capacity, Li-ion, NMC622</v>
@@ -1505,7 +1505,7 @@
         <v>electricity storage capacity</v>
       </c>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:14" ns3:dyDescent="0.2">
       <c r="A52" t="s">
         <v>25</v>
       </c>
@@ -1541,7 +1541,7 @@
         <v>6.8493150684931514</v>
       </c>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:14" ns3:dyDescent="0.2">
       <c r="A53" t="s">
         <v>53</v>
       </c>
@@ -1582,7 +1582,7 @@
       <c r="M53" s="3"/>
       <c r="N53" s="3"/>
     </row>
-    <row r="55" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:14" ht="16" ns3:dyDescent="0.2">
       <c r="A55" s="2" t="s">
         <v>0</v>
       </c>
@@ -1590,7 +1590,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:14" ns3:dyDescent="0.2">
       <c r="A56" t="s">
         <v>1</v>
       </c>
@@ -1598,7 +1598,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:14" ns3:dyDescent="0.2">
       <c r="A57" t="s">
         <v>2</v>
       </c>
@@ -1606,7 +1606,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:14" ns3:dyDescent="0.2">
       <c r="A58" t="s">
         <v>4</v>
       </c>
@@ -1614,7 +1614,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:14" ns3:dyDescent="0.2">
       <c r="A59" t="s">
         <v>5</v>
       </c>
@@ -1622,7 +1622,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:14" ns3:dyDescent="0.2">
       <c r="A60" t="s">
         <v>6</v>
       </c>
@@ -1631,12 +1631,12 @@
       </c>
       <c r="E60" s="3"/>
     </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:14" ns3:dyDescent="0.2">
       <c r="A61" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="62" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:14" ht="16" ns3:dyDescent="0.2">
       <c r="A62" s="2" t="s">
         <v>9</v>
       </c>
@@ -1645,7 +1645,7 @@
         <v>0.1988</v>
       </c>
     </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:14" ns3:dyDescent="0.2">
       <c r="A63" s="1" t="s">
         <v>10</v>
       </c>
@@ -1680,7 +1680,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="64" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:14" ht="16" ns3:dyDescent="0.2">
       <c r="A64" s="4" t="str">
         <f>B55</f>
         <v>market for battery capacity, Li-ion, NMC811</v>
@@ -1703,7 +1703,7 @@
         <v>electricity storage capacity</v>
       </c>
     </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:14" ns3:dyDescent="0.2">
       <c r="A65" t="s">
         <v>24</v>
       </c>
@@ -1739,7 +1739,7 @@
         <v>5.868544600938967</v>
       </c>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:14" ns3:dyDescent="0.2">
       <c r="A66" t="s">
         <v>53</v>
       </c>
@@ -1780,7 +1780,7 @@
       <c r="M66" s="3"/>
       <c r="N66" s="3"/>
     </row>
-    <row r="68" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:14" ht="16" ns3:dyDescent="0.2">
       <c r="A68" s="2" t="s">
         <v>0</v>
       </c>
@@ -1788,7 +1788,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:14" ns3:dyDescent="0.2">
       <c r="A69" t="s">
         <v>1</v>
       </c>
@@ -1798,7 +1798,7 @@
         </is>
       </c>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:14" ns3:dyDescent="0.2">
       <c r="A70" t="s">
         <v>2</v>
       </c>
@@ -1806,7 +1806,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:14" ns3:dyDescent="0.2">
       <c r="A71" t="s">
         <v>4</v>
       </c>
@@ -1814,7 +1814,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:14" ns3:dyDescent="0.2">
       <c r="A72" t="s">
         <v>5</v>
       </c>
@@ -1822,7 +1822,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:14" ns3:dyDescent="0.2">
       <c r="A73" t="s">
         <v>6</v>
       </c>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="E73" s="3"/>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:14" ns3:dyDescent="0.2">
       <c r="A74" t="s">
         <v>48</v>
       </c>
@@ -1840,12 +1840,12 @@
         <v>0.72591000000000006</v>
       </c>
     </row>
-    <row r="75" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:14" ht="16" ns3:dyDescent="0.2">
       <c r="A75" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:14" ns3:dyDescent="0.2">
       <c r="A76" s="1" t="s">
         <v>10</v>
       </c>
@@ -1880,7 +1880,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="77" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:14" ht="16" ns3:dyDescent="0.2">
       <c r="A77" s="4" t="str">
         <f>B68</f>
         <v>market for battery capacity, Li-ion, NMC955</v>
@@ -1903,7 +1903,7 @@
         <v>electricity storage capacity</v>
       </c>
     </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:14" ns3:dyDescent="0.2">
       <c r="A78" t="s">
         <v>63</v>
       </c>
@@ -1939,7 +1939,7 @@
         <v>4.5919374761793241</v>
       </c>
     </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:14" ns3:dyDescent="0.2">
       <c r="A79" t="s">
         <v>53</v>
       </c>
@@ -1980,7 +1980,7 @@
       <c r="M79" s="3"/>
       <c r="N79" s="3"/>
     </row>
-    <row r="81" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:14" ht="16" ns3:dyDescent="0.2">
       <c r="A81" s="2" t="s">
         <v>0</v>
       </c>
@@ -1988,7 +1988,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:14" ns3:dyDescent="0.2">
       <c r="A82" t="s">
         <v>1</v>
       </c>
@@ -1996,7 +1996,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:14" ns3:dyDescent="0.2">
       <c r="A83" t="s">
         <v>2</v>
       </c>
@@ -2004,7 +2004,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:14" ns3:dyDescent="0.2">
       <c r="A84" t="s">
         <v>4</v>
       </c>
@@ -2012,7 +2012,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:14" ns3:dyDescent="0.2">
       <c r="A85" t="s">
         <v>5</v>
       </c>
@@ -2020,7 +2020,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:14" ns3:dyDescent="0.2">
       <c r="A86" t="s">
         <v>6</v>
       </c>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="D86" s="3"/>
     </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:14" ns3:dyDescent="0.2">
       <c r="A87" t="s">
         <v>48</v>
       </c>
@@ -2038,12 +2038,12 @@
         <v>0.70700000000000007</v>
       </c>
     </row>
-    <row r="88" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:14" ht="16" ns3:dyDescent="0.2">
       <c r="A88" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:14" ns3:dyDescent="0.2">
       <c r="A89" s="1" t="s">
         <v>10</v>
       </c>
@@ -2078,7 +2078,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="90" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:14" ht="16" ns3:dyDescent="0.2">
       <c r="A90" s="4" t="str">
         <f>B81</f>
         <v>market for battery capacity, Li-ion, NCA</v>
@@ -2101,7 +2101,7 @@
         <v>electricity storage capacity</v>
       </c>
     </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:14" ns3:dyDescent="0.2">
       <c r="A91" t="s">
         <v>28</v>
       </c>
@@ -2137,7 +2137,7 @@
         <v>5.868544600938967</v>
       </c>
     </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:14" ns3:dyDescent="0.2">
       <c r="A92" t="s">
         <v>53</v>
       </c>
@@ -2178,7 +2178,7 @@
       <c r="M92" s="3"/>
       <c r="N92" s="3"/>
     </row>
-    <row r="94" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:14" ht="16" ns3:dyDescent="0.2">
       <c r="A94" s="2" t="s">
         <v>0</v>
       </c>
@@ -2186,7 +2186,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:14" ns3:dyDescent="0.2">
       <c r="A95" t="s">
         <v>1</v>
       </c>
@@ -2194,7 +2194,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:14" ns3:dyDescent="0.2">
       <c r="A96" t="s">
         <v>2</v>
       </c>
@@ -2202,7 +2202,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:14" ns3:dyDescent="0.2">
       <c r="A97" t="s">
         <v>4</v>
       </c>
@@ -2210,7 +2210,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:14" ns3:dyDescent="0.2">
       <c r="A98" t="s">
         <v>5</v>
       </c>
@@ -2219,7 +2219,7 @@
       </c>
       <c r="E98" s="3"/>
     </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:14" ns3:dyDescent="0.2">
       <c r="A99" t="s">
         <v>6</v>
       </c>
@@ -2227,7 +2227,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:14" ns3:dyDescent="0.2">
       <c r="A100" t="s">
         <v>48</v>
       </c>
@@ -2236,12 +2236,12 @@
         <v>0.64</v>
       </c>
     </row>
-    <row r="101" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:14" ht="16" ns3:dyDescent="0.2">
       <c r="A101" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="102" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:14" ns3:dyDescent="0.2">
       <c r="A102" s="1" t="s">
         <v>10</v>
       </c>
@@ -2276,7 +2276,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="103" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:14" ht="16" ns3:dyDescent="0.2">
       <c r="A103" s="6" t="str">
         <f>B94</f>
         <v>market for battery capacity, Li-ion, LTO</v>
@@ -2299,7 +2299,7 @@
         <v>electricity storage capacity</v>
       </c>
     </row>
-    <row r="104" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:14" ns3:dyDescent="0.2">
       <c r="A104" t="s">
         <v>31</v>
       </c>
@@ -2335,7 +2335,7 @@
         <v>22.977941176470587</v>
       </c>
     </row>
-    <row r="105" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:14" ns3:dyDescent="0.2">
       <c r="A105" t="s">
         <v>53</v>
       </c>
@@ -2376,7 +2376,7 @@
       <c r="M105" s="7"/>
       <c r="N105" s="7"/>
     </row>
-    <row r="107" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:14" ht="16" ns3:dyDescent="0.2">
       <c r="A107" s="2" t="s">
         <v>0</v>
       </c>
@@ -2384,7 +2384,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="108" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:14" ns3:dyDescent="0.2">
       <c r="A108" t="s">
         <v>1</v>
       </c>
@@ -2392,7 +2392,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="109" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:14" ns3:dyDescent="0.2">
       <c r="A109" t="s">
         <v>2</v>
       </c>
@@ -2400,7 +2400,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="110" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:14" ns3:dyDescent="0.2">
       <c r="A110" t="s">
         <v>4</v>
       </c>
@@ -2408,7 +2408,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:14" ns3:dyDescent="0.2">
       <c r="A111" t="s">
         <v>5</v>
       </c>
@@ -2416,7 +2416,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="112" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:14" ns3:dyDescent="0.2">
       <c r="A112" t="s">
         <v>6</v>
       </c>
@@ -2425,7 +2425,7 @@
       </c>
       <c r="E112" s="3"/>
     </row>
-    <row r="113" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:14" ns3:dyDescent="0.2">
       <c r="A113" t="s">
         <v>48</v>
       </c>
@@ -2434,12 +2434,12 @@
         <v>0.87</v>
       </c>
     </row>
-    <row r="114" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:14" ht="16" ns3:dyDescent="0.2">
       <c r="A114" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="115" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:14" ns3:dyDescent="0.2">
       <c r="A115" s="1" t="s">
         <v>10</v>
       </c>
@@ -2474,7 +2474,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="116" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:14" ht="16" ns3:dyDescent="0.2">
       <c r="A116" s="6" t="str">
         <f>B107</f>
         <v>market for battery capacity, Li-ion, LiMn2O4</v>
@@ -2497,7 +2497,7 @@
         <v>electricity storage capacity</v>
       </c>
     </row>
-    <row r="117" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:14" ns3:dyDescent="0.2">
       <c r="A117" t="s">
         <v>50</v>
       </c>
@@ -2533,7 +2533,7 @@
         <v>10.9375</v>
       </c>
     </row>
-    <row r="118" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:14" ns3:dyDescent="0.2">
       <c r="A118" t="s">
         <v>53</v>
       </c>
@@ -2574,7 +2574,7 @@
       <c r="M118" s="7"/>
       <c r="N118" s="7"/>
     </row>
-    <row r="120" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:14" ht="16" ns3:dyDescent="0.2">
       <c r="A120" s="2" t="s">
         <v>0</v>
       </c>
@@ -2582,7 +2582,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="121" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:14" ns3:dyDescent="0.2">
       <c r="A121" t="s">
         <v>1</v>
       </c>
@@ -2590,7 +2590,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="122" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:14" ns3:dyDescent="0.2">
       <c r="A122" t="s">
         <v>2</v>
       </c>
@@ -2598,7 +2598,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="123" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:14" ns3:dyDescent="0.2">
       <c r="A123" t="s">
         <v>4</v>
       </c>
@@ -2606,7 +2606,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:14" ns3:dyDescent="0.2">
       <c r="A124" t="s">
         <v>5</v>
       </c>
@@ -2614,7 +2614,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="125" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:14" ns3:dyDescent="0.2">
       <c r="A125" t="s">
         <v>6</v>
       </c>
@@ -2623,7 +2623,7 @@
       </c>
       <c r="D125" s="3"/>
     </row>
-    <row r="126" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:14" ns3:dyDescent="0.2">
       <c r="A126" t="s">
         <v>48</v>
       </c>
@@ -2632,12 +2632,12 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="127" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:14" ht="16" ns3:dyDescent="0.2">
       <c r="A127" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="128" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:14" ns3:dyDescent="0.2">
       <c r="A128" s="1" t="s">
         <v>10</v>
       </c>
@@ -2672,7 +2672,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="129" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:14" ht="16" ns3:dyDescent="0.2">
       <c r="A129" s="4" t="str">
         <f>B120</f>
         <v>market for battery capacity, Li-sulfur, Li-S</v>
@@ -2695,7 +2695,7 @@
         <v>electricity storage capacity</v>
       </c>
     </row>
-    <row r="130" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:14" ns3:dyDescent="0.2">
       <c r="A130" t="s">
         <v>33</v>
       </c>
@@ -2731,7 +2731,7 @@
         <v>11.111111111111111</v>
       </c>
     </row>
-    <row r="131" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:14" ns3:dyDescent="0.2">
       <c r="A131" t="s">
         <v>53</v>
       </c>
@@ -2772,7 +2772,7 @@
       <c r="M131" s="3"/>
       <c r="N131" s="3"/>
     </row>
-    <row r="133" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:14" ht="16" ns3:dyDescent="0.2">
       <c r="A133" s="2" t="s">
         <v>0</v>
       </c>
@@ -2780,7 +2780,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="134" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:14" ns3:dyDescent="0.2">
       <c r="A134" t="s">
         <v>1</v>
       </c>
@@ -2788,7 +2788,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="135" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:14" ns3:dyDescent="0.2">
       <c r="A135" t="s">
         <v>2</v>
       </c>
@@ -2796,7 +2796,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="136" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:14" ns3:dyDescent="0.2">
       <c r="A136" t="s">
         <v>4</v>
       </c>
@@ -2804,7 +2804,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:14" ns3:dyDescent="0.2">
       <c r="A137" t="s">
         <v>5</v>
       </c>
@@ -2812,7 +2812,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="138" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:14" ns3:dyDescent="0.2">
       <c r="A138" t="s">
         <v>6</v>
       </c>
@@ -2820,7 +2820,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="139" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:14" ns3:dyDescent="0.2">
       <c r="A139" t="s">
         <v>48</v>
       </c>
@@ -2829,12 +2829,12 @@
         <v>0.55000000000000004</v>
       </c>
     </row>
-    <row r="140" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:14" ht="16" ns3:dyDescent="0.2">
       <c r="A140" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="141" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:14" ns3:dyDescent="0.2">
       <c r="A141" s="1" t="s">
         <v>10</v>
       </c>
@@ -2869,7 +2869,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="142" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:14" ht="16" ns3:dyDescent="0.2">
       <c r="A142" s="4" t="str">
         <f>B133</f>
         <v>market for battery capacity, Li-ion, Li-O2</v>
@@ -2892,7 +2892,7 @@
         <v>electricity storage capacity</v>
       </c>
     </row>
-    <row r="143" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:14" ns3:dyDescent="0.2">
       <c r="A143" t="s">
         <v>36</v>
       </c>
@@ -2928,7 +2928,7 @@
         <v>6.3131313131313131</v>
       </c>
     </row>
-    <row r="144" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:14" ns3:dyDescent="0.2">
       <c r="A144" t="s">
         <v>53</v>
       </c>
@@ -2969,7 +2969,7 @@
       <c r="M144" s="7"/>
       <c r="N144" s="7"/>
     </row>
-    <row r="146" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:14" ht="16" ns3:dyDescent="0.2">
       <c r="A146" s="2" t="s">
         <v>0</v>
       </c>
@@ -2977,7 +2977,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="147" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:14" ns3:dyDescent="0.2">
       <c r="A147" t="s">
         <v>1</v>
       </c>
@@ -2985,7 +2985,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="148" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:14" ns3:dyDescent="0.2">
       <c r="A148" t="s">
         <v>2</v>
       </c>
@@ -2993,7 +2993,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="149" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:14" ns3:dyDescent="0.2">
       <c r="A149" t="s">
         <v>4</v>
       </c>
@@ -3001,7 +3001,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:14" ns3:dyDescent="0.2">
       <c r="A150" t="s">
         <v>5</v>
       </c>
@@ -3010,7 +3010,7 @@
       </c>
       <c r="E150" s="3"/>
     </row>
-    <row r="151" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:14" ns3:dyDescent="0.2">
       <c r="A151" t="s">
         <v>6</v>
       </c>
@@ -3018,7 +3018,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="152" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:14" ns3:dyDescent="0.2">
       <c r="A152" t="s">
         <v>48</v>
       </c>
@@ -3027,12 +3027,12 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="153" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:14" ht="16" ns3:dyDescent="0.2">
       <c r="A153" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="154" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:14" ns3:dyDescent="0.2">
       <c r="A154" s="1" t="s">
         <v>10</v>
       </c>
@@ -3067,7 +3067,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="155" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:14" ht="16" ns3:dyDescent="0.2">
       <c r="A155" s="4" t="str">
         <f>B146</f>
         <v>market for battery capacity, Sodium-ion, SiB</v>
@@ -3090,7 +3090,7 @@
         <v>electricity storage capacity</v>
       </c>
     </row>
-    <row r="156" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:14" ns3:dyDescent="0.2">
       <c r="A156" t="s">
         <v>39</v>
       </c>
@@ -3126,7 +3126,7 @@
         <v>11.111111111111111</v>
       </c>
     </row>
-    <row r="157" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:14" ns3:dyDescent="0.2">
       <c r="A157" t="s">
         <v>53</v>
       </c>
@@ -3167,7 +3167,7 @@
       <c r="M157" s="3"/>
       <c r="N157" s="3"/>
     </row>
-    <row r="159" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:14" ht="16" ns3:dyDescent="0.2">
       <c r="A159" s="2" t="s">
         <v>0</v>
       </c>
@@ -3175,7 +3175,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="160" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:14" ns3:dyDescent="0.2">
       <c r="A160" t="s">
         <v>1</v>
       </c>
@@ -3183,7 +3183,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="161" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:14" ns3:dyDescent="0.2">
       <c r="A161" t="s">
         <v>2</v>
       </c>
@@ -3191,7 +3191,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="162" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:14" ns3:dyDescent="0.2">
       <c r="A162" t="s">
         <v>4</v>
       </c>
@@ -3199,7 +3199,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="163" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:14" ns3:dyDescent="0.2">
       <c r="A163" t="s">
         <v>5</v>
       </c>
@@ -3207,7 +3207,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="164" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:14" ns3:dyDescent="0.2">
       <c r="A164" t="s">
         <v>6</v>
       </c>
@@ -3215,7 +3215,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="165" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:14" ns3:dyDescent="0.2">
       <c r="A165" t="s">
         <v>8</v>
       </c>
@@ -3223,7 +3223,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="166" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:14" ns3:dyDescent="0.2">
       <c r="A166" s="1" t="s">
         <v>9</v>
       </c>
@@ -3234,7 +3234,7 @@
       <c r="F166" s="1"/>
       <c r="G166" s="1"/>
     </row>
-    <row r="167" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:14" ns3:dyDescent="0.2">
       <c r="A167" s="1" t="s">
         <v>10</v>
       </c>
@@ -3269,7 +3269,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="168" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:14" ht="16" ns3:dyDescent="0.2">
       <c r="A168" s="5" t="str">
         <f>B159</f>
         <v>market for battery capacity, Sodium-Nickel-Chloride, Na-NiCl</v>
@@ -3292,7 +3292,7 @@
         <v>electricity storage capacity</v>
       </c>
     </row>
-    <row r="169" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:14" ns3:dyDescent="0.2">
       <c r="A169" t="s">
         <v>41</v>
       </c>
@@ -3328,7 +3328,7 @@
         <v>10.775862068965516</v>
       </c>
     </row>
-    <row r="170" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:14" ns3:dyDescent="0.2">
       <c r="A170" t="s">
         <v>53</v>
       </c>
@@ -3369,7 +3369,7 @@
       <c r="M170" s="7"/>
       <c r="N170" s="7"/>
     </row>
-    <row r="172" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:14" ht="16" ns3:dyDescent="0.2">
       <c r="A172" s="2" t="s">
         <v>0</v>
       </c>
@@ -3377,7 +3377,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="173" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:14" ns3:dyDescent="0.2">
       <c r="A173" t="s">
         <v>1</v>
       </c>
@@ -3385,7 +3385,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="174" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:14" ns3:dyDescent="0.2">
       <c r="A174" t="s">
         <v>2</v>
       </c>
@@ -3393,7 +3393,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="175" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:14" ns3:dyDescent="0.2">
       <c r="A175" t="s">
         <v>4</v>
       </c>
@@ -3401,7 +3401,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="176" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:14" ns3:dyDescent="0.2">
       <c r="A176" t="s">
         <v>5</v>
       </c>
@@ -3409,7 +3409,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="177" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:11" ns3:dyDescent="0.2">
       <c r="A177" t="s">
         <v>6</v>
       </c>
@@ -3417,7 +3417,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="178" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:11" ns3:dyDescent="0.2">
       <c r="A178" t="s">
         <v>8</v>
       </c>
@@ -3425,7 +3425,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="179" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:11" ns3:dyDescent="0.2">
       <c r="A179" s="1" t="s">
         <v>9</v>
       </c>
@@ -3436,7 +3436,7 @@
       <c r="F179" s="1"/>
       <c r="G179" s="1"/>
     </row>
-    <row r="180" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:11" ns3:dyDescent="0.2">
       <c r="A180" s="1" t="s">
         <v>10</v>
       </c>
@@ -3461,7 +3461,7 @@
       <c r="J180" s="1"/>
       <c r="K180" s="1"/>
     </row>
-    <row r="181" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:11" ns3:dyDescent="0.2">
       <c r="A181" t="str">
         <f>B172</f>
         <v>market for battery capacity (MIX scenario)</v>
@@ -3487,7 +3487,7 @@
       <c r="J181" s="1"/>
       <c r="K181" s="1"/>
     </row>
-    <row r="182" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:11" ht="16" ns3:dyDescent="0.2">
       <c r="A182" s="4" t="s">
         <v>16</v>
       </c>
@@ -3507,7 +3507,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="183" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:11" ht="16" ns3:dyDescent="0.2">
       <c r="A183" s="4" t="s">
         <v>19</v>
       </c>
@@ -3527,7 +3527,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="184" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:11" ht="16" ns3:dyDescent="0.2">
       <c r="A184" s="4" t="s">
         <v>110</v>
       </c>
@@ -3547,7 +3547,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="185" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:11" ht="16" ns3:dyDescent="0.2">
       <c r="A185" s="4" t="s">
         <v>22</v>
       </c>
@@ -3567,7 +3567,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="186" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:11" ht="16" ns3:dyDescent="0.2">
       <c r="A186" s="4" t="s">
         <v>23</v>
       </c>
@@ -3587,7 +3587,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="187" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:11" ht="16" ns3:dyDescent="0.2">
       <c r="A187" s="4" t="s">
         <v>62</v>
       </c>
@@ -3607,7 +3607,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="188" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:11" ht="16" ns3:dyDescent="0.2">
       <c r="A188" s="4" t="s">
         <v>27</v>
       </c>
@@ -3627,9 +3627,11 @@
         <v>106</v>
       </c>
     </row>
-    <row r="189" spans="1:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="A189" s="6" t="s">
-        <v>30</v>
+    <row r="189" spans="1:11" ht="16" ns3:dyDescent="0.2">
+      <c r="A189" s="6" t="inlineStr">
+        <is>
+          <t>market for battery capacity, ASSB, polymer</t>
+        </is>
       </c>
       <c r="B189">
         <v>0</v>
@@ -3647,9 +3649,11 @@
         <v>106</v>
       </c>
     </row>
-    <row r="190" spans="1:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="A190" s="6" t="s">
-        <v>55</v>
+    <row r="190" spans="1:11" ht="16" ns3:dyDescent="0.2">
+      <c r="A190" s="6" t="inlineStr">
+        <is>
+          <t>market for battery capacity, ASSB, oxidic</t>
+        </is>
       </c>
       <c r="B190">
         <v>0</v>
@@ -3667,7 +3671,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="191" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:11" ht="16" ns3:dyDescent="0.2">
       <c r="A191" s="4" t="s">
         <v>56</v>
       </c>
@@ -3687,7 +3691,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="192" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:11" ht="16" ns3:dyDescent="0.2">
       <c r="A192" s="4" t="s">
         <v>35</v>
       </c>
@@ -3707,7 +3711,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="193" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:11" ht="16" ns3:dyDescent="0.2">
       <c r="A193" s="4" t="s">
         <v>38</v>
       </c>
@@ -3727,9 +3731,11 @@
         <v>106</v>
       </c>
     </row>
-    <row r="194" spans="1:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="A194" s="5" t="s">
-        <v>47</v>
+    <row r="194" spans="1:11" ht="16" ns3:dyDescent="0.2">
+      <c r="A194" s="5" t="inlineStr">
+        <is>
+          <t>market for battery capacity, ASSB, sulfidic</t>
+        </is>
       </c>
       <c r="B194">
         <v>0</v>
@@ -3747,7 +3753,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="196" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:11" ht="16" ns3:dyDescent="0.2">
       <c r="A196" s="2" t="s">
         <v>0</v>
       </c>
@@ -3755,7 +3761,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="197" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:11" ns3:dyDescent="0.2">
       <c r="A197" t="s">
         <v>1</v>
       </c>
@@ -3763,7 +3769,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="198" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:11" ns3:dyDescent="0.2">
       <c r="A198" t="s">
         <v>2</v>
       </c>
@@ -3771,7 +3777,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="199" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:11" ns3:dyDescent="0.2">
       <c r="A199" t="s">
         <v>4</v>
       </c>
@@ -3779,7 +3785,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="200" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:11" ns3:dyDescent="0.2">
       <c r="A200" t="s">
         <v>5</v>
       </c>
@@ -3787,7 +3793,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="201" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:11" ns3:dyDescent="0.2">
       <c r="A201" t="s">
         <v>6</v>
       </c>
@@ -3795,7 +3801,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="202" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:11" ns3:dyDescent="0.2">
       <c r="A202" t="s">
         <v>8</v>
       </c>
@@ -3803,7 +3809,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="203" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:11" ns3:dyDescent="0.2">
       <c r="A203" s="1" t="s">
         <v>9</v>
       </c>
@@ -3814,7 +3820,7 @@
       <c r="F203" s="1"/>
       <c r="G203" s="1"/>
     </row>
-    <row r="204" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:11" ns3:dyDescent="0.2">
       <c r="A204" s="1" t="s">
         <v>10</v>
       </c>
@@ -3839,7 +3845,7 @@
       <c r="J204" s="1"/>
       <c r="K204" s="1"/>
     </row>
-    <row r="205" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:11" ns3:dyDescent="0.2">
       <c r="A205" t="str">
         <f>B196</f>
         <v>market for battery capacity (LFP scenario)</v>
@@ -3865,7 +3871,7 @@
       <c r="J205" s="1"/>
       <c r="K205" s="1"/>
     </row>
-    <row r="206" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:11" ht="16" ns3:dyDescent="0.2">
       <c r="A206" s="4" t="s">
         <v>16</v>
       </c>
@@ -3885,7 +3891,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="207" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:11" ht="16" ns3:dyDescent="0.2">
       <c r="A207" s="4" t="s">
         <v>19</v>
       </c>
@@ -3905,7 +3911,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="208" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:11" ht="16" ns3:dyDescent="0.2">
       <c r="A208" s="4" t="s">
         <v>110</v>
       </c>
@@ -3925,7 +3931,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="209" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A209" s="4" t="s">
         <v>22</v>
       </c>
@@ -3945,7 +3951,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="210" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A210" s="4" t="s">
         <v>23</v>
       </c>
@@ -3965,7 +3971,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="211" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A211" s="4" t="s">
         <v>62</v>
       </c>
@@ -3985,7 +3991,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="212" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A212" s="4" t="s">
         <v>27</v>
       </c>
@@ -4005,9 +4011,11 @@
         <v>106</v>
       </c>
     </row>
-    <row r="213" spans="1:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="A213" s="6" t="s">
-        <v>30</v>
+    <row r="213" spans="1:6" ht="16" ns3:dyDescent="0.2">
+      <c r="A213" s="6" t="inlineStr">
+        <is>
+          <t>market for battery capacity, ASSB, polymer</t>
+        </is>
       </c>
       <c r="B213">
         <v>0</v>
@@ -4025,9 +4033,11 @@
         <v>106</v>
       </c>
     </row>
-    <row r="214" spans="1:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="A214" s="6" t="s">
-        <v>55</v>
+    <row r="214" spans="1:6" ht="16" ns3:dyDescent="0.2">
+      <c r="A214" s="6" t="inlineStr">
+        <is>
+          <t>market for battery capacity, ASSB, oxidic</t>
+        </is>
       </c>
       <c r="B214">
         <v>0</v>
@@ -4045,7 +4055,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="215" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A215" s="4" t="s">
         <v>56</v>
       </c>
@@ -4065,7 +4075,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="216" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A216" s="4" t="s">
         <v>35</v>
       </c>
@@ -4085,7 +4095,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="217" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A217" s="4" t="s">
         <v>38</v>
       </c>
@@ -4105,9 +4115,11 @@
         <v>106</v>
       </c>
     </row>
-    <row r="218" spans="1:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="A218" s="5" t="s">
-        <v>47</v>
+    <row r="218" spans="1:6" ht="16" ns3:dyDescent="0.2">
+      <c r="A218" s="5" t="inlineStr">
+        <is>
+          <t>market for battery capacity, ASSB, sulfidic</t>
+        </is>
       </c>
       <c r="B218">
         <v>0</v>
@@ -4125,7 +4137,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="220" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A220" s="2" t="s">
         <v>0</v>
       </c>
@@ -4133,7 +4145,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="221" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:6" ns3:dyDescent="0.2">
       <c r="A221" t="s">
         <v>1</v>
       </c>
@@ -4141,7 +4153,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="222" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:6" ns3:dyDescent="0.2">
       <c r="A222" t="s">
         <v>2</v>
       </c>
@@ -4149,7 +4161,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="223" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:6" ns3:dyDescent="0.2">
       <c r="A223" t="s">
         <v>4</v>
       </c>
@@ -4157,7 +4169,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="224" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:6" ns3:dyDescent="0.2">
       <c r="A224" t="s">
         <v>5</v>
       </c>
@@ -4165,7 +4177,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="225" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:11" ns3:dyDescent="0.2">
       <c r="A225" t="s">
         <v>6</v>
       </c>
@@ -4173,7 +4185,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="226" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:11" ns3:dyDescent="0.2">
       <c r="A226" t="s">
         <v>8</v>
       </c>
@@ -4181,7 +4193,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="227" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:11" ns3:dyDescent="0.2">
       <c r="A227" s="1" t="s">
         <v>9</v>
       </c>
@@ -4192,7 +4204,7 @@
       <c r="F227" s="1"/>
       <c r="G227" s="1"/>
     </row>
-    <row r="228" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:11" ns3:dyDescent="0.2">
       <c r="A228" s="1" t="s">
         <v>10</v>
       </c>
@@ -4217,7 +4229,7 @@
       <c r="J228" s="1"/>
       <c r="K228" s="1"/>
     </row>
-    <row r="229" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:11" ns3:dyDescent="0.2">
       <c r="A229" t="str">
         <f>B220</f>
         <v>market for battery capacity (NCx scenario)</v>
@@ -4243,7 +4255,7 @@
       <c r="J229" s="1"/>
       <c r="K229" s="1"/>
     </row>
-    <row r="230" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:11" ht="16" ns3:dyDescent="0.2">
       <c r="A230" s="4" t="s">
         <v>16</v>
       </c>
@@ -4263,7 +4275,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="231" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:11" ht="16" ns3:dyDescent="0.2">
       <c r="A231" s="4" t="s">
         <v>19</v>
       </c>
@@ -4283,7 +4295,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="232" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:11" ht="16" ns3:dyDescent="0.2">
       <c r="A232" s="4" t="s">
         <v>110</v>
       </c>
@@ -4303,7 +4315,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="233" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:11" ht="16" ns3:dyDescent="0.2">
       <c r="A233" s="4" t="s">
         <v>22</v>
       </c>
@@ -4323,7 +4335,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="234" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:11" ht="16" ns3:dyDescent="0.2">
       <c r="A234" s="4" t="s">
         <v>23</v>
       </c>
@@ -4343,7 +4355,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="235" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:11" ht="16" ns3:dyDescent="0.2">
       <c r="A235" s="4" t="s">
         <v>62</v>
       </c>
@@ -4363,7 +4375,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="236" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:11" ht="16" ns3:dyDescent="0.2">
       <c r="A236" s="4" t="s">
         <v>27</v>
       </c>
@@ -4383,9 +4395,11 @@
         <v>106</v>
       </c>
     </row>
-    <row r="237" spans="1:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="A237" s="6" t="s">
-        <v>30</v>
+    <row r="237" spans="1:11" ht="16" ns3:dyDescent="0.2">
+      <c r="A237" s="6" t="inlineStr">
+        <is>
+          <t>market for battery capacity, ASSB, polymer</t>
+        </is>
       </c>
       <c r="B237">
         <v>0</v>
@@ -4403,9 +4417,11 @@
         <v>106</v>
       </c>
     </row>
-    <row r="238" spans="1:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="A238" s="6" t="s">
-        <v>55</v>
+    <row r="238" spans="1:11" ht="16" ns3:dyDescent="0.2">
+      <c r="A238" s="6" t="inlineStr">
+        <is>
+          <t>market for battery capacity, ASSB, oxidic</t>
+        </is>
       </c>
       <c r="B238">
         <v>0</v>
@@ -4423,7 +4439,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="239" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:11" ht="16" ns3:dyDescent="0.2">
       <c r="A239" s="4" t="s">
         <v>56</v>
       </c>
@@ -4443,7 +4459,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="240" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:11" ht="16" ns3:dyDescent="0.2">
       <c r="A240" s="4" t="s">
         <v>35</v>
       </c>
@@ -4463,7 +4479,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="241" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:11" ht="16" ns3:dyDescent="0.2">
       <c r="A241" s="4" t="s">
         <v>38</v>
       </c>
@@ -4483,9 +4499,11 @@
         <v>106</v>
       </c>
     </row>
-    <row r="242" spans="1:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="A242" s="5" t="s">
-        <v>47</v>
+    <row r="242" spans="1:11" ht="16" ns3:dyDescent="0.2">
+      <c r="A242" s="5" t="inlineStr">
+        <is>
+          <t>market for battery capacity, ASSB, sulfidic</t>
+        </is>
       </c>
       <c r="B242">
         <v>0</v>
@@ -4503,7 +4521,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="244" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:11" ht="16" ns3:dyDescent="0.2">
       <c r="A244" s="2" t="s">
         <v>0</v>
       </c>
@@ -4511,7 +4529,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="245" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:11" ns3:dyDescent="0.2">
       <c r="A245" t="s">
         <v>1</v>
       </c>
@@ -4519,7 +4537,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="246" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:11" ns3:dyDescent="0.2">
       <c r="A246" t="s">
         <v>2</v>
       </c>
@@ -4527,7 +4545,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="247" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:11" ns3:dyDescent="0.2">
       <c r="A247" t="s">
         <v>4</v>
       </c>
@@ -4535,7 +4553,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="248" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:11" ns3:dyDescent="0.2">
       <c r="A248" t="s">
         <v>5</v>
       </c>
@@ -4543,7 +4561,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="249" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:11" ns3:dyDescent="0.2">
       <c r="A249" t="s">
         <v>6</v>
       </c>
@@ -4551,7 +4569,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="250" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:11" ns3:dyDescent="0.2">
       <c r="A250" t="s">
         <v>8</v>
       </c>
@@ -4559,7 +4577,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="251" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:11" ns3:dyDescent="0.2">
       <c r="A251" s="1" t="s">
         <v>9</v>
       </c>
@@ -4570,7 +4588,7 @@
       <c r="F251" s="1"/>
       <c r="G251" s="1"/>
     </row>
-    <row r="252" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:11" ns3:dyDescent="0.2">
       <c r="A252" s="1" t="s">
         <v>10</v>
       </c>
@@ -4595,7 +4613,7 @@
       <c r="J252" s="1"/>
       <c r="K252" s="1"/>
     </row>
-    <row r="253" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:11" ns3:dyDescent="0.2">
       <c r="A253" t="str">
         <f>B244</f>
         <v>market for battery capacity (PLiB scenario)</v>
@@ -4621,7 +4639,7 @@
       <c r="J253" s="1"/>
       <c r="K253" s="1"/>
     </row>
-    <row r="254" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:11" ht="16" ns3:dyDescent="0.2">
       <c r="A254" s="4" t="s">
         <v>16</v>
       </c>
@@ -4641,7 +4659,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="255" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:11" ht="16" ns3:dyDescent="0.2">
       <c r="A255" s="4" t="s">
         <v>19</v>
       </c>
@@ -4661,7 +4679,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="256" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:11" ht="16" ns3:dyDescent="0.2">
       <c r="A256" s="4" t="s">
         <v>110</v>
       </c>
@@ -4681,7 +4699,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="257" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A257" s="4" t="s">
         <v>22</v>
       </c>
@@ -4701,7 +4719,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="258" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A258" s="4" t="s">
         <v>23</v>
       </c>
@@ -4721,7 +4739,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="259" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A259" s="4" t="s">
         <v>62</v>
       </c>
@@ -4741,7 +4759,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="260" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A260" s="4" t="s">
         <v>27</v>
       </c>
@@ -4761,9 +4779,11 @@
         <v>106</v>
       </c>
     </row>
-    <row r="261" spans="1:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="A261" s="6" t="s">
-        <v>30</v>
+    <row r="261" spans="1:6" ht="16" ns3:dyDescent="0.2">
+      <c r="A261" s="6" t="inlineStr">
+        <is>
+          <t>market for battery capacity, ASSB, polymer</t>
+        </is>
       </c>
       <c r="B261">
         <v>0</v>
@@ -4781,9 +4801,11 @@
         <v>106</v>
       </c>
     </row>
-    <row r="262" spans="1:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="A262" s="6" t="s">
-        <v>55</v>
+    <row r="262" spans="1:6" ht="16" ns3:dyDescent="0.2">
+      <c r="A262" s="6" t="inlineStr">
+        <is>
+          <t>market for battery capacity, ASSB, oxidic</t>
+        </is>
       </c>
       <c r="B262">
         <v>0</v>
@@ -4801,7 +4823,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="263" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A263" s="4" t="s">
         <v>56</v>
       </c>
@@ -4821,7 +4843,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="264" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A264" s="4" t="s">
         <v>35</v>
       </c>
@@ -4841,7 +4863,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="265" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A265" s="4" t="s">
         <v>38</v>
       </c>
@@ -4861,9 +4883,11 @@
         <v>106</v>
       </c>
     </row>
-    <row r="266" spans="1:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="A266" s="5" t="s">
-        <v>47</v>
+    <row r="266" spans="1:6" ht="16" ns3:dyDescent="0.2">
+      <c r="A266" s="5" t="inlineStr">
+        <is>
+          <t>market for battery capacity, ASSB, sulfidic</t>
+        </is>
       </c>
       <c r="B266">
         <v>0</v>
@@ -4882,9 +4906,9 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N266" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:N266" ns2:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" ns4:id="rId1"/>
 </worksheet>
 </file>
 

--- a/premise/data/additional_inventories/lci-battery-capacity.xlsx
+++ b/premise/data/additional_inventories/lci-battery-capacity.xlsx
@@ -4913,16 +4913,16 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E327F433-64CA-4C75-A0BC-FFEEC2922B0D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:ns4="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{E327F433-64CA-4C75-A0BC-FFEEC2922B0D}">
   <dimension ref="A1:N203"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" ns3:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="69.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="24.1640625" customWidth="1"/>
     <col min="6" max="6" width="28.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:14" ht="16" ns3:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -4930,7 +4930,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:14" ns3:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -4938,7 +4938,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:14" ns3:dyDescent="0.2">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -4946,7 +4946,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:14" ns3:dyDescent="0.2">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -4954,7 +4954,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" ns3:dyDescent="0.2">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -4962,7 +4962,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" ns3:dyDescent="0.2">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -4971,7 +4971,7 @@
       </c>
       <c r="F6" s="7"/>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" ns3:dyDescent="0.2">
       <c r="A7" t="s">
         <v>48</v>
       </c>
@@ -4980,13 +4980,13 @@
         <v>0.73</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" ht="16" ns3:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B8" s="7"/>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:14" ns3:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>10</v>
       </c>
@@ -5021,7 +5021,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:14" ht="16" ns3:dyDescent="0.2">
       <c r="A10" s="4" t="str">
         <f>B1</f>
         <v>market for battery capacity, Li-ion, LFP, stationary</v>
@@ -5044,7 +5044,7 @@
         <v>electricity storage capacity</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:14" ns3:dyDescent="0.2">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -5080,7 +5080,7 @@
         <v>9.7847358121330714</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:14" ns3:dyDescent="0.2">
       <c r="A12" t="s">
         <v>53</v>
       </c>
@@ -5121,7 +5121,7 @@
       <c r="M12" s="7"/>
       <c r="N12" s="7"/>
     </row>
-    <row r="14" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:14" ht="16" ns3:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>0</v>
       </c>
@@ -5129,7 +5129,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:14" ns3:dyDescent="0.2">
       <c r="A15" t="s">
         <v>1</v>
       </c>
@@ -5137,7 +5137,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:14" ns3:dyDescent="0.2">
       <c r="A16" t="s">
         <v>2</v>
       </c>
@@ -5145,7 +5145,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:14" ns3:dyDescent="0.2">
       <c r="A17" t="s">
         <v>4</v>
       </c>
@@ -5153,7 +5153,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:14" ns3:dyDescent="0.2">
       <c r="A18" t="s">
         <v>5</v>
       </c>
@@ -5161,7 +5161,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:14" ns3:dyDescent="0.2">
       <c r="A19" t="s">
         <v>6</v>
       </c>
@@ -5169,7 +5169,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:14" ns3:dyDescent="0.2">
       <c r="A20" t="s">
         <v>48</v>
       </c>
@@ -5178,13 +5178,13 @@
         <v>0.73</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:14" ht="16" ns3:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B21" s="3"/>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:14" ns3:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>10</v>
       </c>
@@ -5219,7 +5219,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="23" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:14" ht="16" ns3:dyDescent="0.2">
       <c r="A23" s="4" t="str">
         <f>B14</f>
         <v>market for battery capacity, Li-ion, NMC111, stationary</v>
@@ -5242,7 +5242,7 @@
         <v>electricity storage capacity</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:14" ns3:dyDescent="0.2">
       <c r="A24" t="s">
         <v>20</v>
       </c>
@@ -5278,7 +5278,7 @@
         <v>9.7847358121330714</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:14" ns3:dyDescent="0.2">
       <c r="A25" t="s">
         <v>53</v>
       </c>
@@ -5319,7 +5319,7 @@
       <c r="M25" s="7"/>
       <c r="N25" s="7"/>
     </row>
-    <row r="27" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:14" ht="16" ns3:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>0</v>
       </c>
@@ -5327,7 +5327,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:14" ns3:dyDescent="0.2">
       <c r="A28" t="s">
         <v>1</v>
       </c>
@@ -5335,7 +5335,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:14" ns3:dyDescent="0.2">
       <c r="A29" t="s">
         <v>2</v>
       </c>
@@ -5343,7 +5343,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:14" ns3:dyDescent="0.2">
       <c r="A30" t="s">
         <v>4</v>
       </c>
@@ -5351,7 +5351,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:14" ns3:dyDescent="0.2">
       <c r="A31" t="s">
         <v>5</v>
       </c>
@@ -5359,7 +5359,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:14" ns3:dyDescent="0.2">
       <c r="A32" t="s">
         <v>6</v>
       </c>
@@ -5367,7 +5367,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:14" ns3:dyDescent="0.2">
       <c r="A33" t="s">
         <v>48</v>
       </c>
@@ -5376,13 +5376,13 @@
         <v>0.73</v>
       </c>
     </row>
-    <row r="34" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:14" ht="16" ns3:dyDescent="0.2">
       <c r="A34" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B34" s="3"/>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:14" ns3:dyDescent="0.2">
       <c r="A35" s="1" t="s">
         <v>10</v>
       </c>
@@ -5417,7 +5417,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="36" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:14" ht="16" ns3:dyDescent="0.2">
       <c r="A36" s="4" t="str">
         <f>B27</f>
         <v>market for battery capacity, Li-ion, NMC532, stationary</v>
@@ -5440,7 +5440,7 @@
         <v>electricity storage capacity</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:14" ns3:dyDescent="0.2">
       <c r="A37" t="s">
         <v>112</v>
       </c>
@@ -5476,7 +5476,7 @@
         <v>8.058017727639001</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:14" ns3:dyDescent="0.2">
       <c r="A38" t="s">
         <v>53</v>
       </c>
@@ -5517,7 +5517,7 @@
       <c r="M38" s="3"/>
       <c r="N38" s="3"/>
     </row>
-    <row r="40" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:14" ht="16" ns3:dyDescent="0.2">
       <c r="A40" s="2" t="s">
         <v>0</v>
       </c>
@@ -5525,7 +5525,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:14" ns3:dyDescent="0.2">
       <c r="A41" t="s">
         <v>1</v>
       </c>
@@ -5533,7 +5533,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:14" ns3:dyDescent="0.2">
       <c r="A42" t="s">
         <v>2</v>
       </c>
@@ -5541,7 +5541,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:14" ns3:dyDescent="0.2">
       <c r="A43" t="s">
         <v>4</v>
       </c>
@@ -5549,7 +5549,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:14" ns3:dyDescent="0.2">
       <c r="A44" t="s">
         <v>5</v>
       </c>
@@ -5558,7 +5558,7 @@
       </c>
       <c r="E44" s="3"/>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:14" ns3:dyDescent="0.2">
       <c r="A45" t="s">
         <v>6</v>
       </c>
@@ -5567,7 +5567,7 @@
       </c>
       <c r="E45" s="3"/>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:14" ns3:dyDescent="0.2">
       <c r="A46" t="s">
         <v>48</v>
       </c>
@@ -5576,13 +5576,13 @@
         <v>0.73</v>
       </c>
     </row>
-    <row r="47" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:14" ht="16" ns3:dyDescent="0.2">
       <c r="A47" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B47" s="3"/>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:14" ns3:dyDescent="0.2">
       <c r="A48" s="1" t="s">
         <v>10</v>
       </c>
@@ -5617,7 +5617,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="49" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:14" ht="16" ns3:dyDescent="0.2">
       <c r="A49" s="4" t="str">
         <f>B40</f>
         <v>market for battery capacity, Li-ion, NMC622, stationary</v>
@@ -5640,7 +5640,7 @@
         <v>electricity storage capacity</v>
       </c>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:14" ns3:dyDescent="0.2">
       <c r="A50" t="s">
         <v>25</v>
       </c>
@@ -5676,7 +5676,7 @@
         <v>6.8493150684931514</v>
       </c>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:14" ns3:dyDescent="0.2">
       <c r="A51" t="s">
         <v>53</v>
       </c>
@@ -5717,7 +5717,7 @@
       <c r="M51" s="3"/>
       <c r="N51" s="3"/>
     </row>
-    <row r="53" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:14" ht="16" ns3:dyDescent="0.2">
       <c r="A53" s="2" t="s">
         <v>0</v>
       </c>
@@ -5725,7 +5725,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:14" ns3:dyDescent="0.2">
       <c r="A54" t="s">
         <v>1</v>
       </c>
@@ -5733,7 +5733,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:14" ns3:dyDescent="0.2">
       <c r="A55" t="s">
         <v>2</v>
       </c>
@@ -5741,7 +5741,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:14" ns3:dyDescent="0.2">
       <c r="A56" t="s">
         <v>4</v>
       </c>
@@ -5749,7 +5749,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:14" ns3:dyDescent="0.2">
       <c r="A57" t="s">
         <v>5</v>
       </c>
@@ -5757,7 +5757,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:14" ns3:dyDescent="0.2">
       <c r="A58" t="s">
         <v>6</v>
       </c>
@@ -5766,12 +5766,12 @@
       </c>
       <c r="E58" s="3"/>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:14" ns3:dyDescent="0.2">
       <c r="A59" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="60" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:14" ht="16" ns3:dyDescent="0.2">
       <c r="A60" s="2" t="s">
         <v>9</v>
       </c>
@@ -5780,7 +5780,7 @@
         <v>0.1988</v>
       </c>
     </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:14" ns3:dyDescent="0.2">
       <c r="A61" s="1" t="s">
         <v>10</v>
       </c>
@@ -5815,7 +5815,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="62" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:14" ht="16" ns3:dyDescent="0.2">
       <c r="A62" s="4" t="str">
         <f>B53</f>
         <v>market for battery capacity, Li-ion, NMC811, stationary</v>
@@ -5838,7 +5838,7 @@
         <v>electricity storage capacity</v>
       </c>
     </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:14" ns3:dyDescent="0.2">
       <c r="A63" t="s">
         <v>24</v>
       </c>
@@ -5874,7 +5874,7 @@
         <v>5.868544600938967</v>
       </c>
     </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:14" ns3:dyDescent="0.2">
       <c r="A64" t="s">
         <v>53</v>
       </c>
@@ -5915,7 +5915,7 @@
       <c r="M64" s="3"/>
       <c r="N64" s="3"/>
     </row>
-    <row r="66" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:14" ht="16" ns3:dyDescent="0.2">
       <c r="A66" s="2" t="s">
         <v>0</v>
       </c>
@@ -5923,7 +5923,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:14" ns3:dyDescent="0.2">
       <c r="A67" t="s">
         <v>1</v>
       </c>
@@ -5933,7 +5933,7 @@
         </is>
       </c>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:14" ns3:dyDescent="0.2">
       <c r="A68" t="s">
         <v>2</v>
       </c>
@@ -5941,7 +5941,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:14" ns3:dyDescent="0.2">
       <c r="A69" t="s">
         <v>4</v>
       </c>
@@ -5949,7 +5949,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:14" ns3:dyDescent="0.2">
       <c r="A70" t="s">
         <v>5</v>
       </c>
@@ -5957,7 +5957,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:14" ns3:dyDescent="0.2">
       <c r="A71" t="s">
         <v>6</v>
       </c>
@@ -5966,7 +5966,7 @@
       </c>
       <c r="E71" s="3"/>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:14" ns3:dyDescent="0.2">
       <c r="A72" t="s">
         <v>48</v>
       </c>
@@ -5975,12 +5975,12 @@
         <v>0.72591000000000006</v>
       </c>
     </row>
-    <row r="73" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:14" ht="16" ns3:dyDescent="0.2">
       <c r="A73" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:14" ns3:dyDescent="0.2">
       <c r="A74" s="1" t="s">
         <v>10</v>
       </c>
@@ -6015,7 +6015,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="75" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:14" ht="16" ns3:dyDescent="0.2">
       <c r="A75" s="4" t="str">
         <f>B66</f>
         <v>market for battery capacity, Li-ion, NMC955, stationary</v>
@@ -6038,7 +6038,7 @@
         <v>electricity storage capacity</v>
       </c>
     </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:14" ns3:dyDescent="0.2">
       <c r="A76" t="s">
         <v>63</v>
       </c>
@@ -6074,7 +6074,7 @@
         <v>4.5919374761793241</v>
       </c>
     </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:14" ns3:dyDescent="0.2">
       <c r="A77" t="s">
         <v>53</v>
       </c>
@@ -6115,7 +6115,7 @@
       <c r="M77" s="3"/>
       <c r="N77" s="3"/>
     </row>
-    <row r="80" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:14" ht="16" ns3:dyDescent="0.2">
       <c r="A80" s="2" t="s">
         <v>0</v>
       </c>
@@ -6123,15 +6123,17 @@
         <v>101</v>
       </c>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:11" ns3:dyDescent="0.2">
       <c r="A81" t="s">
         <v>1</v>
       </c>
-      <c r="B81" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>VRFB reference correction v1 (2026-10-17). Independent reconstruction: Oxkem VOS16 2024 electrolyte; Martin 2020 electrochemical reduction; Weber 2018 hardware and lifetime. Nominal capacity uses paired one-electron V charge at Li 2011's 1.25 V standard potential, an explicit reference assumption, not a measured discharge average. Legacy '8.3 MWh' activity name is an identifier, not the reconstructed capacity. The source archive's unspecified remaining-error warning is unresolved; no archive processes are copied. See data/battery/vanadium_reference_design.json and stationary battery documentation for calculations and coverage gaps. Fixed design at all years, no imposed primary/secondary-share change. One nominal gross reference kWh requires 59.6406266373 kg installed system. No 21% extra BoP factor; hardware is already complete. Original capacity bounds mixed incompatible designs; deterministic reference replaces them. Actual discharge performance and generic consumer throughput remain separate limitations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" spans="1:11" ns3:dyDescent="0.2">
       <c r="A82" t="s">
         <v>2</v>
       </c>
@@ -6139,7 +6141,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:11" ns3:dyDescent="0.2">
       <c r="A83" t="s">
         <v>4</v>
       </c>
@@ -6147,7 +6149,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:11" ns3:dyDescent="0.2">
       <c r="A84" t="s">
         <v>5</v>
       </c>
@@ -6156,7 +6158,7 @@
       </c>
       <c r="E84" s="3"/>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:11" ns3:dyDescent="0.2">
       <c r="A85" t="s">
         <v>6</v>
       </c>
@@ -6164,7 +6166,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:11" ns3:dyDescent="0.2">
       <c r="A86" t="s">
         <v>48</v>
       </c>
@@ -6172,12 +6174,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:11" ht="16" ns3:dyDescent="0.2">
       <c r="A87" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:11" ns3:dyDescent="0.2">
       <c r="A88" s="1" t="s">
         <v>10</v>
       </c>
@@ -6212,7 +6214,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="89" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:11" ht="16" ns3:dyDescent="0.2">
       <c r="A89" s="4" t="str">
         <f>B80</f>
         <v>market for battery capacity, redox-flow, Vanadium, stationary</v>
@@ -6235,13 +6237,12 @@
         <v>electricity storage capacity</v>
       </c>
     </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:11" ns3:dyDescent="0.2">
       <c r="A90" t="s">
         <v>85</v>
       </c>
       <c r="B90" s="3">
-        <f>1/(0.0194)</f>
-        <v>51.546391752577321</v>
+        <v>59.64062663729406</v>
       </c>
       <c r="C90" t="s">
         <v>7</v>
@@ -6256,28 +6257,22 @@
         <v>98</v>
       </c>
       <c r="G90">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H90" s="7">
-        <f>B90</f>
-        <v>51.546391752577321</v>
-      </c>
-      <c r="I90" s="3">
-        <f>1/(0.06)</f>
-        <v>16.666666666666668</v>
-      </c>
-      <c r="J90" s="3">
-        <f>1/(0.019)</f>
-        <v>52.631578947368425</v>
-      </c>
-    </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A91" t="s">
-        <v>86</v>
+        <v>59.64062663729406</v>
+      </c>
+      <c r="I90" s="3"/>
+      <c r="J90" s="3"/>
+    </row>
+    <row r="91" spans="1:11" ns3:dyDescent="0.2">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>market for used redox-flow battery, Vanadium, reference design</t>
+        </is>
       </c>
       <c r="B91" s="3">
-        <f>-1*B90</f>
-        <v>-51.546391752577321</v>
+        <v>-59.64062663729406</v>
       </c>
       <c r="C91" t="s">
         <v>7</v>
@@ -6288,41 +6283,36 @@
       <c r="E91" t="s">
         <v>14</v>
       </c>
-      <c r="F91" t="s">
-        <v>87</v>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>used redox-flow battery, Vanadium, reference design</t>
+        </is>
       </c>
       <c r="G91">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H91" s="7">
-        <f>B91</f>
-        <v>-51.546391752577321</v>
-      </c>
-      <c r="I91" s="3">
-        <f>-1*J90</f>
-        <v>-52.631578947368425</v>
-      </c>
-      <c r="J91" s="3">
-        <f>-1*I90</f>
-        <v>-16.666666666666668</v>
-      </c>
+        <v>-59.64062663729406</v>
+      </c>
+      <c r="I91" s="3"/>
+      <c r="J91" s="3"/>
       <c r="K91" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:11" ns3:dyDescent="0.2">
       <c r="B92" s="3"/>
       <c r="H92" s="7"/>
       <c r="I92" s="3"/>
       <c r="J92" s="3"/>
     </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:11" ns3:dyDescent="0.2">
       <c r="B93" s="3"/>
       <c r="H93" s="7"/>
       <c r="I93" s="3"/>
       <c r="J93" s="3"/>
     </row>
-    <row r="94" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:11" ht="16" ns3:dyDescent="0.2">
       <c r="A94" s="2" t="s">
         <v>0</v>
       </c>
@@ -6330,7 +6320,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:11" ns3:dyDescent="0.2">
       <c r="A95" t="s">
         <v>1</v>
       </c>
@@ -6338,7 +6328,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:11" ns3:dyDescent="0.2">
       <c r="A96" t="s">
         <v>2</v>
       </c>
@@ -6346,7 +6336,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:11" ns3:dyDescent="0.2">
       <c r="A97" t="s">
         <v>4</v>
       </c>
@@ -6354,7 +6344,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:11" ns3:dyDescent="0.2">
       <c r="A98" t="s">
         <v>5</v>
       </c>
@@ -6363,7 +6353,7 @@
       </c>
       <c r="E98" s="3"/>
     </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:11" ns3:dyDescent="0.2">
       <c r="A99" t="s">
         <v>6</v>
       </c>
@@ -6371,7 +6361,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:11" ns3:dyDescent="0.2">
       <c r="A100" t="s">
         <v>48</v>
       </c>
@@ -6379,12 +6369,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:11" ht="16" ns3:dyDescent="0.2">
       <c r="A101" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:11" ns3:dyDescent="0.2">
       <c r="A102" s="1" t="s">
         <v>10</v>
       </c>
@@ -6419,7 +6409,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="103" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:11" ht="16" ns3:dyDescent="0.2">
       <c r="A103" s="4" t="str">
         <f>B94</f>
         <v>market for battery capacity, lead acid, rechargeable, stationary</v>
@@ -6442,7 +6432,7 @@
         <v>electricity storage capacity</v>
       </c>
     </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:11" ns3:dyDescent="0.2">
       <c r="A104" t="s">
         <v>90</v>
       </c>
@@ -6478,7 +6468,7 @@
         <v>37.037037037037038</v>
       </c>
     </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:11" ns3:dyDescent="0.2">
       <c r="A105" t="s">
         <v>92</v>
       </c>
@@ -6517,13 +6507,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:11" ns3:dyDescent="0.2">
       <c r="B106" s="3"/>
       <c r="H106" s="7"/>
       <c r="I106" s="3"/>
       <c r="J106" s="3"/>
     </row>
-    <row r="108" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:11" ht="16" ns3:dyDescent="0.2">
       <c r="A108" s="2" t="s">
         <v>0</v>
       </c>
@@ -6531,7 +6521,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:11" ns3:dyDescent="0.2">
       <c r="A109" t="s">
         <v>1</v>
       </c>
@@ -6539,7 +6529,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:11" ns3:dyDescent="0.2">
       <c r="A110" t="s">
         <v>2</v>
       </c>
@@ -6547,7 +6537,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:11" ns3:dyDescent="0.2">
       <c r="A111" t="s">
         <v>4</v>
       </c>
@@ -6555,7 +6545,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:11" ns3:dyDescent="0.2">
       <c r="A112" t="s">
         <v>5</v>
       </c>
@@ -6564,7 +6554,7 @@
       </c>
       <c r="E112" s="3"/>
     </row>
-    <row r="113" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:14" ns3:dyDescent="0.2">
       <c r="A113" t="s">
         <v>6</v>
       </c>
@@ -6572,7 +6562,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="114" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:14" ns3:dyDescent="0.2">
       <c r="A114" t="s">
         <v>48</v>
       </c>
@@ -6581,12 +6571,12 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="115" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:14" ht="16" ns3:dyDescent="0.2">
       <c r="A115" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="116" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:14" ns3:dyDescent="0.2">
       <c r="A116" s="1" t="s">
         <v>10</v>
       </c>
@@ -6621,7 +6611,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="117" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:14" ht="16" ns3:dyDescent="0.2">
       <c r="A117" s="4" t="str">
         <f>B108</f>
         <v>market for battery capacity, Sodium-ion, SiB, stationary</v>
@@ -6644,7 +6634,7 @@
         <v>electricity storage capacity</v>
       </c>
     </row>
-    <row r="118" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:14" ns3:dyDescent="0.2">
       <c r="A118" t="s">
         <v>39</v>
       </c>
@@ -6680,7 +6670,7 @@
         <v>11.111111111111111</v>
       </c>
     </row>
-    <row r="119" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:14" ns3:dyDescent="0.2">
       <c r="A119" t="s">
         <v>53</v>
       </c>
@@ -6721,7 +6711,7 @@
       <c r="M119" s="3"/>
       <c r="N119" s="3"/>
     </row>
-    <row r="121" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:14" ht="16" ns3:dyDescent="0.2">
       <c r="A121" s="2" t="s">
         <v>0</v>
       </c>
@@ -6729,7 +6719,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="122" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:14" ns3:dyDescent="0.2">
       <c r="A122" t="s">
         <v>1</v>
       </c>
@@ -6737,7 +6727,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="123" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:14" ns3:dyDescent="0.2">
       <c r="A123" t="s">
         <v>2</v>
       </c>
@@ -6745,7 +6735,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="124" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:14" ns3:dyDescent="0.2">
       <c r="A124" t="s">
         <v>4</v>
       </c>
@@ -6753,7 +6743,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:14" ns3:dyDescent="0.2">
       <c r="A125" t="s">
         <v>5</v>
       </c>
@@ -6761,7 +6751,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="126" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:14" ns3:dyDescent="0.2">
       <c r="A126" t="s">
         <v>6</v>
       </c>
@@ -6769,7 +6759,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="127" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:14" ns3:dyDescent="0.2">
       <c r="A127" t="s">
         <v>8</v>
       </c>
@@ -6777,7 +6767,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="128" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:14" ns3:dyDescent="0.2">
       <c r="A128" s="1" t="s">
         <v>9</v>
       </c>
@@ -6788,7 +6778,7 @@
       <c r="F128" s="1"/>
       <c r="G128" s="1"/>
     </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:11" ns3:dyDescent="0.2">
       <c r="A129" s="1" t="s">
         <v>10</v>
       </c>
@@ -6823,7 +6813,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="130" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:11" ht="16" ns3:dyDescent="0.2">
       <c r="A130" s="5" t="str">
         <f>B121</f>
         <v>market for battery capacity, Sodium-Nickel-Chloride, Na-NiCl, stationary</v>
@@ -6846,7 +6836,7 @@
         <v>electricity storage capacity</v>
       </c>
     </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:11" ns3:dyDescent="0.2">
       <c r="A131" t="s">
         <v>41</v>
       </c>
@@ -6882,7 +6872,7 @@
         <v>10.775862068965516</v>
       </c>
     </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:11" ns3:dyDescent="0.2">
       <c r="A132" t="s">
         <v>53</v>
       </c>
@@ -6921,13 +6911,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:11" ns3:dyDescent="0.2">
       <c r="B133" s="3"/>
       <c r="H133" s="7"/>
       <c r="I133" s="7"/>
       <c r="J133" s="7"/>
     </row>
-    <row r="135" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:11" ht="16" ns3:dyDescent="0.2">
       <c r="A135" s="2" t="s">
         <v>0</v>
       </c>
@@ -6935,7 +6925,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="136" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:11" ns3:dyDescent="0.2">
       <c r="A136" t="s">
         <v>1</v>
       </c>
@@ -6943,7 +6933,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:11" ns3:dyDescent="0.2">
       <c r="A137" t="s">
         <v>2</v>
       </c>
@@ -6951,7 +6941,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="138" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:11" ns3:dyDescent="0.2">
       <c r="A138" t="s">
         <v>4</v>
       </c>
@@ -6959,7 +6949,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:11" ns3:dyDescent="0.2">
       <c r="A139" t="s">
         <v>5</v>
       </c>
@@ -6967,7 +6957,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="140" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:11" ns3:dyDescent="0.2">
       <c r="A140" t="s">
         <v>6</v>
       </c>
@@ -6975,7 +6965,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="141" spans="1:11" s="6" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:11" s="6" customFormat="1" ht="16" ns3:dyDescent="0.2">
       <c r="A141" t="s">
         <v>8</v>
       </c>
@@ -6992,7 +6982,7 @@
       <c r="J141"/>
       <c r="K141"/>
     </row>
-    <row r="142" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:11" ns3:dyDescent="0.2">
       <c r="A142" s="1" t="s">
         <v>9</v>
       </c>
@@ -7003,7 +6993,7 @@
       <c r="F142" s="1"/>
       <c r="G142" s="1"/>
     </row>
-    <row r="143" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:11" ns3:dyDescent="0.2">
       <c r="A143" s="1" t="s">
         <v>10</v>
       </c>
@@ -7028,7 +7018,7 @@
       <c r="J143" s="1"/>
       <c r="K143" s="1"/>
     </row>
-    <row r="144" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:11" ns3:dyDescent="0.2">
       <c r="A144" t="str">
         <f>B135</f>
         <v>market for battery capacity, stationary (CONT scenario)</v>
@@ -7055,7 +7045,7 @@
       <c r="J144" s="1"/>
       <c r="K144" s="1"/>
     </row>
-    <row r="145" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:11" ht="16" ns3:dyDescent="0.2">
       <c r="A145" s="6" t="s">
         <v>79</v>
       </c>
@@ -7075,7 +7065,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="146" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:11" ht="16" ns3:dyDescent="0.2">
       <c r="A146" s="6" t="s">
         <v>80</v>
       </c>
@@ -7095,7 +7085,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="147" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:11" ht="16" ns3:dyDescent="0.2">
       <c r="A147" s="6" t="s">
         <v>114</v>
       </c>
@@ -7115,7 +7105,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="148" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:11" ht="16" ns3:dyDescent="0.2">
       <c r="A148" s="6" t="s">
         <v>81</v>
       </c>
@@ -7135,7 +7125,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="149" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:11" ht="16" ns3:dyDescent="0.2">
       <c r="A149" s="6" t="s">
         <v>82</v>
       </c>
@@ -7155,7 +7145,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="150" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:11" ht="16" ns3:dyDescent="0.2">
       <c r="A150" s="6" t="s">
         <v>83</v>
       </c>
@@ -7175,7 +7165,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="151" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:11" ht="16" ns3:dyDescent="0.2">
       <c r="A151" s="6" t="s">
         <v>84</v>
       </c>
@@ -7195,7 +7185,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="152" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:11" ht="16" ns3:dyDescent="0.2">
       <c r="A152" s="4" t="s">
         <v>101</v>
       </c>
@@ -7215,7 +7205,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="153" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:11" ht="16" ns3:dyDescent="0.2">
       <c r="A153" s="6" t="s">
         <v>89</v>
       </c>
@@ -7240,7 +7230,7 @@
       <c r="J153" s="6"/>
       <c r="K153" s="6"/>
     </row>
-    <row r="154" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:11" ht="16" ns3:dyDescent="0.2">
       <c r="A154" s="6" t="s">
         <v>95</v>
       </c>
@@ -7260,7 +7250,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="156" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:11" ht="16" ns3:dyDescent="0.2">
       <c r="A156" s="2" t="s">
         <v>0</v>
       </c>
@@ -7268,7 +7258,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="157" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:11" ns3:dyDescent="0.2">
       <c r="A157" t="s">
         <v>1</v>
       </c>
@@ -7276,7 +7266,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="158" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:11" ns3:dyDescent="0.2">
       <c r="A158" t="s">
         <v>2</v>
       </c>
@@ -7284,7 +7274,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="159" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:11" ns3:dyDescent="0.2">
       <c r="A159" t="s">
         <v>4</v>
       </c>
@@ -7292,7 +7282,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="160" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:11" ns3:dyDescent="0.2">
       <c r="A160" t="s">
         <v>5</v>
       </c>
@@ -7300,7 +7290,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="161" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:11" ns3:dyDescent="0.2">
       <c r="A161" t="s">
         <v>6</v>
       </c>
@@ -7308,7 +7298,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="162" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:11" ns3:dyDescent="0.2">
       <c r="A162" t="s">
         <v>8</v>
       </c>
@@ -7316,7 +7306,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="163" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:11" ns3:dyDescent="0.2">
       <c r="A163" s="1" t="s">
         <v>9</v>
       </c>
@@ -7327,7 +7317,7 @@
       <c r="F163" s="1"/>
       <c r="G163" s="1"/>
     </row>
-    <row r="164" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:11" ns3:dyDescent="0.2">
       <c r="A164" s="1" t="s">
         <v>10</v>
       </c>
@@ -7352,7 +7342,7 @@
       <c r="J164" s="1"/>
       <c r="K164" s="1"/>
     </row>
-    <row r="165" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:11" ns3:dyDescent="0.2">
       <c r="A165" t="str">
         <f>B156</f>
         <v>market for battery capacity, stationary (TC scenario)</v>
@@ -7379,7 +7369,7 @@
       <c r="J165" s="1"/>
       <c r="K165" s="1"/>
     </row>
-    <row r="166" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:11" ht="16" ns3:dyDescent="0.2">
       <c r="A166" s="6" t="s">
         <v>79</v>
       </c>
@@ -7399,7 +7389,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="167" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:11" ht="16" ns3:dyDescent="0.2">
       <c r="A167" s="6" t="s">
         <v>80</v>
       </c>
@@ -7419,7 +7409,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="168" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:11" ht="16" ns3:dyDescent="0.2">
       <c r="A168" s="6" t="s">
         <v>114</v>
       </c>
@@ -7439,7 +7429,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="169" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:11" ht="16" ns3:dyDescent="0.2">
       <c r="A169" s="6" t="s">
         <v>81</v>
       </c>
@@ -7459,7 +7449,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="170" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:11" ht="16" ns3:dyDescent="0.2">
       <c r="A170" s="6" t="s">
         <v>82</v>
       </c>
@@ -7479,7 +7469,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="171" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:11" ht="16" ns3:dyDescent="0.2">
       <c r="A171" s="6" t="s">
         <v>83</v>
       </c>
@@ -7499,7 +7489,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="172" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:11" ht="16" ns3:dyDescent="0.2">
       <c r="A172" s="6" t="s">
         <v>84</v>
       </c>
@@ -7519,7 +7509,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="173" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:11" ht="16" ns3:dyDescent="0.2">
       <c r="A173" s="6" t="s">
         <v>101</v>
       </c>
@@ -7539,7 +7529,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="174" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:11" ht="16" ns3:dyDescent="0.2">
       <c r="A174" s="6" t="s">
         <v>89</v>
       </c>
@@ -7561,7 +7551,7 @@
       <c r="G174" s="6"/>
       <c r="H174" s="6"/>
     </row>
-    <row r="175" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:11" ht="16" ns3:dyDescent="0.2">
       <c r="A175" s="6" t="s">
         <v>95</v>
       </c>
@@ -7581,10 +7571,10 @@
         <v>106</v>
       </c>
     </row>
-    <row r="176" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:11" ht="16" ns3:dyDescent="0.2">
       <c r="A176" s="4"/>
     </row>
-    <row r="177" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:11" ht="16" ns3:dyDescent="0.2">
       <c r="A177" s="2" t="s">
         <v>0</v>
       </c>
@@ -7592,7 +7582,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="178" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:11" ns3:dyDescent="0.2">
       <c r="A178" t="s">
         <v>1</v>
       </c>
@@ -7600,7 +7590,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="179" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:11" ns3:dyDescent="0.2">
       <c r="A179" t="s">
         <v>2</v>
       </c>
@@ -7608,7 +7598,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="180" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:11" ns3:dyDescent="0.2">
       <c r="A180" t="s">
         <v>4</v>
       </c>
@@ -7616,7 +7606,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="181" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:11" ns3:dyDescent="0.2">
       <c r="A181" t="s">
         <v>5</v>
       </c>
@@ -7624,7 +7614,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="182" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:11" ns3:dyDescent="0.2">
       <c r="A182" t="s">
         <v>6</v>
       </c>
@@ -7632,7 +7622,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="183" spans="1:11" s="6" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:11" s="6" customFormat="1" ht="16" ns3:dyDescent="0.2">
       <c r="A183" t="s">
         <v>8</v>
       </c>
@@ -7649,7 +7639,7 @@
       <c r="J183"/>
       <c r="K183"/>
     </row>
-    <row r="184" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:11" ns3:dyDescent="0.2">
       <c r="A184" s="1" t="s">
         <v>9</v>
       </c>
@@ -7660,7 +7650,7 @@
       <c r="F184" s="1"/>
       <c r="G184" s="1"/>
     </row>
-    <row r="185" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:11" ns3:dyDescent="0.2">
       <c r="A185" s="1" t="s">
         <v>10</v>
       </c>
@@ -7695,7 +7685,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="186" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:11" ns3:dyDescent="0.2">
       <c r="A186" t="str">
         <f>B177</f>
         <v>electricity supply, from stationary battery (CONT scenario)</v>
@@ -7723,7 +7713,7 @@
       <c r="J186" s="1"/>
       <c r="K186" s="1"/>
     </row>
-    <row r="187" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:11" ht="16" ns3:dyDescent="0.2">
       <c r="A187" s="6" t="s">
         <v>96</v>
       </c>
@@ -7759,7 +7749,7 @@
         <v>6.6666666666666664E-4</v>
       </c>
     </row>
-    <row r="188" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:11" ht="16" ns3:dyDescent="0.2">
       <c r="A188" s="8" t="s">
         <v>105</v>
       </c>
@@ -7795,7 +7785,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="189" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:11" ht="16" ns3:dyDescent="0.2">
       <c r="A189" s="8" t="s">
         <v>105</v>
       </c>
@@ -7818,57 +7808,57 @@
         <v>0</v>
       </c>
     </row>
-    <row r="190" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:11" ns3:dyDescent="0.2">
       <c r="G190" s="1"/>
       <c r="H190" s="1"/>
       <c r="I190" s="1"/>
       <c r="J190" s="1"/>
       <c r="K190" s="1"/>
     </row>
-    <row r="191" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:11" ht="16" ns3:dyDescent="0.2">
       <c r="A191" s="6"/>
     </row>
-    <row r="192" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:11" ht="16" ns3:dyDescent="0.2">
       <c r="A192" s="6"/>
     </row>
-    <row r="193" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:7" ht="16" ns3:dyDescent="0.2">
       <c r="A193" s="6"/>
     </row>
-    <row r="194" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:7" ht="16" ns3:dyDescent="0.2">
       <c r="A194" s="6"/>
     </row>
-    <row r="195" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:7" ht="16" ns3:dyDescent="0.2">
       <c r="A195" s="6"/>
     </row>
-    <row r="196" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:7" ht="16" ns3:dyDescent="0.2">
       <c r="A196" s="6"/>
     </row>
-    <row r="197" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:7" ht="16" ns3:dyDescent="0.2">
       <c r="A197" s="6"/>
     </row>
-    <row r="198" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:7" ht="16" ns3:dyDescent="0.2">
       <c r="A198" s="6"/>
     </row>
-    <row r="199" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:7" ht="16" ns3:dyDescent="0.2">
       <c r="A199" s="6"/>
       <c r="B199" s="6"/>
       <c r="G199" s="6"/>
     </row>
-    <row r="200" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:7" ht="16" ns3:dyDescent="0.2">
       <c r="A200" s="6"/>
     </row>
-    <row r="201" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:7" ht="16" ns3:dyDescent="0.2">
       <c r="A201" s="4"/>
     </row>
-    <row r="202" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:7" ht="16" ns3:dyDescent="0.2">
       <c r="A202" s="4"/>
     </row>
-    <row r="203" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:7" ht="16" ns3:dyDescent="0.2">
       <c r="A203" s="5"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N203" xr:uid="{E327F433-64CA-4C75-A0BC-FFEEC2922B0D}"/>
+  <autoFilter ref="A1:N203" ns2:uid="{E327F433-64CA-4C75-A0BC-FFEEC2922B0D}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" ns4:id="rId1"/>
 </worksheet>
 </file>
--- a/premise/data/additional_inventories/lci-battery-capacity.xlsx
+++ b/premise/data/additional_inventories/lci-battery-capacity.xlsx
@@ -2981,8 +2981,12 @@
       <c r="A147" t="s">
         <v>1</v>
       </c>
-      <c r="B147" t="s">
-        <v>70</v>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>APPROVED SODIUM-ION CAPACITY BASELINE NORMALIZATION, 2026-10-18. Zhang et al. (2024), Future climate impacts of sodium-ion batteries, Resources, Conservation and Recycling 202, 107362, DOI 10.1016/j.resconrec.2023.107362, Table 4, page 5: baseline NMMT/HC cell specific energy is 157 Wh/kg (0.157 kWh/kg), consistent with the existing source description and Premise density baseline. Primary paper: https://pub.epsilon.slu.se/32553/1/zhang-s-et-al-20240122.pdf . The linked existing SIB module recipe contains 0.7515918465419887 kg NMMT cell/kg module (lci-batteries-SIB.xlsx, sodium-ion batteries B493); its battery market purchases one kg of this module per kg delivered. Use this actual recipe coefficient, not a rounded 75 percent fraction, and 0.157 kWh/kg cell: 1/(0.157*0.7515918465419887) = 8.474582023338275 kg delivered module/kWh gross capacity. The previous 1/(0.16*0.75) = 8.333333333333334 kg represented 0.9833326658924353 kWh under those declared specifications. The module dose increases 1.6949842800592974 percent; this is not a percent change in overall transport or system metal demand. Set battery cell mass share to the linked recipe coefficient. Keep existing cell-specific density uncertainty endpoints 0.12 and 0.18 kWh/kg, translating them with the same module fraction; retain triangular type 5, equal negative waste mass and paired signed bounds/locations. Update formula caches consistently. The original rounded specific-energy/fraction/mass figures below are historical notes superseded by this paragraph. All supplier identities/geographies, the one-kWh output, cell/module manufacturing recipes, other chemistries, prospective density trajectory and lifetime/per-MJ allocations remain unchanged. This normalizes to declared cell energy and an existing module proxy; it does not validate measured pack performance, future electrochemical charge, cycle life or operating conditions. The Li-S-derived module architecture and missing BMS/cooling coverage remain unresolved. No electronics, racks, treatment route, recovery credit or primary/secondary share is added. Current full-system metal effects remain unquantified without a scenario rebuild.
+PREVIOUS SOURCE NOTES (ROUNDED VALUES SUPERSEDED ABOVE):
+This dataset provides 1 kWh of battery gross capacity (NOT net), using a Sodium-ion battery. Specific energy density in 2020: 0.157 kWh/kg cell. Battery management (BoP) mass share: 25%. Battery energy density in 2020: 0.12 kWh/kg battery. Battery mass per kWh: 8.5 kg. Lifetime: 628 kWh/kg cell (4000 cycles x 0.157 kWh) or 2'500-4'000 cycles. Source for parameters: Zhang, S., Steubing, B., Potter, H. K., Hansson, P. A., &amp; Nordberg, Å. (2024). Future climate impacts of sodium-ion batteries. Resources, Conservation and Recycling, 202, 107362. https://doi.org/10.1016/j.resconrec.2023.107362. Min and max values from: Hasselwander, S.; Meyer, M.; Österle, I. Techno-Economic Analysis of Different Battery Cell Chemistries for the Passenger Vehicle Market. Batteries 2023, 9, 379. https://doi.org/10.3390/batteries9070379.</t>
+        </is>
       </c>
     </row>
     <row r="148" spans="1:14" ns3:dyDescent="0.2">
@@ -3023,8 +3027,8 @@
         <v>48</v>
       </c>
       <c r="B152">
-        <f>1-0.25</f>
-        <v>0.75</v>
+        <f>0.7515918465419887</f>
+        <v>0.7515918465419887</v>
       </c>
     </row>
     <row r="153" spans="1:14" ht="16" ns3:dyDescent="0.2">
@@ -3095,8 +3099,8 @@
         <v>39</v>
       </c>
       <c r="B156" s="3">
-        <f>1/(0.16*75%)</f>
-        <v>8.3333333333333339</v>
+        <f>1/(0.157*$B$152)</f>
+        <v>8.474582023338275</v>
       </c>
       <c r="C156" t="s">
         <v>7</v>
@@ -3115,15 +3119,15 @@
       </c>
       <c r="H156" s="7">
         <f>B156</f>
-        <v>8.3333333333333339</v>
+        <v>8.474582023338275</v>
       </c>
       <c r="I156" s="3">
-        <f>1/(0.18*75%)</f>
-        <v>7.4074074074074066</v>
+        <f>1/(0.18*$B$152)</f>
+        <v>7.391718764800606</v>
       </c>
       <c r="J156" s="3">
-        <f>1/(0.12*75%)</f>
-        <v>11.111111111111111</v>
+        <f>1/(0.12*$B$152)</f>
+        <v>11.08757814720091</v>
       </c>
     </row>
     <row r="157" spans="1:14" ns3:dyDescent="0.2">
@@ -3132,7 +3136,7 @@
       </c>
       <c r="B157" s="3">
         <f>-1*B156</f>
-        <v>-8.3333333333333339</v>
+        <v>-8.474582023338275</v>
       </c>
       <c r="C157" t="s">
         <v>7</v>
@@ -3151,15 +3155,15 @@
       </c>
       <c r="H157" s="7">
         <f>B157</f>
-        <v>-8.3333333333333339</v>
+        <v>-8.474582023338275</v>
       </c>
       <c r="I157" s="3">
-        <f>-1/(0.12*75%)</f>
-        <v>-11.111111111111111</v>
+        <f>-1/(0.12*$B$152)</f>
+        <v>-11.08757814720091</v>
       </c>
       <c r="J157" s="3">
-        <f>-1/(0.18*75%)</f>
-        <v>-7.4074074074074066</v>
+        <f>-1/(0.18*$B$152)</f>
+        <v>-7.391718764800606</v>
       </c>
       <c r="K157" t="b">
         <v>1</v>

--- a/premise/data/additional_inventories/lci-battery-capacity.xlsx
+++ b/premise/data/additional_inventories/lci-battery-capacity.xlsx
@@ -6529,8 +6529,12 @@
       <c r="A109" t="s">
         <v>1</v>
       </c>
-      <c r="B109" t="s">
-        <v>70</v>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>APPROVED STATIONARY SODIUM-ION CAPACITY BASELINE NORMALIZATION, 2026-10-18. Zhang et al. (2024), Future climate impacts of sodium-ion batteries, Resources, Conservation and Recycling 202, 107362, DOI 10.1016/j.resconrec.2023.107362, Table 4, page 5: baseline NMMT/HC cell specific energy is 157 Wh/kg (0.157 kWh/kg), consistent with the existing source description and Premise density baseline. Primary paper: https://pub.epsilon.slu.se/32553/1/zhang-s-et-al-20240122.pdf . The linked existing SIB module recipe contains 0.7515918465419887 kg NMMT cell/kg module (lci-batteries-SIB.xlsx, sodium-ion batteries B493); its battery market purchases one kg of this module per kg delivered. Use this actual recipe coefficient, not a rounded 75 percent fraction, and 0.157 kWh/kg cell: 1/(0.157*0.7515918465419887) = 8.474582023338275 kg delivered module/kWh gross capacity. The previous 1/(0.16*0.75) = 8.333333333333334 kg represented 0.9833326658924353 kWh under those declared specifications. The module dose increases 1.6949842800592974 percent; this is not a percent change in overall transport or system metal demand. Set battery cell mass share to the linked recipe coefficient. Keep existing cell-specific density uncertainty endpoints 0.12 and 0.18 kWh/kg, translating them with the same module fraction; retain triangular type 5, equal negative waste mass and paired signed bounds/locations. Update formula caches consistently. The original rounded specific-energy/fraction/mass figures below are historical notes superseded by this paragraph. All supplier identities/geographies, the one-kWh output, cell/module manufacturing recipes, other chemistries, prospective density trajectory and lifetime/per-MJ allocations remain unchanged. This normalizes to declared cell energy and an existing module proxy; it does not validate measured pack performance, future electrochemical charge, cycle life or operating conditions. The Li-S-derived module architecture and missing BMS/cooling coverage remain unresolved. No electronics, racks, treatment route, recovery credit or primary/secondary share is added. Current full-system metal effects remain unquantified without a scenario rebuild. STATIONARY MAPPING LIMITATION: This stationary capacity-market name is absent from the existing density aliases. The current unmodified updater therefore leaves its mass and uncertainty bounds fixed through 2050. This corrects the initial normalization only; it does not implement the mobile density trajectory or resolve that mapping gap. The stationary market was inactive in the last 28-case audit, so no current system-metal effect is inferred. The previous mobile correction is preserved.
+PREVIOUS SOURCE NOTES (ROUNDED VALUES SUPERSEDED ABOVE):
+This dataset provides 1 kWh of battery gross capacity (NOT net), using a Sodium-ion battery. Specific energy density in 2020: 0.157 kWh/kg cell. Battery management (BoP) mass share: 25%. Battery energy density in 2020: 0.12 kWh/kg battery. Battery mass per kWh: 8.5 kg. Lifetime: 628 kWh/kg cell (4000 cycles x 0.157 kWh) or 2'500-4'000 cycles. Source for parameters: Zhang, S., Steubing, B., Potter, H. K., Hansson, P. A., &amp; Nordberg, Å. (2024). Future climate impacts of sodium-ion batteries. Resources, Conservation and Recycling, 202, 107362. https://doi.org/10.1016/j.resconrec.2023.107362. Min and max values from: Hasselwander, S.; Meyer, M.; Österle, I. Techno-Economic Analysis of Different Battery Cell Chemistries for the Passenger Vehicle Market. Batteries 2023, 9, 379. https://doi.org/10.3390/batteries9070379.</t>
+        </is>
       </c>
     </row>
     <row r="110" spans="1:11" ns3:dyDescent="0.2">
@@ -6571,8 +6575,8 @@
         <v>48</v>
       </c>
       <c r="B114">
-        <f>1-0.25</f>
-        <v>0.75</v>
+        <f>0.7515918465419887</f>
+        <v>0.7515918465419887</v>
       </c>
     </row>
     <row r="115" spans="1:14" ht="16" ns3:dyDescent="0.2">
@@ -6643,8 +6647,8 @@
         <v>39</v>
       </c>
       <c r="B118" s="3">
-        <f>1/(0.16*75%)</f>
-        <v>8.3333333333333339</v>
+        <f>1/(0.157*$B$114)</f>
+        <v>8.474582023338275</v>
       </c>
       <c r="C118" t="s">
         <v>7</v>
@@ -6663,15 +6667,15 @@
       </c>
       <c r="H118" s="7">
         <f>B118</f>
-        <v>8.3333333333333339</v>
+        <v>8.474582023338275</v>
       </c>
       <c r="I118" s="3">
-        <f>1/(0.18*75%)</f>
-        <v>7.4074074074074066</v>
+        <f>1/(0.18*$B$114)</f>
+        <v>7.391718764800606</v>
       </c>
       <c r="J118" s="3">
-        <f>1/(0.12*75%)</f>
-        <v>11.111111111111111</v>
+        <f>1/(0.12*$B$114)</f>
+        <v>11.08757814720091</v>
       </c>
     </row>
     <row r="119" spans="1:14" ns3:dyDescent="0.2">
@@ -6680,7 +6684,7 @@
       </c>
       <c r="B119" s="3">
         <f>-1*B118</f>
-        <v>-8.3333333333333339</v>
+        <v>-8.474582023338275</v>
       </c>
       <c r="C119" t="s">
         <v>7</v>
@@ -6699,15 +6703,15 @@
       </c>
       <c r="H119" s="7">
         <f>B119</f>
-        <v>-8.3333333333333339</v>
+        <v>-8.474582023338275</v>
       </c>
       <c r="I119" s="3">
-        <f>-1/(0.12*75%)</f>
-        <v>-11.111111111111111</v>
+        <f>-1/(0.12*$B$114)</f>
+        <v>-11.08757814720091</v>
       </c>
       <c r="J119" s="3">
-        <f>-1/(0.18*75%)</f>
-        <v>-7.4074074074074066</v>
+        <f>-1/(0.18*$B$114)</f>
+        <v>-7.391718764800606</v>
       </c>
       <c r="K119" t="b">
         <v>1</v>

--- a/premise/data/additional_inventories/lci-battery-capacity.xlsx
+++ b/premise/data/additional_inventories/lci-battery-capacity.xlsx
@@ -2784,8 +2784,12 @@
       <c r="A134" t="s">
         <v>1</v>
       </c>
-      <c r="B134" t="s">
-        <v>49</v>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>APPROVED Li-O2 SINGLE RECYCLING BOUNDARY, 2026-10-18. Wang, Deng and Yuan (2020), DOI 10.1016/j.jclepro.2020.121339, supporting information Table S16, explicitly describes recycling per 1 kg Li-O2 battery system. Its six treatment coefficients are retained. Set the former -1/321 kg/kg internal treatment fragment to a deterministic zero and apply end of life only at market for battery capacity, Li-ion, Li-O2: the full purchased battery mass is sent to treatment of LiO2 battery, for recycling (RER; waste LiO2 battery). Standalone manufacture is manufacturing-only. DefaultInventory may retain the zero exchange; it contributes no treatment flow. Do not add a second generic Li-ion route. This restores a single historical source-specific accounting route; treatment yields, whole-system mass normalization, modern recovery and primary/secondary shares remain unvalidated. No new recovery credit or change to manufacturing recipes, density or lifetime. The capacity-level treatment amount, sign, triangular bounds and all manufacturing mass formulas/caches are unchanged; purchased and treated mass remain paired as battery density changes.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+This dataset provides 1 kWh of battery gross capacity (NOT net), using a Lithium-oxygen Li-O2 battery. Specific energy density in 2020: 0.360 kWh/kg cell. Battery management (BoP) mass share: 45%. Battery energy density in 2020: 0.238 kWh/kg battery (excl. O2 tanks). System energy density in 2020: 0.198 kWh/kg battery (incl. O2 tanks). Battery mass per kWh: 5.05 kg. Battery lifetime: 305 kWh/kg (1.76 MJ/km x 2e5 km / 321 kg). Source for parameters: Originally from Wang, F., Deng, Y., &amp; Yuan, C. (2020). Life cycle assessment of lithium oxygen battery for electric vehicles. Journal of Cleaner Production, 264, 121339. https://doi.org/10.1016/j.jclepro.2020.121339</t>
+        </is>
       </c>
     </row>
     <row r="135" spans="1:14" ns3:dyDescent="0.2">
@@ -2929,8 +2933,10 @@
       </c>
     </row>
     <row r="144" spans="1:14" ns3:dyDescent="0.2">
-      <c r="A144" t="s">
-        <v>53</v>
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>treatment of LiO2 battery, for recycling</t>
+        </is>
       </c>
       <c r="B144" s="3">
         <f>-1*B143</f>
@@ -2939,14 +2945,18 @@
       <c r="C144" t="s">
         <v>7</v>
       </c>
-      <c r="D144" t="s">
-        <v>3</v>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
       </c>
       <c r="E144" t="s">
         <v>14</v>
       </c>
-      <c r="F144" t="s">
-        <v>54</v>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>waste LiO2 battery</t>
+        </is>
       </c>
       <c r="G144">
         <v>5</v>

--- a/premise/data/additional_inventories/lci-battery-capacity.xlsx
+++ b/premise/data/additional_inventories/lci-battery-capacity.xlsx
@@ -2586,8 +2586,12 @@
       <c r="A121" t="s">
         <v>1</v>
       </c>
-      <c r="B121" t="s">
-        <v>71</v>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>APPROVED Li-S BASE-DESIGN ENGINEERING RECONCILIATION, item15, 2026-10-18. Wickerts corrected SI, DOI10.1021/acssuschemeng.4c01782.s001 Tables S19/S21: use baseline B recipe with the existing150 Wh/kg-cell and1500-cycle reference, rather than technical T ingredients associated with500 Wh/kg. Per cell: Li4g, separator6g, cathode8g, electrolyte29g, pouch.13g, negative tab.12g, positive tab.069g. Detailed retained masses sum47.319g, conflicting with source46g average. Adopt47.319g as the explicit engineering mass basis (not a measured corrected source cell); no arbitrary rescaling of individual ingredients. At150 Wh/kg this is7.09785 Wh/cell. Cathode B perkg: sulfur.28, CMK3.22, PVDF.13, acetonitrile.044, foil.38, organic waste-.054; inputs1.054kg=1kg product+.054kg waste. Preserve process-specific energy and transport. Source PVDF binder uses the existing polyvinylfluoride supply as an explicitly retained cross-version fluoropolymer proxy; exact binder chemistry remains a coverage/model gap, not a verified PVDF route. Per-cell assembly/formation/factory requirements retain their source cell amounts and are divided by47.319g. Module408cells=19.306152kg plus.275Al busbar+.593bimetal+.085Cu+2.75PP+2.5steel =25.509152kg. Cell share is0.7568323713779275. The mobile capacity market normalizes exactly to1 gross kWh at.150kWh/kg-cell, with.120-.180 endpoints and paired waste masses. Future density factors remain the existing relative learning assumption with fixed recipe; this does not validate a future physical cell design, cycle aging or calendar life. Controls/cooling are treated separately under item13. Source average-mass conflict and future recipe evolution remain explicit gaps. This supersedes older24.971kg-module/46g-cell and500Wh/kg-composition statements below.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+This dataset provides 1 kWh of battery gross capacity (NOT net), using a Li-ion Li-S battery. Specific energy density in 2020: 0.15 kWh/kg cell, 0.5 kWh/kg cell in the future. Battery management (BoP) mass share: 25%. Battery energy density in 2020: 0.11 kWh/kg battery. Battery mass per kWh: 8.9 kg. Cycle life: 800-1'500 or Lifetime: 225 kWh/kg. Source: Wickerts et al. (2023). Prospective Life Cycle Assessment of Lithium-Sulfur Batteries for Stationary Energy Storage. ACS Sustainable Chemistry &amp; Engineering. https://doi.org/10.1021/acssuschemeng.3c00141</t>
+        </is>
       </c>
     </row>
     <row r="122" spans="1:14" ns3:dyDescent="0.2">
@@ -2628,8 +2632,8 @@
         <v>48</v>
       </c>
       <c r="B126">
-        <f>1-0.25</f>
-        <v>0.75</v>
+        <f>0.7568323713779275</f>
+        <v>0.7568323713779275</v>
       </c>
     </row>
     <row r="127" spans="1:14" ht="16" ns3:dyDescent="0.2">
@@ -2700,8 +2704,8 @@
         <v>33</v>
       </c>
       <c r="B130" s="3">
-        <f>1/(0.15*75%)</f>
-        <v>8.8888888888888893</v>
+        <f>8.808643655832261</f>
+        <v>8.808643655832261</v>
       </c>
       <c r="C130" t="s">
         <v>7</v>
@@ -2719,16 +2723,16 @@
         <v>5</v>
       </c>
       <c r="H130" s="7">
-        <f>B130</f>
-        <v>8.8888888888888893</v>
+        <f>8.808643655832261</f>
+        <v>8.808643655832261</v>
       </c>
       <c r="I130" s="3">
-        <f>1/(0.18*75%)</f>
-        <v>7.4074074074074066</v>
+        <f>7.340536379860217</f>
+        <v>7.340536379860217</v>
       </c>
       <c r="J130" s="3">
-        <f>1/(0.12*75%)</f>
-        <v>11.111111111111111</v>
+        <f>11.010804569790327</f>
+        <v>11.010804569790327</v>
       </c>
     </row>
     <row r="131" spans="1:14" ns3:dyDescent="0.2">
@@ -2736,8 +2740,8 @@
         <v>53</v>
       </c>
       <c r="B131" s="3">
-        <f>-1*B130</f>
-        <v>-8.8888888888888893</v>
+        <f>-8.808643655832261</f>
+        <v>-8.808643655832261</v>
       </c>
       <c r="C131" t="s">
         <v>7</v>
@@ -2755,16 +2759,16 @@
         <v>5</v>
       </c>
       <c r="H131" s="7">
-        <f>B131</f>
-        <v>-8.8888888888888893</v>
+        <f>-8.808643655832261</f>
+        <v>-8.808643655832261</v>
       </c>
       <c r="I131" s="3">
-        <f>-1/(0.12*75%)</f>
-        <v>-11.111111111111111</v>
+        <f>-11.010804569790327</f>
+        <v>-11.010804569790327</v>
       </c>
       <c r="J131" s="3">
-        <f>-1/(0.18*75%)</f>
-        <v>-7.4074074074074066</v>
+        <f>-7.340536379860217</f>
+        <v>-7.340536379860217</v>
       </c>
       <c r="K131" t="b">
         <v>1</v>

--- a/premise/data/additional_inventories/lci-battery-capacity.xlsx
+++ b/premise/data/additional_inventories/lci-battery-capacity.xlsx
@@ -2588,7 +2588,9 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>APPROVED Li-S BASE-DESIGN ENGINEERING RECONCILIATION, item15, 2026-10-18. Wickerts corrected SI, DOI10.1021/acssuschemeng.4c01782.s001 Tables S19/S21: use baseline B recipe with the existing150 Wh/kg-cell and1500-cycle reference, rather than technical T ingredients associated with500 Wh/kg. Per cell: Li4g, separator6g, cathode8g, electrolyte29g, pouch.13g, negative tab.12g, positive tab.069g. Detailed retained masses sum47.319g, conflicting with source46g average. Adopt47.319g as the explicit engineering mass basis (not a measured corrected source cell); no arbitrary rescaling of individual ingredients. At150 Wh/kg this is7.09785 Wh/cell. Cathode B perkg: sulfur.28, CMK3.22, PVDF.13, acetonitrile.044, foil.38, organic waste-.054; inputs1.054kg=1kg product+.054kg waste. Preserve process-specific energy and transport. Source PVDF binder uses the existing polyvinylfluoride supply as an explicitly retained cross-version fluoropolymer proxy; exact binder chemistry remains a coverage/model gap, not a verified PVDF route. Per-cell assembly/formation/factory requirements retain their source cell amounts and are divided by47.319g. Module408cells=19.306152kg plus.275Al busbar+.593bimetal+.085Cu+2.75PP+2.5steel =25.509152kg. Cell share is0.7568323713779275. The mobile capacity market normalizes exactly to1 gross kWh at.150kWh/kg-cell, with.120-.180 endpoints and paired waste masses. Future density factors remain the existing relative learning assumption with fixed recipe; this does not validate a future physical cell design, cycle aging or calendar life. Controls/cooling are treated separately under item13. Source average-mass conflict and future recipe evolution remain explicit gaps. This supersedes older24.971kg-module/46g-cell and500Wh/kg-composition statements below.
+          <t>APPROVED ENGINEERING CONTROL/THERMAL COVERAGE, item13, 2026-10-18. Wickerts corrected SI DOI10.1021/acssuschemeng.4c01782.s001 S26/S27; original Ellingsen2014 SI S39/S40, DOI10.1111/jiec.12072. Separate module monitoring from central protection: per16-module reference,1.1kg populated PCB monitors, central0.49kg populated PCB+2.8kg HV system+1.2kg LV system+.028kg fasteners=4.518kg. Use existing HV/LV/fastener process providers and generic populated through-hole PCB perkg; this is an explicit board-technology/material proxy rather than the source-specific board fabrication model. No whole BMS is added on top. Adopt one nominal10kg liquid-cooling assembly per reference: Al9.08, steel.23, PVC/rubber pipe.0096, thermal pad.2 (silicon.06, glass.02, ABS.12), ethylene glycol.48kg; source-rounded sum9.9996kg. Metal working/injection services are included; 100percent retention of listed finished materials is assumed. No stationary rack housing/container, common vehicle body or roadway is added. Monitoring/protection/cooling are added once as a unit-valued capacity input; kg module and matching waste remain separate, so density learning does not shrink fixed controls. Central and cooling hardware are conservatively co-replaced with each delivered pack; longer independent hardware life is not established. End-of-life uses the existing generic used Li-ion route for15.6176kg of auxiliary hardware per reference, without recovery credits; this is a treatment proxy for controls/cooling, not proof of chemistry-specific recovery. Source thermal duty, pump/radiator performance, protection ratings, inverter/pack interface, full outer pack enclosure and vehicle-specific module topology remain coverage/design gaps. The SIB cell-mass-equivalent module retains its existing18.768kg cell+6.203kg module hardware reference; it is not a demonstrated integer21700-cell topology. LiS uses the corrected19.306152kg cell+6.203kg module hardware. These are engineering references, not fleet-validated designs; use0.5-2x auxiliary-size and independent-replacement-life sensitivities. Reference gross capacity is16*19.306152kg cell*0.15kWh/kg=46.3347648kWh; dose=0.0215820670357649unit/kWh. Existing cell density, kg-module recipe, energy/per-MJ coefficients and cycle assumptions are preserved.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+APPROVED Li-S BASE-DESIGN ENGINEERING RECONCILIATION, item15, 2026-10-18. Wickerts corrected SI, DOI10.1021/acssuschemeng.4c01782.s001 Tables S19/S21: use baseline B recipe with the existing150 Wh/kg-cell and1500-cycle reference, rather than technical T ingredients associated with500 Wh/kg. Per cell: Li4g, separator6g, cathode8g, electrolyte29g, pouch.13g, negative tab.12g, positive tab.069g. Detailed retained masses sum47.319g, conflicting with source46g average. Adopt47.319g as the explicit engineering mass basis (not a measured corrected source cell); no arbitrary rescaling of individual ingredients. At150 Wh/kg this is7.09785 Wh/cell. Cathode B perkg: sulfur.28, CMK3.22, PVDF.13, acetonitrile.044, foil.38, organic waste-.054; inputs1.054kg=1kg product+.054kg waste. Preserve process-specific energy and transport. Source PVDF binder uses the existing polyvinylfluoride supply as an explicitly retained cross-version fluoropolymer proxy; exact binder chemistry remains a coverage/model gap, not a verified PVDF route. Per-cell assembly/formation/factory requirements retain their source cell amounts and are divided by47.319g. Module408cells=19.306152kg plus.275Al busbar+.593bimetal+.085Cu+2.75PP+2.5steel =25.509152kg. Cell share is0.7568323713779275. The mobile capacity market normalizes exactly to1 gross kWh at.150kWh/kg-cell, with.120-.180 endpoints and paired waste masses. Future density factors remain the existing relative learning assumption with fixed recipe; this does not validate a future physical cell design, cycle aging or calendar life. Controls/cooling are treated separately under item13. Source average-mass conflict and future recipe evolution remain explicit gaps. This supersedes older24.971kg-module/46g-cell and500Wh/kg-composition statements below.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 This dataset provides 1 kWh of battery gross capacity (NOT net), using a Li-ion Li-S battery. Specific energy density in 2020: 0.15 kWh/kg cell, 0.5 kWh/kg cell in the future. Battery management (BoP) mass share: 25%. Battery energy density in 2020: 0.11 kWh/kg battery. Battery mass per kWh: 8.9 kg. Cycle life: 800-1'500 or Lifetime: 225 kWh/kg. Source: Wickerts et al. (2023). Prospective Life Cycle Assessment of Lithium-Sulfur Batteries for Stationary Energy Storage. ACS Sustainable Chemistry &amp; Engineering. https://doi.org/10.1021/acssuschemeng.3c00141</t>
         </is>
@@ -2775,6 +2777,41 @@
       </c>
       <c r="M131" s="3"/>
       <c r="N131" s="3"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>battery controls and cooling, 16-module engineering reference</t>
+        </is>
+      </c>
+      <c r="B132">
+        <v>0.0215820670357649</v>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>battery controls and cooling, 16-module engineering reference</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>Engineering auxiliary input; fixed unit reference, includes own separate15.6176kg waste.</t>
+        </is>
+      </c>
     </row>
     <row r="133" spans="1:14" ht="16" ns3:dyDescent="0.2">
       <c r="A133" s="2" t="s">
@@ -2997,7 +3034,9 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>APPROVED SODIUM-ION CAPACITY BASELINE NORMALIZATION, 2026-10-18. Zhang et al. (2024), Future climate impacts of sodium-ion batteries, Resources, Conservation and Recycling 202, 107362, DOI 10.1016/j.resconrec.2023.107362, Table 4, page 5: baseline NMMT/HC cell specific energy is 157 Wh/kg (0.157 kWh/kg), consistent with the existing source description and Premise density baseline. Primary paper: https://pub.epsilon.slu.se/32553/1/zhang-s-et-al-20240122.pdf . The linked existing SIB module recipe contains 0.7515918465419887 kg NMMT cell/kg module (lci-batteries-SIB.xlsx, sodium-ion batteries B493); its battery market purchases one kg of this module per kg delivered. Use this actual recipe coefficient, not a rounded 75 percent fraction, and 0.157 kWh/kg cell: 1/(0.157*0.7515918465419887) = 8.474582023338275 kg delivered module/kWh gross capacity. The previous 1/(0.16*0.75) = 8.333333333333334 kg represented 0.9833326658924353 kWh under those declared specifications. The module dose increases 1.6949842800592974 percent; this is not a percent change in overall transport or system metal demand. Set battery cell mass share to the linked recipe coefficient. Keep existing cell-specific density uncertainty endpoints 0.12 and 0.18 kWh/kg, translating them with the same module fraction; retain triangular type 5, equal negative waste mass and paired signed bounds/locations. Update formula caches consistently. The original rounded specific-energy/fraction/mass figures below are historical notes superseded by this paragraph. All supplier identities/geographies, the one-kWh output, cell/module manufacturing recipes, other chemistries, prospective density trajectory and lifetime/per-MJ allocations remain unchanged. This normalizes to declared cell energy and an existing module proxy; it does not validate measured pack performance, future electrochemical charge, cycle life or operating conditions. The Li-S-derived module architecture and missing BMS/cooling coverage remain unresolved. No electronics, racks, treatment route, recovery credit or primary/secondary share is added. Current full-system metal effects remain unquantified without a scenario rebuild.
+          <t>APPROVED ENGINEERING CONTROL/THERMAL COVERAGE, item13, 2026-10-18. Wickerts corrected SI DOI10.1021/acssuschemeng.4c01782.s001 S26/S27; original Ellingsen2014 SI S39/S40, DOI10.1111/jiec.12072. Separate module monitoring from central protection: per16-module reference,1.1kg populated PCB monitors, central0.49kg populated PCB+2.8kg HV system+1.2kg LV system+.028kg fasteners=4.518kg. Use existing HV/LV/fastener process providers and generic populated through-hole PCB perkg; this is an explicit board-technology/material proxy rather than the source-specific board fabrication model. No whole BMS is added on top. Adopt one nominal10kg liquid-cooling assembly per reference: Al9.08, steel.23, PVC/rubber pipe.0096, thermal pad.2 (silicon.06, glass.02, ABS.12), ethylene glycol.48kg; source-rounded sum9.9996kg. Metal working/injection services are included; 100percent retention of listed finished materials is assumed. No stationary rack housing/container, common vehicle body or roadway is added. Monitoring/protection/cooling are added once as a unit-valued capacity input; kg module and matching waste remain separate, so density learning does not shrink fixed controls. Central and cooling hardware are conservatively co-replaced with each delivered pack; longer independent hardware life is not established. End-of-life uses the existing generic used Li-ion route for15.6176kg of auxiliary hardware per reference, without recovery credits; this is a treatment proxy for controls/cooling, not proof of chemistry-specific recovery. Source thermal duty, pump/radiator performance, protection ratings, inverter/pack interface, full outer pack enclosure and vehicle-specific module topology remain coverage/design gaps. The SIB cell-mass-equivalent module retains its existing18.768kg cell+6.203kg module hardware reference; it is not a demonstrated integer21700-cell topology. LiS uses the corrected19.306152kg cell+6.203kg module hardware. These are engineering references, not fleet-validated designs; use0.5-2x auxiliary-size and independent-replacement-life sensitivities. Reference gross capacity is16*18.768kg cell*0.157kWh/kg=47.145216000000005kWh; dose=0.02121105988781555unit/kWh. Existing cell density, kg-module recipe, energy/per-MJ coefficients and cycle assumptions are preserved.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+APPROVED SODIUM-ION CAPACITY BASELINE NORMALIZATION, 2026-10-18. Zhang et al. (2024), Future climate impacts of sodium-ion batteries, Resources, Conservation and Recycling 202, 107362, DOI 10.1016/j.resconrec.2023.107362, Table 4, page 5: baseline NMMT/HC cell specific energy is 157 Wh/kg (0.157 kWh/kg), consistent with the existing source description and Premise density baseline. Primary paper: https://pub.epsilon.slu.se/32553/1/zhang-s-et-al-20240122.pdf . The linked existing SIB module recipe contains 0.7515918465419887 kg NMMT cell/kg module (lci-batteries-SIB.xlsx, sodium-ion batteries B493); its battery market purchases one kg of this module per kg delivered. Use this actual recipe coefficient, not a rounded 75 percent fraction, and 0.157 kWh/kg cell: 1/(0.157*0.7515918465419887) = 8.474582023338275 kg delivered module/kWh gross capacity. The previous 1/(0.16*0.75) = 8.333333333333334 kg represented 0.9833326658924353 kWh under those declared specifications. The module dose increases 1.6949842800592974 percent; this is not a percent change in overall transport or system metal demand. Set battery cell mass share to the linked recipe coefficient. Keep existing cell-specific density uncertainty endpoints 0.12 and 0.18 kWh/kg, translating them with the same module fraction; retain triangular type 5, equal negative waste mass and paired signed bounds/locations. Update formula caches consistently. The original rounded specific-energy/fraction/mass figures below are historical notes superseded by this paragraph. All supplier identities/geographies, the one-kWh output, cell/module manufacturing recipes, other chemistries, prospective density trajectory and lifetime/per-MJ allocations remain unchanged. This normalizes to declared cell energy and an existing module proxy; it does not validate measured pack performance, future electrochemical charge, cycle life or operating conditions. The Li-S-derived module architecture and missing BMS/cooling coverage remain unresolved. No electronics, racks, treatment route, recovery credit or primary/secondary share is added. Current full-system metal effects remain unquantified without a scenario rebuild.
 PREVIOUS SOURCE NOTES (ROUNDED VALUES SUPERSEDED ABOVE):
 This dataset provides 1 kWh of battery gross capacity (NOT net), using a Sodium-ion battery. Specific energy density in 2020: 0.157 kWh/kg cell. Battery management (BoP) mass share: 25%. Battery energy density in 2020: 0.12 kWh/kg battery. Battery mass per kWh: 8.5 kg. Lifetime: 628 kWh/kg cell (4000 cycles x 0.157 kWh) or 2'500-4'000 cycles. Source for parameters: Zhang, S., Steubing, B., Potter, H. K., Hansson, P. A., &amp; Nordberg, Å. (2024). Future climate impacts of sodium-ion batteries. Resources, Conservation and Recycling, 202, 107362. https://doi.org/10.1016/j.resconrec.2023.107362. Min and max values from: Hasselwander, S.; Meyer, M.; Österle, I. Techno-Economic Analysis of Different Battery Cell Chemistries for the Passenger Vehicle Market. Batteries 2023, 9, 379. https://doi.org/10.3390/batteries9070379.</t>
         </is>
@@ -3184,6 +3223,41 @@
       </c>
       <c r="M157" s="3"/>
       <c r="N157" s="3"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>battery controls and cooling, 16-module engineering reference</t>
+        </is>
+      </c>
+      <c r="B158">
+        <v>0.02121105988781555</v>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>battery controls and cooling, 16-module engineering reference</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>Engineering auxiliary input; fixed unit reference, includes own separate15.6176kg waste.</t>
+        </is>
+      </c>
     </row>
     <row r="159" spans="1:14" ht="16" ns3:dyDescent="0.2">
       <c r="A159" s="2" t="s">
@@ -6545,7 +6619,9 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>APPROVED STATIONARY SODIUM-ION CAPACITY BASELINE NORMALIZATION, 2026-10-18. Zhang et al. (2024), Future climate impacts of sodium-ion batteries, Resources, Conservation and Recycling 202, 107362, DOI 10.1016/j.resconrec.2023.107362, Table 4, page 5: baseline NMMT/HC cell specific energy is 157 Wh/kg (0.157 kWh/kg), consistent with the existing source description and Premise density baseline. Primary paper: https://pub.epsilon.slu.se/32553/1/zhang-s-et-al-20240122.pdf . The linked existing SIB module recipe contains 0.7515918465419887 kg NMMT cell/kg module (lci-batteries-SIB.xlsx, sodium-ion batteries B493); its battery market purchases one kg of this module per kg delivered. Use this actual recipe coefficient, not a rounded 75 percent fraction, and 0.157 kWh/kg cell: 1/(0.157*0.7515918465419887) = 8.474582023338275 kg delivered module/kWh gross capacity. The previous 1/(0.16*0.75) = 8.333333333333334 kg represented 0.9833326658924353 kWh under those declared specifications. The module dose increases 1.6949842800592974 percent; this is not a percent change in overall transport or system metal demand. Set battery cell mass share to the linked recipe coefficient. Keep existing cell-specific density uncertainty endpoints 0.12 and 0.18 kWh/kg, translating them with the same module fraction; retain triangular type 5, equal negative waste mass and paired signed bounds/locations. Update formula caches consistently. The original rounded specific-energy/fraction/mass figures below are historical notes superseded by this paragraph. All supplier identities/geographies, the one-kWh output, cell/module manufacturing recipes, other chemistries, prospective density trajectory and lifetime/per-MJ allocations remain unchanged. This normalizes to declared cell energy and an existing module proxy; it does not validate measured pack performance, future electrochemical charge, cycle life or operating conditions. The Li-S-derived module architecture and missing BMS/cooling coverage remain unresolved. No electronics, racks, treatment route, recovery credit or primary/secondary share is added. Current full-system metal effects remain unquantified without a scenario rebuild. STATIONARY MAPPING LIMITATION: This stationary capacity-market name is absent from the existing density aliases. The current unmodified updater therefore leaves its mass and uncertainty bounds fixed through 2050. This corrects the initial normalization only; it does not implement the mobile density trajectory or resolve that mapping gap. The stationary market was inactive in the last 28-case audit, so no current system-metal effect is inferred. The previous mobile correction is preserved.
+          <t>APPROVED ENGINEERING CONTROL/THERMAL COVERAGE, item13, 2026-10-18. Wickerts corrected SI DOI10.1021/acssuschemeng.4c01782.s001 S26/S27; original Ellingsen2014 SI S39/S40, DOI10.1111/jiec.12072. Separate module monitoring from central protection: per16-module reference,1.1kg populated PCB monitors, central0.49kg populated PCB+2.8kg HV system+1.2kg LV system+.028kg fasteners=4.518kg. Use existing HV/LV/fastener process providers and generic populated through-hole PCB perkg; this is an explicit board-technology/material proxy rather than the source-specific board fabrication model. No whole BMS is added on top. Adopt one nominal10kg liquid-cooling assembly per reference: Al9.08, steel.23, PVC/rubber pipe.0096, thermal pad.2 (silicon.06, glass.02, ABS.12), ethylene glycol.48kg; source-rounded sum9.9996kg. Metal working/injection services are included; 100percent retention of listed finished materials is assumed. No stationary rack housing/container, common vehicle body or roadway is added. Monitoring/protection/cooling are added once as a unit-valued capacity input; kg module and matching waste remain separate, so density learning does not shrink fixed controls. Central and cooling hardware are conservatively co-replaced with each delivered pack; longer independent hardware life is not established. End-of-life uses the existing generic used Li-ion route for15.6176kg of auxiliary hardware per reference, without recovery credits; this is a treatment proxy for controls/cooling, not proof of chemistry-specific recovery. Source thermal duty, pump/radiator performance, protection ratings, inverter/pack interface, full outer pack enclosure and vehicle-specific module topology remain coverage/design gaps. The SIB cell-mass-equivalent module retains its existing18.768kg cell+6.203kg module hardware reference; it is not a demonstrated integer21700-cell topology. LiS uses the corrected19.306152kg cell+6.203kg module hardware. These are engineering references, not fleet-validated designs; use0.5-2x auxiliary-size and independent-replacement-life sensitivities. Reference gross capacity is16*18.768kg cell*0.157kWh/kg=47.145216000000005kWh; dose=0.02121105988781555unit/kWh. Existing cell density, kg-module recipe, energy/per-MJ coefficients and cycle assumptions are preserved.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+APPROVED STATIONARY SODIUM-ION CAPACITY BASELINE NORMALIZATION, 2026-10-18. Zhang et al. (2024), Future climate impacts of sodium-ion batteries, Resources, Conservation and Recycling 202, 107362, DOI 10.1016/j.resconrec.2023.107362, Table 4, page 5: baseline NMMT/HC cell specific energy is 157 Wh/kg (0.157 kWh/kg), consistent with the existing source description and Premise density baseline. Primary paper: https://pub.epsilon.slu.se/32553/1/zhang-s-et-al-20240122.pdf . The linked existing SIB module recipe contains 0.7515918465419887 kg NMMT cell/kg module (lci-batteries-SIB.xlsx, sodium-ion batteries B493); its battery market purchases one kg of this module per kg delivered. Use this actual recipe coefficient, not a rounded 75 percent fraction, and 0.157 kWh/kg cell: 1/(0.157*0.7515918465419887) = 8.474582023338275 kg delivered module/kWh gross capacity. The previous 1/(0.16*0.75) = 8.333333333333334 kg represented 0.9833326658924353 kWh under those declared specifications. The module dose increases 1.6949842800592974 percent; this is not a percent change in overall transport or system metal demand. Set battery cell mass share to the linked recipe coefficient. Keep existing cell-specific density uncertainty endpoints 0.12 and 0.18 kWh/kg, translating them with the same module fraction; retain triangular type 5, equal negative waste mass and paired signed bounds/locations. Update formula caches consistently. The original rounded specific-energy/fraction/mass figures below are historical notes superseded by this paragraph. All supplier identities/geographies, the one-kWh output, cell/module manufacturing recipes, other chemistries, prospective density trajectory and lifetime/per-MJ allocations remain unchanged. This normalizes to declared cell energy and an existing module proxy; it does not validate measured pack performance, future electrochemical charge, cycle life or operating conditions. The Li-S-derived module architecture and missing BMS/cooling coverage remain unresolved. No electronics, racks, treatment route, recovery credit or primary/secondary share is added. Current full-system metal effects remain unquantified without a scenario rebuild. STATIONARY MAPPING LIMITATION: This stationary capacity-market name is absent from the existing density aliases. The current unmodified updater therefore leaves its mass and uncertainty bounds fixed through 2050. This corrects the initial normalization only; it does not implement the mobile density trajectory or resolve that mapping gap. The stationary market was inactive in the last 28-case audit, so no current system-metal effect is inferred. The previous mobile correction is preserved.
 PREVIOUS SOURCE NOTES (ROUNDED VALUES SUPERSEDED ABOVE):
 This dataset provides 1 kWh of battery gross capacity (NOT net), using a Sodium-ion battery. Specific energy density in 2020: 0.157 kWh/kg cell. Battery management (BoP) mass share: 25%. Battery energy density in 2020: 0.12 kWh/kg battery. Battery mass per kWh: 8.5 kg. Lifetime: 628 kWh/kg cell (4000 cycles x 0.157 kWh) or 2'500-4'000 cycles. Source for parameters: Zhang, S., Steubing, B., Potter, H. K., Hansson, P. A., &amp; Nordberg, Å. (2024). Future climate impacts of sodium-ion batteries. Resources, Conservation and Recycling, 202, 107362. https://doi.org/10.1016/j.resconrec.2023.107362. Min and max values from: Hasselwander, S.; Meyer, M.; Österle, I. Techno-Economic Analysis of Different Battery Cell Chemistries for the Passenger Vehicle Market. Batteries 2023, 9, 379. https://doi.org/10.3390/batteries9070379.</t>
         </is>
@@ -6732,6 +6808,41 @@
       </c>
       <c r="M119" s="3"/>
       <c r="N119" s="3"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>battery controls and cooling, 16-module engineering reference</t>
+        </is>
+      </c>
+      <c r="B120">
+        <v>0.02121105988781555</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>battery controls and cooling, 16-module engineering reference</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>Engineering auxiliary input; fixed unit reference, includes own separate15.6176kg waste.</t>
+        </is>
+      </c>
     </row>
     <row r="121" spans="1:14" ht="16" ns3:dyDescent="0.2">
       <c r="A121" s="2" t="s">

--- a/premise/data/additional_inventories/lci-battery-capacity.xlsx
+++ b/premise/data/additional_inventories/lci-battery-capacity.xlsx
@@ -799,8 +799,12 @@
       <c r="A4" t="s">
         <v>1</v>
       </c>
-      <c r="B4" t="s">
-        <v>65</v>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. Chemistry=LFP; geometry proxy=LFP; cellmass=147.58kg, scalablehardware=196.85000000000002kg, assumed cellbaseline=0.16kWh/kg, grossreference=23.612800000000004kWh, fixedcontrolmass=6.668kg. Retained listed hardware material coefficients sum1kg/kg; upstream cell/processing yields are not overwritten. Raw source rounding and cell-specific gaps remain in those providers. Cell-share metadata now refers only to scalable hardware; total installed pack also includes fixed unit-valued control hardware.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+This dataset provides 1 kWh of battery gross capacity (NOT net), using a Li-ion LFP battery. Specific energy density in 2020: (min, mean, max) 0.140, 0.160, 0.190 kWh/kg cell. Battery management (BoP) mass share: 27%. Battery energy density in 2020: 0.10 kWh/kg battery. Battery mass per kWh: 8.6 kg. Lifetime: 3'000-3'500 cycles. Source for parameters: Hasselwander, S.; Meyer, M.; Österle, I. Techno-Economic Analysis of Different Battery Cell Chemistries for the Passenger Vehicle Market. Batteries 2023, 9, 379. https://doi.org/10.3390/batteries9070379.</t>
+        </is>
       </c>
     </row>
     <row r="5" spans="1:14" ns3:dyDescent="0.2">
@@ -841,8 +845,8 @@
         <v>48</v>
       </c>
       <c r="B9">
-        <f>1-0.27</f>
-        <v>0.73</v>
+        <f>0.7497078994157989</f>
+        <v>0.7497078994157989</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="16" ns3:dyDescent="0.2">
@@ -910,12 +914,14 @@
       </c>
     </row>
     <row r="13" spans="1:14" ns3:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>17</v>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>market for battery hardware, Li-ion, LFP, engineering reference</t>
+        </is>
       </c>
       <c r="B13" s="7">
-        <f>1/(0.16*(1-27%))</f>
-        <v>8.5616438356164384</v>
+        <f>8.336580159913266</f>
+        <v>8.336580159913266</v>
       </c>
       <c r="C13" t="s">
         <v>7</v>
@@ -926,23 +932,25 @@
       <c r="E13" t="s">
         <v>14</v>
       </c>
-      <c r="F13" t="s">
-        <v>18</v>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>battery hardware, Li-ion, LFP, engineering reference</t>
+        </is>
       </c>
       <c r="G13">
         <v>5</v>
       </c>
       <c r="H13" s="7">
-        <f>B13</f>
-        <v>8.5616438356164384</v>
+        <f>8.336580159913266</f>
+        <v>8.336580159913266</v>
       </c>
       <c r="I13" s="7">
-        <f>1/(0.19*(1-27%))</f>
-        <v>7.2098053352559486</v>
+        <f>7.020278029400646</f>
+        <v>7.020278029400646</v>
       </c>
       <c r="J13" s="7">
-        <f>1/(0.14*(1-27%))</f>
-        <v>9.7847358121330714</v>
+        <f>9.527520182758018</f>
+        <v>9.527520182758018</v>
       </c>
     </row>
     <row r="14" spans="1:14" ns3:dyDescent="0.2">
@@ -950,8 +958,8 @@
         <v>53</v>
       </c>
       <c r="B14" s="7">
-        <f>-1*B13</f>
-        <v>-8.5616438356164384</v>
+        <f>-8.336580159913266</f>
+        <v>-8.336580159913266</v>
       </c>
       <c r="C14" t="s">
         <v>7</v>
@@ -969,22 +977,52 @@
         <v>5</v>
       </c>
       <c r="H14" s="7">
-        <f>B14</f>
-        <v>-8.5616438356164384</v>
+        <f>-8.336580159913266</f>
+        <v>-8.336580159913266</v>
       </c>
       <c r="I14" s="7">
-        <f>-1/(0.14*(1-27%))</f>
-        <v>-9.7847358121330714</v>
+        <f>-9.527520182758018</f>
+        <v>-9.527520182758018</v>
       </c>
       <c r="J14" s="7">
-        <f>-1/(0.19*(1-27%))</f>
-        <v>-7.2098053352559486</v>
+        <f>-7.020278029400646</f>
+        <v>-7.020278029400646</v>
       </c>
       <c r="K14" t="b">
         <v>1</v>
       </c>
       <c r="M14" s="7"/>
       <c r="N14" s="7"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>battery monitoring and central controls, LFP, engineering reference</t>
+        </is>
+      </c>
+      <c r="B15">
+        <v>0.042349911912183215</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>battery monitoring and central controls, LFP, engineering reference</t>
+        </is>
+      </c>
     </row>
     <row r="16" spans="1:14" ht="16" ns3:dyDescent="0.2">
       <c r="A16" s="2" t="s">
@@ -998,8 +1036,12 @@
       <c r="A17" t="s">
         <v>1</v>
       </c>
-      <c r="B17" t="s">
-        <v>66</v>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. Chemistry=NMC111; geometry proxy=NMC111; cellmass=119.77kg, scalablehardware=158.94000000000003kg, assumed cellbaseline=0.18kWh/kg, grossreference=21.5586kWh, fixedcontrolmass=6.548kg. Retained listed hardware material coefficients sum1kg/kg; upstream cell/processing yields are not overwritten. Raw source rounding and cell-specific gaps remain in those providers. Cell-share metadata now refers only to scalable hardware; total installed pack also includes fixed unit-valued control hardware.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+This dataset provides 1 kWh of battery gross capacity (NOT net), using a Li-ion NMC111 battery. Specific cell energy density in 2020: (min, mean, max) 0.150, 0.180, 0.190 kWh/kg cell. Battery management (BoP) mass share: 27%. Battery energy density in 2020: 0.13 kWh/kg battery. Battery mass per kWh: 7.6 kg. Lifetime: 1'000-1'800 cycles. Source for parameters: Hasselwander, S.; Meyer, M.; Österle, I. Techno-Economic Analysis of Different Battery Cell Chemistries for the Passenger Vehicle Market. Batteries 2023, 9, 379. https://doi.org/10.3390/batteries9070379.</t>
+        </is>
       </c>
     </row>
     <row r="18" spans="1:14" ns3:dyDescent="0.2">
@@ -1039,8 +1081,8 @@
         <v>48</v>
       </c>
       <c r="B22">
-        <f>1-0.27</f>
-        <v>0.73</v>
+        <f>0.753554800553668</f>
+        <v>0.753554800553668</v>
       </c>
     </row>
     <row r="23" spans="1:14" ht="16" ns3:dyDescent="0.2">
@@ -1108,12 +1150,14 @@
       </c>
     </row>
     <row r="26" spans="1:14" ns3:dyDescent="0.2">
-      <c r="A26" t="s">
-        <v>20</v>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>market for battery hardware, Li-ion, NMC111, engineering reference</t>
+        </is>
       </c>
       <c r="B26" s="3">
-        <f>1/(0.18*73%)</f>
-        <v>7.6103500761035017</v>
+        <f>7.372463889120817</f>
+        <v>7.372463889120817</v>
       </c>
       <c r="C26" t="s">
         <v>7</v>
@@ -1124,23 +1168,25 @@
       <c r="E26" t="s">
         <v>14</v>
       </c>
-      <c r="F26" t="s">
-        <v>21</v>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>battery hardware, Li-ion, NMC111, engineering reference</t>
+        </is>
       </c>
       <c r="G26">
         <v>5</v>
       </c>
       <c r="H26" s="7">
-        <f>B26</f>
-        <v>7.6103500761035017</v>
+        <f>7.372463889120817</f>
+        <v>7.372463889120817</v>
       </c>
       <c r="I26" s="7">
-        <f>1/(0.19*73%)</f>
-        <v>7.2098053352559486</v>
+        <f>6.984439473903931</f>
+        <v>6.984439473903931</v>
       </c>
       <c r="J26" s="7">
-        <f>1/(0.14*73%)</f>
-        <v>9.7847358121330714</v>
+        <f>9.478882143155333</f>
+        <v>9.478882143155333</v>
       </c>
     </row>
     <row r="27" spans="1:14" ns3:dyDescent="0.2">
@@ -1148,8 +1194,8 @@
         <v>53</v>
       </c>
       <c r="B27" s="3">
-        <f>-1*B26</f>
-        <v>-7.6103500761035017</v>
+        <f>-7.372463889120817</f>
+        <v>-7.372463889120817</v>
       </c>
       <c r="C27" t="s">
         <v>7</v>
@@ -1167,22 +1213,52 @@
         <v>5</v>
       </c>
       <c r="H27" s="7">
-        <f>B27</f>
-        <v>-7.6103500761035017</v>
+        <f>-7.372463889120817</f>
+        <v>-7.372463889120817</v>
       </c>
       <c r="I27" s="7">
-        <f>-1/(0.14*(1-27%))</f>
-        <v>-9.7847358121330714</v>
+        <f>-9.478882143155333</f>
+        <v>-9.478882143155333</v>
       </c>
       <c r="J27" s="7">
-        <f>-1/(0.19*73%)</f>
-        <v>-7.2098053352559486</v>
+        <f>-6.984439473903931</f>
+        <v>-6.984439473903931</v>
       </c>
       <c r="K27" t="b">
         <v>1</v>
       </c>
       <c r="M27" s="7"/>
       <c r="N27" s="7"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>battery monitoring and central controls, NMC111, engineering reference</t>
+        </is>
+      </c>
+      <c r="B28">
+        <v>0.046385201265388296</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>battery monitoring and central controls, NMC111, engineering reference</t>
+        </is>
+      </c>
     </row>
     <row r="29" spans="1:14" ht="16" ns3:dyDescent="0.2">
       <c r="A29" s="2" t="s">
@@ -1196,8 +1272,12 @@
       <c r="A30" t="s">
         <v>1</v>
       </c>
-      <c r="B30" t="s">
-        <v>111</v>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. Chemistry=NMC532; geometry proxy=NMC622; cellmass=108.03kg, scalablehardware=145.74kg, assumed cellbaseline=0.2kWh/kg, grossreference=21.606kWh, fixedcontrolmass=6.538kg. Retained listed hardware material coefficients sum1kg/kg; upstream cell/processing yields are not overwritten. Raw source rounding and cell-specific gaps remain in those providers. Cell-share metadata now refers only to scalable hardware; total installed pack also includes fixed unit-valued control hardware.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+This dataset provides 1 kWh of battery gross capacity (NOT net), using a Li-ion NMC532 battery. Specific energy density in 2020: (min, mean, max) 0.170, 0.200, 0.220 kWh/kg cell. Battery management (BoP) mass share: 27%. Battery energy density in 2020: 0.150 kWh/kg battery. Battery mass per kWh: 6.95 kg. Lifetime: 1'000-1'500 cycles. Source for parameters: Hasselwander, S.; Meyer, M.; Österle, I. Techno-Economic Analysis of Different Battery Cell Chemistries for the Passenger Vehicle Market. Batteries 2023, 9, 379. https://doi.org/10.3390/batteries9070379.</t>
+        </is>
       </c>
     </row>
     <row r="31" spans="1:14" ns3:dyDescent="0.2">
@@ -1237,8 +1317,8 @@
         <v>48</v>
       </c>
       <c r="B35">
-        <f>1-0.27</f>
-        <v>0.73</v>
+        <f>0.7412515438452038</f>
+        <v>0.7412515438452038</v>
       </c>
     </row>
     <row r="36" spans="1:14" ht="16" ns3:dyDescent="0.2">
@@ -1306,12 +1386,14 @@
       </c>
     </row>
     <row r="39" spans="1:14" ns3:dyDescent="0.2">
-      <c r="A39" t="s">
-        <v>112</v>
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>market for battery hardware, Li-ion, NMC532, engineering reference</t>
+        </is>
       </c>
       <c r="B39" s="3">
-        <f>1/(0.2*73%)</f>
-        <v>6.8493150684931514</v>
+        <f>6.7453485143015826</f>
+        <v>6.7453485143015826</v>
       </c>
       <c r="C39" t="s">
         <v>7</v>
@@ -1322,23 +1404,25 @@
       <c r="E39" t="s">
         <v>14</v>
       </c>
-      <c r="F39" t="s">
-        <v>113</v>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>battery hardware, Li-ion, NMC532, engineering reference</t>
+        </is>
       </c>
       <c r="G39">
         <v>5</v>
       </c>
       <c r="H39" s="7">
-        <f>B39</f>
-        <v>6.8493150684931514</v>
+        <f>6.7453485143015826</f>
+        <v>6.7453485143015826</v>
       </c>
       <c r="I39" s="3">
-        <f>1/(0.22*73%)</f>
-        <v>6.2266500622665006</v>
+        <f>6.132135013001438</f>
+        <v>6.132135013001438</v>
       </c>
       <c r="J39" s="3">
-        <f>1/(0.17*73%)</f>
-        <v>8.058017727639001</v>
+        <f>7.9357041344724495</f>
+        <v>7.9357041344724495</v>
       </c>
     </row>
     <row r="40" spans="1:14" ns3:dyDescent="0.2">
@@ -1346,8 +1430,8 @@
         <v>53</v>
       </c>
       <c r="B40" s="3">
-        <f>-1*B39</f>
-        <v>-6.8493150684931514</v>
+        <f>-6.7453485143015826</f>
+        <v>-6.7453485143015826</v>
       </c>
       <c r="C40" t="s">
         <v>7</v>
@@ -1365,22 +1449,52 @@
         <v>5</v>
       </c>
       <c r="H40" s="7">
-        <f>B40</f>
-        <v>-6.8493150684931514</v>
+        <f>-6.7453485143015826</f>
+        <v>-6.7453485143015826</v>
       </c>
       <c r="I40" s="3">
-        <f>-1/(0.17*73%)</f>
-        <v>-8.058017727639001</v>
+        <f>-7.9357041344724495</f>
+        <v>-7.9357041344724495</v>
       </c>
       <c r="J40" s="3">
-        <f>-1/(0.22*73%)</f>
-        <v>-6.2266500622665006</v>
+        <f>-6.132135013001438</f>
+        <v>-6.132135013001438</v>
       </c>
       <c r="K40" t="b">
         <v>1</v>
       </c>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>battery monitoring and central controls, NMC532, engineering reference</t>
+        </is>
+      </c>
+      <c r="B41">
+        <v>0.04628343978524484</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>battery monitoring and central controls, NMC532, engineering reference</t>
+        </is>
+      </c>
     </row>
     <row r="42" spans="1:14" ht="16" ns3:dyDescent="0.2">
       <c r="A42" s="2" t="s">
@@ -1394,8 +1508,12 @@
       <c r="A43" t="s">
         <v>1</v>
       </c>
-      <c r="B43" t="s">
-        <v>67</v>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. Chemistry=NMC622; geometry proxy=NMC622; cellmass=108.03kg, scalablehardware=145.74kg, assumed cellbaseline=0.24kWh/kg, grossreference=25.9272kWh, fixedcontrolmass=6.538kg. Retained listed hardware material coefficients sum1kg/kg; upstream cell/processing yields are not overwritten. Raw source rounding and cell-specific gaps remain in those providers. Cell-share metadata now refers only to scalable hardware; total installed pack also includes fixed unit-valued control hardware.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+This dataset provides 1 kWh of battery gross capacity (NOT net), using a Li-ion NMC622 battery. Specific energy density in 2020: (min, mean, max) 0.200, 0.240, 0.280 kWh/kg cell. Battery management (BoP) mass share: 27%. Battery energy density in 2020: 0.180 kWh/kg battery. Battery mass per kWh: 6.85 kg. Lifetime: 1'000-1'500 cycles. Source for parameters: Hasselwander, S.; Meyer, M.; Österle, I. Techno-Economic Analysis of Different Battery Cell Chemistries for the Passenger Vehicle Market. Batteries 2023, 9, 379. https://doi.org/10.3390/batteries9070379.</t>
+        </is>
       </c>
     </row>
     <row r="44" spans="1:14" ns3:dyDescent="0.2">
@@ -1437,8 +1555,8 @@
         <v>48</v>
       </c>
       <c r="B48">
-        <f>1-0.27</f>
-        <v>0.73</v>
+        <f>0.7412515438452038</f>
+        <v>0.7412515438452038</v>
       </c>
     </row>
     <row r="49" spans="1:14" ht="16" ns3:dyDescent="0.2">
@@ -1506,12 +1624,14 @@
       </c>
     </row>
     <row r="52" spans="1:14" ns3:dyDescent="0.2">
-      <c r="A52" t="s">
-        <v>25</v>
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>market for battery hardware, Li-ion, NMC622, engineering reference</t>
+        </is>
       </c>
       <c r="B52" s="3">
-        <f>1/(0.24*73%)</f>
-        <v>5.7077625570776256</v>
+        <f>5.621123761917986</f>
+        <v>5.621123761917986</v>
       </c>
       <c r="C52" t="s">
         <v>7</v>
@@ -1522,23 +1642,25 @@
       <c r="E52" t="s">
         <v>14</v>
       </c>
-      <c r="F52" t="s">
-        <v>26</v>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>battery hardware, Li-ion, NMC622, engineering reference</t>
+        </is>
       </c>
       <c r="G52">
         <v>5</v>
       </c>
       <c r="H52" s="7">
-        <f>B52</f>
-        <v>5.7077625570776256</v>
+        <f>5.621123761917986</f>
+        <v>5.621123761917986</v>
       </c>
       <c r="I52" s="3">
-        <f>1/(0.28*73%)</f>
-        <v>4.8923679060665357</v>
+        <f>4.818106081643988</f>
+        <v>4.818106081643988</v>
       </c>
       <c r="J52" s="3">
-        <f>1/(0.2*73%)</f>
-        <v>6.8493150684931514</v>
+        <f>6.745348514301584</f>
+        <v>6.745348514301584</v>
       </c>
     </row>
     <row r="53" spans="1:14" ns3:dyDescent="0.2">
@@ -1546,8 +1668,8 @@
         <v>53</v>
       </c>
       <c r="B53" s="3">
-        <f>-1*B52</f>
-        <v>-5.7077625570776256</v>
+        <f>-5.621123761917986</f>
+        <v>-5.621123761917986</v>
       </c>
       <c r="C53" t="s">
         <v>7</v>
@@ -1565,22 +1687,52 @@
         <v>5</v>
       </c>
       <c r="H53" s="7">
-        <f>B53</f>
-        <v>-5.7077625570776256</v>
+        <f>-5.621123761917986</f>
+        <v>-5.621123761917986</v>
       </c>
       <c r="I53" s="3">
-        <f>-1/(0.2*73%)</f>
-        <v>-6.8493150684931514</v>
+        <f>-6.745348514301584</f>
+        <v>-6.745348514301584</v>
       </c>
       <c r="J53" s="3">
-        <f>-1/(0.28*73%)</f>
-        <v>-4.8923679060665357</v>
+        <f>-4.818106081643988</f>
+        <v>-4.818106081643988</v>
       </c>
       <c r="K53" t="b">
         <v>1</v>
       </c>
       <c r="M53" s="3"/>
       <c r="N53" s="3"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>battery monitoring and central controls, NMC622, engineering reference</t>
+        </is>
+      </c>
+      <c r="B54">
+        <v>0.0385695331543707</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>battery monitoring and central controls, NMC622, engineering reference</t>
+        </is>
+      </c>
     </row>
     <row r="55" spans="1:14" ht="16" ns3:dyDescent="0.2">
       <c r="A55" s="2" t="s">
@@ -1594,8 +1746,12 @@
       <c r="A56" t="s">
         <v>1</v>
       </c>
-      <c r="B56" t="s">
-        <v>68</v>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. Chemistry=NMC811; geometry proxy=NMC811; cellmass=112.37kg, scalablehardware=151.63000000000002kg, assumed cellbaseline=0.28kWh/kg, grossreference=31.463600000000003kWh, fixedcontrolmass=6.568kg. Retained listed hardware material coefficients sum1kg/kg; upstream cell/processing yields are not overwritten. Raw source rounding and cell-specific gaps remain in those providers. Cell-share metadata now refers only to scalable hardware; total installed pack also includes fixed unit-valued control hardware.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+This dataset provides 1 kWh of battery gross capacity (not NET), using a Li-ion NMC811 battery. Specific energy density in 2020: (min, mean, max) 0.240, 0.280, 0.340 kWh/kg cell. Battery management (BoP) mass share: 29%. Battery energy density in 2020: 0.20 kWh/kg battery. Battery mass per kWh: 5.03 kg. Lifetime: 1'000-1'200 cycles. Source for parameters: Hasselwander, S.; Meyer, M.; Österle, I. Techno-Economic Analysis of Different Battery Cell Chemistries for the Passenger Vehicle Market. Batteries 2023, 9, 379. https://doi.org/10.3390/batteries9070379.</t>
+        </is>
       </c>
     </row>
     <row r="57" spans="1:14" ns3:dyDescent="0.2">
@@ -1634,6 +1790,9 @@
     <row r="61" spans="1:14" ns3:dyDescent="0.2">
       <c r="A61" t="s">
         <v>48</v>
+      </c>
+      <c r="B61">
+        <v>0.7410802611620391</v>
       </c>
     </row>
     <row r="62" spans="1:14" ht="16" ns3:dyDescent="0.2">
@@ -1704,12 +1863,14 @@
       </c>
     </row>
     <row r="65" spans="1:14" ns3:dyDescent="0.2">
-      <c r="A65" t="s">
-        <v>24</v>
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>market for battery hardware, Li-ion, NMC811, engineering reference</t>
+        </is>
       </c>
       <c r="B65" s="3">
-        <f>1/(0.28*71%)</f>
-        <v>5.0301810865191143</v>
+        <f>4.819219669713574</f>
+        <v>4.819219669713574</v>
       </c>
       <c r="C65" t="s">
         <v>7</v>
@@ -1720,23 +1881,25 @@
       <c r="E65" t="s">
         <v>14</v>
       </c>
-      <c r="F65" t="s">
-        <v>46</v>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>battery hardware, Li-ion, NMC811, engineering reference</t>
+        </is>
       </c>
       <c r="G65">
         <v>5</v>
       </c>
       <c r="H65" s="7">
-        <f>B65</f>
-        <v>5.0301810865191143</v>
+        <f>4.819219669713574</f>
+        <v>4.819219669713574</v>
       </c>
       <c r="I65" s="3">
-        <f>1/(0.34*71%)</f>
-        <v>4.1425020712510356</v>
+        <f>3.96876913976412</f>
+        <v>3.96876913976412</v>
       </c>
       <c r="J65" s="3">
-        <f>1/(0.24*71%)</f>
-        <v>5.868544600938967</v>
+        <f>5.622422947999169</f>
+        <v>5.622422947999169</v>
       </c>
     </row>
     <row r="66" spans="1:14" ns3:dyDescent="0.2">
@@ -1744,8 +1907,8 @@
         <v>53</v>
       </c>
       <c r="B66" s="3">
-        <f>-1*B65</f>
-        <v>-5.0301810865191143</v>
+        <f>-4.819219669713574</f>
+        <v>-4.819219669713574</v>
       </c>
       <c r="C66" t="s">
         <v>7</v>
@@ -1763,22 +1926,52 @@
         <v>5</v>
       </c>
       <c r="H66" s="7">
-        <f>B66</f>
-        <v>-5.0301810865191143</v>
+        <f>-4.819219669713574</f>
+        <v>-4.819219669713574</v>
       </c>
       <c r="I66" s="3">
-        <f>-1/(0.24*71%)</f>
-        <v>-5.868544600938967</v>
+        <f>-5.622422947999169</f>
+        <v>-5.622422947999169</v>
       </c>
       <c r="J66" s="3">
-        <f>-1/(0.34*71%)</f>
-        <v>-4.1425020712510356</v>
+        <f>-3.96876913976412</f>
+        <v>-3.96876913976412</v>
       </c>
       <c r="K66" t="b">
         <v>1</v>
       </c>
       <c r="M66" s="3"/>
       <c r="N66" s="3"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>battery monitoring and central controls, NMC811, engineering reference</t>
+        </is>
+      </c>
+      <c r="B67">
+        <v>0.03178275848917479</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>battery monitoring and central controls, NMC811, engineering reference</t>
+        </is>
+      </c>
     </row>
     <row r="68" spans="1:14" ht="16" ns3:dyDescent="0.2">
       <c r="A68" s="2" t="s">
@@ -1794,7 +1987,9 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Provides 1 kWh gross battery capacity using a Li-ion NMC955 pack. The complete-pack manufacturing recipe in lci-batteries-NMC955-LTO.xlsx contains 0.72591 kg cells per kg pack (72.591% cells, 27.409% other pack components). Use this manufactured cell fraction instead of the former generic 71% assumption. At the retained 2020 cell energy densities (minimum/mean/maximum) of 0.300/0.340/0.380 kWh per kg cell, pack mass is 1/(cell density * cell mass share): mean 4.051709537805285 kg/kWh, range 3.625213796983677 to 4.591937476179324 kg/kWh. Manufacturing and end of life use equal pack mass; signed disposal bounds mirror the manufacturing bounds. Source density/lifetime parameters: Hasselwander et al. (2023), https://doi.org/10.3390/batteries9070379. The source lifetime of 1000-1500 cycles and the existing future density trajectory remain modelling assumptions. Matching cell fraction is an allocation correction, not validation of practical cell performance. Rebuild scenario databases to apply.</t>
+          <t>APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. Chemistry=NMC955; geometry proxy=NMC622; cellmass=108.03kg, scalablehardware=145.74kg, assumed cellbaseline=0.34kWh/kg, grossreference=36.7302kWh, fixedcontrolmass=6.538kg. Retained listed hardware material coefficients sum1kg/kg; upstream cell/processing yields are not overwritten. Raw source rounding and cell-specific gaps remain in those providers. Cell-share metadata now refers only to scalable hardware; total installed pack also includes fixed unit-valued control hardware.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+Provides 1 kWh gross battery capacity using a Li-ion NMC955 pack. The complete-pack manufacturing recipe in lci-batteries-NMC955-LTO.xlsx contains 0.72591 kg cells per kg pack (72.591% cells, 27.409% other pack components). Use this manufactured cell fraction instead of the former generic 71% assumption. At the retained 2020 cell energy densities (minimum/mean/maximum) of 0.300/0.340/0.380 kWh per kg cell, pack mass is 1/(cell density * cell mass share): mean 4.051709537805285 kg/kWh, range 3.625213796983677 to 4.591937476179324 kg/kWh. Manufacturing and end of life use equal pack mass; signed disposal bounds mirror the manufacturing bounds. Source density/lifetime parameters: Hasselwander et al. (2023), https://doi.org/10.3390/batteries9070379. The source lifetime of 1000-1500 cycles and the existing future density trajectory remain modelling assumptions. Matching cell fraction is an allocation correction, not validation of practical cell performance. Rebuild scenario databases to apply.</t>
         </is>
       </c>
     </row>
@@ -1836,8 +2031,8 @@
         <v>48</v>
       </c>
       <c r="B74">
-        <f>0.72591</f>
-        <v>0.72591000000000006</v>
+        <f>0.7412515438452038</f>
+        <v>0.7412515438452038</v>
       </c>
     </row>
     <row r="75" spans="1:14" ht="16" ns3:dyDescent="0.2">
@@ -1904,12 +2099,14 @@
       </c>
     </row>
     <row r="78" spans="1:14" ns3:dyDescent="0.2">
-      <c r="A78" t="s">
-        <v>63</v>
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>market for battery hardware, Li-ion, NMC955, engineering reference</t>
+        </is>
       </c>
       <c r="B78" s="3">
-        <f>1/(0.34*$B$74)</f>
-        <v>4.0517095378052854</v>
+        <f>3.967852067236225</f>
+        <v>3.967852067236225</v>
       </c>
       <c r="C78" t="s">
         <v>7</v>
@@ -1920,23 +2117,25 @@
       <c r="E78" t="s">
         <v>14</v>
       </c>
-      <c r="F78" t="s">
-        <v>64</v>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>battery hardware, Li-ion, NMC955, engineering reference</t>
+        </is>
       </c>
       <c r="G78">
         <v>5</v>
       </c>
       <c r="H78" s="7">
-        <f>B78</f>
-        <v>4.0517095378052854</v>
+        <f>3.967852067236225</f>
+        <v>3.967852067236225</v>
       </c>
       <c r="I78" s="3">
-        <f>1/(0.38*$B$74)</f>
-        <v>3.6252137969836769</v>
+        <f>3.550183428579781</f>
+        <v>3.550183428579781</v>
       </c>
       <c r="J78" s="3">
-        <f>1/(0.3*$B$74)</f>
-        <v>4.5919374761793241</v>
+        <f>4.496899009534389</f>
+        <v>4.496899009534389</v>
       </c>
     </row>
     <row r="79" spans="1:14" ns3:dyDescent="0.2">
@@ -1944,8 +2143,8 @@
         <v>53</v>
       </c>
       <c r="B79" s="3">
-        <f>-1*B78</f>
-        <v>-4.0517095378052854</v>
+        <f>-3.967852067236225</f>
+        <v>-3.967852067236225</v>
       </c>
       <c r="C79" t="s">
         <v>7</v>
@@ -1963,22 +2162,52 @@
         <v>5</v>
       </c>
       <c r="H79" s="7">
-        <f>B79</f>
-        <v>-4.0517095378052854</v>
+        <f>-3.967852067236225</f>
+        <v>-3.967852067236225</v>
       </c>
       <c r="I79" s="3">
-        <f>-J78</f>
-        <v>-4.5919374761793241</v>
+        <f>-4.496899009534389</f>
+        <v>-4.496899009534389</v>
       </c>
       <c r="J79" s="3">
-        <f>-I78</f>
-        <v>-3.6252137969836769</v>
+        <f>-3.550183428579781</f>
+        <v>-3.550183428579781</v>
       </c>
       <c r="K79" t="b">
         <v>1</v>
       </c>
       <c r="M79" s="3"/>
       <c r="N79" s="3"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>battery monitoring and central controls, NMC955, engineering reference</t>
+        </is>
+      </c>
+      <c r="B80">
+        <v>0.027225552814849903</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>battery monitoring and central controls, NMC955, engineering reference</t>
+        </is>
+      </c>
     </row>
     <row r="81" spans="1:14" ht="16" ns3:dyDescent="0.2">
       <c r="A81" s="2" t="s">
@@ -1992,8 +2221,12 @@
       <c r="A82" t="s">
         <v>1</v>
       </c>
-      <c r="B82" t="s">
-        <v>69</v>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. Chemistry=NCA; geometry proxy=NCA; cellmass=104.96kg, scalablehardware=142.36999999999998kg, assumed cellbaseline=0.28kWh/kg, grossreference=29.3888kWh, fixedcontrolmass=6.548kg. Retained listed hardware material coefficients sum1kg/kg; upstream cell/processing yields are not overwritten. Raw source rounding and cell-specific gaps remain in those providers. Cell-share metadata now refers only to scalable hardware; total installed pack also includes fixed unit-valued control hardware.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+This dataset provides 1 kWh of battery gross capacity (not NET), using a Li-ion NCA battery. Specific energy density in 2020: (min, mean, max) 0.240, 0.280, 0.340 kWh/kg cell. Battery management (BoP) mass share: 29%. Battery energy density in 2020: 0.20 kWh/kg battery. Battery mass per kWh: 5.03 kg. Lifetime: 800-1'600 cycles. Source for parameters: Hasselwander, S.; Meyer, M.; Österle, I. Techno-Economic Analysis of Different Battery Cell Chemistries for the Passenger Vehicle Market. Batteries 2023, 9, 379. https://doi.org/10.3390/batteries9070379.</t>
+        </is>
       </c>
     </row>
     <row r="83" spans="1:14" ns3:dyDescent="0.2">
@@ -2034,8 +2267,8 @@
         <v>48</v>
       </c>
       <c r="B87">
-        <f>1-0.293</f>
-        <v>0.70700000000000007</v>
+        <f>0.7372339678303015</f>
+        <v>0.7372339678303015</v>
       </c>
     </row>
     <row r="88" spans="1:14" ht="16" ns3:dyDescent="0.2">
@@ -2102,12 +2335,14 @@
       </c>
     </row>
     <row r="91" spans="1:14" ns3:dyDescent="0.2">
-      <c r="A91" t="s">
-        <v>28</v>
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>market for battery hardware, Li-ion, NCA, engineering reference</t>
+        </is>
       </c>
       <c r="B91" s="3">
-        <f>1/(0.28*71%)</f>
-        <v>5.0301810865191143</v>
+        <f>4.844362478222996</f>
+        <v>4.844362478222996</v>
       </c>
       <c r="C91" t="s">
         <v>7</v>
@@ -2118,23 +2353,25 @@
       <c r="E91" t="s">
         <v>14</v>
       </c>
-      <c r="F91" t="s">
-        <v>29</v>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>battery hardware, Li-ion, NCA, engineering reference</t>
+        </is>
       </c>
       <c r="G91">
         <v>5</v>
       </c>
       <c r="H91" s="7">
-        <f>B91</f>
-        <v>5.0301810865191143</v>
+        <f>4.844362478222996</f>
+        <v>4.844362478222996</v>
       </c>
       <c r="I91" s="3">
-        <f>1/(0.34*71%)</f>
-        <v>4.1425020712510356</v>
+        <f>3.989474982065997</f>
+        <v>3.989474982065997</v>
       </c>
       <c r="J91" s="3">
-        <f>1/(0.24*71%)</f>
-        <v>5.868544600938967</v>
+        <f>5.651756224593496</f>
+        <v>5.651756224593496</v>
       </c>
     </row>
     <row r="92" spans="1:14" ns3:dyDescent="0.2">
@@ -2142,8 +2379,8 @@
         <v>53</v>
       </c>
       <c r="B92" s="3">
-        <f>-1*B91</f>
-        <v>-5.0301810865191143</v>
+        <f>-4.844362478222996</f>
+        <v>-4.844362478222996</v>
       </c>
       <c r="C92" t="s">
         <v>7</v>
@@ -2161,22 +2398,52 @@
         <v>5</v>
       </c>
       <c r="H92" s="7">
-        <f>B92</f>
-        <v>-5.0301810865191143</v>
+        <f>-4.844362478222996</f>
+        <v>-4.844362478222996</v>
       </c>
       <c r="I92" s="3">
-        <f>-1/(0.24*71%)</f>
-        <v>-5.868544600938967</v>
+        <f>-5.651756224593496</f>
+        <v>-5.651756224593496</v>
       </c>
       <c r="J92" s="3">
-        <f>-1/(0.34*71%)</f>
-        <v>-4.1425020712510356</v>
+        <f>-3.989474982065997</f>
+        <v>-3.989474982065997</v>
       </c>
       <c r="K92" t="b">
         <v>1</v>
       </c>
       <c r="M92" s="3"/>
       <c r="N92" s="3"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>battery monitoring and central controls, NCA, engineering reference</t>
+        </is>
+      </c>
+      <c r="B93">
+        <v>0.03402656794425087</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>battery monitoring and central controls, NCA, engineering reference</t>
+        </is>
+      </c>
     </row>
     <row r="94" spans="1:14" ht="16" ns3:dyDescent="0.2">
       <c r="A94" s="2" t="s">
@@ -2190,8 +2457,12 @@
       <c r="A95" t="s">
         <v>1</v>
       </c>
-      <c r="B95" t="s">
-        <v>43</v>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. Chemistry=LTO; geometry proxy=NMC622; cellmass=108.03kg, scalablehardware=145.74kg, assumed cellbaseline=0.085kWh/kg, grossreference=9.18255kWh, fixedcontrolmass=6.538kg. Retained listed hardware material coefficients sum1kg/kg; upstream cell/processing yields are not overwritten. Raw source rounding and cell-specific gaps remain in those providers. Cell-share metadata now refers only to scalable hardware; total installed pack also includes fixed unit-valued control hardware.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+This dataset provides 1 kWh of battery gross capacity (NOT net), using a Li-ion LTO battery. Specific energy density in 2020: 0.085 kWh/kg cell. Battery management (BoP) mass share: 36%. Battery energy density in 2020: 0.053 kWh/kg battery. Battery mass per kWh: 18.4 kg. Lifetime: 10'000 cycles. Source for parameters: Life cycle assessment of battery electric buses. Transportation Research Part D: Transport and Environment. Linda Ager-Wick Ellingsen, Rebecca Jayne Thorne, Julia Wind, Erik Figenbaum, Mia Romare and Anders Nordelöf.</t>
+        </is>
       </c>
     </row>
     <row r="96" spans="1:14" ns3:dyDescent="0.2">
@@ -2232,8 +2503,8 @@
         <v>48</v>
       </c>
       <c r="B100">
-        <f>1-0.36</f>
-        <v>0.64</v>
+        <f>0.7412515438452038</f>
+        <v>0.7412515438452038</v>
       </c>
     </row>
     <row r="101" spans="1:14" ht="16" ns3:dyDescent="0.2">
@@ -2300,12 +2571,14 @@
       </c>
     </row>
     <row r="104" spans="1:14" ns3:dyDescent="0.2">
-      <c r="A104" t="s">
-        <v>31</v>
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>market for battery hardware, Li-ion, LTO, engineering reference</t>
+        </is>
       </c>
       <c r="B104" s="3">
-        <f>1/(0.085*64%)</f>
-        <v>18.382352941176471</v>
+        <f>15.871408268944903</f>
+        <v>15.871408268944903</v>
       </c>
       <c r="C104" t="s">
         <v>7</v>
@@ -2316,23 +2589,25 @@
       <c r="E104" t="s">
         <v>14</v>
       </c>
-      <c r="F104" t="s">
-        <v>32</v>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>battery hardware, Li-ion, LTO, engineering reference</t>
+        </is>
       </c>
       <c r="G104">
         <v>5</v>
       </c>
       <c r="H104" s="7">
-        <f>B104</f>
-        <v>18.382352941176471</v>
+        <f>15.871408268944903</f>
+        <v>15.871408268944903</v>
       </c>
       <c r="I104" s="7">
-        <f>B104*0.75</f>
-        <v>13.786764705882353</v>
+        <f>11.903556201708676</f>
+        <v>11.903556201708676</v>
       </c>
       <c r="J104" s="7">
-        <f>B104*1.25</f>
-        <v>22.977941176470587</v>
+        <f>19.839260336181127</f>
+        <v>19.839260336181127</v>
       </c>
     </row>
     <row r="105" spans="1:14" ns3:dyDescent="0.2">
@@ -2340,8 +2615,8 @@
         <v>53</v>
       </c>
       <c r="B105" s="3">
-        <f>-1*B104</f>
-        <v>-18.382352941176471</v>
+        <f>-15.871408268944903</f>
+        <v>-15.871408268944903</v>
       </c>
       <c r="C105" t="s">
         <v>7</v>
@@ -2359,22 +2634,52 @@
         <v>5</v>
       </c>
       <c r="H105" s="7">
-        <f>B105</f>
-        <v>-18.382352941176471</v>
+        <f>-15.871408268944903</f>
+        <v>-15.871408268944903</v>
       </c>
       <c r="I105" s="7">
-        <f>B105*1.25</f>
-        <v>-22.977941176470587</v>
+        <f>-19.839260336181127</f>
+        <v>-19.839260336181127</v>
       </c>
       <c r="J105" s="7">
-        <f>B105*0.75</f>
-        <v>-13.786764705882353</v>
+        <f>-11.903556201708676</f>
+        <v>-11.903556201708676</v>
       </c>
       <c r="K105" t="b">
         <v>1</v>
       </c>
       <c r="M105" s="7"/>
       <c r="N105" s="7"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>battery monitoring and central controls, LTO, engineering reference</t>
+        </is>
+      </c>
+      <c r="B106">
+        <v>0.10890221125939961</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>battery monitoring and central controls, LTO, engineering reference</t>
+        </is>
+      </c>
     </row>
     <row r="107" spans="1:14" ht="16" ns3:dyDescent="0.2">
       <c r="A107" s="2" t="s">
@@ -2388,8 +2693,12 @@
       <c r="A108" t="s">
         <v>1</v>
       </c>
-      <c r="B108" t="s">
-        <v>52</v>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. Chemistry=LiMn2O4; geometry proxy=LiMn2O4; cellmass=146.26999999999998kg, scalablehardware=188.1kg, assumed cellbaseline=0.13kWh/kg, grossreference=19.015099999999997kWh, fixedcontrolmass=6.478kg. Retained listed hardware material coefficients sum1kg/kg; upstream cell/processing yields are not overwritten. Raw source rounding and cell-specific gaps remain in those providers. Cell-share metadata now refers only to scalable hardware; total installed pack also includes fixed unit-valued control hardware.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+This dataset provides 1 kWh of battery gross capacity (NOT net), using a Li-ion LMO battery. Specific energy density in 2020: 0.13 kWh/kg cell. Battery management (BoP) mass share: 13%. Battery energy density in 2020: 0.114 kWh/kg battery. Battery mass per kWh: 18.4 kg. Lifetime: 10'000 cycles. Source for parameters: Life cycle assessment of battery electric buses. Transportation Research Part D: Transport and Environment. Linda Ager-Wick Ellingsen, Rebecca Jayne Thorne, Julia Wind, Erik Figenbaum, Mia Romare and Anders Nordelöf.</t>
+        </is>
       </c>
     </row>
     <row r="109" spans="1:14" ns3:dyDescent="0.2">
@@ -2430,8 +2739,8 @@
         <v>48</v>
       </c>
       <c r="B113">
-        <f>1-0.13</f>
-        <v>0.87</v>
+        <f>0.7776182881446039</f>
+        <v>0.7776182881446039</v>
       </c>
     </row>
     <row r="114" spans="1:14" ht="16" ns3:dyDescent="0.2">
@@ -2498,12 +2807,14 @@
       </c>
     </row>
     <row r="117" spans="1:14" ns3:dyDescent="0.2">
-      <c r="A117" t="s">
-        <v>50</v>
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>market for battery hardware, Li-ion, LiMn2O4, engineering reference</t>
+        </is>
       </c>
       <c r="B117" s="3">
-        <f>1/(32/280)</f>
-        <v>8.75</v>
+        <f>9.89213835320351</f>
+        <v>9.89213835320351</v>
       </c>
       <c r="C117" t="s">
         <v>7</v>
@@ -2514,23 +2825,25 @@
       <c r="E117" t="s">
         <v>14</v>
       </c>
-      <c r="F117" t="s">
-        <v>51</v>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>battery hardware, Li-ion, LiMn2O4, engineering reference</t>
+        </is>
       </c>
       <c r="G117">
         <v>5</v>
       </c>
       <c r="H117" s="7">
-        <f>B117</f>
-        <v>8.75</v>
+        <f>9.89213835320351</f>
+        <v>9.89213835320351</v>
       </c>
       <c r="I117" s="7">
-        <f>B117*0.75</f>
-        <v>6.5625</v>
+        <f>7.419103764902632</f>
+        <v>7.419103764902632</v>
       </c>
       <c r="J117" s="7">
-        <f>B117*1.25</f>
-        <v>10.9375</v>
+        <f>12.365172941504387</f>
+        <v>12.365172941504387</v>
       </c>
     </row>
     <row r="118" spans="1:14" ns3:dyDescent="0.2">
@@ -2538,8 +2851,8 @@
         <v>53</v>
       </c>
       <c r="B118" s="3">
-        <f>-1*B117</f>
-        <v>-8.75</v>
+        <f>-9.89213835320351</f>
+        <v>-9.89213835320351</v>
       </c>
       <c r="C118" t="s">
         <v>7</v>
@@ -2557,22 +2870,52 @@
         <v>5</v>
       </c>
       <c r="H118" s="7">
-        <f>B118</f>
-        <v>-8.75</v>
+        <f>-9.89213835320351</f>
+        <v>-9.89213835320351</v>
       </c>
       <c r="I118" s="7">
-        <f>B118*1.25</f>
-        <v>-10.9375</v>
+        <f>-12.365172941504387</f>
+        <v>-12.365172941504387</v>
       </c>
       <c r="J118" s="7">
-        <f>B118*0.75</f>
-        <v>-6.5625</v>
+        <f>-7.419103764902632</f>
+        <v>-7.419103764902632</v>
       </c>
       <c r="K118" t="b">
         <v>1</v>
       </c>
       <c r="M118" s="7"/>
       <c r="N118" s="7"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>battery monitoring and central controls, LiMn2O4, engineering reference</t>
+        </is>
+      </c>
+      <c r="B119">
+        <v>0.05258978390857793</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>battery monitoring and central controls, LiMn2O4, engineering reference</t>
+        </is>
+      </c>
     </row>
     <row r="120" spans="1:14" ht="16" ns3:dyDescent="0.2">
       <c r="A120" s="2" t="s">
@@ -5026,8 +5369,12 @@
       <c r="A2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
-        <v>65</v>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. Chemistry=LFP; geometry proxy=LFP; cellmass=147.58kg, scalablehardware=196.85000000000002kg, assumed cellbaseline=0.16kWh/kg, grossreference=23.612800000000004kWh, fixedcontrolmass=6.668kg. Retained listed hardware material coefficients sum1kg/kg; upstream cell/processing yields are not overwritten. Raw source rounding and cell-specific gaps remain in those providers. Cell-share metadata now refers only to scalable hardware; total installed pack also includes fixed unit-valued control hardware.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+This dataset provides 1 kWh of battery gross capacity (NOT net), using a Li-ion LFP battery. Specific energy density in 2020: (min, mean, max) 0.140, 0.160, 0.190 kWh/kg cell. Battery management (BoP) mass share: 27%. Battery energy density in 2020: 0.10 kWh/kg battery. Battery mass per kWh: 8.6 kg. Lifetime: 3'000-3'500 cycles. Source for parameters: Hasselwander, S.; Meyer, M.; Österle, I. Techno-Economic Analysis of Different Battery Cell Chemistries for the Passenger Vehicle Market. Batteries 2023, 9, 379. https://doi.org/10.3390/batteries9070379.</t>
+        </is>
       </c>
     </row>
     <row r="3" spans="1:14" ns3:dyDescent="0.2">
@@ -5068,8 +5415,8 @@
         <v>48</v>
       </c>
       <c r="B7">
-        <f>1-0.27</f>
-        <v>0.73</v>
+        <f>0.7497078994157989</f>
+        <v>0.7497078994157989</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="16" ns3:dyDescent="0.2">
@@ -5137,12 +5484,14 @@
       </c>
     </row>
     <row r="11" spans="1:14" ns3:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>17</v>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>market for battery hardware, Li-ion, LFP, engineering reference</t>
+        </is>
       </c>
       <c r="B11" s="7">
-        <f>1/(0.16*(1-27%))</f>
-        <v>8.5616438356164384</v>
+        <f>8.336580159913266</f>
+        <v>8.336580159913266</v>
       </c>
       <c r="C11" t="s">
         <v>7</v>
@@ -5153,23 +5502,25 @@
       <c r="E11" t="s">
         <v>14</v>
       </c>
-      <c r="F11" t="s">
-        <v>18</v>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>battery hardware, Li-ion, LFP, engineering reference</t>
+        </is>
       </c>
       <c r="G11">
         <v>5</v>
       </c>
       <c r="H11" s="7">
-        <f>B11</f>
-        <v>8.5616438356164384</v>
+        <f>8.336580159913266</f>
+        <v>8.336580159913266</v>
       </c>
       <c r="I11" s="7">
-        <f>1/(0.19*(1-27%))</f>
-        <v>7.2098053352559486</v>
+        <f>7.020278029400646</f>
+        <v>7.020278029400646</v>
       </c>
       <c r="J11" s="7">
-        <f>1/(0.14*(1-27%))</f>
-        <v>9.7847358121330714</v>
+        <f>9.527520182758018</f>
+        <v>9.527520182758018</v>
       </c>
     </row>
     <row r="12" spans="1:14" ns3:dyDescent="0.2">
@@ -5177,8 +5528,8 @@
         <v>53</v>
       </c>
       <c r="B12" s="7">
-        <f>-1*B11</f>
-        <v>-8.5616438356164384</v>
+        <f>-8.336580159913266</f>
+        <v>-8.336580159913266</v>
       </c>
       <c r="C12" t="s">
         <v>7</v>
@@ -5196,22 +5547,52 @@
         <v>5</v>
       </c>
       <c r="H12" s="7">
-        <f>B12</f>
-        <v>-8.5616438356164384</v>
+        <f>-8.336580159913266</f>
+        <v>-8.336580159913266</v>
       </c>
       <c r="I12" s="7">
-        <f>-1/(0.14*(1-27%))</f>
-        <v>-9.7847358121330714</v>
+        <f>-9.527520182758018</f>
+        <v>-9.527520182758018</v>
       </c>
       <c r="J12" s="7">
-        <f>-1/(0.19*(1-27%))</f>
-        <v>-7.2098053352559486</v>
+        <f>-7.020278029400646</f>
+        <v>-7.020278029400646</v>
       </c>
       <c r="K12" t="b">
         <v>1</v>
       </c>
       <c r="M12" s="7"/>
       <c r="N12" s="7"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>battery monitoring and central controls, LFP, engineering reference</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>0.042349911912183215</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>battery monitoring and central controls, LFP, engineering reference</t>
+        </is>
+      </c>
     </row>
     <row r="14" spans="1:14" ht="16" ns3:dyDescent="0.2">
       <c r="A14" s="2" t="s">
@@ -5225,8 +5606,12 @@
       <c r="A15" t="s">
         <v>1</v>
       </c>
-      <c r="B15" t="s">
-        <v>66</v>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. Chemistry=NMC111; geometry proxy=NMC111; cellmass=119.77kg, scalablehardware=158.94000000000003kg, assumed cellbaseline=0.18kWh/kg, grossreference=21.5586kWh, fixedcontrolmass=6.548kg. Retained listed hardware material coefficients sum1kg/kg; upstream cell/processing yields are not overwritten. Raw source rounding and cell-specific gaps remain in those providers. Cell-share metadata now refers only to scalable hardware; total installed pack also includes fixed unit-valued control hardware.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+This dataset provides 1 kWh of battery gross capacity (NOT net), using a Li-ion NMC111 battery. Specific cell energy density in 2020: (min, mean, max) 0.150, 0.180, 0.190 kWh/kg cell. Battery management (BoP) mass share: 27%. Battery energy density in 2020: 0.13 kWh/kg battery. Battery mass per kWh: 7.6 kg. Lifetime: 1'000-1'800 cycles. Source for parameters: Hasselwander, S.; Meyer, M.; Österle, I. Techno-Economic Analysis of Different Battery Cell Chemistries for the Passenger Vehicle Market. Batteries 2023, 9, 379. https://doi.org/10.3390/batteries9070379.</t>
+        </is>
       </c>
     </row>
     <row r="16" spans="1:14" ns3:dyDescent="0.2">
@@ -5266,8 +5651,8 @@
         <v>48</v>
       </c>
       <c r="B20">
-        <f>1-0.27</f>
-        <v>0.73</v>
+        <f>0.753554800553668</f>
+        <v>0.753554800553668</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="16" ns3:dyDescent="0.2">
@@ -5335,12 +5720,14 @@
       </c>
     </row>
     <row r="24" spans="1:14" ns3:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>20</v>
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>market for battery hardware, Li-ion, NMC111, engineering reference</t>
+        </is>
       </c>
       <c r="B24" s="3">
-        <f>1/(0.18*73%)</f>
-        <v>7.6103500761035017</v>
+        <f>7.372463889120817</f>
+        <v>7.372463889120817</v>
       </c>
       <c r="C24" t="s">
         <v>7</v>
@@ -5351,23 +5738,25 @@
       <c r="E24" t="s">
         <v>14</v>
       </c>
-      <c r="F24" t="s">
-        <v>21</v>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>battery hardware, Li-ion, NMC111, engineering reference</t>
+        </is>
       </c>
       <c r="G24">
         <v>5</v>
       </c>
       <c r="H24" s="7">
-        <f>B24</f>
-        <v>7.6103500761035017</v>
+        <f>7.372463889120817</f>
+        <v>7.372463889120817</v>
       </c>
       <c r="I24" s="7">
-        <f>1/(0.19*73%)</f>
-        <v>7.2098053352559486</v>
+        <f>6.984439473903931</f>
+        <v>6.984439473903931</v>
       </c>
       <c r="J24" s="7">
-        <f>1/(0.14*73%)</f>
-        <v>9.7847358121330714</v>
+        <f>9.478882143155333</f>
+        <v>9.478882143155333</v>
       </c>
     </row>
     <row r="25" spans="1:14" ns3:dyDescent="0.2">
@@ -5375,8 +5764,8 @@
         <v>53</v>
       </c>
       <c r="B25" s="3">
-        <f>-1*B24</f>
-        <v>-7.6103500761035017</v>
+        <f>-7.372463889120817</f>
+        <v>-7.372463889120817</v>
       </c>
       <c r="C25" t="s">
         <v>7</v>
@@ -5394,22 +5783,52 @@
         <v>5</v>
       </c>
       <c r="H25" s="7">
-        <f>B25</f>
-        <v>-7.6103500761035017</v>
+        <f>-7.372463889120817</f>
+        <v>-7.372463889120817</v>
       </c>
       <c r="I25" s="7">
-        <f>-1/(0.14*(1-27%))</f>
-        <v>-9.7847358121330714</v>
+        <f>-9.478882143155333</f>
+        <v>-9.478882143155333</v>
       </c>
       <c r="J25" s="7">
-        <f>-1/(0.19*73%)</f>
-        <v>-7.2098053352559486</v>
+        <f>-6.984439473903931</f>
+        <v>-6.984439473903931</v>
       </c>
       <c r="K25" t="b">
         <v>1</v>
       </c>
       <c r="M25" s="7"/>
       <c r="N25" s="7"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>battery monitoring and central controls, NMC111, engineering reference</t>
+        </is>
+      </c>
+      <c r="B26">
+        <v>0.046385201265388296</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>battery monitoring and central controls, NMC111, engineering reference</t>
+        </is>
+      </c>
     </row>
     <row r="27" spans="1:14" ht="16" ns3:dyDescent="0.2">
       <c r="A27" s="2" t="s">
@@ -5423,8 +5842,12 @@
       <c r="A28" t="s">
         <v>1</v>
       </c>
-      <c r="B28" t="s">
-        <v>111</v>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. Chemistry=NMC532; geometry proxy=NMC622; cellmass=108.03kg, scalablehardware=145.74kg, assumed cellbaseline=0.2kWh/kg, grossreference=21.606kWh, fixedcontrolmass=6.538kg. Retained listed hardware material coefficients sum1kg/kg; upstream cell/processing yields are not overwritten. Raw source rounding and cell-specific gaps remain in those providers. Cell-share metadata now refers only to scalable hardware; total installed pack also includes fixed unit-valued control hardware.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+This dataset provides 1 kWh of battery gross capacity (NOT net), using a Li-ion NMC532 battery. Specific energy density in 2020: (min, mean, max) 0.170, 0.200, 0.220 kWh/kg cell. Battery management (BoP) mass share: 27%. Battery energy density in 2020: 0.150 kWh/kg battery. Battery mass per kWh: 6.95 kg. Lifetime: 1'000-1'500 cycles. Source for parameters: Hasselwander, S.; Meyer, M.; Österle, I. Techno-Economic Analysis of Different Battery Cell Chemistries for the Passenger Vehicle Market. Batteries 2023, 9, 379. https://doi.org/10.3390/batteries9070379.</t>
+        </is>
       </c>
     </row>
     <row r="29" spans="1:14" ns3:dyDescent="0.2">
@@ -5464,8 +5887,8 @@
         <v>48</v>
       </c>
       <c r="B33">
-        <f>1-0.27</f>
-        <v>0.73</v>
+        <f>0.7412515438452038</f>
+        <v>0.7412515438452038</v>
       </c>
     </row>
     <row r="34" spans="1:14" ht="16" ns3:dyDescent="0.2">
@@ -5533,12 +5956,14 @@
       </c>
     </row>
     <row r="37" spans="1:14" ns3:dyDescent="0.2">
-      <c r="A37" t="s">
-        <v>112</v>
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>market for battery hardware, Li-ion, NMC532, engineering reference</t>
+        </is>
       </c>
       <c r="B37" s="3">
-        <f>1/(0.2*73%)</f>
-        <v>6.8493150684931514</v>
+        <f>6.7453485143015826</f>
+        <v>6.7453485143015826</v>
       </c>
       <c r="C37" t="s">
         <v>7</v>
@@ -5549,23 +5974,25 @@
       <c r="E37" t="s">
         <v>14</v>
       </c>
-      <c r="F37" t="s">
-        <v>113</v>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>battery hardware, Li-ion, NMC532, engineering reference</t>
+        </is>
       </c>
       <c r="G37">
         <v>5</v>
       </c>
       <c r="H37" s="7">
-        <f>B37</f>
-        <v>6.8493150684931514</v>
+        <f>6.7453485143015826</f>
+        <v>6.7453485143015826</v>
       </c>
       <c r="I37" s="3">
-        <f>1/(0.22*73%)</f>
-        <v>6.2266500622665006</v>
+        <f>6.132135013001438</f>
+        <v>6.132135013001438</v>
       </c>
       <c r="J37" s="3">
-        <f>1/(0.17*73%)</f>
-        <v>8.058017727639001</v>
+        <f>7.9357041344724495</f>
+        <v>7.9357041344724495</v>
       </c>
     </row>
     <row r="38" spans="1:14" ns3:dyDescent="0.2">
@@ -5573,8 +6000,8 @@
         <v>53</v>
       </c>
       <c r="B38" s="3">
-        <f>-1*B37</f>
-        <v>-6.8493150684931514</v>
+        <f>-6.7453485143015826</f>
+        <v>-6.7453485143015826</v>
       </c>
       <c r="C38" t="s">
         <v>7</v>
@@ -5592,22 +6019,52 @@
         <v>5</v>
       </c>
       <c r="H38" s="7">
-        <f>B38</f>
-        <v>-6.8493150684931514</v>
+        <f>-6.7453485143015826</f>
+        <v>-6.7453485143015826</v>
       </c>
       <c r="I38" s="3">
-        <f>-1/(0.17*73%)</f>
-        <v>-8.058017727639001</v>
+        <f>-7.9357041344724495</f>
+        <v>-7.9357041344724495</v>
       </c>
       <c r="J38" s="3">
-        <f>-1/(0.22*73%)</f>
-        <v>-6.2266500622665006</v>
+        <f>-6.132135013001438</f>
+        <v>-6.132135013001438</v>
       </c>
       <c r="K38" t="b">
         <v>1</v>
       </c>
       <c r="M38" s="3"/>
       <c r="N38" s="3"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>battery monitoring and central controls, NMC532, engineering reference</t>
+        </is>
+      </c>
+      <c r="B39">
+        <v>0.04628343978524484</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>battery monitoring and central controls, NMC532, engineering reference</t>
+        </is>
+      </c>
     </row>
     <row r="40" spans="1:14" ht="16" ns3:dyDescent="0.2">
       <c r="A40" s="2" t="s">
@@ -5621,8 +6078,12 @@
       <c r="A41" t="s">
         <v>1</v>
       </c>
-      <c r="B41" t="s">
-        <v>67</v>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. Chemistry=NMC622; geometry proxy=NMC622; cellmass=108.03kg, scalablehardware=145.74kg, assumed cellbaseline=0.24kWh/kg, grossreference=25.9272kWh, fixedcontrolmass=6.538kg. Retained listed hardware material coefficients sum1kg/kg; upstream cell/processing yields are not overwritten. Raw source rounding and cell-specific gaps remain in those providers. Cell-share metadata now refers only to scalable hardware; total installed pack also includes fixed unit-valued control hardware.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+This dataset provides 1 kWh of battery gross capacity (NOT net), using a Li-ion NMC622 battery. Specific energy density in 2020: (min, mean, max) 0.200, 0.240, 0.280 kWh/kg cell. Battery management (BoP) mass share: 27%. Battery energy density in 2020: 0.180 kWh/kg battery. Battery mass per kWh: 6.85 kg. Lifetime: 1'000-1'500 cycles. Source for parameters: Hasselwander, S.; Meyer, M.; Österle, I. Techno-Economic Analysis of Different Battery Cell Chemistries for the Passenger Vehicle Market. Batteries 2023, 9, 379. https://doi.org/10.3390/batteries9070379.</t>
+        </is>
       </c>
     </row>
     <row r="42" spans="1:14" ns3:dyDescent="0.2">
@@ -5664,8 +6125,8 @@
         <v>48</v>
       </c>
       <c r="B46">
-        <f>1-0.27</f>
-        <v>0.73</v>
+        <f>0.7412515438452038</f>
+        <v>0.7412515438452038</v>
       </c>
     </row>
     <row r="47" spans="1:14" ht="16" ns3:dyDescent="0.2">
@@ -5733,12 +6194,14 @@
       </c>
     </row>
     <row r="50" spans="1:14" ns3:dyDescent="0.2">
-      <c r="A50" t="s">
-        <v>25</v>
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>market for battery hardware, Li-ion, NMC622, engineering reference</t>
+        </is>
       </c>
       <c r="B50" s="3">
-        <f>1/(0.24*73%)</f>
-        <v>5.7077625570776256</v>
+        <f>5.621123761917986</f>
+        <v>5.621123761917986</v>
       </c>
       <c r="C50" t="s">
         <v>7</v>
@@ -5749,23 +6212,25 @@
       <c r="E50" t="s">
         <v>14</v>
       </c>
-      <c r="F50" t="s">
-        <v>26</v>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>battery hardware, Li-ion, NMC622, engineering reference</t>
+        </is>
       </c>
       <c r="G50">
         <v>5</v>
       </c>
       <c r="H50" s="7">
-        <f>B50</f>
-        <v>5.7077625570776256</v>
+        <f>5.621123761917986</f>
+        <v>5.621123761917986</v>
       </c>
       <c r="I50" s="3">
-        <f>1/(0.28*73%)</f>
-        <v>4.8923679060665357</v>
+        <f>4.818106081643988</f>
+        <v>4.818106081643988</v>
       </c>
       <c r="J50" s="3">
-        <f>1/(0.2*73%)</f>
-        <v>6.8493150684931514</v>
+        <f>6.745348514301584</f>
+        <v>6.745348514301584</v>
       </c>
     </row>
     <row r="51" spans="1:14" ns3:dyDescent="0.2">
@@ -5773,8 +6238,8 @@
         <v>53</v>
       </c>
       <c r="B51" s="3">
-        <f>-1*B50</f>
-        <v>-5.7077625570776256</v>
+        <f>-5.621123761917986</f>
+        <v>-5.621123761917986</v>
       </c>
       <c r="C51" t="s">
         <v>7</v>
@@ -5792,22 +6257,52 @@
         <v>5</v>
       </c>
       <c r="H51" s="7">
-        <f>B51</f>
-        <v>-5.7077625570776256</v>
+        <f>-5.621123761917986</f>
+        <v>-5.621123761917986</v>
       </c>
       <c r="I51" s="3">
-        <f>-1/(0.2*73%)</f>
-        <v>-6.8493150684931514</v>
+        <f>-6.745348514301584</f>
+        <v>-6.745348514301584</v>
       </c>
       <c r="J51" s="3">
-        <f>-1/(0.28*73%)</f>
-        <v>-4.8923679060665357</v>
+        <f>-4.818106081643988</f>
+        <v>-4.818106081643988</v>
       </c>
       <c r="K51" t="b">
         <v>1</v>
       </c>
       <c r="M51" s="3"/>
       <c r="N51" s="3"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>battery monitoring and central controls, NMC622, engineering reference</t>
+        </is>
+      </c>
+      <c r="B52">
+        <v>0.0385695331543707</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>battery monitoring and central controls, NMC622, engineering reference</t>
+        </is>
+      </c>
     </row>
     <row r="53" spans="1:14" ht="16" ns3:dyDescent="0.2">
       <c r="A53" s="2" t="s">
@@ -5821,8 +6316,12 @@
       <c r="A54" t="s">
         <v>1</v>
       </c>
-      <c r="B54" t="s">
-        <v>68</v>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. Chemistry=NMC811; geometry proxy=NMC811; cellmass=112.37kg, scalablehardware=151.63000000000002kg, assumed cellbaseline=0.28kWh/kg, grossreference=31.463600000000003kWh, fixedcontrolmass=6.568kg. Retained listed hardware material coefficients sum1kg/kg; upstream cell/processing yields are not overwritten. Raw source rounding and cell-specific gaps remain in those providers. Cell-share metadata now refers only to scalable hardware; total installed pack also includes fixed unit-valued control hardware.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+This dataset provides 1 kWh of battery gross capacity (not NET), using a Li-ion NMC811 battery. Specific energy density in 2020: (min, mean, max) 0.240, 0.280, 0.340 kWh/kg cell. Battery management (BoP) mass share: 29%. Battery energy density in 2020: 0.20 kWh/kg battery. Battery mass per kWh: 5.03 kg. Lifetime: 1'000-1'200 cycles. Source for parameters: Hasselwander, S.; Meyer, M.; Österle, I. Techno-Economic Analysis of Different Battery Cell Chemistries for the Passenger Vehicle Market. Batteries 2023, 9, 379. https://doi.org/10.3390/batteries9070379.</t>
+        </is>
       </c>
     </row>
     <row r="55" spans="1:14" ns3:dyDescent="0.2">
@@ -5861,6 +6360,9 @@
     <row r="59" spans="1:14" ns3:dyDescent="0.2">
       <c r="A59" t="s">
         <v>48</v>
+      </c>
+      <c r="B59">
+        <v>0.7410802611620391</v>
       </c>
     </row>
     <row r="60" spans="1:14" ht="16" ns3:dyDescent="0.2">
@@ -5931,12 +6433,14 @@
       </c>
     </row>
     <row r="63" spans="1:14" ns3:dyDescent="0.2">
-      <c r="A63" t="s">
-        <v>24</v>
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>market for battery hardware, Li-ion, NMC811, engineering reference</t>
+        </is>
       </c>
       <c r="B63" s="3">
-        <f>1/(0.28*71%)</f>
-        <v>5.0301810865191143</v>
+        <f>4.819219669713574</f>
+        <v>4.819219669713574</v>
       </c>
       <c r="C63" t="s">
         <v>7</v>
@@ -5947,23 +6451,25 @@
       <c r="E63" t="s">
         <v>14</v>
       </c>
-      <c r="F63" t="s">
-        <v>46</v>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>battery hardware, Li-ion, NMC811, engineering reference</t>
+        </is>
       </c>
       <c r="G63">
         <v>5</v>
       </c>
       <c r="H63" s="7">
-        <f>B63</f>
-        <v>5.0301810865191143</v>
+        <f>4.819219669713574</f>
+        <v>4.819219669713574</v>
       </c>
       <c r="I63" s="3">
-        <f>1/(0.34*71%)</f>
-        <v>4.1425020712510356</v>
+        <f>3.96876913976412</f>
+        <v>3.96876913976412</v>
       </c>
       <c r="J63" s="3">
-        <f>1/(0.24*71%)</f>
-        <v>5.868544600938967</v>
+        <f>5.622422947999169</f>
+        <v>5.622422947999169</v>
       </c>
     </row>
     <row r="64" spans="1:14" ns3:dyDescent="0.2">
@@ -5971,8 +6477,8 @@
         <v>53</v>
       </c>
       <c r="B64" s="3">
-        <f>-1*B63</f>
-        <v>-5.0301810865191143</v>
+        <f>-4.819219669713574</f>
+        <v>-4.819219669713574</v>
       </c>
       <c r="C64" t="s">
         <v>7</v>
@@ -5990,22 +6496,52 @@
         <v>5</v>
       </c>
       <c r="H64" s="7">
-        <f>B64</f>
-        <v>-5.0301810865191143</v>
+        <f>-4.819219669713574</f>
+        <v>-4.819219669713574</v>
       </c>
       <c r="I64" s="3">
-        <f>-1/(0.24*71%)</f>
-        <v>-5.868544600938967</v>
+        <f>-5.622422947999169</f>
+        <v>-5.622422947999169</v>
       </c>
       <c r="J64" s="3">
-        <f>-1/(0.34*71%)</f>
-        <v>-4.1425020712510356</v>
+        <f>-3.96876913976412</f>
+        <v>-3.96876913976412</v>
       </c>
       <c r="K64" t="b">
         <v>1</v>
       </c>
       <c r="M64" s="3"/>
       <c r="N64" s="3"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>battery monitoring and central controls, NMC811, engineering reference</t>
+        </is>
+      </c>
+      <c r="B65">
+        <v>0.03178275848917479</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>battery monitoring and central controls, NMC811, engineering reference</t>
+        </is>
+      </c>
     </row>
     <row r="66" spans="1:14" ht="16" ns3:dyDescent="0.2">
       <c r="A66" s="2" t="s">
@@ -6021,7 +6557,9 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Provides 1 kWh gross battery capacity using a Li-ion NMC955 pack. The complete-pack manufacturing recipe in lci-batteries-NMC955-LTO.xlsx contains 0.72591 kg cells per kg pack (72.591% cells, 27.409% other pack components). Use this manufactured cell fraction instead of the former generic 71% assumption. At the retained 2020 cell energy densities (minimum/mean/maximum) of 0.300/0.340/0.380 kWh per kg cell, pack mass is 1/(cell density * cell mass share): mean 4.051709537805285 kg/kWh, range 3.625213796983677 to 4.591937476179324 kg/kWh. Manufacturing and end of life use equal pack mass; signed disposal bounds mirror the manufacturing bounds. Source density/lifetime parameters: Hasselwander et al. (2023), https://doi.org/10.3390/batteries9070379. The source lifetime of 1000-1500 cycles and the existing future density trajectory remain modelling assumptions. Matching cell fraction is an allocation correction, not validation of practical cell performance. Rebuild scenario databases to apply.</t>
+          <t>APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. Chemistry=NMC955; geometry proxy=NMC622; cellmass=108.03kg, scalablehardware=145.74kg, assumed cellbaseline=0.34kWh/kg, grossreference=36.7302kWh, fixedcontrolmass=6.538kg. Retained listed hardware material coefficients sum1kg/kg; upstream cell/processing yields are not overwritten. Raw source rounding and cell-specific gaps remain in those providers. Cell-share metadata now refers only to scalable hardware; total installed pack also includes fixed unit-valued control hardware.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+Provides 1 kWh gross battery capacity using a Li-ion NMC955 pack. The complete-pack manufacturing recipe in lci-batteries-NMC955-LTO.xlsx contains 0.72591 kg cells per kg pack (72.591% cells, 27.409% other pack components). Use this manufactured cell fraction instead of the former generic 71% assumption. At the retained 2020 cell energy densities (minimum/mean/maximum) of 0.300/0.340/0.380 kWh per kg cell, pack mass is 1/(cell density * cell mass share): mean 4.051709537805285 kg/kWh, range 3.625213796983677 to 4.591937476179324 kg/kWh. Manufacturing and end of life use equal pack mass; signed disposal bounds mirror the manufacturing bounds. Source density/lifetime parameters: Hasselwander et al. (2023), https://doi.org/10.3390/batteries9070379. The source lifetime of 1000-1500 cycles and the existing future density trajectory remain modelling assumptions. Matching cell fraction is an allocation correction, not validation of practical cell performance. Rebuild scenario databases to apply.</t>
         </is>
       </c>
     </row>
@@ -6063,8 +6601,8 @@
         <v>48</v>
       </c>
       <c r="B72">
-        <f>0.72591</f>
-        <v>0.72591000000000006</v>
+        <f>0.7412515438452038</f>
+        <v>0.7412515438452038</v>
       </c>
     </row>
     <row r="73" spans="1:14" ht="16" ns3:dyDescent="0.2">
@@ -6131,12 +6669,14 @@
       </c>
     </row>
     <row r="76" spans="1:14" ns3:dyDescent="0.2">
-      <c r="A76" t="s">
-        <v>63</v>
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>market for battery hardware, Li-ion, NMC955, engineering reference</t>
+        </is>
       </c>
       <c r="B76" s="3">
-        <f>1/(0.34*$B$72)</f>
-        <v>4.0517095378052854</v>
+        <f>3.967852067236225</f>
+        <v>3.967852067236225</v>
       </c>
       <c r="C76" t="s">
         <v>7</v>
@@ -6147,23 +6687,25 @@
       <c r="E76" t="s">
         <v>14</v>
       </c>
-      <c r="F76" t="s">
-        <v>64</v>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>battery hardware, Li-ion, NMC955, engineering reference</t>
+        </is>
       </c>
       <c r="G76">
         <v>5</v>
       </c>
       <c r="H76" s="7">
-        <f>B76</f>
-        <v>4.0517095378052854</v>
+        <f>3.967852067236225</f>
+        <v>3.967852067236225</v>
       </c>
       <c r="I76" s="3">
-        <f>1/(0.38*$B$72)</f>
-        <v>3.6252137969836769</v>
+        <f>3.550183428579781</f>
+        <v>3.550183428579781</v>
       </c>
       <c r="J76" s="3">
-        <f>1/(0.3*$B$72)</f>
-        <v>4.5919374761793241</v>
+        <f>4.496899009534389</f>
+        <v>4.496899009534389</v>
       </c>
     </row>
     <row r="77" spans="1:14" ns3:dyDescent="0.2">
@@ -6171,8 +6713,8 @@
         <v>53</v>
       </c>
       <c r="B77" s="3">
-        <f>-1*B76</f>
-        <v>-4.0517095378052854</v>
+        <f>-3.967852067236225</f>
+        <v>-3.967852067236225</v>
       </c>
       <c r="C77" t="s">
         <v>7</v>
@@ -6190,22 +6732,52 @@
         <v>5</v>
       </c>
       <c r="H77" s="7">
-        <f>B77</f>
-        <v>-4.0517095378052854</v>
+        <f>-3.967852067236225</f>
+        <v>-3.967852067236225</v>
       </c>
       <c r="I77" s="3">
-        <f>-J76</f>
-        <v>-4.5919374761793241</v>
+        <f>-4.496899009534389</f>
+        <v>-4.496899009534389</v>
       </c>
       <c r="J77" s="3">
-        <f>-I76</f>
-        <v>-3.6252137969836769</v>
+        <f>-3.550183428579781</f>
+        <v>-3.550183428579781</v>
       </c>
       <c r="K77" t="b">
         <v>1</v>
       </c>
       <c r="M77" s="3"/>
       <c r="N77" s="3"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>battery monitoring and central controls, NMC955, engineering reference</t>
+        </is>
+      </c>
+      <c r="B79">
+        <v>0.027225552814849903</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>battery monitoring and central controls, NMC955, engineering reference</t>
+        </is>
+      </c>
     </row>
     <row r="80" spans="1:14" ht="16" ns3:dyDescent="0.2">
       <c r="A80" s="2" t="s">

--- a/premise/data/additional_inventories/lci-battery-capacity.xlsx
+++ b/premise/data/additional_inventories/lci-battery-capacity.xlsx
@@ -3170,7 +3170,9 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>APPROVED Li-O2 SINGLE RECYCLING BOUNDARY, 2026-10-18. Wang, Deng and Yuan (2020), DOI 10.1016/j.jclepro.2020.121339, supporting information Table S16, explicitly describes recycling per 1 kg Li-O2 battery system. Its six treatment coefficients are retained. Set the former -1/321 kg/kg internal treatment fragment to a deterministic zero and apply end of life only at market for battery capacity, Li-ion, Li-O2: the full purchased battery mass is sent to treatment of LiO2 battery, for recycling (RER; waste LiO2 battery). Standalone manufacture is manufacturing-only. DefaultInventory may retain the zero exchange; it contributes no treatment flow. Do not add a second generic Li-ion route. This restores a single historical source-specific accounting route; treatment yields, whole-system mass normalization, modern recovery and primary/secondary shares remain unvalidated. No new recovery credit or change to manufacturing recipes, density or lifetime. The capacity-level treatment amount, sign, triangular bounds and all manufacturing mass formulas/caches are unchanged; purchased and treated mass remain paired as battery density changes.
+          <t>APPROVED Li-O2 HIERARCHICAL ENGINEERING RECONCILIATION, item18, 2026-10-18. Wang,Deng,Yuan2020 DOI10.1016/j.jclepro.2020.121339, SI TablesS3/S4/S5/S16; Kanthal resistance-wire datasheet https://www.kanthal.com/products/datasheets/material-datasheets/wire/resistance-heating-wire-and-resistance-wire/nikrothal-80/. Adopt TableS3 detailed retained geometry: cell182.6kg, module hardware19.51, pack hardware43.67, oxygen tank55, BMS4,cooling29.07 =&gt;333.85kg at63.5grosskWh. This conflicts with source headline321kg/267kg pack and with TableS5 gross material figures; do not mix those bases. Scalable cell/module/pack hardware=245.78kg; fixed-per-reference auxiliary hardware=88.07kg. Listed component masses, not proportional normalization of contradictory gross LCI tables, define this engineering reference. Known cell ingredients total182.59kg;0.01kg unspecified cathode catalyst remains a documented composition gap, not zero-metal proof. The sourceS4 fluoropolymer binder is not substituted for the unidentified S3 catalyst; binder quantity/fate is also unresolved, and that old process input is disabled in this reference. Electrolyte total59.11kg is split by inheritedS4 salt:solvent ratio.016:.308; LiClO4 process is the inherited salt provider, and ethylene-glycol dimethyl ether remains an explicitly imperfect TEGDME solvent proxy. Lithium protective film/pouch/separator process recipes remain inherited and unvalidated. Collector feed is1kg metal/kg foil at100percent reference retention; matching rolling and restored facility proxy are preserved. Terminal metal fractions are2.44kgAl/10.5kg and8.06kgCu/10.5kg, with matching working services; old overlapping gross feed and implied manufacturing scrap are disabled under the explicit100percent retention reference. Module and pack known material inputs followS3, with no new gross-yield claim. Module monitor.67kg is counted once; BMS4kg is assigned to central protection only using4/4.518 of the separate engineering central-control package. This functional repartition is an assumption, not a source breakdown. Cooling uses7kg Al plus22.07kg pureEG reference (alternative50/50 coolant is a sensitivity); thermal duty, pump/hoses remain gaps. Heater.2kg uses an idealized binary80Ni/20Cr resistance-alloy reference, consistent with a NiCr class but not a complete measured battery heater/Nikrothal composition; electronic/heater construction is unresolved. Preserve historical source-specific S16 recycling coefficients without new recovery credits. Capacity purchases245.78/63.5kg scalable hardware plus one auxiliary lifecycle unit per63.5kWh. Its negative waste equals scalable mass; auxiliary unit carries its own88.07kg waste. Future density factors scale hardware and its waste together; fixed auxiliary manufacture/treatment stay paired. Existing relative density learning is retained as an engineering ratio; absolute cell energy63.5/182.6=.347754655kWh/kg and fixed recipe are not a validated future design. Original full-battery market remains manufacturing-only at333.85kg component-sum basis; capacity uses the separately named hardware market. Vehicle energy/lifetime allocation is unchanged. Source contradictions, catalyst, solvent, future structure and recovery performance remain explicit gaps.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+APPROVED Li-O2 SINGLE RECYCLING BOUNDARY, 2026-10-18. Wang, Deng and Yuan (2020), DOI 10.1016/j.jclepro.2020.121339, supporting information Table S16, explicitly describes recycling per 1 kg Li-O2 battery system. Its six treatment coefficients are retained. Set the former -1/321 kg/kg internal treatment fragment to a deterministic zero and apply end of life only at market for battery capacity, Li-ion, Li-O2: the full purchased battery mass is sent to treatment of LiO2 battery, for recycling (RER; waste LiO2 battery). Standalone manufacture is manufacturing-only. DefaultInventory may retain the zero exchange; it contributes no treatment flow. Do not add a second generic Li-ion route. This restores a single historical source-specific accounting route; treatment yields, whole-system mass normalization, modern recovery and primary/secondary shares remain unvalidated. No new recovery credit or change to manufacturing recipes, density or lifetime. The capacity-level treatment amount, sign, triangular bounds and all manufacturing mass formulas/caches are unchanged; purchased and treated mass remain paired as battery density changes.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 This dataset provides 1 kWh of battery gross capacity (NOT net), using a Lithium-oxygen Li-O2 battery. Specific energy density in 2020: 0.360 kWh/kg cell. Battery management (BoP) mass share: 45%. Battery energy density in 2020: 0.238 kWh/kg battery (excl. O2 tanks). System energy density in 2020: 0.198 kWh/kg battery (incl. O2 tanks). Battery mass per kWh: 5.05 kg. Battery lifetime: 305 kWh/kg (1.76 MJ/km x 2e5 km / 321 kg). Source for parameters: Originally from Wang, F., Deng, Y., &amp; Yuan, C. (2020). Life cycle assessment of lithium oxygen battery for electric vehicles. Journal of Cleaner Production, 264, 121339. https://doi.org/10.1016/j.jclepro.2020.121339</t>
         </is>
@@ -3213,8 +3215,8 @@
         <v>48</v>
       </c>
       <c r="B139">
-        <f>1-0.45</f>
-        <v>0.55000000000000004</v>
+        <f>0.7429408414028806</f>
+        <v>0.7429408414028806</v>
       </c>
     </row>
     <row r="140" spans="1:14" ht="16" ns3:dyDescent="0.2">
@@ -3281,12 +3283,14 @@
       </c>
     </row>
     <row r="143" spans="1:14" ns3:dyDescent="0.2">
-      <c r="A143" t="s">
-        <v>36</v>
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>market for battery hardware, Li-oxygen, engineering reference</t>
+        </is>
       </c>
       <c r="B143" s="3">
-        <f>1/0.198</f>
-        <v>5.0505050505050502</v>
+        <f>3.870551181102362</f>
+        <v>3.870551181102362</v>
       </c>
       <c r="C143" t="s">
         <v>7</v>
@@ -3297,23 +3301,25 @@
       <c r="E143" t="s">
         <v>14</v>
       </c>
-      <c r="F143" t="s">
-        <v>37</v>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>battery hardware, Li-oxygen, engineering reference</t>
+        </is>
       </c>
       <c r="G143">
         <v>5</v>
       </c>
       <c r="H143" s="7">
-        <f>B143</f>
-        <v>5.0505050505050502</v>
+        <f>3.870551181102362</f>
+        <v>3.870551181102362</v>
       </c>
       <c r="I143" s="7">
-        <f>B143*0.75</f>
-        <v>3.7878787878787876</v>
+        <f>2.9029133858267713</f>
+        <v>2.9029133858267713</v>
       </c>
       <c r="J143" s="7">
-        <f>B143*1.25</f>
-        <v>6.3131313131313131</v>
+        <f>4.838188976377952</f>
+        <v>4.838188976377952</v>
       </c>
     </row>
     <row r="144" spans="1:14" ns3:dyDescent="0.2">
@@ -3323,8 +3329,8 @@
         </is>
       </c>
       <c r="B144" s="3">
-        <f>-1*B143</f>
-        <v>-5.0505050505050502</v>
+        <f>-3.870551181102362</f>
+        <v>-3.870551181102362</v>
       </c>
       <c r="C144" t="s">
         <v>7</v>
@@ -3346,22 +3352,57 @@
         <v>5</v>
       </c>
       <c r="H144" s="7">
-        <f>B144</f>
-        <v>-5.0505050505050502</v>
+        <f>-3.870551181102362</f>
+        <v>-3.870551181102362</v>
       </c>
       <c r="I144" s="7">
-        <f>B144*1.25</f>
-        <v>-6.3131313131313131</v>
+        <f>-4.838188976377952</f>
+        <v>-4.838188976377952</v>
       </c>
       <c r="J144" s="7">
-        <f>B144*0.75</f>
-        <v>-3.7878787878787876</v>
+        <f>-2.9029133858267713</f>
+        <v>-2.9029133858267713</v>
       </c>
       <c r="K144" t="b">
         <v>1</v>
       </c>
       <c r="M144" s="7"/>
       <c r="N144" s="7"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>battery auxiliary lifecycle, Li-O2 engineering reference</t>
+        </is>
+      </c>
+      <c r="B145">
+        <v>0.015748031496062992</v>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>battery auxiliary lifecycle, Li-O2 engineering reference</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>Fixed88.07kg auxiliary hardware plus matching dedicated end-of-life.</t>
+        </is>
+      </c>
     </row>
     <row r="146" spans="1:14" ht="16" ns3:dyDescent="0.2">
       <c r="A146" s="2" t="s">

--- a/premise/data/additional_inventories/lci-battery-capacity.xlsx
+++ b/premise/data/additional_inventories/lci-battery-capacity.xlsx
@@ -7232,7 +7232,9 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>APPROVED ENGINEERING CONTROL/THERMAL COVERAGE, item13, 2026-10-18. Wickerts corrected SI DOI10.1021/acssuschemeng.4c01782.s001 S26/S27; original Ellingsen2014 SI S39/S40, DOI10.1111/jiec.12072. Separate module monitoring from central protection: per16-module reference,1.1kg populated PCB monitors, central0.49kg populated PCB+2.8kg HV system+1.2kg LV system+.028kg fasteners=4.518kg. Use existing HV/LV/fastener process providers and generic populated through-hole PCB perkg; this is an explicit board-technology/material proxy rather than the source-specific board fabrication model. No whole BMS is added on top. Adopt one nominal10kg liquid-cooling assembly per reference: Al9.08, steel.23, PVC/rubber pipe.0096, thermal pad.2 (silicon.06, glass.02, ABS.12), ethylene glycol.48kg; source-rounded sum9.9996kg. Metal working/injection services are included; 100percent retention of listed finished materials is assumed. No stationary rack housing/container, common vehicle body or roadway is added. Monitoring/protection/cooling are added once as a unit-valued capacity input; kg module and matching waste remain separate, so density learning does not shrink fixed controls. Central and cooling hardware are conservatively co-replaced with each delivered pack; longer independent hardware life is not established. End-of-life uses the existing generic used Li-ion route for15.6176kg of auxiliary hardware per reference, without recovery credits; this is a treatment proxy for controls/cooling, not proof of chemistry-specific recovery. Source thermal duty, pump/radiator performance, protection ratings, inverter/pack interface, full outer pack enclosure and vehicle-specific module topology remain coverage/design gaps. The SIB cell-mass-equivalent module retains its existing18.768kg cell+6.203kg module hardware reference; it is not a demonstrated integer21700-cell topology. LiS uses the corrected19.306152kg cell+6.203kg module hardware. These are engineering references, not fleet-validated designs; use0.5-2x auxiliary-size and independent-replacement-life sensitivities. Reference gross capacity is16*18.768kg cell*0.157kWh/kg=47.145216000000005kWh; dose=0.02121105988781555unit/kWh. Existing cell density, kg-module recipe, energy/per-MJ coefficients and cycle assumptions are preserved.
+          <t>APPROVED STATIONARY SODIUM-ION SHARED CAPACITY REFERENCE, item21,2026-10-18. The stationary NMMT/HC module recipe and baseline specific energy match the existing chemistry-specific capacity reference. Its stationary name is absent from energy_density.yaml, so direct kg inputs stay constant while the common chemistry reference follows157Wh/kg-cell in2020 to200Wh/kg-cell in2050. Preserve workbook-only scope by purchasing exactly1kWh of market for battery capacity,Sodium-ion,SiB atGLO. This existing reference already supplies module manufacturing, equal negative end-of-life mass and the separately fixed-unit monitoring/protection/cooling package. Remove the stationary wrapper duplicate kg-manufacturing, waste and auxiliary inputs; do not add end-of-life twice. The wrapper itself is unmapped and receives no second density adjustment. Original stationary storage operating efficiency, calendar/cycle life and aggregate scenario shares are unchanged; this capacity reference contains manufacture and end-of-life rather than vehicle operation. The cell density trajectory is the existing scenario assumption, not a measured stationary pack design. Expected module mass8.474582023338275kg/kWh in2020 and6.652546888320545kg/kWh in2050, with fixed auxiliary input0.02121105988781555unit/kWh. No runtime or YAML modification.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+APPROVED ENGINEERING CONTROL/THERMAL COVERAGE, item13, 2026-10-18. Wickerts corrected SI DOI10.1021/acssuschemeng.4c01782.s001 S26/S27; original Ellingsen2014 SI S39/S40, DOI10.1111/jiec.12072. Separate module monitoring from central protection: per16-module reference,1.1kg populated PCB monitors, central0.49kg populated PCB+2.8kg HV system+1.2kg LV system+.028kg fasteners=4.518kg. Use existing HV/LV/fastener process providers and generic populated through-hole PCB perkg; this is an explicit board-technology/material proxy rather than the source-specific board fabrication model. No whole BMS is added on top. Adopt one nominal10kg liquid-cooling assembly per reference: Al9.08, steel.23, PVC/rubber pipe.0096, thermal pad.2 (silicon.06, glass.02, ABS.12), ethylene glycol.48kg; source-rounded sum9.9996kg. Metal working/injection services are included; 100percent retention of listed finished materials is assumed. No stationary rack housing/container, common vehicle body or roadway is added. Monitoring/protection/cooling are added once as a unit-valued capacity input; kg module and matching waste remain separate, so density learning does not shrink fixed controls. Central and cooling hardware are conservatively co-replaced with each delivered pack; longer independent hardware life is not established. End-of-life uses the existing generic used Li-ion route for15.6176kg of auxiliary hardware per reference, without recovery credits; this is a treatment proxy for controls/cooling, not proof of chemistry-specific recovery. Source thermal duty, pump/radiator performance, protection ratings, inverter/pack interface, full outer pack enclosure and vehicle-specific module topology remain coverage/design gaps. The SIB cell-mass-equivalent module retains its existing18.768kg cell+6.203kg module hardware reference; it is not a demonstrated integer21700-cell topology. LiS uses the corrected19.306152kg cell+6.203kg module hardware. These are engineering references, not fleet-validated designs; use0.5-2x auxiliary-size and independent-replacement-life sensitivities. Reference gross capacity is16*18.768kg cell*0.157kWh/kg=47.145216000000005kWh; dose=0.02121105988781555unit/kWh. Existing cell density, kg-module recipe, energy/per-MJ coefficients and cycle assumptions are preserved.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 APPROVED STATIONARY SODIUM-ION CAPACITY BASELINE NORMALIZATION, 2026-10-18. Zhang et al. (2024), Future climate impacts of sodium-ion batteries, Resources, Conservation and Recycling 202, 107362, DOI 10.1016/j.resconrec.2023.107362, Table 4, page 5: baseline NMMT/HC cell specific energy is 157 Wh/kg (0.157 kWh/kg), consistent with the existing source description and Premise density baseline. Primary paper: https://pub.epsilon.slu.se/32553/1/zhang-s-et-al-20240122.pdf . The linked existing SIB module recipe contains 0.7515918465419887 kg NMMT cell/kg module (lci-batteries-SIB.xlsx, sodium-ion batteries B493); its battery market purchases one kg of this module per kg delivered. Use this actual recipe coefficient, not a rounded 75 percent fraction, and 0.157 kWh/kg cell: 1/(0.157*0.7515918465419887) = 8.474582023338275 kg delivered module/kWh gross capacity. The previous 1/(0.16*0.75) = 8.333333333333334 kg represented 0.9833326658924353 kWh under those declared specifications. The module dose increases 1.6949842800592974 percent; this is not a percent change in overall transport or system metal demand. Set battery cell mass share to the linked recipe coefficient. Keep existing cell-specific density uncertainty endpoints 0.12 and 0.18 kWh/kg, translating them with the same module fraction; retain triangular type 5, equal negative waste mass and paired signed bounds/locations. Update formula caches consistently. The original rounded specific-energy/fraction/mass figures below are historical notes superseded by this paragraph. All supplier identities/geographies, the one-kWh output, cell/module manufacturing recipes, other chemistries, prospective density trajectory and lifetime/per-MJ allocations remain unchanged. This normalizes to declared cell energy and an existing module proxy; it does not validate measured pack performance, future electrochemical charge, cycle life or operating conditions. The Li-S-derived module architecture and missing BMS/cooling coverage remain unresolved. No electronics, racks, treatment route, recovery credit or primary/secondary share is added. Current full-system metal effects remain unquantified without a scenario rebuild. STATIONARY MAPPING LIMITATION: This stationary capacity-market name is absent from the existing density aliases. The current unmodified updater therefore leaves its mass and uncertainty bounds fixed through 2050. This corrects the initial normalization only; it does not implement the mobile density trajectory or resolve that mapping gap. The stationary market was inactive in the last 28-case audit, so no current system-metal effect is inferred. The previous mobile correction is preserved.
 PREVIOUS SOURCE NOTES (ROUNDED VALUES SUPERSEDED ABOVE):
@@ -7346,15 +7348,19 @@
       </c>
     </row>
     <row r="118" spans="1:14" ns3:dyDescent="0.2">
-      <c r="A118" t="s">
-        <v>39</v>
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>market for battery capacity, Sodium-ion, SiB</t>
+        </is>
       </c>
       <c r="B118" s="3">
-        <f>1/(0.157*$B$114)</f>
-        <v>8.474582023338275</v>
-      </c>
-      <c r="C118" t="s">
-        <v>7</v>
+        <f>1</f>
+        <v>1</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
       </c>
       <c r="D118" t="s">
         <v>3</v>
@@ -7362,100 +7368,41 @@
       <c r="E118" t="s">
         <v>14</v>
       </c>
-      <c r="F118" t="s">
-        <v>40</v>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>electricity storage capacity</t>
+        </is>
       </c>
       <c r="G118">
-        <v>5</v>
-      </c>
-      <c r="H118" s="7">
-        <f>B118</f>
-        <v>8.474582023338275</v>
-      </c>
-      <c r="I118" s="3">
-        <f>1/(0.18*$B$114)</f>
-        <v>7.391718764800606</v>
-      </c>
-      <c r="J118" s="3">
-        <f>1/(0.12*$B$114)</f>
-        <v>11.08757814720091</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H118" s="7"/>
+      <c r="I118" s="3"/>
+      <c r="J118" s="3"/>
     </row>
     <row r="119" spans="1:14" ns3:dyDescent="0.2">
-      <c r="A119" t="s">
-        <v>53</v>
-      </c>
-      <c r="B119" s="3">
-        <f>-1*B118</f>
-        <v>-8.474582023338275</v>
-      </c>
-      <c r="C119" t="s">
-        <v>7</v>
-      </c>
-      <c r="D119" t="s">
-        <v>3</v>
-      </c>
-      <c r="E119" t="s">
-        <v>14</v>
-      </c>
-      <c r="F119" t="s">
-        <v>54</v>
-      </c>
-      <c r="G119">
-        <v>5</v>
-      </c>
-      <c r="H119" s="7">
-        <f>B119</f>
-        <v>-8.474582023338275</v>
-      </c>
-      <c r="I119" s="3">
-        <f>-1/(0.12*$B$114)</f>
-        <v>-11.08757814720091</v>
-      </c>
-      <c r="J119" s="3">
-        <f>-1/(0.18*$B$114)</f>
-        <v>-7.391718764800606</v>
-      </c>
-      <c r="K119" t="b">
-        <v>1</v>
-      </c>
+      <c r="A119"/>
+      <c r="B119" s="3"/>
+      <c r="C119"/>
+      <c r="D119"/>
+      <c r="E119"/>
+      <c r="F119"/>
+      <c r="G119"/>
+      <c r="H119" s="7"/>
+      <c r="I119" s="3"/>
+      <c r="J119" s="3"/>
+      <c r="K119"/>
       <c r="M119" s="3"/>
       <c r="N119" s="3"/>
     </row>
     <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>battery controls and cooling, 16-module engineering reference</t>
-        </is>
-      </c>
-      <c r="B120">
-        <v>0.02121105988781555</v>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>technosphere</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>battery controls and cooling, 16-module engineering reference</t>
-        </is>
-      </c>
-      <c r="L120" t="inlineStr">
-        <is>
-          <t>Engineering auxiliary input; fixed unit reference, includes own separate15.6176kg waste.</t>
-        </is>
-      </c>
+      <c r="A120"/>
+      <c r="B120"/>
+      <c r="C120"/>
+      <c r="D120"/>
+      <c r="E120"/>
+      <c r="F120"/>
+      <c r="L120"/>
     </row>
     <row r="121" spans="1:14" ht="16" ns3:dyDescent="0.2">
       <c r="A121" s="2" t="s">

--- a/premise/data/additional_inventories/lci-battery-capacity.xlsx
+++ b/premise/data/additional_inventories/lci-battery-capacity.xlsx
@@ -2459,7 +2459,9 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. Chemistry=LTO; geometry proxy=NMC622; cellmass=108.03kg, scalablehardware=145.74kg, assumed cellbaseline=0.085kWh/kg, grossreference=9.18255kWh, fixedcontrolmass=6.538kg. Retained listed hardware material coefficients sum1kg/kg; upstream cell/processing yields are not overwritten. Raw source rounding and cell-specific gaps remain in those providers. Cell-share metadata now refers only to scalable hardware; total installed pack also includes fixed unit-valued control hardware.
+          <t>APPROVED SOURCE-CONSISTENT NCA/LTO CELL AND CAPACITY REFERENCE,item22,2026-10-18. Schmidt etal2019 DOI10.1021/acs.est.8b05313, Supporting Data es8b05313_si_002.zip, NCA LTO battery import.xlsx summary!H54=16.040428932169362kg/kWh dry cell components excluding pouch, H56=.5181296021158341kg/kWh pouch; H60=1000/(H54+H56)=60.39173022998696Wh/kg-cell. This is the source harmonized historical NCA/LTO engineering design, not modern fleet validation. The current capacity reference85Wh/kg is inconsistent with that recipe. Restore seven component fractions to source per-kWh masses divided by16.558558534285197kg/kWh; the old six non-pouch fractions were multiplied by rounded.060kWh/kg and the pouch filled the remainder, rather than using the source pouch mass. This restores source component ratios and a1kg component-sum cell. Preserve all previously corrected upstream electrode/graphite/collector recipes and supplier identities, cell water/electricity/heat proxies, reference pack cellmass108.03kg and non-cell geometry37.71kg (NMC622 geometry proxy), controls/protection6.538kg per reference and all vehicle energy/cycle/replacement assumptions. Factory utilities and upstream manufacturing yields remain inherited proxies rather than a claim of complete original-source reproduction. Use exact source cell energy.060391730229986965kWh/kg in the capacity market. Scalable hardware145.74kg now represents6.524118616745492grosskWh, hence22.338649641643293kg/kWh instead of15.871408268944903. Pair identical negative waste mass and signed uncertainty endpoints; retain prior engineering75-125percent mass range, without claiming source statistical confidence. Fixed-unit controls remain unchanged per reference pack, but dose becomes1/6.524118616745492unit/kWh to share the same capacity basis. No future LTO improvement is assumed; existing2020/2050 density-factor ratio is1 even though its YAML absolute values are historical50Wh/kg. No runtime/YAML changes. Original standalone75/25 LTO battery market remains a separate legacy assembly reference, while capacity markets buy the explicit hardware/central-control reference. Source pack48.6049Wh/kg excludes BMS/cooling and is distinct from the adopted cell-specific60.3917Wh/kg. Remaining material-grade, utility, thermal rating, life and future-design limitations remain explicit.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. Chemistry=LTO; geometry proxy=NMC622; cellmass=108.03kg, scalablehardware=145.74kg, assumed cellbaseline=0.085kWh/kg, grossreference=9.18255kWh, fixedcontrolmass=6.538kg. Retained listed hardware material coefficients sum1kg/kg; upstream cell/processing yields are not overwritten. Raw source rounding and cell-specific gaps remain in those providers. Cell-share metadata now refers only to scalable hardware; total installed pack also includes fixed unit-valued control hardware.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 This dataset provides 1 kWh of battery gross capacity (NOT net), using a Li-ion LTO battery. Specific energy density in 2020: 0.085 kWh/kg cell. Battery management (BoP) mass share: 36%. Battery energy density in 2020: 0.053 kWh/kg battery. Battery mass per kWh: 18.4 kg. Lifetime: 10'000 cycles. Source for parameters: Life cycle assessment of battery electric buses. Transportation Research Part D: Transport and Environment. Linda Ager-Wick Ellingsen, Rebecca Jayne Thorne, Julia Wind, Erik Figenbaum, Mia Romare and Anders Nordelöf.</t>
         </is>
@@ -2577,8 +2579,8 @@
         </is>
       </c>
       <c r="B104" s="3">
-        <f>15.871408268944903</f>
-        <v>15.871408268944903</v>
+        <f>1/(0.060391730229986965*$B$100)</f>
+        <v>22.338649641643293</v>
       </c>
       <c r="C104" t="s">
         <v>7</v>
@@ -2598,16 +2600,16 @@
         <v>5</v>
       </c>
       <c r="H104" s="7">
-        <f>15.871408268944903</f>
-        <v>15.871408268944903</v>
+        <f>B104</f>
+        <v>22.338649641643293</v>
       </c>
       <c r="I104" s="7">
-        <f>11.903556201708676</f>
-        <v>11.903556201708676</v>
+        <f>B104*0.75</f>
+        <v>16.753987231232472</v>
       </c>
       <c r="J104" s="7">
-        <f>19.839260336181127</f>
-        <v>19.839260336181127</v>
+        <f>B104*1.25</f>
+        <v>27.923312052054115</v>
       </c>
     </row>
     <row r="105" spans="1:14" ns3:dyDescent="0.2">
@@ -2615,8 +2617,8 @@
         <v>53</v>
       </c>
       <c r="B105" s="3">
-        <f>-15.871408268944903</f>
-        <v>-15.871408268944903</v>
+        <f>-B104</f>
+        <v>-22.338649641643293</v>
       </c>
       <c r="C105" t="s">
         <v>7</v>
@@ -2634,16 +2636,16 @@
         <v>5</v>
       </c>
       <c r="H105" s="7">
-        <f>-15.871408268944903</f>
-        <v>-15.871408268944903</v>
+        <f>B105</f>
+        <v>-22.338649641643293</v>
       </c>
       <c r="I105" s="7">
-        <f>-19.839260336181127</f>
-        <v>-19.839260336181127</v>
+        <f>B105*1.25</f>
+        <v>-27.923312052054115</v>
       </c>
       <c r="J105" s="7">
-        <f>-11.903556201708676</f>
-        <v>-11.903556201708676</v>
+        <f>B105*0.75</f>
+        <v>-16.753987231232472</v>
       </c>
       <c r="K105" t="b">
         <v>1</v>
@@ -2658,7 +2660,7 @@
         </is>
       </c>
       <c r="B106">
-        <v>0.10890221125939961</v>
+        <v>0.1532774093704082</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>

--- a/premise/data/additional_inventories/lci-battery-capacity.xlsx
+++ b/premise/data/additional_inventories/lci-battery-capacity.xlsx
@@ -771,7 +771,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:ns4="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N266"/>
+  <dimension ref="A1:N314"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" ns3:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="46.5" customWidth="1"/>
@@ -5381,6 +5381,1048 @@
       </c>
       <c r="F266" t="s">
         <v>106</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>high-power battery capacity, FCEV car, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B271">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>high-power battery capacity, FCEV car, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>Toyota Mirai2 manufacturer https://newsroom.toyota.eu/introducing-the-all-new-toyota-mirai/; AKASOL AKASYSTEM15OEM37PRC May2021 https://www.act-news.com/wp-content/uploads/2020/11/210525_LowRes_AK_Datenblatt_AKASystem_15-OEM-37-PRC_2021_2159x2794mm_EN.pdf; Dai2018 Table8 https://publications.anl.gov/anlpubs/2018/10/146906.pdf.</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>APPROVED FCEV HIGH-POWER PACK ENGINEERING REFERENCES, item24, 2026-10-18. Toyota Mirai2 manufacturer https://newsroom.toyota.eu/introducing-the-all-new-toyota-mirai/; AKASOL AKASYSTEM15OEM37PRC May2021 https://www.act-news.com/wp-content/uploads/2020/11/210525_LowRes_AK_Datenblatt_AKASystem_15-OEM-37-PRC_2021_2159x2794mm_EN.pdf; Dai2018 Table8 https://publications.anl.gov/anlpubs/2018/10/146906.pdf. Match complete physical pack mass and nominal energy, not the changing BEV MIX. Car reference44.6kg/1.2432kWh (=310.8V*4Ah/1000),31.5kW for10seconds; truck reference238kg/25kWh,36kW continuous charge,50kW continuous RMS discharge,150kW10second discharge. Retain existing vehicle capacities/power sizing and lifetime replacement counts. These manufacturer ratings are NOT inferred from chemistry or treated as continuous pulse ratings. Material split remains an engineering proxy:70percent cells, as in the truck sizing source; assume the same70percent for cars. NMC622 cell manufacturing is a bulk-composition proxy, NOT a measured Mirai/AKASOL cell design or a validated high-power electrode/capacity recipe. Thus mass-equivalence is corrected while chemistry-specific metal intensities remain uncertain. Sensitivity cell share50-80percent and alternative documented high-power chemistries. One4.518kg central-control/protection assembly per reference pack; remaining mass is allocated using public Dai non-electronic hardware proportions. Car air-cooled reference excludes liquid coolant; unknown fan/duct design is embedded in the residual housing proxy, not independently validated. Truck liquid cooling retains Dai50/50 glycol/water proportions; pump/thermal ratings remain gaps. No module electronics are added on top of the central package; missing distributed monitoring is a coverage gap. All retained material inputs use100percent assembly retention reference; generic working services additional. Equal negative used-battery treatment equals complete manufactured reference mass, including controls, once; no duplicated control waste. These dedicated capacity providers are deliberately outside generic chemistry-density and MIX updates, preserving the already-declared fixed2020 FCEV hardware assumption through2050. Do not interpret corrected mass as a validated manufacturer BOM, annual procurement or primary/secondary content.</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>high-power battery capacity, FCEV car, engineering reference</t>
+        </is>
+      </c>
+      <c r="B278">
+        <v>1</v>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>high-power battery capacity, FCEV car, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>market for battery cell, Li-ion, NMC622</t>
+        </is>
+      </c>
+      <c r="B279">
+        <v>25.11261261261261</v>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>battery cell, Li-ion, NMC622</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>battery central controls and protection, engineering reference</t>
+        </is>
+      </c>
+      <c r="B280">
+        <v>0.8043758043758044</v>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>battery central controls and protection, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>market for copper, cathode</t>
+        </is>
+      </c>
+      <c r="B281">
+        <v>0.12078060465157239</v>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>metal working, average for copper product manufacturing</t>
+        </is>
+      </c>
+      <c r="B282">
+        <v>0.12078060465157239</v>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>metal working, average for copper product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>market for aluminium, wrought alloy</t>
+        </is>
+      </c>
+      <c r="B283">
+        <v>6.566284025961444</v>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>aluminium, wrought alloy</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>metal working, average for aluminium product manufacturing</t>
+        </is>
+      </c>
+      <c r="B284">
+        <v>6.566284025961444</v>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>metal working, average for aluminium product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>market for polyethylene, high density, granulate</t>
+        </is>
+      </c>
+      <c r="B285">
+        <v>0.19742983452660873</v>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>polyethylene, high density, granulate</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>market for glass fibre reinforced plastic, polyester resin, hand lay-up</t>
+        </is>
+      </c>
+      <c r="B286">
+        <v>0.025549743291678775</v>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>glass fibre reinforced plastic, polyester resin, hand lay-up</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>market for steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="B287">
+        <v>0.21833416994707314</v>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>metal working, average for steel product manufacturing</t>
+        </is>
+      </c>
+      <c r="B288">
+        <v>0.21833416994707314</v>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>metal working, average for steel product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>market for used Li-ion battery</t>
+        </is>
+      </c>
+      <c r="B289">
+        <v>-35.87516087516087</v>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>used Li-ion battery</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>high-power battery capacity, FCEV truck, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B294">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>high-power battery capacity, FCEV truck, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>Toyota Mirai2 manufacturer https://newsroom.toyota.eu/introducing-the-all-new-toyota-mirai/; AKASOL AKASYSTEM15OEM37PRC May2021 https://www.act-news.com/wp-content/uploads/2020/11/210525_LowRes_AK_Datenblatt_AKASystem_15-OEM-37-PRC_2021_2159x2794mm_EN.pdf; Dai2018 Table8 https://publications.anl.gov/anlpubs/2018/10/146906.pdf.</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>APPROVED FCEV HIGH-POWER PACK ENGINEERING REFERENCES, item24, 2026-10-18. Toyota Mirai2 manufacturer https://newsroom.toyota.eu/introducing-the-all-new-toyota-mirai/; AKASOL AKASYSTEM15OEM37PRC May2021 https://www.act-news.com/wp-content/uploads/2020/11/210525_LowRes_AK_Datenblatt_AKASystem_15-OEM-37-PRC_2021_2159x2794mm_EN.pdf; Dai2018 Table8 https://publications.anl.gov/anlpubs/2018/10/146906.pdf. Match complete physical pack mass and nominal energy, not the changing BEV MIX. Car reference44.6kg/1.2432kWh (=310.8V*4Ah/1000),31.5kW for10seconds; truck reference238kg/25kWh,36kW continuous charge,50kW continuous RMS discharge,150kW10second discharge. Retain existing vehicle capacities/power sizing and lifetime replacement counts. These manufacturer ratings are NOT inferred from chemistry or treated as continuous pulse ratings. Material split remains an engineering proxy:70percent cells, as in the truck sizing source; assume the same70percent for cars. NMC622 cell manufacturing is a bulk-composition proxy, NOT a measured Mirai/AKASOL cell design or a validated high-power electrode/capacity recipe. Thus mass-equivalence is corrected while chemistry-specific metal intensities remain uncertain. Sensitivity cell share50-80percent and alternative documented high-power chemistries. One4.518kg central-control/protection assembly per reference pack; remaining mass is allocated using public Dai non-electronic hardware proportions. Car air-cooled reference excludes liquid coolant; unknown fan/duct design is embedded in the residual housing proxy, not independently validated. Truck liquid cooling retains Dai50/50 glycol/water proportions; pump/thermal ratings remain gaps. No module electronics are added on top of the central package; missing distributed monitoring is a coverage gap. All retained material inputs use100percent assembly retention reference; generic working services additional. Equal negative used-battery treatment equals complete manufactured reference mass, including controls, once; no duplicated control waste. These dedicated capacity providers are deliberately outside generic chemistry-density and MIX updates, preserving the already-declared fixed2020 FCEV hardware assumption through2050. Do not interpret corrected mass as a validated manufacturer BOM, annual procurement or primary/secondary content.</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>high-power battery capacity, FCEV truck, engineering reference</t>
+        </is>
+      </c>
+      <c r="B301">
+        <v>1</v>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>high-power battery capacity, FCEV truck, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>market for battery cell, Li-ion, NMC622</t>
+        </is>
+      </c>
+      <c r="B302">
+        <v>6.664</v>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>battery cell, Li-ion, NMC622</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>battery central controls and protection, engineering reference</t>
+        </is>
+      </c>
+      <c r="B303">
+        <v>0.04</v>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>battery central controls and protection, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>market for copper, cathode</t>
+        </is>
+      </c>
+      <c r="B304">
+        <v>0.03689062848050915</v>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>metal working, average for copper product manufacturing</t>
+        </is>
+      </c>
+      <c r="B305">
+        <v>0.03689062848050915</v>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>metal working, average for copper product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>market for aluminium, wrought alloy</t>
+        </is>
+      </c>
+      <c r="B306">
+        <v>2.005573206046141</v>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>aluminium, wrought alloy</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>metal working, average for aluminium product manufacturing</t>
+        </is>
+      </c>
+      <c r="B307">
+        <v>2.005573206046141</v>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>metal working, average for aluminium product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>market for polyethylene, high density, granulate</t>
+        </is>
+      </c>
+      <c r="B308">
+        <v>0.06030198886237072</v>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>polyethylene, high density, granulate</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>market for glass fibre reinforced plastic, polyester resin, hand lay-up</t>
+        </is>
+      </c>
+      <c r="B309">
+        <v>0.007803786793953858</v>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>glass fibre reinforced plastic, polyester resin, hand lay-up</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>market for steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="B310">
+        <v>0.06668690533015115</v>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>metal working, average for steel product manufacturing</t>
+        </is>
+      </c>
+      <c r="B311">
+        <v>0.06668690533015115</v>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>metal working, average for steel product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>ethylene glycols production, thermal hydrolysis of ethylene oxide</t>
+        </is>
+      </c>
+      <c r="B312">
+        <v>0.2490117422434367</v>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>ethylene glycol</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>market for water, deionised</t>
+        </is>
+      </c>
+      <c r="B313">
+        <v>0.2490117422434367</v>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>water, deionised</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>market for used Li-ion battery</t>
+        </is>
+      </c>
+      <c r="B314">
+        <v>-9.52</v>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>used Li-ion battery</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/premise/data/additional_inventories/lci-battery-capacity.xlsx
+++ b/premise/data/additional_inventories/lci-battery-capacity.xlsx
@@ -771,7 +771,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:ns4="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N314"/>
+  <dimension ref="A1:N339"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" ns3:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="46.5" customWidth="1"/>
@@ -6420,6 +6420,632 @@
         </is>
       </c>
       <c r="G314" t="inlineStr">
+        <is>
+          <t>used Li-ion battery</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>battery capacity, hydrogen rail, LFP engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B319">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>battery capacity, hydrogen rail, LFP engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>Knibbe2023 DOI10.1016/j.est.2023.108090,3.6MWhLFP/860kWreference and133Wh/kgpack; Dai2018 public LFP non-cell material proportions https://publications.anl.gov/anlpubs/2018/10/146906.pdf Table8.</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>APPROVED HYDROGEN-RAIL COMPLETE LFP CAPACITY REFERENCE, issue33, 2026-10-18. Knibbe2023 DOI10.1016/j.est.2023.108090,3.6MWhLFP/860kWreference and133Wh/kgpack; Dai2018 public LFP non-cell material proportions https://publications.anl.gov/anlpubs/2018/10/146906.pdf Table8. Replace old whole-pack23.5kWh/165kg conversion purchased as bareNMC622cells with a complete3.6MWhLFP reference. Referencepack133Wh/kg =&gt;27067.66917293233kg installed; existing40year/15year lifetime convention gives9600kWh manufactured and treated, not annual procurement.15years remains an engineering calendar assumption, not demonstrated rail LFP cycle life; sensitivity10-20years and source-specific duty/aging remains required. At860kW total stored energy/power=4.186h; battery peakpower and simultaneous fuel-cell duty are not proven by this ratio. Per1kWh:6.25kg cells at existing160Wh/kgcell reference. Assume modular100kWh subsystems, each112series-equivalent3.2V LFPcells at279.017857Ah; series/parallel arrangement and thermal ratings are a design reference, not measured locomotive architecture. One existing6.668kg LFP monitoring/central-controls package per100kWh; other retained mass uses Dai non-electronic module/pack material proportions including50/50glycol/water. This hardware geometry/control allocation is an explicit engineering transfer. Complete pack mass/cellcapacity/control+waste close together. Controls package already treats its6.668kg, so local battery waste excludes that mass; no duplicate EOL. Source cell manufacturing chemistry, electronics-specific materials and thermal duty remain proxies; source133Wh/kg is not certification of this constructed BOM. Existing rail inventory had fixed barecell mass over time; this dedicated fixed-reference provider retains that temporal boundary and is outside generic road density-learning markets. No future LFP electrode evolution is claimed. No locomotive body, tender or track added. Rail source and explicit passenger-energy link are both changed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I325" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>battery capacity, hydrogen rail, LFP engineering reference</t>
+        </is>
+      </c>
+      <c r="B326">
+        <v>1</v>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>battery capacity, hydrogen rail, LFP engineering reference</t>
+        </is>
+      </c>
+      <c r="I326" t="inlineStr">
+        <is>
+          <t>battery capacity, hydrogen rail, LFP engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>market for battery cell, Li-ion, LFP</t>
+        </is>
+      </c>
+      <c r="B327">
+        <v>6.25</v>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>battery cell, Li-ion, LFP</t>
+        </is>
+      </c>
+      <c r="I327" t="inlineStr">
+        <is>
+          <t>battery cell, Li-ion, LFP</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>battery monitoring and central controls, LFP, engineering reference</t>
+        </is>
+      </c>
+      <c r="B328">
+        <v>0.01</v>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>battery monitoring and central controls, LFP, engineering reference</t>
+        </is>
+      </c>
+      <c r="I328" t="inlineStr">
+        <is>
+          <t>battery monitoring and central controls, LFP, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>market for copper, cathode</t>
+        </is>
+      </c>
+      <c r="B329">
+        <v>0.01512710646109896</v>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+      <c r="I329" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>metal working, average for copper product manufacturing</t>
+        </is>
+      </c>
+      <c r="B330">
+        <v>0.01512710646109896</v>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>metal working, average for copper product manufacturing</t>
+        </is>
+      </c>
+      <c r="I330" t="inlineStr">
+        <is>
+          <t>metal working, average for copper product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>market for aluminium, wrought alloy</t>
+        </is>
+      </c>
+      <c r="B331">
+        <v>0.8717605062178482</v>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>aluminium, wrought alloy</t>
+        </is>
+      </c>
+      <c r="I331" t="inlineStr">
+        <is>
+          <t>aluminium, wrought alloy</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>metal working, average for aluminium product manufacturing</t>
+        </is>
+      </c>
+      <c r="B332">
+        <v>0.8717605062178482</v>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>metal working, average for aluminium product manufacturing</t>
+        </is>
+      </c>
+      <c r="I332" t="inlineStr">
+        <is>
+          <t>metal working, average for aluminium product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>market for polyethylene, high density, granulate</t>
+        </is>
+      </c>
+      <c r="B333">
+        <v>0.02439855880822413</v>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>polyethylene, high density, granulate</t>
+        </is>
+      </c>
+      <c r="I333" t="inlineStr">
+        <is>
+          <t>polyethylene, high density, granulate</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>market for glass fibre reinforced plastic, polyester resin, hand lay-up</t>
+        </is>
+      </c>
+      <c r="B334">
+        <v>0.003171812645069137</v>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>glass fibre reinforced plastic, polyester resin, hand lay-up</t>
+        </is>
+      </c>
+      <c r="I334" t="inlineStr">
+        <is>
+          <t>glass fibre reinforced plastic, polyester resin, hand lay-up</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>market for steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="B335">
+        <v>0.03513392468384275</v>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="I335" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>metal working, average for steel product manufacturing</t>
+        </is>
+      </c>
+      <c r="B336">
+        <v>0.03513392468384275</v>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>metal working, average for steel product manufacturing</t>
+        </is>
+      </c>
+      <c r="I336" t="inlineStr">
+        <is>
+          <t>metal working, average for steel product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>ethylene glycols production, thermal hydrolysis of ethylene oxide</t>
+        </is>
+      </c>
+      <c r="B337">
+        <v>0.12626254183255986</v>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>ethylene glycol</t>
+        </is>
+      </c>
+      <c r="I337" t="inlineStr">
+        <is>
+          <t>ethylene glycol</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>market for water, deionised</t>
+        </is>
+      </c>
+      <c r="B338">
+        <v>0.12626254183255986</v>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>water, deionised</t>
+        </is>
+      </c>
+      <c r="I338" t="inlineStr">
+        <is>
+          <t>water, deionised</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>market for used Li-ion battery</t>
+        </is>
+      </c>
+      <c r="B339">
+        <v>-7.452116992481203</v>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>used Li-ion battery</t>
+        </is>
+      </c>
+      <c r="I339" t="inlineStr">
         <is>
           <t>used Li-ion battery</t>
         </is>

--- a/premise/data/additional_inventories/lci-battery-capacity.xlsx
+++ b/premise/data/additional_inventories/lci-battery-capacity.xlsx
@@ -771,7 +771,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:ns4="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N339"/>
+  <dimension ref="A1:N374"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" ns3:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="46.5" customWidth="1"/>
@@ -7046,6 +7046,733 @@
         </is>
       </c>
       <c r="I339" t="inlineStr">
+        <is>
+          <t>used Li-ion battery</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>battery hardware, fuel-cell bus LTO, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B344">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>battery hardware, fuel-cell bus LTO, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>Forsee Power PULSE15 manufacturer https://www.forseepower.com/lithium-ion-battery/high-power-batteries/pulse-15/ :14.6kWh,260kg,635V,LTO,63kWcontinuous,127kW10seconds,liquidcooling,15years/15000cycles.2020CaetanoH2 application https://www.forseepower.com/wp-content/uploads/2023/07/2020-01-27-Forsee-Power_CP-Caetano-h2_EN.pdf . Internal BOM not published.</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>APPROVED FUEL-CELL BUS BUFFER REFERENCE, issue59, 2026-10-18. Forsee Power PULSE15 manufacturer https://www.forseepower.com/lithium-ion-battery/high-power-batteries/pulse-15/ :14.6kWh,260kg,635V,LTO,63kWcontinuous,127kW10seconds,liquidcooling,15years/15000cycles.2020CaetanoH2 application https://www.forseepower.com/wp-content/uploads/2023/07/2020-01-27-Forsee-Power_CP-Caetano-h2_EN.pdf . Internal BOM not published. Replace six genericMIX highenergy batteries with a bus-specific fixed highpower LTO reference. Select smallest integer parallelpack count meeting both original nominalkWh and entire motorcontinuouspower/63kW; this deliberately conservative power check does not credit fuelcell contribution. Eachpack14.6kWh/260kg; preserve635V inparallel,do not addseriesvoltage. Nominalenergy is not advertised usableenergy; assume80%usable only as explicit sensitivity,not manufacturerDoD. Lifetime packcount=installedcount*ceil(vehicleyears/15); cyclethroughput unknown despite15000cycle claim. Sourcebatteryreplacement assumptions superseded explicitly, not appliedtwice. Internal cell reference:existing LTO cell chemistry/production recipe transferred at assumed80Wh/kgcell (sensitivity60-100),182.5kgcells/pack. Existing60Wh/kgrecipe coefficient is a different engineeringdesign;80Wh/kg is NOT measured PULSEcellperformance. Actual cathode,cellformat,cellcount,energy/power capability remain unresolved.6.538kg controls perpack from16module NMC955reference,architecture transfer not measured PULSEBMS. Other70.962kg casing/cooling/busbars assigned explicit engineering proportions50%Al,15%Cu,10%steel,10%PA,15%50/50glycolwater. Source260kg ensures physicalmassclosure; no assertion this unpublished BOM matches actualmanufacturer. Fixeddesign has no highenergy density trajectory or genericMIXchemistry switching; actualfuturepower/cellredesign requires evidence. Packdisposal covers253.462kg noncontrols,controlshelper disposes6.538kg,onceeach. Update vehicle specification notes and productionassembly mass by installedmassdelta; common glider unchanged, lifetimeenergy/service demand unchanged pending a new driving/thermal simulation. This changed mass/reference is therefore a manufacturing audit correction,not a validated roadperformance prediction. No extra wholevehicle procurement, primarysecondaryshares or recyclingcredit. Refresh affected storedperMJ equipment from actualsource inventories.</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H350" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I350" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>battery hardware, fuel-cell bus LTO, engineering reference</t>
+        </is>
+      </c>
+      <c r="B351">
+        <v>1</v>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>battery hardware, fuel-cell bus LTO, engineering reference</t>
+        </is>
+      </c>
+      <c r="I351" t="inlineStr">
+        <is>
+          <t>battery hardware, fuel-cell bus LTO, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>battery cell production, Li-ion, LTO</t>
+        </is>
+      </c>
+      <c r="B352">
+        <v>182.5</v>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>battery cell, Li-ion, LTO</t>
+        </is>
+      </c>
+      <c r="I352" t="inlineStr">
+        <is>
+          <t>battery cell, Li-ion, LTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>market for aluminium, wrought alloy</t>
+        </is>
+      </c>
+      <c r="B353">
+        <v>35.481</v>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>aluminium, wrought alloy</t>
+        </is>
+      </c>
+      <c r="I353" t="inlineStr">
+        <is>
+          <t>aluminium, wrought alloy</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>market for copper, cathode</t>
+        </is>
+      </c>
+      <c r="B354">
+        <v>10.6443</v>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+      <c r="I354" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>market for steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="B355">
+        <v>7.0962000000000005</v>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="I355" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>market for nylon 6</t>
+        </is>
+      </c>
+      <c r="B356">
+        <v>7.0962000000000005</v>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>nylon 6</t>
+        </is>
+      </c>
+      <c r="I356" t="inlineStr">
+        <is>
+          <t>nylon 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>ethylene glycols production, thermal hydrolysis of ethylene oxide</t>
+        </is>
+      </c>
+      <c r="B357">
+        <v>5.32215</v>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>ethylene glycol</t>
+        </is>
+      </c>
+      <c r="I357" t="inlineStr">
+        <is>
+          <t>ethylene glycol</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>market for water, deionised</t>
+        </is>
+      </c>
+      <c r="B358">
+        <v>5.32215</v>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>water, deionised</t>
+        </is>
+      </c>
+      <c r="I358" t="inlineStr">
+        <is>
+          <t>water, deionised</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B359">
+        <v>260</v>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="I359" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>high-power battery capacity, fuel-cell bus LTO, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B364">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>high-power battery capacity, fuel-cell bus LTO, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>Forsee Power PULSE15 manufacturer https://www.forseepower.com/lithium-ion-battery/high-power-batteries/pulse-15/ :14.6kWh,260kg,635V,LTO,63kWcontinuous,127kW10seconds,liquidcooling,15years/15000cycles.2020CaetanoH2 application https://www.forseepower.com/wp-content/uploads/2023/07/2020-01-27-Forsee-Power_CP-Caetano-h2_EN.pdf . Internal BOM not published.</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>APPROVED FUEL-CELL BUS BUFFER REFERENCE, issue59, 2026-10-18. Forsee Power PULSE15 manufacturer https://www.forseepower.com/lithium-ion-battery/high-power-batteries/pulse-15/ :14.6kWh,260kg,635V,LTO,63kWcontinuous,127kW10seconds,liquidcooling,15years/15000cycles.2020CaetanoH2 application https://www.forseepower.com/wp-content/uploads/2023/07/2020-01-27-Forsee-Power_CP-Caetano-h2_EN.pdf . Internal BOM not published. Replace six genericMIX highenergy batteries with a bus-specific fixed highpower LTO reference. Select smallest integer parallelpack count meeting both original nominalkWh and entire motorcontinuouspower/63kW; this deliberately conservative power check does not credit fuelcell contribution. Eachpack14.6kWh/260kg; preserve635V inparallel,do not addseriesvoltage. Nominalenergy is not advertised usableenergy; assume80%usable only as explicit sensitivity,not manufacturerDoD. Lifetime packcount=installedcount*ceil(vehicleyears/15); cyclethroughput unknown despite15000cycle claim. Sourcebatteryreplacement assumptions superseded explicitly, not appliedtwice. Internal cell reference:existing LTO cell chemistry/production recipe transferred at assumed80Wh/kgcell (sensitivity60-100),182.5kgcells/pack. Existing60Wh/kgrecipe coefficient is a different engineeringdesign;80Wh/kg is NOT measured PULSEcellperformance. Actual cathode,cellformat,cellcount,energy/power capability remain unresolved.6.538kg controls perpack from16module NMC955reference,architecture transfer not measured PULSEBMS. Other70.962kg casing/cooling/busbars assigned explicit engineering proportions50%Al,15%Cu,10%steel,10%PA,15%50/50glycolwater. Source260kg ensures physicalmassclosure; no assertion this unpublished BOM matches actualmanufacturer. Fixeddesign has no highenergy density trajectory or genericMIXchemistry switching; actualfuturepower/cellredesign requires evidence. Packdisposal covers253.462kg noncontrols,controlshelper disposes6.538kg,onceeach. Update vehicle specification notes and productionassembly mass by installedmassdelta; common glider unchanged, lifetimeenergy/service demand unchanged pending a new driving/thermal simulation. This changed mass/reference is therefore a manufacturing audit correction,not a validated roadperformance prediction. No extra wholevehicle procurement, primarysecondaryshares or recyclingcredit. Refresh affected storedperMJ equipment from actualsource inventories.</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G370" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H370" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I370" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>high-power battery capacity, fuel-cell bus LTO, engineering reference</t>
+        </is>
+      </c>
+      <c r="B371">
+        <v>1</v>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G371" t="inlineStr">
+        <is>
+          <t>high-power battery capacity, fuel-cell bus LTO, engineering reference</t>
+        </is>
+      </c>
+      <c r="I371" t="inlineStr">
+        <is>
+          <t>high-power battery capacity, fuel-cell bus LTO, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>battery hardware, fuel-cell bus LTO, engineering reference</t>
+        </is>
+      </c>
+      <c r="B372">
+        <v>0.0684931506849315</v>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G372" t="inlineStr">
+        <is>
+          <t>battery hardware, fuel-cell bus LTO, engineering reference</t>
+        </is>
+      </c>
+      <c r="I372" t="inlineStr">
+        <is>
+          <t>battery hardware, fuel-cell bus LTO, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>battery monitoring and central controls, NMC955, engineering reference</t>
+        </is>
+      </c>
+      <c r="B373">
+        <v>0.0684931506849315</v>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G373" t="inlineStr">
+        <is>
+          <t>battery monitoring and central controls, NMC955, engineering reference</t>
+        </is>
+      </c>
+      <c r="I373" t="inlineStr">
+        <is>
+          <t>battery monitoring and central controls, NMC955, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>market for used Li-ion battery</t>
+        </is>
+      </c>
+      <c r="B374">
+        <v>-17.360410958904108</v>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G374" t="inlineStr">
+        <is>
+          <t>used Li-ion battery</t>
+        </is>
+      </c>
+      <c r="I374" t="inlineStr">
         <is>
           <t>used Li-ion battery</t>
         </is>

--- a/premise/data/additional_inventories/lci-battery-capacity.xlsx
+++ b/premise/data/additional_inventories/lci-battery-capacity.xlsx
@@ -801,7 +801,9 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. Chemistry=LFP; geometry proxy=LFP; cellmass=147.58kg, scalablehardware=196.85000000000002kg, assumed cellbaseline=0.16kWh/kg, grossreference=23.612800000000004kWh, fixedcontrolmass=6.668kg. Retained listed hardware material coefficients sum1kg/kg; upstream cell/processing yields are not overwritten. Raw source rounding and cell-specific gaps remain in those providers. Cell-share metadata now refers only to scalable hardware; total installed pack also includes fixed unit-valued control hardware.
+          <t>APPROVED CELL-ONLY DENSITY LEARNING AND FIXED PACK HARDWARE, issue63, 2026-10-18. Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign. For nine conventionalmobile chemistries,LiS,SIB,LiO2 andthreeASSB references,split active capacitypath into kgcellmanufacture and one fixednoncellreference unit perbaseline nominalkWh. Preserve exactbaselinecell mass,allnoncellmaterials,processservices,controls,transport and totaldisposal. Unitbasis is the original explicitly sizedpack architecture attributed to1nominalkWh,not onephysicalpackper1kWh or a newcapacity. Existingruntime scaling appliesonly kgexchanges of namedcapacitydatasets; thus cellmanufacturekg and matchingusedcellkg followunchangeddensityfactor,while casing,busbars,coolant,packaging and theirdisposal are fixedinsideunitprovider. Existing separatelyunitizedcentral/modulecontrols,oxygenlifecycle,cooling are unchanged. No runtime/YAML/learningcurve edit. Noncellhelper buys originalnoncellprocesses once,plusits originalfraction ofusedbattery treatment;Negative cellwaste moves inside the scalablecellprovider at-1kg/kgcell, so it follows exactly the samecellmass; reuse originalcapacitywasterow forfixedunit without movingworkbookrows. The fixedunit is deterministic; prior signed mass uncertainty is removed from thatrow,while original scaledcell distribution is retained. No negativecredit tocancel a completepack orsecondwholepack disposal. LiS/SIB unfold onlyone-to-one packmarket/module boundary; sourcefinishedpackfreight divided bybaselinecell/noncellmass,cellfreight followscellmass andnoncellfreight fixed,baselinefreight identical. Existing cellrecipe andits internalcollectors/separator/case are retained andscale with cellmass: this is a reference ofsamecellformat atgreatercapacity,not proofphysicalcollectorareaorcellhousing canfallthatway. Propercellredesign/areal loading and lifetimepower/cycle behavior remainuncertainties. Fixedpackcurrent,busbarthermal/cooling design is conservativecomparison,not automatically optimalfuturelightweightdesign. No newachieveddensity or unsupportedstructurallearning. Controlsremainexistingfixedarchitecture,not resolvedvehicle-specificchannelcount. HighpowerFCEVcar/truck/bus andhydrogenrail fixedreferences remainoutsidegenericmobilecellcurve. Legacywholepackprovidersremainforotherconsumers; unrelatedstationary/homebattery andflow/leadacid designs needseparatelyscopednoncellaudit,not silentlyredefinedhere. Comparefixednoncellreference toformerproportionalhardware trajectory at2030/2050; baseline mustbeidentical andstaticnoncellwaste mustnotdecay.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. Chemistry=LFP; geometry proxy=LFP; cellmass=147.58kg, scalablehardware=196.85000000000002kg, assumed cellbaseline=0.16kWh/kg, grossreference=23.612800000000004kWh, fixedcontrolmass=6.668kg. Retained listed hardware material coefficients sum1kg/kg; upstream cell/processing yields are not overwritten. Raw source rounding and cell-specific gaps remain in those providers. Cell-share metadata now refers only to scalable hardware; total installed pack also includes fixed unit-valued control hardware.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 This dataset provides 1 kWh of battery gross capacity (NOT net), using a Li-ion LFP battery. Specific energy density in 2020: (min, mean, max) 0.140, 0.160, 0.190 kWh/kg cell. Battery management (BoP) mass share: 27%. Battery energy density in 2020: 0.10 kWh/kg battery. Battery mass per kWh: 8.6 kg. Lifetime: 3'000-3'500 cycles. Source for parameters: Hasselwander, S.; Meyer, M.; Österle, I. Techno-Economic Analysis of Different Battery Cell Chemistries for the Passenger Vehicle Market. Batteries 2023, 9, 379. https://doi.org/10.3390/batteries9070379.</t>
         </is>
@@ -916,80 +918,92 @@
     <row r="13" spans="1:14" ns3:dyDescent="0.2">
       <c r="A13" t="inlineStr">
         <is>
-          <t>market for battery hardware, Li-ion, LFP, engineering reference</t>
+          <t>market for battery cells, Li-ion, LFP, density-scaled reference</t>
         </is>
       </c>
       <c r="B13" s="7">
-        <f>8.336580159913266</f>
-        <v>8.336580159913266</v>
+        <f>6.249999999999999</f>
+        <v>6.249999999999999</v>
       </c>
       <c r="C13" t="s">
         <v>7</v>
       </c>
-      <c r="D13" t="s">
-        <v>3</v>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
       </c>
       <c r="E13" t="s">
         <v>14</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>battery hardware, Li-ion, LFP, engineering reference</t>
+          <t>market for battery cells, Li-ion, LFP, density-scaled reference</t>
         </is>
       </c>
       <c r="G13">
         <v>5</v>
       </c>
       <c r="H13" s="7">
-        <f>8.336580159913266</f>
-        <v>8.336580159913266</v>
+        <f>6.249999999999999</f>
+        <v>6.249999999999999</v>
       </c>
       <c r="I13" s="7">
-        <f>7.020278029400646</f>
-        <v>7.020278029400646</v>
+        <f>5.263157894736842</f>
+        <v>5.263157894736842</v>
       </c>
       <c r="J13" s="7">
-        <f>9.527520182758018</f>
-        <v>9.527520182758018</v>
+        <f>7.1428571428571415</f>
+        <v>7.1428571428571415</v>
       </c>
     </row>
     <row r="14" spans="1:14" ns3:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>53</v>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>battery fixed noncell hardware, Li-ion, LFP, baseline-kWh reference</t>
+        </is>
       </c>
       <c r="B14" s="7">
-        <f>-8.336580159913266</f>
-        <v>-8.336580159913266</v>
-      </c>
-      <c r="C14" t="s">
-        <v>7</v>
-      </c>
-      <c r="D14" t="s">
-        <v>3</v>
+        <f>1</f>
+        <v>1</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
       </c>
       <c r="E14" t="s">
         <v>14</v>
       </c>
-      <c r="F14" t="s">
-        <v>54</v>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>battery fixed noncell hardware, Li-ion, LFP, baseline-kWh reference</t>
+        </is>
       </c>
       <c r="G14">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H14" s="7">
-        <f>-8.336580159913266</f>
-        <v>-8.336580159913266</v>
+        <f>1</f>
+        <v>1</v>
       </c>
       <c r="I14" s="7">
-        <f>-9.527520182758018</f>
-        <v>-9.527520182758018</v>
+        <f>1</f>
+        <v>1</v>
       </c>
       <c r="J14" s="7">
-        <f>-7.020278029400646</f>
-        <v>-7.020278029400646</v>
-      </c>
-      <c r="K14" t="b">
-        <v>1</v>
+        <f>1</f>
+        <v>1</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="M14" s="7"/>
       <c r="N14" s="7"/>
@@ -1038,7 +1052,9 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. Chemistry=NMC111; geometry proxy=NMC111; cellmass=119.77kg, scalablehardware=158.94000000000003kg, assumed cellbaseline=0.18kWh/kg, grossreference=21.5586kWh, fixedcontrolmass=6.548kg. Retained listed hardware material coefficients sum1kg/kg; upstream cell/processing yields are not overwritten. Raw source rounding and cell-specific gaps remain in those providers. Cell-share metadata now refers only to scalable hardware; total installed pack also includes fixed unit-valued control hardware.
+          <t>APPROVED CELL-ONLY DENSITY LEARNING AND FIXED PACK HARDWARE, issue63, 2026-10-18. Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign. For nine conventionalmobile chemistries,LiS,SIB,LiO2 andthreeASSB references,split active capacitypath into kgcellmanufacture and one fixednoncellreference unit perbaseline nominalkWh. Preserve exactbaselinecell mass,allnoncellmaterials,processservices,controls,transport and totaldisposal. Unitbasis is the original explicitly sizedpack architecture attributed to1nominalkWh,not onephysicalpackper1kWh or a newcapacity. Existingruntime scaling appliesonly kgexchanges of namedcapacitydatasets; thus cellmanufacturekg and matchingusedcellkg followunchangeddensityfactor,while casing,busbars,coolant,packaging and theirdisposal are fixedinsideunitprovider. Existing separatelyunitizedcentral/modulecontrols,oxygenlifecycle,cooling are unchanged. No runtime/YAML/learningcurve edit. Noncellhelper buys originalnoncellprocesses once,plusits originalfraction ofusedbattery treatment;Negative cellwaste moves inside the scalablecellprovider at-1kg/kgcell, so it follows exactly the samecellmass; reuse originalcapacitywasterow forfixedunit without movingworkbookrows. The fixedunit is deterministic; prior signed mass uncertainty is removed from thatrow,while original scaledcell distribution is retained. No negativecredit tocancel a completepack orsecondwholepack disposal. LiS/SIB unfold onlyone-to-one packmarket/module boundary; sourcefinishedpackfreight divided bybaselinecell/noncellmass,cellfreight followscellmass andnoncellfreight fixed,baselinefreight identical. Existing cellrecipe andits internalcollectors/separator/case are retained andscale with cellmass: this is a reference ofsamecellformat atgreatercapacity,not proofphysicalcollectorareaorcellhousing canfallthatway. Propercellredesign/areal loading and lifetimepower/cycle behavior remainuncertainties. Fixedpackcurrent,busbarthermal/cooling design is conservativecomparison,not automatically optimalfuturelightweightdesign. No newachieveddensity or unsupportedstructurallearning. Controlsremainexistingfixedarchitecture,not resolvedvehicle-specificchannelcount. HighpowerFCEVcar/truck/bus andhydrogenrail fixedreferences remainoutsidegenericmobilecellcurve. Legacywholepackprovidersremainforotherconsumers; unrelatedstationary/homebattery andflow/leadacid designs needseparatelyscopednoncellaudit,not silentlyredefinedhere. Comparefixednoncellreference toformerproportionalhardware trajectory at2030/2050; baseline mustbeidentical andstaticnoncellwaste mustnotdecay.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. Chemistry=NMC111; geometry proxy=NMC111; cellmass=119.77kg, scalablehardware=158.94000000000003kg, assumed cellbaseline=0.18kWh/kg, grossreference=21.5586kWh, fixedcontrolmass=6.548kg. Retained listed hardware material coefficients sum1kg/kg; upstream cell/processing yields are not overwritten. Raw source rounding and cell-specific gaps remain in those providers. Cell-share metadata now refers only to scalable hardware; total installed pack also includes fixed unit-valued control hardware.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 This dataset provides 1 kWh of battery gross capacity (NOT net), using a Li-ion NMC111 battery. Specific cell energy density in 2020: (min, mean, max) 0.150, 0.180, 0.190 kWh/kg cell. Battery management (BoP) mass share: 27%. Battery energy density in 2020: 0.13 kWh/kg battery. Battery mass per kWh: 7.6 kg. Lifetime: 1'000-1'800 cycles. Source for parameters: Hasselwander, S.; Meyer, M.; Österle, I. Techno-Economic Analysis of Different Battery Cell Chemistries for the Passenger Vehicle Market. Batteries 2023, 9, 379. https://doi.org/10.3390/batteries9070379.</t>
         </is>
@@ -1152,80 +1168,92 @@
     <row r="26" spans="1:14" ns3:dyDescent="0.2">
       <c r="A26" t="inlineStr">
         <is>
-          <t>market for battery hardware, Li-ion, NMC111, engineering reference</t>
+          <t>market for battery cells, Li-ion, NMC111, density-scaled reference</t>
         </is>
       </c>
       <c r="B26" s="3">
-        <f>7.372463889120817</f>
-        <v>7.372463889120817</v>
+        <f>5.555555555555555</f>
+        <v>5.555555555555555</v>
       </c>
       <c r="C26" t="s">
         <v>7</v>
       </c>
-      <c r="D26" t="s">
-        <v>3</v>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
       </c>
       <c r="E26" t="s">
         <v>14</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>battery hardware, Li-ion, NMC111, engineering reference</t>
+          <t>market for battery cells, Li-ion, NMC111, density-scaled reference</t>
         </is>
       </c>
       <c r="G26">
         <v>5</v>
       </c>
       <c r="H26" s="7">
-        <f>7.372463889120817</f>
-        <v>7.372463889120817</v>
+        <f>5.555555555555555</f>
+        <v>5.555555555555555</v>
       </c>
       <c r="I26" s="7">
-        <f>6.984439473903931</f>
-        <v>6.984439473903931</v>
+        <f>5.263157894736842</f>
+        <v>5.263157894736842</v>
       </c>
       <c r="J26" s="7">
-        <f>9.478882143155333</f>
-        <v>9.478882143155333</v>
+        <f>7.142857142857141</f>
+        <v>7.142857142857141</v>
       </c>
     </row>
     <row r="27" spans="1:14" ns3:dyDescent="0.2">
-      <c r="A27" t="s">
-        <v>53</v>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>battery fixed noncell hardware, Li-ion, NMC111, baseline-kWh reference</t>
+        </is>
       </c>
       <c r="B27" s="3">
-        <f>-7.372463889120817</f>
-        <v>-7.372463889120817</v>
-      </c>
-      <c r="C27" t="s">
-        <v>7</v>
-      </c>
-      <c r="D27" t="s">
-        <v>3</v>
+        <f>1</f>
+        <v>1</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
       </c>
       <c r="E27" t="s">
         <v>14</v>
       </c>
-      <c r="F27" t="s">
-        <v>54</v>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>battery fixed noncell hardware, Li-ion, NMC111, baseline-kWh reference</t>
+        </is>
       </c>
       <c r="G27">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H27" s="7">
-        <f>-7.372463889120817</f>
-        <v>-7.372463889120817</v>
+        <f>1</f>
+        <v>1</v>
       </c>
       <c r="I27" s="7">
-        <f>-9.478882143155333</f>
-        <v>-9.478882143155333</v>
+        <f>1</f>
+        <v>1</v>
       </c>
       <c r="J27" s="7">
-        <f>-6.984439473903931</f>
-        <v>-6.984439473903931</v>
-      </c>
-      <c r="K27" t="b">
-        <v>1</v>
+        <f>1</f>
+        <v>1</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="M27" s="7"/>
       <c r="N27" s="7"/>
@@ -1274,7 +1302,9 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. Chemistry=NMC532; geometry proxy=NMC622; cellmass=108.03kg, scalablehardware=145.74kg, assumed cellbaseline=0.2kWh/kg, grossreference=21.606kWh, fixedcontrolmass=6.538kg. Retained listed hardware material coefficients sum1kg/kg; upstream cell/processing yields are not overwritten. Raw source rounding and cell-specific gaps remain in those providers. Cell-share metadata now refers only to scalable hardware; total installed pack also includes fixed unit-valued control hardware.
+          <t>APPROVED CELL-ONLY DENSITY LEARNING AND FIXED PACK HARDWARE, issue63, 2026-10-18. Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign. For nine conventionalmobile chemistries,LiS,SIB,LiO2 andthreeASSB references,split active capacitypath into kgcellmanufacture and one fixednoncellreference unit perbaseline nominalkWh. Preserve exactbaselinecell mass,allnoncellmaterials,processservices,controls,transport and totaldisposal. Unitbasis is the original explicitly sizedpack architecture attributed to1nominalkWh,not onephysicalpackper1kWh or a newcapacity. Existingruntime scaling appliesonly kgexchanges of namedcapacitydatasets; thus cellmanufacturekg and matchingusedcellkg followunchangeddensityfactor,while casing,busbars,coolant,packaging and theirdisposal are fixedinsideunitprovider. Existing separatelyunitizedcentral/modulecontrols,oxygenlifecycle,cooling are unchanged. No runtime/YAML/learningcurve edit. Noncellhelper buys originalnoncellprocesses once,plusits originalfraction ofusedbattery treatment;Negative cellwaste moves inside the scalablecellprovider at-1kg/kgcell, so it follows exactly the samecellmass; reuse originalcapacitywasterow forfixedunit without movingworkbookrows. The fixedunit is deterministic; prior signed mass uncertainty is removed from thatrow,while original scaledcell distribution is retained. No negativecredit tocancel a completepack orsecondwholepack disposal. LiS/SIB unfold onlyone-to-one packmarket/module boundary; sourcefinishedpackfreight divided bybaselinecell/noncellmass,cellfreight followscellmass andnoncellfreight fixed,baselinefreight identical. Existing cellrecipe andits internalcollectors/separator/case are retained andscale with cellmass: this is a reference ofsamecellformat atgreatercapacity,not proofphysicalcollectorareaorcellhousing canfallthatway. Propercellredesign/areal loading and lifetimepower/cycle behavior remainuncertainties. Fixedpackcurrent,busbarthermal/cooling design is conservativecomparison,not automatically optimalfuturelightweightdesign. No newachieveddensity or unsupportedstructurallearning. Controlsremainexistingfixedarchitecture,not resolvedvehicle-specificchannelcount. HighpowerFCEVcar/truck/bus andhydrogenrail fixedreferences remainoutsidegenericmobilecellcurve. Legacywholepackprovidersremainforotherconsumers; unrelatedstationary/homebattery andflow/leadacid designs needseparatelyscopednoncellaudit,not silentlyredefinedhere. Comparefixednoncellreference toformerproportionalhardware trajectory at2030/2050; baseline mustbeidentical andstaticnoncellwaste mustnotdecay.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. Chemistry=NMC532; geometry proxy=NMC622; cellmass=108.03kg, scalablehardware=145.74kg, assumed cellbaseline=0.2kWh/kg, grossreference=21.606kWh, fixedcontrolmass=6.538kg. Retained listed hardware material coefficients sum1kg/kg; upstream cell/processing yields are not overwritten. Raw source rounding and cell-specific gaps remain in those providers. Cell-share metadata now refers only to scalable hardware; total installed pack also includes fixed unit-valued control hardware.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 This dataset provides 1 kWh of battery gross capacity (NOT net), using a Li-ion NMC532 battery. Specific energy density in 2020: (min, mean, max) 0.170, 0.200, 0.220 kWh/kg cell. Battery management (BoP) mass share: 27%. Battery energy density in 2020: 0.150 kWh/kg battery. Battery mass per kWh: 6.95 kg. Lifetime: 1'000-1'500 cycles. Source for parameters: Hasselwander, S.; Meyer, M.; Österle, I. Techno-Economic Analysis of Different Battery Cell Chemistries for the Passenger Vehicle Market. Batteries 2023, 9, 379. https://doi.org/10.3390/batteries9070379.</t>
         </is>
@@ -1388,80 +1418,92 @@
     <row r="39" spans="1:14" ns3:dyDescent="0.2">
       <c r="A39" t="inlineStr">
         <is>
-          <t>market for battery hardware, Li-ion, NMC532, engineering reference</t>
+          <t>market for battery cells, Li-ion, NMC532, density-scaled reference</t>
         </is>
       </c>
       <c r="B39" s="3">
-        <f>6.7453485143015826</f>
-        <v>6.7453485143015826</v>
+        <f>4.999999999999999</f>
+        <v>4.999999999999999</v>
       </c>
       <c r="C39" t="s">
         <v>7</v>
       </c>
-      <c r="D39" t="s">
-        <v>3</v>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
       </c>
       <c r="E39" t="s">
         <v>14</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>battery hardware, Li-ion, NMC532, engineering reference</t>
+          <t>market for battery cells, Li-ion, NMC532, density-scaled reference</t>
         </is>
       </c>
       <c r="G39">
         <v>5</v>
       </c>
       <c r="H39" s="7">
-        <f>6.7453485143015826</f>
-        <v>6.7453485143015826</v>
+        <f>4.999999999999999</f>
+        <v>4.999999999999999</v>
       </c>
       <c r="I39" s="3">
-        <f>6.132135013001438</f>
-        <v>6.132135013001438</v>
+        <f>4.545454545454544</f>
+        <v>4.545454545454544</v>
       </c>
       <c r="J39" s="3">
-        <f>7.9357041344724495</f>
-        <v>7.9357041344724495</v>
+        <f>5.882352941176469</f>
+        <v>5.882352941176469</v>
       </c>
     </row>
     <row r="40" spans="1:14" ns3:dyDescent="0.2">
-      <c r="A40" t="s">
-        <v>53</v>
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>battery fixed noncell hardware, Li-ion, NMC532, baseline-kWh reference</t>
+        </is>
       </c>
       <c r="B40" s="3">
-        <f>-6.7453485143015826</f>
-        <v>-6.7453485143015826</v>
-      </c>
-      <c r="C40" t="s">
-        <v>7</v>
-      </c>
-      <c r="D40" t="s">
-        <v>3</v>
+        <f>1</f>
+        <v>1</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
       </c>
       <c r="E40" t="s">
         <v>14</v>
       </c>
-      <c r="F40" t="s">
-        <v>54</v>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>battery fixed noncell hardware, Li-ion, NMC532, baseline-kWh reference</t>
+        </is>
       </c>
       <c r="G40">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H40" s="7">
-        <f>-6.7453485143015826</f>
-        <v>-6.7453485143015826</v>
+        <f>1</f>
+        <v>1</v>
       </c>
       <c r="I40" s="3">
-        <f>-7.9357041344724495</f>
-        <v>-7.9357041344724495</v>
+        <f>1</f>
+        <v>1</v>
       </c>
       <c r="J40" s="3">
-        <f>-6.132135013001438</f>
-        <v>-6.132135013001438</v>
-      </c>
-      <c r="K40" t="b">
-        <v>1</v>
+        <f>1</f>
+        <v>1</v>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
@@ -1510,7 +1552,9 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. Chemistry=NMC622; geometry proxy=NMC622; cellmass=108.03kg, scalablehardware=145.74kg, assumed cellbaseline=0.24kWh/kg, grossreference=25.9272kWh, fixedcontrolmass=6.538kg. Retained listed hardware material coefficients sum1kg/kg; upstream cell/processing yields are not overwritten. Raw source rounding and cell-specific gaps remain in those providers. Cell-share metadata now refers only to scalable hardware; total installed pack also includes fixed unit-valued control hardware.
+          <t>APPROVED CELL-ONLY DENSITY LEARNING AND FIXED PACK HARDWARE, issue63, 2026-10-18. Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign. For nine conventionalmobile chemistries,LiS,SIB,LiO2 andthreeASSB references,split active capacitypath into kgcellmanufacture and one fixednoncellreference unit perbaseline nominalkWh. Preserve exactbaselinecell mass,allnoncellmaterials,processservices,controls,transport and totaldisposal. Unitbasis is the original explicitly sizedpack architecture attributed to1nominalkWh,not onephysicalpackper1kWh or a newcapacity. Existingruntime scaling appliesonly kgexchanges of namedcapacitydatasets; thus cellmanufacturekg and matchingusedcellkg followunchangeddensityfactor,while casing,busbars,coolant,packaging and theirdisposal are fixedinsideunitprovider. Existing separatelyunitizedcentral/modulecontrols,oxygenlifecycle,cooling are unchanged. No runtime/YAML/learningcurve edit. Noncellhelper buys originalnoncellprocesses once,plusits originalfraction ofusedbattery treatment;Negative cellwaste moves inside the scalablecellprovider at-1kg/kgcell, so it follows exactly the samecellmass; reuse originalcapacitywasterow forfixedunit without movingworkbookrows. The fixedunit is deterministic; prior signed mass uncertainty is removed from thatrow,while original scaledcell distribution is retained. No negativecredit tocancel a completepack orsecondwholepack disposal. LiS/SIB unfold onlyone-to-one packmarket/module boundary; sourcefinishedpackfreight divided bybaselinecell/noncellmass,cellfreight followscellmass andnoncellfreight fixed,baselinefreight identical. Existing cellrecipe andits internalcollectors/separator/case are retained andscale with cellmass: this is a reference ofsamecellformat atgreatercapacity,not proofphysicalcollectorareaorcellhousing canfallthatway. Propercellredesign/areal loading and lifetimepower/cycle behavior remainuncertainties. Fixedpackcurrent,busbarthermal/cooling design is conservativecomparison,not automatically optimalfuturelightweightdesign. No newachieveddensity or unsupportedstructurallearning. Controlsremainexistingfixedarchitecture,not resolvedvehicle-specificchannelcount. HighpowerFCEVcar/truck/bus andhydrogenrail fixedreferences remainoutsidegenericmobilecellcurve. Legacywholepackprovidersremainforotherconsumers; unrelatedstationary/homebattery andflow/leadacid designs needseparatelyscopednoncellaudit,not silentlyredefinedhere. Comparefixednoncellreference toformerproportionalhardware trajectory at2030/2050; baseline mustbeidentical andstaticnoncellwaste mustnotdecay.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. Chemistry=NMC622; geometry proxy=NMC622; cellmass=108.03kg, scalablehardware=145.74kg, assumed cellbaseline=0.24kWh/kg, grossreference=25.9272kWh, fixedcontrolmass=6.538kg. Retained listed hardware material coefficients sum1kg/kg; upstream cell/processing yields are not overwritten. Raw source rounding and cell-specific gaps remain in those providers. Cell-share metadata now refers only to scalable hardware; total installed pack also includes fixed unit-valued control hardware.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 This dataset provides 1 kWh of battery gross capacity (NOT net), using a Li-ion NMC622 battery. Specific energy density in 2020: (min, mean, max) 0.200, 0.240, 0.280 kWh/kg cell. Battery management (BoP) mass share: 27%. Battery energy density in 2020: 0.180 kWh/kg battery. Battery mass per kWh: 6.85 kg. Lifetime: 1'000-1'500 cycles. Source for parameters: Hasselwander, S.; Meyer, M.; Österle, I. Techno-Economic Analysis of Different Battery Cell Chemistries for the Passenger Vehicle Market. Batteries 2023, 9, 379. https://doi.org/10.3390/batteries9070379.</t>
         </is>
@@ -1626,80 +1670,92 @@
     <row r="52" spans="1:14" ns3:dyDescent="0.2">
       <c r="A52" t="inlineStr">
         <is>
-          <t>market for battery hardware, Li-ion, NMC622, engineering reference</t>
+          <t>market for battery cells, Li-ion, NMC622, density-scaled reference</t>
         </is>
       </c>
       <c r="B52" s="3">
-        <f>5.621123761917986</f>
-        <v>5.621123761917986</v>
+        <f>4.166666666666667</f>
+        <v>4.166666666666667</v>
       </c>
       <c r="C52" t="s">
         <v>7</v>
       </c>
-      <c r="D52" t="s">
-        <v>3</v>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
       </c>
       <c r="E52" t="s">
         <v>14</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>battery hardware, Li-ion, NMC622, engineering reference</t>
+          <t>market for battery cells, Li-ion, NMC622, density-scaled reference</t>
         </is>
       </c>
       <c r="G52">
         <v>5</v>
       </c>
       <c r="H52" s="7">
-        <f>5.621123761917986</f>
-        <v>5.621123761917986</v>
+        <f>4.166666666666667</f>
+        <v>4.166666666666667</v>
       </c>
       <c r="I52" s="3">
-        <f>4.818106081643988</f>
-        <v>4.818106081643988</v>
+        <f>3.571428571428571</f>
+        <v>3.571428571428571</v>
       </c>
       <c r="J52" s="3">
-        <f>6.745348514301584</f>
-        <v>6.745348514301584</v>
+        <f>5.000000000000001</f>
+        <v>5.000000000000001</v>
       </c>
     </row>
     <row r="53" spans="1:14" ns3:dyDescent="0.2">
-      <c r="A53" t="s">
-        <v>53</v>
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>battery fixed noncell hardware, Li-ion, NMC622, baseline-kWh reference</t>
+        </is>
       </c>
       <c r="B53" s="3">
-        <f>-5.621123761917986</f>
-        <v>-5.621123761917986</v>
-      </c>
-      <c r="C53" t="s">
-        <v>7</v>
-      </c>
-      <c r="D53" t="s">
-        <v>3</v>
+        <f>1</f>
+        <v>1</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
       </c>
       <c r="E53" t="s">
         <v>14</v>
       </c>
-      <c r="F53" t="s">
-        <v>54</v>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>battery fixed noncell hardware, Li-ion, NMC622, baseline-kWh reference</t>
+        </is>
       </c>
       <c r="G53">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H53" s="7">
-        <f>-5.621123761917986</f>
-        <v>-5.621123761917986</v>
+        <f>1</f>
+        <v>1</v>
       </c>
       <c r="I53" s="3">
-        <f>-6.745348514301584</f>
-        <v>-6.745348514301584</v>
+        <f>1</f>
+        <v>1</v>
       </c>
       <c r="J53" s="3">
-        <f>-4.818106081643988</f>
-        <v>-4.818106081643988</v>
-      </c>
-      <c r="K53" t="b">
-        <v>1</v>
+        <f>1</f>
+        <v>1</v>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="M53" s="3"/>
       <c r="N53" s="3"/>
@@ -1748,7 +1804,9 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. Chemistry=NMC811; geometry proxy=NMC811; cellmass=112.37kg, scalablehardware=151.63000000000002kg, assumed cellbaseline=0.28kWh/kg, grossreference=31.463600000000003kWh, fixedcontrolmass=6.568kg. Retained listed hardware material coefficients sum1kg/kg; upstream cell/processing yields are not overwritten. Raw source rounding and cell-specific gaps remain in those providers. Cell-share metadata now refers only to scalable hardware; total installed pack also includes fixed unit-valued control hardware.
+          <t>APPROVED CELL-ONLY DENSITY LEARNING AND FIXED PACK HARDWARE, issue63, 2026-10-18. Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign. For nine conventionalmobile chemistries,LiS,SIB,LiO2 andthreeASSB references,split active capacitypath into kgcellmanufacture and one fixednoncellreference unit perbaseline nominalkWh. Preserve exactbaselinecell mass,allnoncellmaterials,processservices,controls,transport and totaldisposal. Unitbasis is the original explicitly sizedpack architecture attributed to1nominalkWh,not onephysicalpackper1kWh or a newcapacity. Existingruntime scaling appliesonly kgexchanges of namedcapacitydatasets; thus cellmanufacturekg and matchingusedcellkg followunchangeddensityfactor,while casing,busbars,coolant,packaging and theirdisposal are fixedinsideunitprovider. Existing separatelyunitizedcentral/modulecontrols,oxygenlifecycle,cooling are unchanged. No runtime/YAML/learningcurve edit. Noncellhelper buys originalnoncellprocesses once,plusits originalfraction ofusedbattery treatment;Negative cellwaste moves inside the scalablecellprovider at-1kg/kgcell, so it follows exactly the samecellmass; reuse originalcapacitywasterow forfixedunit without movingworkbookrows. The fixedunit is deterministic; prior signed mass uncertainty is removed from thatrow,while original scaledcell distribution is retained. No negativecredit tocancel a completepack orsecondwholepack disposal. LiS/SIB unfold onlyone-to-one packmarket/module boundary; sourcefinishedpackfreight divided bybaselinecell/noncellmass,cellfreight followscellmass andnoncellfreight fixed,baselinefreight identical. Existing cellrecipe andits internalcollectors/separator/case are retained andscale with cellmass: this is a reference ofsamecellformat atgreatercapacity,not proofphysicalcollectorareaorcellhousing canfallthatway. Propercellredesign/areal loading and lifetimepower/cycle behavior remainuncertainties. Fixedpackcurrent,busbarthermal/cooling design is conservativecomparison,not automatically optimalfuturelightweightdesign. No newachieveddensity or unsupportedstructurallearning. Controlsremainexistingfixedarchitecture,not resolvedvehicle-specificchannelcount. HighpowerFCEVcar/truck/bus andhydrogenrail fixedreferences remainoutsidegenericmobilecellcurve. Legacywholepackprovidersremainforotherconsumers; unrelatedstationary/homebattery andflow/leadacid designs needseparatelyscopednoncellaudit,not silentlyredefinedhere. Comparefixednoncellreference toformerproportionalhardware trajectory at2030/2050; baseline mustbeidentical andstaticnoncellwaste mustnotdecay.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. Chemistry=NMC811; geometry proxy=NMC811; cellmass=112.37kg, scalablehardware=151.63000000000002kg, assumed cellbaseline=0.28kWh/kg, grossreference=31.463600000000003kWh, fixedcontrolmass=6.568kg. Retained listed hardware material coefficients sum1kg/kg; upstream cell/processing yields are not overwritten. Raw source rounding and cell-specific gaps remain in those providers. Cell-share metadata now refers only to scalable hardware; total installed pack also includes fixed unit-valued control hardware.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 This dataset provides 1 kWh of battery gross capacity (not NET), using a Li-ion NMC811 battery. Specific energy density in 2020: (min, mean, max) 0.240, 0.280, 0.340 kWh/kg cell. Battery management (BoP) mass share: 29%. Battery energy density in 2020: 0.20 kWh/kg battery. Battery mass per kWh: 5.03 kg. Lifetime: 1'000-1'200 cycles. Source for parameters: Hasselwander, S.; Meyer, M.; Österle, I. Techno-Economic Analysis of Different Battery Cell Chemistries for the Passenger Vehicle Market. Batteries 2023, 9, 379. https://doi.org/10.3390/batteries9070379.</t>
         </is>
@@ -1865,80 +1923,92 @@
     <row r="65" spans="1:14" ns3:dyDescent="0.2">
       <c r="A65" t="inlineStr">
         <is>
-          <t>market for battery hardware, Li-ion, NMC811, engineering reference</t>
+          <t>market for battery cells, Li-ion, NMC811, density-scaled reference</t>
         </is>
       </c>
       <c r="B65" s="3">
-        <f>4.819219669713574</f>
-        <v>4.819219669713574</v>
+        <f>3.571428571428571</f>
+        <v>3.571428571428571</v>
       </c>
       <c r="C65" t="s">
         <v>7</v>
       </c>
-      <c r="D65" t="s">
-        <v>3</v>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
       </c>
       <c r="E65" t="s">
         <v>14</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>battery hardware, Li-ion, NMC811, engineering reference</t>
+          <t>market for battery cells, Li-ion, NMC811, density-scaled reference</t>
         </is>
       </c>
       <c r="G65">
         <v>5</v>
       </c>
       <c r="H65" s="7">
-        <f>4.819219669713574</f>
-        <v>4.819219669713574</v>
+        <f>3.571428571428571</f>
+        <v>3.571428571428571</v>
       </c>
       <c r="I65" s="3">
-        <f>3.96876913976412</f>
-        <v>3.96876913976412</v>
+        <f>2.9411764705882355</f>
+        <v>2.9411764705882355</v>
       </c>
       <c r="J65" s="3">
-        <f>5.622422947999169</f>
-        <v>5.622422947999169</v>
+        <f>4.166666666666666</f>
+        <v>4.166666666666666</v>
       </c>
     </row>
     <row r="66" spans="1:14" ns3:dyDescent="0.2">
-      <c r="A66" t="s">
-        <v>53</v>
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>battery fixed noncell hardware, Li-ion, NMC811, baseline-kWh reference</t>
+        </is>
       </c>
       <c r="B66" s="3">
-        <f>-4.819219669713574</f>
-        <v>-4.819219669713574</v>
-      </c>
-      <c r="C66" t="s">
-        <v>7</v>
-      </c>
-      <c r="D66" t="s">
-        <v>3</v>
+        <f>1</f>
+        <v>1</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
       </c>
       <c r="E66" t="s">
         <v>14</v>
       </c>
-      <c r="F66" t="s">
-        <v>54</v>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>battery fixed noncell hardware, Li-ion, NMC811, baseline-kWh reference</t>
+        </is>
       </c>
       <c r="G66">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H66" s="7">
-        <f>-4.819219669713574</f>
-        <v>-4.819219669713574</v>
+        <f>1</f>
+        <v>1</v>
       </c>
       <c r="I66" s="3">
-        <f>-5.622422947999169</f>
-        <v>-5.622422947999169</v>
+        <f>1</f>
+        <v>1</v>
       </c>
       <c r="J66" s="3">
-        <f>-3.96876913976412</f>
-        <v>-3.96876913976412</v>
-      </c>
-      <c r="K66" t="b">
-        <v>1</v>
+        <f>1</f>
+        <v>1</v>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="M66" s="3"/>
       <c r="N66" s="3"/>
@@ -1987,7 +2057,9 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. Chemistry=NMC955; geometry proxy=NMC622; cellmass=108.03kg, scalablehardware=145.74kg, assumed cellbaseline=0.34kWh/kg, grossreference=36.7302kWh, fixedcontrolmass=6.538kg. Retained listed hardware material coefficients sum1kg/kg; upstream cell/processing yields are not overwritten. Raw source rounding and cell-specific gaps remain in those providers. Cell-share metadata now refers only to scalable hardware; total installed pack also includes fixed unit-valued control hardware.
+          <t>APPROVED CELL-ONLY DENSITY LEARNING AND FIXED PACK HARDWARE, issue63, 2026-10-18. Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign. For nine conventionalmobile chemistries,LiS,SIB,LiO2 andthreeASSB references,split active capacitypath into kgcellmanufacture and one fixednoncellreference unit perbaseline nominalkWh. Preserve exactbaselinecell mass,allnoncellmaterials,processservices,controls,transport and totaldisposal. Unitbasis is the original explicitly sizedpack architecture attributed to1nominalkWh,not onephysicalpackper1kWh or a newcapacity. Existingruntime scaling appliesonly kgexchanges of namedcapacitydatasets; thus cellmanufacturekg and matchingusedcellkg followunchangeddensityfactor,while casing,busbars,coolant,packaging and theirdisposal are fixedinsideunitprovider. Existing separatelyunitizedcentral/modulecontrols,oxygenlifecycle,cooling are unchanged. No runtime/YAML/learningcurve edit. Noncellhelper buys originalnoncellprocesses once,plusits originalfraction ofusedbattery treatment;Negative cellwaste moves inside the scalablecellprovider at-1kg/kgcell, so it follows exactly the samecellmass; reuse originalcapacitywasterow forfixedunit without movingworkbookrows. The fixedunit is deterministic; prior signed mass uncertainty is removed from thatrow,while original scaledcell distribution is retained. No negativecredit tocancel a completepack orsecondwholepack disposal. LiS/SIB unfold onlyone-to-one packmarket/module boundary; sourcefinishedpackfreight divided bybaselinecell/noncellmass,cellfreight followscellmass andnoncellfreight fixed,baselinefreight identical. Existing cellrecipe andits internalcollectors/separator/case are retained andscale with cellmass: this is a reference ofsamecellformat atgreatercapacity,not proofphysicalcollectorareaorcellhousing canfallthatway. Propercellredesign/areal loading and lifetimepower/cycle behavior remainuncertainties. Fixedpackcurrent,busbarthermal/cooling design is conservativecomparison,not automatically optimalfuturelightweightdesign. No newachieveddensity or unsupportedstructurallearning. Controlsremainexistingfixedarchitecture,not resolvedvehicle-specificchannelcount. HighpowerFCEVcar/truck/bus andhydrogenrail fixedreferences remainoutsidegenericmobilecellcurve. Legacywholepackprovidersremainforotherconsumers; unrelatedstationary/homebattery andflow/leadacid designs needseparatelyscopednoncellaudit,not silentlyredefinedhere. Comparefixednoncellreference toformerproportionalhardware trajectory at2030/2050; baseline mustbeidentical andstaticnoncellwaste mustnotdecay.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. Chemistry=NMC955; geometry proxy=NMC622; cellmass=108.03kg, scalablehardware=145.74kg, assumed cellbaseline=0.34kWh/kg, grossreference=36.7302kWh, fixedcontrolmass=6.538kg. Retained listed hardware material coefficients sum1kg/kg; upstream cell/processing yields are not overwritten. Raw source rounding and cell-specific gaps remain in those providers. Cell-share metadata now refers only to scalable hardware; total installed pack also includes fixed unit-valued control hardware.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 Provides 1 kWh gross battery capacity using a Li-ion NMC955 pack. The complete-pack manufacturing recipe in lci-batteries-NMC955-LTO.xlsx contains 0.72591 kg cells per kg pack (72.591% cells, 27.409% other pack components). Use this manufactured cell fraction instead of the former generic 71% assumption. At the retained 2020 cell energy densities (minimum/mean/maximum) of 0.300/0.340/0.380 kWh per kg cell, pack mass is 1/(cell density * cell mass share): mean 4.051709537805285 kg/kWh, range 3.625213796983677 to 4.591937476179324 kg/kWh. Manufacturing and end of life use equal pack mass; signed disposal bounds mirror the manufacturing bounds. Source density/lifetime parameters: Hasselwander et al. (2023), https://doi.org/10.3390/batteries9070379. The source lifetime of 1000-1500 cycles and the existing future density trajectory remain modelling assumptions. Matching cell fraction is an allocation correction, not validation of practical cell performance. Rebuild scenario databases to apply.</t>
         </is>
@@ -2101,80 +2173,92 @@
     <row r="78" spans="1:14" ns3:dyDescent="0.2">
       <c r="A78" t="inlineStr">
         <is>
-          <t>market for battery hardware, Li-ion, NMC955, engineering reference</t>
+          <t>market for battery cells, Li-ion, NMC955, density-scaled reference</t>
         </is>
       </c>
       <c r="B78" s="3">
-        <f>3.967852067236225</f>
-        <v>3.967852067236225</v>
+        <f>2.941176470588235</f>
+        <v>2.941176470588235</v>
       </c>
       <c r="C78" t="s">
         <v>7</v>
       </c>
-      <c r="D78" t="s">
-        <v>3</v>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
       </c>
       <c r="E78" t="s">
         <v>14</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>battery hardware, Li-ion, NMC955, engineering reference</t>
+          <t>market for battery cells, Li-ion, NMC955, density-scaled reference</t>
         </is>
       </c>
       <c r="G78">
         <v>5</v>
       </c>
       <c r="H78" s="7">
-        <f>3.967852067236225</f>
-        <v>3.967852067236225</v>
+        <f>2.941176470588235</f>
+        <v>2.941176470588235</v>
       </c>
       <c r="I78" s="3">
-        <f>3.550183428579781</f>
-        <v>3.550183428579781</v>
+        <f>2.6315789473684212</f>
+        <v>2.6315789473684212</v>
       </c>
       <c r="J78" s="3">
-        <f>4.496899009534389</f>
-        <v>4.496899009534389</v>
+        <f>3.333333333333334</f>
+        <v>3.333333333333334</v>
       </c>
     </row>
     <row r="79" spans="1:14" ns3:dyDescent="0.2">
-      <c r="A79" t="s">
-        <v>53</v>
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>battery fixed noncell hardware, Li-ion, NMC955, baseline-kWh reference</t>
+        </is>
       </c>
       <c r="B79" s="3">
-        <f>-3.967852067236225</f>
-        <v>-3.967852067236225</v>
-      </c>
-      <c r="C79" t="s">
-        <v>7</v>
-      </c>
-      <c r="D79" t="s">
-        <v>3</v>
+        <f>1</f>
+        <v>1</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
       </c>
       <c r="E79" t="s">
         <v>14</v>
       </c>
-      <c r="F79" t="s">
-        <v>54</v>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>battery fixed noncell hardware, Li-ion, NMC955, baseline-kWh reference</t>
+        </is>
       </c>
       <c r="G79">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H79" s="7">
-        <f>-3.967852067236225</f>
-        <v>-3.967852067236225</v>
+        <f>1</f>
+        <v>1</v>
       </c>
       <c r="I79" s="3">
-        <f>-4.496899009534389</f>
-        <v>-4.496899009534389</v>
+        <f>1</f>
+        <v>1</v>
       </c>
       <c r="J79" s="3">
-        <f>-3.550183428579781</f>
-        <v>-3.550183428579781</v>
-      </c>
-      <c r="K79" t="b">
-        <v>1</v>
+        <f>1</f>
+        <v>1</v>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="M79" s="3"/>
       <c r="N79" s="3"/>
@@ -2223,7 +2307,9 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. Chemistry=NCA; geometry proxy=NCA; cellmass=104.96kg, scalablehardware=142.36999999999998kg, assumed cellbaseline=0.28kWh/kg, grossreference=29.3888kWh, fixedcontrolmass=6.548kg. Retained listed hardware material coefficients sum1kg/kg; upstream cell/processing yields are not overwritten. Raw source rounding and cell-specific gaps remain in those providers. Cell-share metadata now refers only to scalable hardware; total installed pack also includes fixed unit-valued control hardware.
+          <t>APPROVED CELL-ONLY DENSITY LEARNING AND FIXED PACK HARDWARE, issue63, 2026-10-18. Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign. For nine conventionalmobile chemistries,LiS,SIB,LiO2 andthreeASSB references,split active capacitypath into kgcellmanufacture and one fixednoncellreference unit perbaseline nominalkWh. Preserve exactbaselinecell mass,allnoncellmaterials,processservices,controls,transport and totaldisposal. Unitbasis is the original explicitly sizedpack architecture attributed to1nominalkWh,not onephysicalpackper1kWh or a newcapacity. Existingruntime scaling appliesonly kgexchanges of namedcapacitydatasets; thus cellmanufacturekg and matchingusedcellkg followunchangeddensityfactor,while casing,busbars,coolant,packaging and theirdisposal are fixedinsideunitprovider. Existing separatelyunitizedcentral/modulecontrols,oxygenlifecycle,cooling are unchanged. No runtime/YAML/learningcurve edit. Noncellhelper buys originalnoncellprocesses once,plusits originalfraction ofusedbattery treatment;Negative cellwaste moves inside the scalablecellprovider at-1kg/kgcell, so it follows exactly the samecellmass; reuse originalcapacitywasterow forfixedunit without movingworkbookrows. The fixedunit is deterministic; prior signed mass uncertainty is removed from thatrow,while original scaledcell distribution is retained. No negativecredit tocancel a completepack orsecondwholepack disposal. LiS/SIB unfold onlyone-to-one packmarket/module boundary; sourcefinishedpackfreight divided bybaselinecell/noncellmass,cellfreight followscellmass andnoncellfreight fixed,baselinefreight identical. Existing cellrecipe andits internalcollectors/separator/case are retained andscale with cellmass: this is a reference ofsamecellformat atgreatercapacity,not proofphysicalcollectorareaorcellhousing canfallthatway. Propercellredesign/areal loading and lifetimepower/cycle behavior remainuncertainties. Fixedpackcurrent,busbarthermal/cooling design is conservativecomparison,not automatically optimalfuturelightweightdesign. No newachieveddensity or unsupportedstructurallearning. Controlsremainexistingfixedarchitecture,not resolvedvehicle-specificchannelcount. HighpowerFCEVcar/truck/bus andhydrogenrail fixedreferences remainoutsidegenericmobilecellcurve. Legacywholepackprovidersremainforotherconsumers; unrelatedstationary/homebattery andflow/leadacid designs needseparatelyscopednoncellaudit,not silentlyredefinedhere. Comparefixednoncellreference toformerproportionalhardware trajectory at2030/2050; baseline mustbeidentical andstaticnoncellwaste mustnotdecay.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. Chemistry=NCA; geometry proxy=NCA; cellmass=104.96kg, scalablehardware=142.36999999999998kg, assumed cellbaseline=0.28kWh/kg, grossreference=29.3888kWh, fixedcontrolmass=6.548kg. Retained listed hardware material coefficients sum1kg/kg; upstream cell/processing yields are not overwritten. Raw source rounding and cell-specific gaps remain in those providers. Cell-share metadata now refers only to scalable hardware; total installed pack also includes fixed unit-valued control hardware.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 This dataset provides 1 kWh of battery gross capacity (not NET), using a Li-ion NCA battery. Specific energy density in 2020: (min, mean, max) 0.240, 0.280, 0.340 kWh/kg cell. Battery management (BoP) mass share: 29%. Battery energy density in 2020: 0.20 kWh/kg battery. Battery mass per kWh: 5.03 kg. Lifetime: 800-1'600 cycles. Source for parameters: Hasselwander, S.; Meyer, M.; Österle, I. Techno-Economic Analysis of Different Battery Cell Chemistries for the Passenger Vehicle Market. Batteries 2023, 9, 379. https://doi.org/10.3390/batteries9070379.</t>
         </is>
@@ -2337,80 +2423,92 @@
     <row r="91" spans="1:14" ns3:dyDescent="0.2">
       <c r="A91" t="inlineStr">
         <is>
-          <t>market for battery hardware, Li-ion, NCA, engineering reference</t>
+          <t>market for battery cells, Li-ion, NCA, density-scaled reference</t>
         </is>
       </c>
       <c r="B91" s="3">
-        <f>4.844362478222996</f>
-        <v>4.844362478222996</v>
+        <f>3.571428571428571</f>
+        <v>3.571428571428571</v>
       </c>
       <c r="C91" t="s">
         <v>7</v>
       </c>
-      <c r="D91" t="s">
-        <v>3</v>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
       </c>
       <c r="E91" t="s">
         <v>14</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>battery hardware, Li-ion, NCA, engineering reference</t>
+          <t>market for battery cells, Li-ion, NCA, density-scaled reference</t>
         </is>
       </c>
       <c r="G91">
         <v>5</v>
       </c>
       <c r="H91" s="7">
-        <f>4.844362478222996</f>
-        <v>4.844362478222996</v>
+        <f>3.571428571428571</f>
+        <v>3.571428571428571</v>
       </c>
       <c r="I91" s="3">
-        <f>3.989474982065997</f>
-        <v>3.989474982065997</v>
+        <f>2.9411764705882355</f>
+        <v>2.9411764705882355</v>
       </c>
       <c r="J91" s="3">
-        <f>5.651756224593496</f>
-        <v>5.651756224593496</v>
+        <f>4.166666666666667</f>
+        <v>4.166666666666667</v>
       </c>
     </row>
     <row r="92" spans="1:14" ns3:dyDescent="0.2">
-      <c r="A92" t="s">
-        <v>53</v>
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>battery fixed noncell hardware, Li-ion, NCA, baseline-kWh reference</t>
+        </is>
       </c>
       <c r="B92" s="3">
-        <f>-4.844362478222996</f>
-        <v>-4.844362478222996</v>
-      </c>
-      <c r="C92" t="s">
-        <v>7</v>
-      </c>
-      <c r="D92" t="s">
-        <v>3</v>
+        <f>1</f>
+        <v>1</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
       </c>
       <c r="E92" t="s">
         <v>14</v>
       </c>
-      <c r="F92" t="s">
-        <v>54</v>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>battery fixed noncell hardware, Li-ion, NCA, baseline-kWh reference</t>
+        </is>
       </c>
       <c r="G92">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H92" s="7">
-        <f>-4.844362478222996</f>
-        <v>-4.844362478222996</v>
+        <f>1</f>
+        <v>1</v>
       </c>
       <c r="I92" s="3">
-        <f>-5.651756224593496</f>
-        <v>-5.651756224593496</v>
+        <f>1</f>
+        <v>1</v>
       </c>
       <c r="J92" s="3">
-        <f>-3.989474982065997</f>
-        <v>-3.989474982065997</v>
-      </c>
-      <c r="K92" t="b">
-        <v>1</v>
+        <f>1</f>
+        <v>1</v>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="M92" s="3"/>
       <c r="N92" s="3"/>
@@ -2459,7 +2557,9 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>APPROVED SOURCE-CONSISTENT NCA/LTO CELL AND CAPACITY REFERENCE,item22,2026-10-18. Schmidt etal2019 DOI10.1021/acs.est.8b05313, Supporting Data es8b05313_si_002.zip, NCA LTO battery import.xlsx summary!H54=16.040428932169362kg/kWh dry cell components excluding pouch, H56=.5181296021158341kg/kWh pouch; H60=1000/(H54+H56)=60.39173022998696Wh/kg-cell. This is the source harmonized historical NCA/LTO engineering design, not modern fleet validation. The current capacity reference85Wh/kg is inconsistent with that recipe. Restore seven component fractions to source per-kWh masses divided by16.558558534285197kg/kWh; the old six non-pouch fractions were multiplied by rounded.060kWh/kg and the pouch filled the remainder, rather than using the source pouch mass. This restores source component ratios and a1kg component-sum cell. Preserve all previously corrected upstream electrode/graphite/collector recipes and supplier identities, cell water/electricity/heat proxies, reference pack cellmass108.03kg and non-cell geometry37.71kg (NMC622 geometry proxy), controls/protection6.538kg per reference and all vehicle energy/cycle/replacement assumptions. Factory utilities and upstream manufacturing yields remain inherited proxies rather than a claim of complete original-source reproduction. Use exact source cell energy.060391730229986965kWh/kg in the capacity market. Scalable hardware145.74kg now represents6.524118616745492grosskWh, hence22.338649641643293kg/kWh instead of15.871408268944903. Pair identical negative waste mass and signed uncertainty endpoints; retain prior engineering75-125percent mass range, without claiming source statistical confidence. Fixed-unit controls remain unchanged per reference pack, but dose becomes1/6.524118616745492unit/kWh to share the same capacity basis. No future LTO improvement is assumed; existing2020/2050 density-factor ratio is1 even though its YAML absolute values are historical50Wh/kg. No runtime/YAML changes. Original standalone75/25 LTO battery market remains a separate legacy assembly reference, while capacity markets buy the explicit hardware/central-control reference. Source pack48.6049Wh/kg excludes BMS/cooling and is distinct from the adopted cell-specific60.3917Wh/kg. Remaining material-grade, utility, thermal rating, life and future-design limitations remain explicit.
+          <t>APPROVED CELL-ONLY DENSITY LEARNING AND FIXED PACK HARDWARE, issue63, 2026-10-18. Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign. For nine conventionalmobile chemistries,LiS,SIB,LiO2 andthreeASSB references,split active capacitypath into kgcellmanufacture and one fixednoncellreference unit perbaseline nominalkWh. Preserve exactbaselinecell mass,allnoncellmaterials,processservices,controls,transport and totaldisposal. Unitbasis is the original explicitly sizedpack architecture attributed to1nominalkWh,not onephysicalpackper1kWh or a newcapacity. Existingruntime scaling appliesonly kgexchanges of namedcapacitydatasets; thus cellmanufacturekg and matchingusedcellkg followunchangeddensityfactor,while casing,busbars,coolant,packaging and theirdisposal are fixedinsideunitprovider. Existing separatelyunitizedcentral/modulecontrols,oxygenlifecycle,cooling are unchanged. No runtime/YAML/learningcurve edit. Noncellhelper buys originalnoncellprocesses once,plusits originalfraction ofusedbattery treatment;Negative cellwaste moves inside the scalablecellprovider at-1kg/kgcell, so it follows exactly the samecellmass; reuse originalcapacitywasterow forfixedunit without movingworkbookrows. The fixedunit is deterministic; prior signed mass uncertainty is removed from thatrow,while original scaledcell distribution is retained. No negativecredit tocancel a completepack orsecondwholepack disposal. LiS/SIB unfold onlyone-to-one packmarket/module boundary; sourcefinishedpackfreight divided bybaselinecell/noncellmass,cellfreight followscellmass andnoncellfreight fixed,baselinefreight identical. Existing cellrecipe andits internalcollectors/separator/case are retained andscale with cellmass: this is a reference ofsamecellformat atgreatercapacity,not proofphysicalcollectorareaorcellhousing canfallthatway. Propercellredesign/areal loading and lifetimepower/cycle behavior remainuncertainties. Fixedpackcurrent,busbarthermal/cooling design is conservativecomparison,not automatically optimalfuturelightweightdesign. No newachieveddensity or unsupportedstructurallearning. Controlsremainexistingfixedarchitecture,not resolvedvehicle-specificchannelcount. HighpowerFCEVcar/truck/bus andhydrogenrail fixedreferences remainoutsidegenericmobilecellcurve. Legacywholepackprovidersremainforotherconsumers; unrelatedstationary/homebattery andflow/leadacid designs needseparatelyscopednoncellaudit,not silentlyredefinedhere. Comparefixednoncellreference toformerproportionalhardware trajectory at2030/2050; baseline mustbeidentical andstaticnoncellwaste mustnotdecay.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+APPROVED SOURCE-CONSISTENT NCA/LTO CELL AND CAPACITY REFERENCE,item22,2026-10-18. Schmidt etal2019 DOI10.1021/acs.est.8b05313, Supporting Data es8b05313_si_002.zip, NCA LTO battery import.xlsx summary!H54=16.040428932169362kg/kWh dry cell components excluding pouch, H56=.5181296021158341kg/kWh pouch; H60=1000/(H54+H56)=60.39173022998696Wh/kg-cell. This is the source harmonized historical NCA/LTO engineering design, not modern fleet validation. The current capacity reference85Wh/kg is inconsistent with that recipe. Restore seven component fractions to source per-kWh masses divided by16.558558534285197kg/kWh; the old six non-pouch fractions were multiplied by rounded.060kWh/kg and the pouch filled the remainder, rather than using the source pouch mass. This restores source component ratios and a1kg component-sum cell. Preserve all previously corrected upstream electrode/graphite/collector recipes and supplier identities, cell water/electricity/heat proxies, reference pack cellmass108.03kg and non-cell geometry37.71kg (NMC622 geometry proxy), controls/protection6.538kg per reference and all vehicle energy/cycle/replacement assumptions. Factory utilities and upstream manufacturing yields remain inherited proxies rather than a claim of complete original-source reproduction. Use exact source cell energy.060391730229986965kWh/kg in the capacity market. Scalable hardware145.74kg now represents6.524118616745492grosskWh, hence22.338649641643293kg/kWh instead of15.871408268944903. Pair identical negative waste mass and signed uncertainty endpoints; retain prior engineering75-125percent mass range, without claiming source statistical confidence. Fixed-unit controls remain unchanged per reference pack, but dose becomes1/6.524118616745492unit/kWh to share the same capacity basis. No future LTO improvement is assumed; existing2020/2050 density-factor ratio is1 even though its YAML absolute values are historical50Wh/kg. No runtime/YAML changes. Original standalone75/25 LTO battery market remains a separate legacy assembly reference, while capacity markets buy the explicit hardware/central-control reference. Source pack48.6049Wh/kg excludes BMS/cooling and is distinct from the adopted cell-specific60.3917Wh/kg. Remaining material-grade, utility, thermal rating, life and future-design limitations remain explicit.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. Chemistry=LTO; geometry proxy=NMC622; cellmass=108.03kg, scalablehardware=145.74kg, assumed cellbaseline=0.085kWh/kg, grossreference=9.18255kWh, fixedcontrolmass=6.538kg. Retained listed hardware material coefficients sum1kg/kg; upstream cell/processing yields are not overwritten. Raw source rounding and cell-specific gaps remain in those providers. Cell-share metadata now refers only to scalable hardware; total installed pack also includes fixed unit-valued control hardware.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
@@ -2575,80 +2675,92 @@
     <row r="104" spans="1:14" ns3:dyDescent="0.2">
       <c r="A104" t="inlineStr">
         <is>
-          <t>market for battery hardware, Li-ion, LTO, engineering reference</t>
+          <t>market for battery cells, Li-ion, LTO, density-scaled reference</t>
         </is>
       </c>
       <c r="B104" s="3">
-        <f>1/(0.060391730229986965*$B$100)</f>
-        <v>22.338649641643293</v>
+        <f>16.558558534285197</f>
+        <v>16.558558534285197</v>
       </c>
       <c r="C104" t="s">
         <v>7</v>
       </c>
-      <c r="D104" t="s">
-        <v>3</v>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
       </c>
       <c r="E104" t="s">
         <v>14</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>battery hardware, Li-ion, LTO, engineering reference</t>
+          <t>market for battery cells, Li-ion, LTO, density-scaled reference</t>
         </is>
       </c>
       <c r="G104">
         <v>5</v>
       </c>
       <c r="H104" s="7">
-        <f>B104</f>
-        <v>22.338649641643293</v>
+        <f>16.558558534285197</f>
+        <v>16.558558534285197</v>
       </c>
       <c r="I104" s="7">
-        <f>B104*0.75</f>
-        <v>16.753987231232472</v>
+        <f>12.4189189007139</f>
+        <v>12.4189189007139</v>
       </c>
       <c r="J104" s="7">
-        <f>B104*1.25</f>
-        <v>27.923312052054115</v>
+        <f>20.698198167856496</f>
+        <v>20.698198167856496</v>
       </c>
     </row>
     <row r="105" spans="1:14" ns3:dyDescent="0.2">
-      <c r="A105" t="s">
-        <v>53</v>
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>battery fixed noncell hardware, Li-ion, LTO, baseline-kWh reference</t>
+        </is>
       </c>
       <c r="B105" s="3">
-        <f>-B104</f>
-        <v>-22.338649641643293</v>
-      </c>
-      <c r="C105" t="s">
-        <v>7</v>
-      </c>
-      <c r="D105" t="s">
-        <v>3</v>
+        <f>1</f>
+        <v>1</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
       </c>
       <c r="E105" t="s">
         <v>14</v>
       </c>
-      <c r="F105" t="s">
-        <v>54</v>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>battery fixed noncell hardware, Li-ion, LTO, baseline-kWh reference</t>
+        </is>
       </c>
       <c r="G105">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H105" s="7">
-        <f>B105</f>
-        <v>-22.338649641643293</v>
+        <f>1</f>
+        <v>1</v>
       </c>
       <c r="I105" s="7">
-        <f>B105*1.25</f>
-        <v>-27.923312052054115</v>
+        <f>1</f>
+        <v>1</v>
       </c>
       <c r="J105" s="7">
-        <f>B105*0.75</f>
-        <v>-16.753987231232472</v>
-      </c>
-      <c r="K105" t="b">
-        <v>1</v>
+        <f>1</f>
+        <v>1</v>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="M105" s="7"/>
       <c r="N105" s="7"/>
@@ -2697,7 +2809,9 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. Chemistry=LiMn2O4; geometry proxy=LiMn2O4; cellmass=146.26999999999998kg, scalablehardware=188.1kg, assumed cellbaseline=0.13kWh/kg, grossreference=19.015099999999997kWh, fixedcontrolmass=6.478kg. Retained listed hardware material coefficients sum1kg/kg; upstream cell/processing yields are not overwritten. Raw source rounding and cell-specific gaps remain in those providers. Cell-share metadata now refers only to scalable hardware; total installed pack also includes fixed unit-valued control hardware.
+          <t>APPROVED CELL-ONLY DENSITY LEARNING AND FIXED PACK HARDWARE, issue63, 2026-10-18. Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign. For nine conventionalmobile chemistries,LiS,SIB,LiO2 andthreeASSB references,split active capacitypath into kgcellmanufacture and one fixednoncellreference unit perbaseline nominalkWh. Preserve exactbaselinecell mass,allnoncellmaterials,processservices,controls,transport and totaldisposal. Unitbasis is the original explicitly sizedpack architecture attributed to1nominalkWh,not onephysicalpackper1kWh or a newcapacity. Existingruntime scaling appliesonly kgexchanges of namedcapacitydatasets; thus cellmanufacturekg and matchingusedcellkg followunchangeddensityfactor,while casing,busbars,coolant,packaging and theirdisposal are fixedinsideunitprovider. Existing separatelyunitizedcentral/modulecontrols,oxygenlifecycle,cooling are unchanged. No runtime/YAML/learningcurve edit. Noncellhelper buys originalnoncellprocesses once,plusits originalfraction ofusedbattery treatment;Negative cellwaste moves inside the scalablecellprovider at-1kg/kgcell, so it follows exactly the samecellmass; reuse originalcapacitywasterow forfixedunit without movingworkbookrows. The fixedunit is deterministic; prior signed mass uncertainty is removed from thatrow,while original scaledcell distribution is retained. No negativecredit tocancel a completepack orsecondwholepack disposal. LiS/SIB unfold onlyone-to-one packmarket/module boundary; sourcefinishedpackfreight divided bybaselinecell/noncellmass,cellfreight followscellmass andnoncellfreight fixed,baselinefreight identical. Existing cellrecipe andits internalcollectors/separator/case are retained andscale with cellmass: this is a reference ofsamecellformat atgreatercapacity,not proofphysicalcollectorareaorcellhousing canfallthatway. Propercellredesign/areal loading and lifetimepower/cycle behavior remainuncertainties. Fixedpackcurrent,busbarthermal/cooling design is conservativecomparison,not automatically optimalfuturelightweightdesign. No newachieveddensity or unsupportedstructurallearning. Controlsremainexistingfixedarchitecture,not resolvedvehicle-specificchannelcount. HighpowerFCEVcar/truck/bus andhydrogenrail fixedreferences remainoutsidegenericmobilecellcurve. Legacywholepackprovidersremainforotherconsumers; unrelatedstationary/homebattery andflow/leadacid designs needseparatelyscopednoncellaudit,not silentlyredefinedhere. Comparefixednoncellreference toformerproportionalhardware trajectory at2030/2050; baseline mustbeidentical andstaticnoncellwaste mustnotdecay.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. Chemistry=LiMn2O4; geometry proxy=LiMn2O4; cellmass=146.26999999999998kg, scalablehardware=188.1kg, assumed cellbaseline=0.13kWh/kg, grossreference=19.015099999999997kWh, fixedcontrolmass=6.478kg. Retained listed hardware material coefficients sum1kg/kg; upstream cell/processing yields are not overwritten. Raw source rounding and cell-specific gaps remain in those providers. Cell-share metadata now refers only to scalable hardware; total installed pack also includes fixed unit-valued control hardware.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 This dataset provides 1 kWh of battery gross capacity (NOT net), using a Li-ion LMO battery. Specific energy density in 2020: 0.13 kWh/kg cell. Battery management (BoP) mass share: 13%. Battery energy density in 2020: 0.114 kWh/kg battery. Battery mass per kWh: 18.4 kg. Lifetime: 10'000 cycles. Source for parameters: Life cycle assessment of battery electric buses. Transportation Research Part D: Transport and Environment. Linda Ager-Wick Ellingsen, Rebecca Jayne Thorne, Julia Wind, Erik Figenbaum, Mia Romare and Anders Nordelöf.</t>
         </is>
@@ -2811,80 +2925,92 @@
     <row r="117" spans="1:14" ns3:dyDescent="0.2">
       <c r="A117" t="inlineStr">
         <is>
-          <t>market for battery hardware, Li-ion, LiMn2O4, engineering reference</t>
+          <t>market for battery cells, Li-ion, LiMn2O4, density-scaled reference</t>
         </is>
       </c>
       <c r="B117" s="3">
-        <f>9.89213835320351</f>
-        <v>9.89213835320351</v>
+        <f>7.692307692307694</f>
+        <v>7.692307692307694</v>
       </c>
       <c r="C117" t="s">
         <v>7</v>
       </c>
-      <c r="D117" t="s">
-        <v>3</v>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
       </c>
       <c r="E117" t="s">
         <v>14</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>battery hardware, Li-ion, LiMn2O4, engineering reference</t>
+          <t>market for battery cells, Li-ion, LiMn2O4, density-scaled reference</t>
         </is>
       </c>
       <c r="G117">
         <v>5</v>
       </c>
       <c r="H117" s="7">
-        <f>9.89213835320351</f>
-        <v>9.89213835320351</v>
+        <f>7.692307692307695</f>
+        <v>7.692307692307695</v>
       </c>
       <c r="I117" s="7">
-        <f>7.419103764902632</f>
-        <v>7.419103764902632</v>
+        <f>5.76923076923077</f>
+        <v>5.76923076923077</v>
       </c>
       <c r="J117" s="7">
-        <f>12.365172941504387</f>
-        <v>12.365172941504387</v>
+        <f>9.615384615384617</f>
+        <v>9.615384615384617</v>
       </c>
     </row>
     <row r="118" spans="1:14" ns3:dyDescent="0.2">
-      <c r="A118" t="s">
-        <v>53</v>
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>battery fixed noncell hardware, Li-ion, LiMn2O4, baseline-kWh reference</t>
+        </is>
       </c>
       <c r="B118" s="3">
-        <f>-9.89213835320351</f>
-        <v>-9.89213835320351</v>
-      </c>
-      <c r="C118" t="s">
-        <v>7</v>
-      </c>
-      <c r="D118" t="s">
-        <v>3</v>
+        <f>1</f>
+        <v>1</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
       </c>
       <c r="E118" t="s">
         <v>14</v>
       </c>
-      <c r="F118" t="s">
-        <v>54</v>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>battery fixed noncell hardware, Li-ion, LiMn2O4, baseline-kWh reference</t>
+        </is>
       </c>
       <c r="G118">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H118" s="7">
-        <f>-9.89213835320351</f>
-        <v>-9.89213835320351</v>
+        <f>1</f>
+        <v>1</v>
       </c>
       <c r="I118" s="7">
-        <f>-12.365172941504387</f>
-        <v>-12.365172941504387</v>
+        <f>1</f>
+        <v>1</v>
       </c>
       <c r="J118" s="7">
-        <f>-7.419103764902632</f>
-        <v>-7.419103764902632</v>
-      </c>
-      <c r="K118" t="b">
-        <v>1</v>
+        <f>1</f>
+        <v>1</v>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="M118" s="7"/>
       <c r="N118" s="7"/>
@@ -2933,7 +3059,9 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>APPROVED ENGINEERING CONTROL/THERMAL COVERAGE, item13, 2026-10-18. Wickerts corrected SI DOI10.1021/acssuschemeng.4c01782.s001 S26/S27; original Ellingsen2014 SI S39/S40, DOI10.1111/jiec.12072. Separate module monitoring from central protection: per16-module reference,1.1kg populated PCB monitors, central0.49kg populated PCB+2.8kg HV system+1.2kg LV system+.028kg fasteners=4.518kg. Use existing HV/LV/fastener process providers and generic populated through-hole PCB perkg; this is an explicit board-technology/material proxy rather than the source-specific board fabrication model. No whole BMS is added on top. Adopt one nominal10kg liquid-cooling assembly per reference: Al9.08, steel.23, PVC/rubber pipe.0096, thermal pad.2 (silicon.06, glass.02, ABS.12), ethylene glycol.48kg; source-rounded sum9.9996kg. Metal working/injection services are included; 100percent retention of listed finished materials is assumed. No stationary rack housing/container, common vehicle body or roadway is added. Monitoring/protection/cooling are added once as a unit-valued capacity input; kg module and matching waste remain separate, so density learning does not shrink fixed controls. Central and cooling hardware are conservatively co-replaced with each delivered pack; longer independent hardware life is not established. End-of-life uses the existing generic used Li-ion route for15.6176kg of auxiliary hardware per reference, without recovery credits; this is a treatment proxy for controls/cooling, not proof of chemistry-specific recovery. Source thermal duty, pump/radiator performance, protection ratings, inverter/pack interface, full outer pack enclosure and vehicle-specific module topology remain coverage/design gaps. The SIB cell-mass-equivalent module retains its existing18.768kg cell+6.203kg module hardware reference; it is not a demonstrated integer21700-cell topology. LiS uses the corrected19.306152kg cell+6.203kg module hardware. These are engineering references, not fleet-validated designs; use0.5-2x auxiliary-size and independent-replacement-life sensitivities. Reference gross capacity is16*19.306152kg cell*0.15kWh/kg=46.3347648kWh; dose=0.0215820670357649unit/kWh. Existing cell density, kg-module recipe, energy/per-MJ coefficients and cycle assumptions are preserved.
+          <t>APPROVED CELL-ONLY DENSITY LEARNING AND FIXED PACK HARDWARE, issue63, 2026-10-18. Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign. For nine conventionalmobile chemistries,LiS,SIB,LiO2 andthreeASSB references,split active capacitypath into kgcellmanufacture and one fixednoncellreference unit perbaseline nominalkWh. Preserve exactbaselinecell mass,allnoncellmaterials,processservices,controls,transport and totaldisposal. Unitbasis is the original explicitly sizedpack architecture attributed to1nominalkWh,not onephysicalpackper1kWh or a newcapacity. Existingruntime scaling appliesonly kgexchanges of namedcapacitydatasets; thus cellmanufacturekg and matchingusedcellkg followunchangeddensityfactor,while casing,busbars,coolant,packaging and theirdisposal are fixedinsideunitprovider. Existing separatelyunitizedcentral/modulecontrols,oxygenlifecycle,cooling are unchanged. No runtime/YAML/learningcurve edit. Noncellhelper buys originalnoncellprocesses once,plusits originalfraction ofusedbattery treatment;Negative cellwaste moves inside the scalablecellprovider at-1kg/kgcell, so it follows exactly the samecellmass; reuse originalcapacitywasterow forfixedunit without movingworkbookrows. The fixedunit is deterministic; prior signed mass uncertainty is removed from thatrow,while original scaledcell distribution is retained. No negativecredit tocancel a completepack orsecondwholepack disposal. LiS/SIB unfold onlyone-to-one packmarket/module boundary; sourcefinishedpackfreight divided bybaselinecell/noncellmass,cellfreight followscellmass andnoncellfreight fixed,baselinefreight identical. Existing cellrecipe andits internalcollectors/separator/case are retained andscale with cellmass: this is a reference ofsamecellformat atgreatercapacity,not proofphysicalcollectorareaorcellhousing canfallthatway. Propercellredesign/areal loading and lifetimepower/cycle behavior remainuncertainties. Fixedpackcurrent,busbarthermal/cooling design is conservativecomparison,not automatically optimalfuturelightweightdesign. No newachieveddensity or unsupportedstructurallearning. Controlsremainexistingfixedarchitecture,not resolvedvehicle-specificchannelcount. HighpowerFCEVcar/truck/bus andhydrogenrail fixedreferences remainoutsidegenericmobilecellcurve. Legacywholepackprovidersremainforotherconsumers; unrelatedstationary/homebattery andflow/leadacid designs needseparatelyscopednoncellaudit,not silentlyredefinedhere. Comparefixednoncellreference toformerproportionalhardware trajectory at2030/2050; baseline mustbeidentical andstaticnoncellwaste mustnotdecay.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+APPROVED ENGINEERING CONTROL/THERMAL COVERAGE, item13, 2026-10-18. Wickerts corrected SI DOI10.1021/acssuschemeng.4c01782.s001 S26/S27; original Ellingsen2014 SI S39/S40, DOI10.1111/jiec.12072. Separate module monitoring from central protection: per16-module reference,1.1kg populated PCB monitors, central0.49kg populated PCB+2.8kg HV system+1.2kg LV system+.028kg fasteners=4.518kg. Use existing HV/LV/fastener process providers and generic populated through-hole PCB perkg; this is an explicit board-technology/material proxy rather than the source-specific board fabrication model. No whole BMS is added on top. Adopt one nominal10kg liquid-cooling assembly per reference: Al9.08, steel.23, PVC/rubber pipe.0096, thermal pad.2 (silicon.06, glass.02, ABS.12), ethylene glycol.48kg; source-rounded sum9.9996kg. Metal working/injection services are included; 100percent retention of listed finished materials is assumed. No stationary rack housing/container, common vehicle body or roadway is added. Monitoring/protection/cooling are added once as a unit-valued capacity input; kg module and matching waste remain separate, so density learning does not shrink fixed controls. Central and cooling hardware are conservatively co-replaced with each delivered pack; longer independent hardware life is not established. End-of-life uses the existing generic used Li-ion route for15.6176kg of auxiliary hardware per reference, without recovery credits; this is a treatment proxy for controls/cooling, not proof of chemistry-specific recovery. Source thermal duty, pump/radiator performance, protection ratings, inverter/pack interface, full outer pack enclosure and vehicle-specific module topology remain coverage/design gaps. The SIB cell-mass-equivalent module retains its existing18.768kg cell+6.203kg module hardware reference; it is not a demonstrated integer21700-cell topology. LiS uses the corrected19.306152kg cell+6.203kg module hardware. These are engineering references, not fleet-validated designs; use0.5-2x auxiliary-size and independent-replacement-life sensitivities. Reference gross capacity is16*19.306152kg cell*0.15kWh/kg=46.3347648kWh; dose=0.0215820670357649unit/kWh. Existing cell density, kg-module recipe, energy/per-MJ coefficients and cycle assumptions are preserved.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 APPROVED Li-S BASE-DESIGN ENGINEERING RECONCILIATION, item15, 2026-10-18. Wickerts corrected SI, DOI10.1021/acssuschemeng.4c01782.s001 Tables S19/S21: use baseline B recipe with the existing150 Wh/kg-cell and1500-cycle reference, rather than technical T ingredients associated with500 Wh/kg. Per cell: Li4g, separator6g, cathode8g, electrolyte29g, pouch.13g, negative tab.12g, positive tab.069g. Detailed retained masses sum47.319g, conflicting with source46g average. Adopt47.319g as the explicit engineering mass basis (not a measured corrected source cell); no arbitrary rescaling of individual ingredients. At150 Wh/kg this is7.09785 Wh/cell. Cathode B perkg: sulfur.28, CMK3.22, PVDF.13, acetonitrile.044, foil.38, organic waste-.054; inputs1.054kg=1kg product+.054kg waste. Preserve process-specific energy and transport. Source PVDF binder uses the existing polyvinylfluoride supply as an explicitly retained cross-version fluoropolymer proxy; exact binder chemistry remains a coverage/model gap, not a verified PVDF route. Per-cell assembly/formation/factory requirements retain their source cell amounts and are divided by47.319g. Module408cells=19.306152kg plus.275Al busbar+.593bimetal+.085Cu+2.75PP+2.5steel =25.509152kg. Cell share is0.7568323713779275. The mobile capacity market normalizes exactly to1 gross kWh at.150kWh/kg-cell, with.120-.180 endpoints and paired waste masses. Future density factors remain the existing relative learning assumption with fixed recipe; this does not validate a future physical cell design, cycle aging or calendar life. Controls/cooling are treated separately under item13. Source average-mass conflict and future recipe evolution remain explicit gaps. This supersedes older24.971kg-module/46g-cell and500Wh/kg-composition statements below.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
@@ -3047,78 +3175,94 @@
       </c>
     </row>
     <row r="130" spans="1:14" ns3:dyDescent="0.2">
-      <c r="A130" t="s">
-        <v>33</v>
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>market for battery cells, Li-sulfur, Li-S, density-scaled reference</t>
+        </is>
       </c>
       <c r="B130" s="3">
-        <f>8.808643655832261</f>
-        <v>8.808643655832261</v>
+        <f>6.666666666666667</f>
+        <v>6.666666666666667</v>
       </c>
       <c r="C130" t="s">
         <v>7</v>
       </c>
-      <c r="D130" t="s">
-        <v>3</v>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
       </c>
       <c r="E130" t="s">
         <v>14</v>
       </c>
-      <c r="F130" t="s">
-        <v>34</v>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>market for battery cells, Li-sulfur, Li-S, density-scaled reference</t>
+        </is>
       </c>
       <c r="G130">
         <v>5</v>
       </c>
       <c r="H130" s="7">
-        <f>8.808643655832261</f>
-        <v>8.808643655832261</v>
+        <f>6.666666666666667</f>
+        <v>6.666666666666667</v>
       </c>
       <c r="I130" s="3">
-        <f>7.340536379860217</f>
-        <v>7.340536379860217</v>
+        <f>5.555555555555555</f>
+        <v>5.555555555555555</v>
       </c>
       <c r="J130" s="3">
-        <f>11.010804569790327</f>
-        <v>11.010804569790327</v>
+        <f>8.333333333333334</f>
+        <v>8.333333333333334</v>
       </c>
     </row>
     <row r="131" spans="1:14" ns3:dyDescent="0.2">
-      <c r="A131" t="s">
-        <v>53</v>
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>battery fixed noncell hardware, Li-sulfur, Li-S, baseline-kWh reference</t>
+        </is>
       </c>
       <c r="B131" s="3">
-        <f>-8.808643655832261</f>
-        <v>-8.808643655832261</v>
-      </c>
-      <c r="C131" t="s">
-        <v>7</v>
-      </c>
-      <c r="D131" t="s">
-        <v>3</v>
+        <f>1</f>
+        <v>1</v>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
       </c>
       <c r="E131" t="s">
         <v>14</v>
       </c>
-      <c r="F131" t="s">
-        <v>54</v>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>battery fixed noncell hardware, Li-sulfur, Li-S, baseline-kWh reference</t>
+        </is>
       </c>
       <c r="G131">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H131" s="7">
-        <f>-8.808643655832261</f>
-        <v>-8.808643655832261</v>
+        <f>1</f>
+        <v>1</v>
       </c>
       <c r="I131" s="3">
-        <f>-11.010804569790327</f>
-        <v>-11.010804569790327</v>
+        <f>1</f>
+        <v>1</v>
       </c>
       <c r="J131" s="3">
-        <f>-7.340536379860217</f>
-        <v>-7.340536379860217</v>
-      </c>
-      <c r="K131" t="b">
-        <v>1</v>
+        <f>1</f>
+        <v>1</v>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="M131" s="3"/>
       <c r="N131" s="3"/>
@@ -3172,7 +3316,9 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>APPROVED Li-O2 HIERARCHICAL ENGINEERING RECONCILIATION, item18, 2026-10-18. Wang,Deng,Yuan2020 DOI10.1016/j.jclepro.2020.121339, SI TablesS3/S4/S5/S16; Kanthal resistance-wire datasheet https://www.kanthal.com/products/datasheets/material-datasheets/wire/resistance-heating-wire-and-resistance-wire/nikrothal-80/. Adopt TableS3 detailed retained geometry: cell182.6kg, module hardware19.51, pack hardware43.67, oxygen tank55, BMS4,cooling29.07 =&gt;333.85kg at63.5grosskWh. This conflicts with source headline321kg/267kg pack and with TableS5 gross material figures; do not mix those bases. Scalable cell/module/pack hardware=245.78kg; fixed-per-reference auxiliary hardware=88.07kg. Listed component masses, not proportional normalization of contradictory gross LCI tables, define this engineering reference. Known cell ingredients total182.59kg;0.01kg unspecified cathode catalyst remains a documented composition gap, not zero-metal proof. The sourceS4 fluoropolymer binder is not substituted for the unidentified S3 catalyst; binder quantity/fate is also unresolved, and that old process input is disabled in this reference. Electrolyte total59.11kg is split by inheritedS4 salt:solvent ratio.016:.308; LiClO4 process is the inherited salt provider, and ethylene-glycol dimethyl ether remains an explicitly imperfect TEGDME solvent proxy. Lithium protective film/pouch/separator process recipes remain inherited and unvalidated. Collector feed is1kg metal/kg foil at100percent reference retention; matching rolling and restored facility proxy are preserved. Terminal metal fractions are2.44kgAl/10.5kg and8.06kgCu/10.5kg, with matching working services; old overlapping gross feed and implied manufacturing scrap are disabled under the explicit100percent retention reference. Module and pack known material inputs followS3, with no new gross-yield claim. Module monitor.67kg is counted once; BMS4kg is assigned to central protection only using4/4.518 of the separate engineering central-control package. This functional repartition is an assumption, not a source breakdown. Cooling uses7kg Al plus22.07kg pureEG reference (alternative50/50 coolant is a sensitivity); thermal duty, pump/hoses remain gaps. Heater.2kg uses an idealized binary80Ni/20Cr resistance-alloy reference, consistent with a NiCr class but not a complete measured battery heater/Nikrothal composition; electronic/heater construction is unresolved. Preserve historical source-specific S16 recycling coefficients without new recovery credits. Capacity purchases245.78/63.5kg scalable hardware plus one auxiliary lifecycle unit per63.5kWh. Its negative waste equals scalable mass; auxiliary unit carries its own88.07kg waste. Future density factors scale hardware and its waste together; fixed auxiliary manufacture/treatment stay paired. Existing relative density learning is retained as an engineering ratio; absolute cell energy63.5/182.6=.347754655kWh/kg and fixed recipe are not a validated future design. Original full-battery market remains manufacturing-only at333.85kg component-sum basis; capacity uses the separately named hardware market. Vehicle energy/lifetime allocation is unchanged. Source contradictions, catalyst, solvent, future structure and recovery performance remain explicit gaps.
+          <t>APPROVED CELL-ONLY DENSITY LEARNING AND FIXED PACK HARDWARE, issue63, 2026-10-18. Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign. For nine conventionalmobile chemistries,LiS,SIB,LiO2 andthreeASSB references,split active capacitypath into kgcellmanufacture and one fixednoncellreference unit perbaseline nominalkWh. Preserve exactbaselinecell mass,allnoncellmaterials,processservices,controls,transport and totaldisposal. Unitbasis is the original explicitly sizedpack architecture attributed to1nominalkWh,not onephysicalpackper1kWh or a newcapacity. Existingruntime scaling appliesonly kgexchanges of namedcapacitydatasets; thus cellmanufacturekg and matchingusedcellkg followunchangeddensityfactor,while casing,busbars,coolant,packaging and theirdisposal are fixedinsideunitprovider. Existing separatelyunitizedcentral/modulecontrols,oxygenlifecycle,cooling are unchanged. No runtime/YAML/learningcurve edit. Noncellhelper buys originalnoncellprocesses once,plusits originalfraction ofusedbattery treatment;Negative cellwaste moves inside the scalablecellprovider at-1kg/kgcell, so it follows exactly the samecellmass; reuse originalcapacitywasterow forfixedunit without movingworkbookrows. The fixedunit is deterministic; prior signed mass uncertainty is removed from thatrow,while original scaledcell distribution is retained. No negativecredit tocancel a completepack orsecondwholepack disposal. LiS/SIB unfold onlyone-to-one packmarket/module boundary; sourcefinishedpackfreight divided bybaselinecell/noncellmass,cellfreight followscellmass andnoncellfreight fixed,baselinefreight identical. Existing cellrecipe andits internalcollectors/separator/case are retained andscale with cellmass: this is a reference ofsamecellformat atgreatercapacity,not proofphysicalcollectorareaorcellhousing canfallthatway. Propercellredesign/areal loading and lifetimepower/cycle behavior remainuncertainties. Fixedpackcurrent,busbarthermal/cooling design is conservativecomparison,not automatically optimalfuturelightweightdesign. No newachieveddensity or unsupportedstructurallearning. Controlsremainexistingfixedarchitecture,not resolvedvehicle-specificchannelcount. HighpowerFCEVcar/truck/bus andhydrogenrail fixedreferences remainoutsidegenericmobilecellcurve. Legacywholepackprovidersremainforotherconsumers; unrelatedstationary/homebattery andflow/leadacid designs needseparatelyscopednoncellaudit,not silentlyredefinedhere. Comparefixednoncellreference toformerproportionalhardware trajectory at2030/2050; baseline mustbeidentical andstaticnoncellwaste mustnotdecay.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+APPROVED Li-O2 HIERARCHICAL ENGINEERING RECONCILIATION, item18, 2026-10-18. Wang,Deng,Yuan2020 DOI10.1016/j.jclepro.2020.121339, SI TablesS3/S4/S5/S16; Kanthal resistance-wire datasheet https://www.kanthal.com/products/datasheets/material-datasheets/wire/resistance-heating-wire-and-resistance-wire/nikrothal-80/. Adopt TableS3 detailed retained geometry: cell182.6kg, module hardware19.51, pack hardware43.67, oxygen tank55, BMS4,cooling29.07 =&gt;333.85kg at63.5grosskWh. This conflicts with source headline321kg/267kg pack and with TableS5 gross material figures; do not mix those bases. Scalable cell/module/pack hardware=245.78kg; fixed-per-reference auxiliary hardware=88.07kg. Listed component masses, not proportional normalization of contradictory gross LCI tables, define this engineering reference. Known cell ingredients total182.59kg;0.01kg unspecified cathode catalyst remains a documented composition gap, not zero-metal proof. The sourceS4 fluoropolymer binder is not substituted for the unidentified S3 catalyst; binder quantity/fate is also unresolved, and that old process input is disabled in this reference. Electrolyte total59.11kg is split by inheritedS4 salt:solvent ratio.016:.308; LiClO4 process is the inherited salt provider, and ethylene-glycol dimethyl ether remains an explicitly imperfect TEGDME solvent proxy. Lithium protective film/pouch/separator process recipes remain inherited and unvalidated. Collector feed is1kg metal/kg foil at100percent reference retention; matching rolling and restored facility proxy are preserved. Terminal metal fractions are2.44kgAl/10.5kg and8.06kgCu/10.5kg, with matching working services; old overlapping gross feed and implied manufacturing scrap are disabled under the explicit100percent retention reference. Module and pack known material inputs followS3, with no new gross-yield claim. Module monitor.67kg is counted once; BMS4kg is assigned to central protection only using4/4.518 of the separate engineering central-control package. This functional repartition is an assumption, not a source breakdown. Cooling uses7kg Al plus22.07kg pureEG reference (alternative50/50 coolant is a sensitivity); thermal duty, pump/hoses remain gaps. Heater.2kg uses an idealized binary80Ni/20Cr resistance-alloy reference, consistent with a NiCr class but not a complete measured battery heater/Nikrothal composition; electronic/heater construction is unresolved. Preserve historical source-specific S16 recycling coefficients without new recovery credits. Capacity purchases245.78/63.5kg scalable hardware plus one auxiliary lifecycle unit per63.5kWh. Its negative waste equals scalable mass; auxiliary unit carries its own88.07kg waste. Future density factors scale hardware and its waste together; fixed auxiliary manufacture/treatment stay paired. Existing relative density learning is retained as an engineering ratio; absolute cell energy63.5/182.6=.347754655kWh/kg and fixed recipe are not a validated future design. Original full-battery market remains manufacturing-only at333.85kg component-sum basis; capacity uses the separately named hardware market. Vehicle energy/lifetime allocation is unchanged. Source contradictions, catalyst, solvent, future structure and recovery performance remain explicit gaps.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 APPROVED Li-O2 SINGLE RECYCLING BOUNDARY, 2026-10-18. Wang, Deng and Yuan (2020), DOI 10.1016/j.jclepro.2020.121339, supporting information Table S16, explicitly describes recycling per 1 kg Li-O2 battery system. Its six treatment coefficients are retained. Set the former -1/321 kg/kg internal treatment fragment to a deterministic zero and apply end of life only at market for battery capacity, Li-ion, Li-O2: the full purchased battery mass is sent to treatment of LiO2 battery, for recycling (RER; waste LiO2 battery). Standalone manufacture is manufacturing-only. DefaultInventory may retain the zero exchange; it contributes no treatment flow. Do not add a second generic Li-ion route. This restores a single historical source-specific accounting route; treatment yields, whole-system mass normalization, modern recovery and primary/secondary shares remain unvalidated. No new recovery credit or change to manufacturing recipes, density or lifetime. The capacity-level treatment amount, sign, triangular bounds and all manufacturing mass formulas/caches are unchanged; purchased and treated mass remain paired as battery density changes.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
@@ -3287,59 +3433,63 @@
     <row r="143" spans="1:14" ns3:dyDescent="0.2">
       <c r="A143" t="inlineStr">
         <is>
-          <t>market for battery hardware, Li-oxygen, engineering reference</t>
+          <t>market for battery cells, Li-ion, Li-O2, density-scaled reference</t>
         </is>
       </c>
       <c r="B143" s="3">
-        <f>3.870551181102362</f>
-        <v>3.870551181102362</v>
+        <f>2.875590551181102</f>
+        <v>2.875590551181102</v>
       </c>
       <c r="C143" t="s">
         <v>7</v>
       </c>
-      <c r="D143" t="s">
-        <v>3</v>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
       </c>
       <c r="E143" t="s">
         <v>14</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>battery hardware, Li-oxygen, engineering reference</t>
+          <t>market for battery cells, Li-ion, Li-O2, density-scaled reference</t>
         </is>
       </c>
       <c r="G143">
         <v>5</v>
       </c>
       <c r="H143" s="7">
-        <f>3.870551181102362</f>
-        <v>3.870551181102362</v>
+        <f>2.875590551181102</f>
+        <v>2.875590551181102</v>
       </c>
       <c r="I143" s="7">
-        <f>2.9029133858267713</f>
-        <v>2.9029133858267713</v>
+        <f>2.1566929133858266</f>
+        <v>2.1566929133858266</v>
       </c>
       <c r="J143" s="7">
-        <f>4.838188976377952</f>
-        <v>4.838188976377952</v>
+        <f>3.5944881889763773</f>
+        <v>3.5944881889763773</v>
       </c>
     </row>
     <row r="144" spans="1:14" ns3:dyDescent="0.2">
       <c r="A144" t="inlineStr">
         <is>
-          <t>treatment of LiO2 battery, for recycling</t>
+          <t>battery fixed noncell hardware, Li-ion, Li-O2, baseline-kWh reference</t>
         </is>
       </c>
       <c r="B144" s="3">
-        <f>-3.870551181102362</f>
-        <v>-3.870551181102362</v>
-      </c>
-      <c r="C144" t="s">
-        <v>7</v>
+        <f>1</f>
+        <v>1</v>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>RER</t>
+          <t>GLO</t>
         </is>
       </c>
       <c r="E144" t="s">
@@ -3347,26 +3497,28 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>waste LiO2 battery</t>
+          <t>battery fixed noncell hardware, Li-ion, Li-O2, baseline-kWh reference</t>
         </is>
       </c>
       <c r="G144">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H144" s="7">
-        <f>-3.870551181102362</f>
-        <v>-3.870551181102362</v>
+        <f>1</f>
+        <v>1</v>
       </c>
       <c r="I144" s="7">
-        <f>-4.838188976377952</f>
-        <v>-4.838188976377952</v>
+        <f>1</f>
+        <v>1</v>
       </c>
       <c r="J144" s="7">
-        <f>-2.9029133858267713</f>
-        <v>-2.9029133858267713</v>
-      </c>
-      <c r="K144" t="b">
-        <v>1</v>
+        <f>1</f>
+        <v>1</v>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="M144" s="7"/>
       <c r="N144" s="7"/>
@@ -3420,7 +3572,9 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>APPROVED ENGINEERING CONTROL/THERMAL COVERAGE, item13, 2026-10-18. Wickerts corrected SI DOI10.1021/acssuschemeng.4c01782.s001 S26/S27; original Ellingsen2014 SI S39/S40, DOI10.1111/jiec.12072. Separate module monitoring from central protection: per16-module reference,1.1kg populated PCB monitors, central0.49kg populated PCB+2.8kg HV system+1.2kg LV system+.028kg fasteners=4.518kg. Use existing HV/LV/fastener process providers and generic populated through-hole PCB perkg; this is an explicit board-technology/material proxy rather than the source-specific board fabrication model. No whole BMS is added on top. Adopt one nominal10kg liquid-cooling assembly per reference: Al9.08, steel.23, PVC/rubber pipe.0096, thermal pad.2 (silicon.06, glass.02, ABS.12), ethylene glycol.48kg; source-rounded sum9.9996kg. Metal working/injection services are included; 100percent retention of listed finished materials is assumed. No stationary rack housing/container, common vehicle body or roadway is added. Monitoring/protection/cooling are added once as a unit-valued capacity input; kg module and matching waste remain separate, so density learning does not shrink fixed controls. Central and cooling hardware are conservatively co-replaced with each delivered pack; longer independent hardware life is not established. End-of-life uses the existing generic used Li-ion route for15.6176kg of auxiliary hardware per reference, without recovery credits; this is a treatment proxy for controls/cooling, not proof of chemistry-specific recovery. Source thermal duty, pump/radiator performance, protection ratings, inverter/pack interface, full outer pack enclosure and vehicle-specific module topology remain coverage/design gaps. The SIB cell-mass-equivalent module retains its existing18.768kg cell+6.203kg module hardware reference; it is not a demonstrated integer21700-cell topology. LiS uses the corrected19.306152kg cell+6.203kg module hardware. These are engineering references, not fleet-validated designs; use0.5-2x auxiliary-size and independent-replacement-life sensitivities. Reference gross capacity is16*18.768kg cell*0.157kWh/kg=47.145216000000005kWh; dose=0.02121105988781555unit/kWh. Existing cell density, kg-module recipe, energy/per-MJ coefficients and cycle assumptions are preserved.
+          <t>APPROVED CELL-ONLY DENSITY LEARNING AND FIXED PACK HARDWARE, issue63, 2026-10-18. Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign. For nine conventionalmobile chemistries,LiS,SIB,LiO2 andthreeASSB references,split active capacitypath into kgcellmanufacture and one fixednoncellreference unit perbaseline nominalkWh. Preserve exactbaselinecell mass,allnoncellmaterials,processservices,controls,transport and totaldisposal. Unitbasis is the original explicitly sizedpack architecture attributed to1nominalkWh,not onephysicalpackper1kWh or a newcapacity. Existingruntime scaling appliesonly kgexchanges of namedcapacitydatasets; thus cellmanufacturekg and matchingusedcellkg followunchangeddensityfactor,while casing,busbars,coolant,packaging and theirdisposal are fixedinsideunitprovider. Existing separatelyunitizedcentral/modulecontrols,oxygenlifecycle,cooling are unchanged. No runtime/YAML/learningcurve edit. Noncellhelper buys originalnoncellprocesses once,plusits originalfraction ofusedbattery treatment;Negative cellwaste moves inside the scalablecellprovider at-1kg/kgcell, so it follows exactly the samecellmass; reuse originalcapacitywasterow forfixedunit without movingworkbookrows. The fixedunit is deterministic; prior signed mass uncertainty is removed from thatrow,while original scaledcell distribution is retained. No negativecredit tocancel a completepack orsecondwholepack disposal. LiS/SIB unfold onlyone-to-one packmarket/module boundary; sourcefinishedpackfreight divided bybaselinecell/noncellmass,cellfreight followscellmass andnoncellfreight fixed,baselinefreight identical. Existing cellrecipe andits internalcollectors/separator/case are retained andscale with cellmass: this is a reference ofsamecellformat atgreatercapacity,not proofphysicalcollectorareaorcellhousing canfallthatway. Propercellredesign/areal loading and lifetimepower/cycle behavior remainuncertainties. Fixedpackcurrent,busbarthermal/cooling design is conservativecomparison,not automatically optimalfuturelightweightdesign. No newachieveddensity or unsupportedstructurallearning. Controlsremainexistingfixedarchitecture,not resolvedvehicle-specificchannelcount. HighpowerFCEVcar/truck/bus andhydrogenrail fixedreferences remainoutsidegenericmobilecellcurve. Legacywholepackprovidersremainforotherconsumers; unrelatedstationary/homebattery andflow/leadacid designs needseparatelyscopednoncellaudit,not silentlyredefinedhere. Comparefixednoncellreference toformerproportionalhardware trajectory at2030/2050; baseline mustbeidentical andstaticnoncellwaste mustnotdecay.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+APPROVED ENGINEERING CONTROL/THERMAL COVERAGE, item13, 2026-10-18. Wickerts corrected SI DOI10.1021/acssuschemeng.4c01782.s001 S26/S27; original Ellingsen2014 SI S39/S40, DOI10.1111/jiec.12072. Separate module monitoring from central protection: per16-module reference,1.1kg populated PCB monitors, central0.49kg populated PCB+2.8kg HV system+1.2kg LV system+.028kg fasteners=4.518kg. Use existing HV/LV/fastener process providers and generic populated through-hole PCB perkg; this is an explicit board-technology/material proxy rather than the source-specific board fabrication model. No whole BMS is added on top. Adopt one nominal10kg liquid-cooling assembly per reference: Al9.08, steel.23, PVC/rubber pipe.0096, thermal pad.2 (silicon.06, glass.02, ABS.12), ethylene glycol.48kg; source-rounded sum9.9996kg. Metal working/injection services are included; 100percent retention of listed finished materials is assumed. No stationary rack housing/container, common vehicle body or roadway is added. Monitoring/protection/cooling are added once as a unit-valued capacity input; kg module and matching waste remain separate, so density learning does not shrink fixed controls. Central and cooling hardware are conservatively co-replaced with each delivered pack; longer independent hardware life is not established. End-of-life uses the existing generic used Li-ion route for15.6176kg of auxiliary hardware per reference, without recovery credits; this is a treatment proxy for controls/cooling, not proof of chemistry-specific recovery. Source thermal duty, pump/radiator performance, protection ratings, inverter/pack interface, full outer pack enclosure and vehicle-specific module topology remain coverage/design gaps. The SIB cell-mass-equivalent module retains its existing18.768kg cell+6.203kg module hardware reference; it is not a demonstrated integer21700-cell topology. LiS uses the corrected19.306152kg cell+6.203kg module hardware. These are engineering references, not fleet-validated designs; use0.5-2x auxiliary-size and independent-replacement-life sensitivities. Reference gross capacity is16*18.768kg cell*0.157kWh/kg=47.145216000000005kWh; dose=0.02121105988781555unit/kWh. Existing cell density, kg-module recipe, energy/per-MJ coefficients and cycle assumptions are preserved.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 APPROVED SODIUM-ION CAPACITY BASELINE NORMALIZATION, 2026-10-18. Zhang et al. (2024), Future climate impacts of sodium-ion batteries, Resources, Conservation and Recycling 202, 107362, DOI 10.1016/j.resconrec.2023.107362, Table 4, page 5: baseline NMMT/HC cell specific energy is 157 Wh/kg (0.157 kWh/kg), consistent with the existing source description and Premise density baseline. Primary paper: https://pub.epsilon.slu.se/32553/1/zhang-s-et-al-20240122.pdf . The linked existing SIB module recipe contains 0.7515918465419887 kg NMMT cell/kg module (lci-batteries-SIB.xlsx, sodium-ion batteries B493); its battery market purchases one kg of this module per kg delivered. Use this actual recipe coefficient, not a rounded 75 percent fraction, and 0.157 kWh/kg cell: 1/(0.157*0.7515918465419887) = 8.474582023338275 kg delivered module/kWh gross capacity. The previous 1/(0.16*0.75) = 8.333333333333334 kg represented 0.9833326658924353 kWh under those declared specifications. The module dose increases 1.6949842800592974 percent; this is not a percent change in overall transport or system metal demand. Set battery cell mass share to the linked recipe coefficient. Keep existing cell-specific density uncertainty endpoints 0.12 and 0.18 kWh/kg, translating them with the same module fraction; retain triangular type 5, equal negative waste mass and paired signed bounds/locations. Update formula caches consistently. The original rounded specific-energy/fraction/mass figures below are historical notes superseded by this paragraph. All supplier identities/geographies, the one-kWh output, cell/module manufacturing recipes, other chemistries, prospective density trajectory and lifetime/per-MJ allocations remain unchanged. This normalizes to declared cell energy and an existing module proxy; it does not validate measured pack performance, future electrochemical charge, cycle life or operating conditions. The Li-S-derived module architecture and missing BMS/cooling coverage remain unresolved. No electronics, racks, treatment route, recovery credit or primary/secondary share is added. Current full-system metal effects remain unquantified without a scenario rebuild.
 PREVIOUS SOURCE NOTES (ROUNDED VALUES SUPERSEDED ABOVE):
@@ -3534,78 +3688,94 @@
       </c>
     </row>
     <row r="156" spans="1:14" ns3:dyDescent="0.2">
-      <c r="A156" t="s">
-        <v>39</v>
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>market for battery cells, Sodium-ion, SiB, density-scaled reference</t>
+        </is>
       </c>
       <c r="B156" s="3">
-        <f>1/(0.157*$B$152)</f>
-        <v>8.474582023338275</v>
+        <f>6.369426751592357</f>
+        <v>6.369426751592357</v>
       </c>
       <c r="C156" t="s">
         <v>7</v>
       </c>
-      <c r="D156" t="s">
-        <v>3</v>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
       </c>
       <c r="E156" t="s">
         <v>14</v>
       </c>
-      <c r="F156" t="s">
-        <v>40</v>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>market for battery cells, Sodium-ion, SiB, density-scaled reference</t>
+        </is>
       </c>
       <c r="G156">
         <v>5</v>
       </c>
       <c r="H156" s="7">
-        <f>B156</f>
-        <v>8.474582023338275</v>
+        <f>6.369426751592357</f>
+        <v>6.369426751592357</v>
       </c>
       <c r="I156" s="3">
-        <f>1/(0.18*$B$152)</f>
-        <v>7.391718764800606</v>
+        <f>5.555555555555555</f>
+        <v>5.555555555555555</v>
       </c>
       <c r="J156" s="3">
-        <f>1/(0.12*$B$152)</f>
-        <v>11.08757814720091</v>
+        <f>8.333333333333334</f>
+        <v>8.333333333333334</v>
       </c>
     </row>
     <row r="157" spans="1:14" ns3:dyDescent="0.2">
-      <c r="A157" t="s">
-        <v>53</v>
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>battery fixed noncell hardware, Sodium-ion, SiB, baseline-kWh reference</t>
+        </is>
       </c>
       <c r="B157" s="3">
-        <f>-1*B156</f>
-        <v>-8.474582023338275</v>
-      </c>
-      <c r="C157" t="s">
-        <v>7</v>
-      </c>
-      <c r="D157" t="s">
-        <v>3</v>
+        <f>1</f>
+        <v>1</v>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
       </c>
       <c r="E157" t="s">
         <v>14</v>
       </c>
-      <c r="F157" t="s">
-        <v>54</v>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>battery fixed noncell hardware, Sodium-ion, SiB, baseline-kWh reference</t>
+        </is>
       </c>
       <c r="G157">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H157" s="7">
-        <f>B157</f>
-        <v>-8.474582023338275</v>
+        <f>1</f>
+        <v>1</v>
       </c>
       <c r="I157" s="3">
-        <f>-1/(0.12*$B$152)</f>
-        <v>-11.08757814720091</v>
+        <f>1</f>
+        <v>1</v>
       </c>
       <c r="J157" s="3">
-        <f>-1/(0.18*$B$152)</f>
-        <v>-7.391718764800606</v>
-      </c>
-      <c r="K157" t="b">
-        <v>1</v>
+        <f>1</f>
+        <v>1</v>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="M157" s="3"/>
       <c r="N157" s="3"/>

--- a/premise/data/additional_inventories/lci-battery-capacity.xlsx
+++ b/premise/data/additional_inventories/lci-battery-capacity.xlsx
@@ -7979,7 +7979,9 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. Chemistry=LFP; geometry proxy=LFP; cellmass=147.58kg, scalablehardware=196.85000000000002kg, assumed cellbaseline=0.16kWh/kg, grossreference=23.612800000000004kWh, fixedcontrolmass=6.668kg. Retained listed hardware material coefficients sum1kg/kg; upstream cell/processing yields are not overwritten. Raw source rounding and cell-specific gaps remain in those providers. Cell-share metadata now refers only to scalable hardware; total installed pack also includes fixed unit-valued control hardware.
+          <t>APPROVED STATIONARY CELL-ONLY DENSITY LEARNING, issue64,2026-10-18. Carry the issue63 fixed-noncell boundary through to six stationary lithium-ion capacity references. Preserve original stationary chemistry,baseline complete-pack materials,controls and capacity. Copy the corresponding mobile capacity references at the same chemistry-specific kgcell/kWh and fixed-noncell unit/kWh; these suppliers use the identical existing source pack architecture already used by stationary inventories. This does not transfer vehicle operation,chargers or roads into stationary storage. Only cell manufacture and its pairedcell disposal follow the existing cell-density curve. Noncellcase,busbar,coolant,packaging and associated disposal remain fixed inside the existing unit provider; central/module controls are already supplied once and treated by their own helper. Keep the stationary capacity activity identities so existing stationary scenario markets and dispatch/efficiency assumptions remain. There is no additional outer purchase of mobile capacity, no repeated density scaling and no second waste treatment. LFP,NMC111,NMC532,NMC622,NMC811,NMC955 baseline material/service vectors must match their pre-change stationary references,not only totalkg. The existing mobile geometry is an explicit shared engineering design; stationary-specific container/cooling/inverter topology and replacement lives are not validated by this change. No runtime,YAML or native edits; uncertainty on scalablecell quantity retained, fixedhardware deterministic as inissue63. Sodium-ion stationary already forwards1kWh to its corrected common capacity and needs no second change. Home-storage,leadacid and flowbattery designs remain separate.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. Chemistry=LFP; geometry proxy=LFP; cellmass=147.58kg, scalablehardware=196.85000000000002kg, assumed cellbaseline=0.16kWh/kg, grossreference=23.612800000000004kWh, fixedcontrolmass=6.668kg. Retained listed hardware material coefficients sum1kg/kg; upstream cell/processing yields are not overwritten. Raw source rounding and cell-specific gaps remain in those providers. Cell-share metadata now refers only to scalable hardware; total installed pack also includes fixed unit-valued control hardware.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 This dataset provides 1 kWh of battery gross capacity (NOT net), using a Li-ion LFP battery. Specific energy density in 2020: (min, mean, max) 0.140, 0.160, 0.190 kWh/kg cell. Battery management (BoP) mass share: 27%. Battery energy density in 2020: 0.10 kWh/kg battery. Battery mass per kWh: 8.6 kg. Lifetime: 3'000-3'500 cycles. Source for parameters: Hasselwander, S.; Meyer, M.; Österle, I. Techno-Economic Analysis of Different Battery Cell Chemistries for the Passenger Vehicle Market. Batteries 2023, 9, 379. https://doi.org/10.3390/batteries9070379.</t>
         </is>
@@ -8094,80 +8096,98 @@
     <row r="11" spans="1:14" ns3:dyDescent="0.2">
       <c r="A11" t="inlineStr">
         <is>
-          <t>market for battery hardware, Li-ion, LFP, engineering reference</t>
+          <t>market for battery cells, Li-ion, LFP, density-scaled reference</t>
         </is>
       </c>
       <c r="B11" s="7">
-        <f>8.336580159913266</f>
-        <v>8.336580159913266</v>
-      </c>
-      <c r="C11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D11" t="s">
-        <v>3</v>
-      </c>
-      <c r="E11" t="s">
-        <v>14</v>
+        <f>6.249999999999999</f>
+        <v>6.249999999999999</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>battery hardware, Li-ion, LFP, engineering reference</t>
+          <t>market for battery cells, Li-ion, LFP, density-scaled reference</t>
         </is>
       </c>
       <c r="G11">
         <v>5</v>
       </c>
       <c r="H11" s="7">
-        <f>8.336580159913266</f>
-        <v>8.336580159913266</v>
+        <f>6.249999999999999</f>
+        <v>6.249999999999999</v>
       </c>
       <c r="I11" s="7">
-        <f>7.020278029400646</f>
-        <v>7.020278029400646</v>
+        <f>5.263157894736842</f>
+        <v>5.263157894736842</v>
       </c>
       <c r="J11" s="7">
-        <f>9.527520182758018</f>
-        <v>9.527520182758018</v>
+        <f>7.1428571428571415</f>
+        <v>7.1428571428571415</v>
       </c>
     </row>
     <row r="12" spans="1:14" ns3:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>53</v>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>battery fixed noncell hardware, Li-ion, LFP, baseline-kWh reference</t>
+        </is>
       </c>
       <c r="B12" s="7">
-        <f>-8.336580159913266</f>
-        <v>-8.336580159913266</v>
-      </c>
-      <c r="C12" t="s">
-        <v>7</v>
-      </c>
-      <c r="D12" t="s">
-        <v>3</v>
-      </c>
-      <c r="E12" t="s">
-        <v>14</v>
-      </c>
-      <c r="F12" t="s">
-        <v>54</v>
+        <f>1</f>
+        <v>1</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>battery fixed noncell hardware, Li-ion, LFP, baseline-kWh reference</t>
+        </is>
       </c>
       <c r="G12">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H12" s="7">
-        <f>-8.336580159913266</f>
-        <v>-8.336580159913266</v>
+        <f>1</f>
+        <v>1</v>
       </c>
       <c r="I12" s="7">
-        <f>-9.527520182758018</f>
-        <v>-9.527520182758018</v>
+        <f>1</f>
+        <v>1</v>
       </c>
       <c r="J12" s="7">
-        <f>-7.020278029400646</f>
-        <v>-7.020278029400646</v>
-      </c>
-      <c r="K12" t="b">
-        <v>1</v>
+        <f>1</f>
+        <v>1</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="M12" s="7"/>
       <c r="N12" s="7"/>
@@ -8216,7 +8236,9 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. Chemistry=NMC111; geometry proxy=NMC111; cellmass=119.77kg, scalablehardware=158.94000000000003kg, assumed cellbaseline=0.18kWh/kg, grossreference=21.5586kWh, fixedcontrolmass=6.548kg. Retained listed hardware material coefficients sum1kg/kg; upstream cell/processing yields are not overwritten. Raw source rounding and cell-specific gaps remain in those providers. Cell-share metadata now refers only to scalable hardware; total installed pack also includes fixed unit-valued control hardware.
+          <t>APPROVED STATIONARY CELL-ONLY DENSITY LEARNING, issue64,2026-10-18. Carry the issue63 fixed-noncell boundary through to six stationary lithium-ion capacity references. Preserve original stationary chemistry,baseline complete-pack materials,controls and capacity. Copy the corresponding mobile capacity references at the same chemistry-specific kgcell/kWh and fixed-noncell unit/kWh; these suppliers use the identical existing source pack architecture already used by stationary inventories. This does not transfer vehicle operation,chargers or roads into stationary storage. Only cell manufacture and its pairedcell disposal follow the existing cell-density curve. Noncellcase,busbar,coolant,packaging and associated disposal remain fixed inside the existing unit provider; central/module controls are already supplied once and treated by their own helper. Keep the stationary capacity activity identities so existing stationary scenario markets and dispatch/efficiency assumptions remain. There is no additional outer purchase of mobile capacity, no repeated density scaling and no second waste treatment. LFP,NMC111,NMC532,NMC622,NMC811,NMC955 baseline material/service vectors must match their pre-change stationary references,not only totalkg. The existing mobile geometry is an explicit shared engineering design; stationary-specific container/cooling/inverter topology and replacement lives are not validated by this change. No runtime,YAML or native edits; uncertainty on scalablecell quantity retained, fixedhardware deterministic as inissue63. Sodium-ion stationary already forwards1kWh to its corrected common capacity and needs no second change. Home-storage,leadacid and flowbattery designs remain separate.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. Chemistry=NMC111; geometry proxy=NMC111; cellmass=119.77kg, scalablehardware=158.94000000000003kg, assumed cellbaseline=0.18kWh/kg, grossreference=21.5586kWh, fixedcontrolmass=6.548kg. Retained listed hardware material coefficients sum1kg/kg; upstream cell/processing yields are not overwritten. Raw source rounding and cell-specific gaps remain in those providers. Cell-share metadata now refers only to scalable hardware; total installed pack also includes fixed unit-valued control hardware.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 This dataset provides 1 kWh of battery gross capacity (NOT net), using a Li-ion NMC111 battery. Specific cell energy density in 2020: (min, mean, max) 0.150, 0.180, 0.190 kWh/kg cell. Battery management (BoP) mass share: 27%. Battery energy density in 2020: 0.13 kWh/kg battery. Battery mass per kWh: 7.6 kg. Lifetime: 1'000-1'800 cycles. Source for parameters: Hasselwander, S.; Meyer, M.; Österle, I. Techno-Economic Analysis of Different Battery Cell Chemistries for the Passenger Vehicle Market. Batteries 2023, 9, 379. https://doi.org/10.3390/batteries9070379.</t>
         </is>
@@ -8330,80 +8352,98 @@
     <row r="24" spans="1:14" ns3:dyDescent="0.2">
       <c r="A24" t="inlineStr">
         <is>
-          <t>market for battery hardware, Li-ion, NMC111, engineering reference</t>
+          <t>market for battery cells, Li-ion, NMC111, density-scaled reference</t>
         </is>
       </c>
       <c r="B24" s="3">
-        <f>7.372463889120817</f>
-        <v>7.372463889120817</v>
-      </c>
-      <c r="C24" t="s">
-        <v>7</v>
-      </c>
-      <c r="D24" t="s">
-        <v>3</v>
-      </c>
-      <c r="E24" t="s">
-        <v>14</v>
+        <f>5.555555555555555</f>
+        <v>5.555555555555555</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>battery hardware, Li-ion, NMC111, engineering reference</t>
+          <t>market for battery cells, Li-ion, NMC111, density-scaled reference</t>
         </is>
       </c>
       <c r="G24">
         <v>5</v>
       </c>
       <c r="H24" s="7">
-        <f>7.372463889120817</f>
-        <v>7.372463889120817</v>
+        <f>5.555555555555555</f>
+        <v>5.555555555555555</v>
       </c>
       <c r="I24" s="7">
-        <f>6.984439473903931</f>
-        <v>6.984439473903931</v>
+        <f>5.263157894736842</f>
+        <v>5.263157894736842</v>
       </c>
       <c r="J24" s="7">
-        <f>9.478882143155333</f>
-        <v>9.478882143155333</v>
+        <f>7.142857142857141</f>
+        <v>7.142857142857141</v>
       </c>
     </row>
     <row r="25" spans="1:14" ns3:dyDescent="0.2">
-      <c r="A25" t="s">
-        <v>53</v>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>battery fixed noncell hardware, Li-ion, NMC111, baseline-kWh reference</t>
+        </is>
       </c>
       <c r="B25" s="3">
-        <f>-7.372463889120817</f>
-        <v>-7.372463889120817</v>
-      </c>
-      <c r="C25" t="s">
-        <v>7</v>
-      </c>
-      <c r="D25" t="s">
-        <v>3</v>
-      </c>
-      <c r="E25" t="s">
-        <v>14</v>
-      </c>
-      <c r="F25" t="s">
-        <v>54</v>
+        <f>1</f>
+        <v>1</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>battery fixed noncell hardware, Li-ion, NMC111, baseline-kWh reference</t>
+        </is>
       </c>
       <c r="G25">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H25" s="7">
-        <f>-7.372463889120817</f>
-        <v>-7.372463889120817</v>
+        <f>1</f>
+        <v>1</v>
       </c>
       <c r="I25" s="7">
-        <f>-9.478882143155333</f>
-        <v>-9.478882143155333</v>
+        <f>1</f>
+        <v>1</v>
       </c>
       <c r="J25" s="7">
-        <f>-6.984439473903931</f>
-        <v>-6.984439473903931</v>
-      </c>
-      <c r="K25" t="b">
-        <v>1</v>
+        <f>1</f>
+        <v>1</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="M25" s="7"/>
       <c r="N25" s="7"/>
@@ -8452,7 +8492,9 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. Chemistry=NMC532; geometry proxy=NMC622; cellmass=108.03kg, scalablehardware=145.74kg, assumed cellbaseline=0.2kWh/kg, grossreference=21.606kWh, fixedcontrolmass=6.538kg. Retained listed hardware material coefficients sum1kg/kg; upstream cell/processing yields are not overwritten. Raw source rounding and cell-specific gaps remain in those providers. Cell-share metadata now refers only to scalable hardware; total installed pack also includes fixed unit-valued control hardware.
+          <t>APPROVED STATIONARY CELL-ONLY DENSITY LEARNING, issue64,2026-10-18. Carry the issue63 fixed-noncell boundary through to six stationary lithium-ion capacity references. Preserve original stationary chemistry,baseline complete-pack materials,controls and capacity. Copy the corresponding mobile capacity references at the same chemistry-specific kgcell/kWh and fixed-noncell unit/kWh; these suppliers use the identical existing source pack architecture already used by stationary inventories. This does not transfer vehicle operation,chargers or roads into stationary storage. Only cell manufacture and its pairedcell disposal follow the existing cell-density curve. Noncellcase,busbar,coolant,packaging and associated disposal remain fixed inside the existing unit provider; central/module controls are already supplied once and treated by their own helper. Keep the stationary capacity activity identities so existing stationary scenario markets and dispatch/efficiency assumptions remain. There is no additional outer purchase of mobile capacity, no repeated density scaling and no second waste treatment. LFP,NMC111,NMC532,NMC622,NMC811,NMC955 baseline material/service vectors must match their pre-change stationary references,not only totalkg. The existing mobile geometry is an explicit shared engineering design; stationary-specific container/cooling/inverter topology and replacement lives are not validated by this change. No runtime,YAML or native edits; uncertainty on scalablecell quantity retained, fixedhardware deterministic as inissue63. Sodium-ion stationary already forwards1kWh to its corrected common capacity and needs no second change. Home-storage,leadacid and flowbattery designs remain separate.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. Chemistry=NMC532; geometry proxy=NMC622; cellmass=108.03kg, scalablehardware=145.74kg, assumed cellbaseline=0.2kWh/kg, grossreference=21.606kWh, fixedcontrolmass=6.538kg. Retained listed hardware material coefficients sum1kg/kg; upstream cell/processing yields are not overwritten. Raw source rounding and cell-specific gaps remain in those providers. Cell-share metadata now refers only to scalable hardware; total installed pack also includes fixed unit-valued control hardware.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 This dataset provides 1 kWh of battery gross capacity (NOT net), using a Li-ion NMC532 battery. Specific energy density in 2020: (min, mean, max) 0.170, 0.200, 0.220 kWh/kg cell. Battery management (BoP) mass share: 27%. Battery energy density in 2020: 0.150 kWh/kg battery. Battery mass per kWh: 6.95 kg. Lifetime: 1'000-1'500 cycles. Source for parameters: Hasselwander, S.; Meyer, M.; Österle, I. Techno-Economic Analysis of Different Battery Cell Chemistries for the Passenger Vehicle Market. Batteries 2023, 9, 379. https://doi.org/10.3390/batteries9070379.</t>
         </is>
@@ -8566,80 +8608,98 @@
     <row r="37" spans="1:14" ns3:dyDescent="0.2">
       <c r="A37" t="inlineStr">
         <is>
-          <t>market for battery hardware, Li-ion, NMC532, engineering reference</t>
+          <t>market for battery cells, Li-ion, NMC532, density-scaled reference</t>
         </is>
       </c>
       <c r="B37" s="3">
-        <f>6.7453485143015826</f>
-        <v>6.7453485143015826</v>
-      </c>
-      <c r="C37" t="s">
-        <v>7</v>
-      </c>
-      <c r="D37" t="s">
-        <v>3</v>
-      </c>
-      <c r="E37" t="s">
-        <v>14</v>
+        <f>4.999999999999999</f>
+        <v>4.999999999999999</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>battery hardware, Li-ion, NMC532, engineering reference</t>
+          <t>market for battery cells, Li-ion, NMC532, density-scaled reference</t>
         </is>
       </c>
       <c r="G37">
         <v>5</v>
       </c>
       <c r="H37" s="7">
-        <f>6.7453485143015826</f>
-        <v>6.7453485143015826</v>
+        <f>4.999999999999999</f>
+        <v>4.999999999999999</v>
       </c>
       <c r="I37" s="3">
-        <f>6.132135013001438</f>
-        <v>6.132135013001438</v>
+        <f>4.545454545454544</f>
+        <v>4.545454545454544</v>
       </c>
       <c r="J37" s="3">
-        <f>7.9357041344724495</f>
-        <v>7.9357041344724495</v>
+        <f>5.882352941176469</f>
+        <v>5.882352941176469</v>
       </c>
     </row>
     <row r="38" spans="1:14" ns3:dyDescent="0.2">
-      <c r="A38" t="s">
-        <v>53</v>
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>battery fixed noncell hardware, Li-ion, NMC532, baseline-kWh reference</t>
+        </is>
       </c>
       <c r="B38" s="3">
-        <f>-6.7453485143015826</f>
-        <v>-6.7453485143015826</v>
-      </c>
-      <c r="C38" t="s">
-        <v>7</v>
-      </c>
-      <c r="D38" t="s">
-        <v>3</v>
-      </c>
-      <c r="E38" t="s">
-        <v>14</v>
-      </c>
-      <c r="F38" t="s">
-        <v>54</v>
+        <f>1</f>
+        <v>1</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>battery fixed noncell hardware, Li-ion, NMC532, baseline-kWh reference</t>
+        </is>
       </c>
       <c r="G38">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H38" s="7">
-        <f>-6.7453485143015826</f>
-        <v>-6.7453485143015826</v>
+        <f>1</f>
+        <v>1</v>
       </c>
       <c r="I38" s="3">
-        <f>-7.9357041344724495</f>
-        <v>-7.9357041344724495</v>
+        <f>1</f>
+        <v>1</v>
       </c>
       <c r="J38" s="3">
-        <f>-6.132135013001438</f>
-        <v>-6.132135013001438</v>
-      </c>
-      <c r="K38" t="b">
-        <v>1</v>
+        <f>1</f>
+        <v>1</v>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="M38" s="3"/>
       <c r="N38" s="3"/>
@@ -8688,7 +8748,9 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. Chemistry=NMC622; geometry proxy=NMC622; cellmass=108.03kg, scalablehardware=145.74kg, assumed cellbaseline=0.24kWh/kg, grossreference=25.9272kWh, fixedcontrolmass=6.538kg. Retained listed hardware material coefficients sum1kg/kg; upstream cell/processing yields are not overwritten. Raw source rounding and cell-specific gaps remain in those providers. Cell-share metadata now refers only to scalable hardware; total installed pack also includes fixed unit-valued control hardware.
+          <t>APPROVED STATIONARY CELL-ONLY DENSITY LEARNING, issue64,2026-10-18. Carry the issue63 fixed-noncell boundary through to six stationary lithium-ion capacity references. Preserve original stationary chemistry,baseline complete-pack materials,controls and capacity. Copy the corresponding mobile capacity references at the same chemistry-specific kgcell/kWh and fixed-noncell unit/kWh; these suppliers use the identical existing source pack architecture already used by stationary inventories. This does not transfer vehicle operation,chargers or roads into stationary storage. Only cell manufacture and its pairedcell disposal follow the existing cell-density curve. Noncellcase,busbar,coolant,packaging and associated disposal remain fixed inside the existing unit provider; central/module controls are already supplied once and treated by their own helper. Keep the stationary capacity activity identities so existing stationary scenario markets and dispatch/efficiency assumptions remain. There is no additional outer purchase of mobile capacity, no repeated density scaling and no second waste treatment. LFP,NMC111,NMC532,NMC622,NMC811,NMC955 baseline material/service vectors must match their pre-change stationary references,not only totalkg. The existing mobile geometry is an explicit shared engineering design; stationary-specific container/cooling/inverter topology and replacement lives are not validated by this change. No runtime,YAML or native edits; uncertainty on scalablecell quantity retained, fixedhardware deterministic as inissue63. Sodium-ion stationary already forwards1kWh to its corrected common capacity and needs no second change. Home-storage,leadacid and flowbattery designs remain separate.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. Chemistry=NMC622; geometry proxy=NMC622; cellmass=108.03kg, scalablehardware=145.74kg, assumed cellbaseline=0.24kWh/kg, grossreference=25.9272kWh, fixedcontrolmass=6.538kg. Retained listed hardware material coefficients sum1kg/kg; upstream cell/processing yields are not overwritten. Raw source rounding and cell-specific gaps remain in those providers. Cell-share metadata now refers only to scalable hardware; total installed pack also includes fixed unit-valued control hardware.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 This dataset provides 1 kWh of battery gross capacity (NOT net), using a Li-ion NMC622 battery. Specific energy density in 2020: (min, mean, max) 0.200, 0.240, 0.280 kWh/kg cell. Battery management (BoP) mass share: 27%. Battery energy density in 2020: 0.180 kWh/kg battery. Battery mass per kWh: 6.85 kg. Lifetime: 1'000-1'500 cycles. Source for parameters: Hasselwander, S.; Meyer, M.; Österle, I. Techno-Economic Analysis of Different Battery Cell Chemistries for the Passenger Vehicle Market. Batteries 2023, 9, 379. https://doi.org/10.3390/batteries9070379.</t>
         </is>
@@ -8804,80 +8866,98 @@
     <row r="50" spans="1:14" ns3:dyDescent="0.2">
       <c r="A50" t="inlineStr">
         <is>
-          <t>market for battery hardware, Li-ion, NMC622, engineering reference</t>
+          <t>market for battery cells, Li-ion, NMC622, density-scaled reference</t>
         </is>
       </c>
       <c r="B50" s="3">
-        <f>5.621123761917986</f>
-        <v>5.621123761917986</v>
-      </c>
-      <c r="C50" t="s">
-        <v>7</v>
-      </c>
-      <c r="D50" t="s">
-        <v>3</v>
-      </c>
-      <c r="E50" t="s">
-        <v>14</v>
+        <f>4.166666666666667</f>
+        <v>4.166666666666667</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>battery hardware, Li-ion, NMC622, engineering reference</t>
+          <t>market for battery cells, Li-ion, NMC622, density-scaled reference</t>
         </is>
       </c>
       <c r="G50">
         <v>5</v>
       </c>
       <c r="H50" s="7">
-        <f>5.621123761917986</f>
-        <v>5.621123761917986</v>
+        <f>4.166666666666667</f>
+        <v>4.166666666666667</v>
       </c>
       <c r="I50" s="3">
-        <f>4.818106081643988</f>
-        <v>4.818106081643988</v>
+        <f>3.571428571428571</f>
+        <v>3.571428571428571</v>
       </c>
       <c r="J50" s="3">
-        <f>6.745348514301584</f>
-        <v>6.745348514301584</v>
+        <f>5.000000000000001</f>
+        <v>5.000000000000001</v>
       </c>
     </row>
     <row r="51" spans="1:14" ns3:dyDescent="0.2">
-      <c r="A51" t="s">
-        <v>53</v>
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>battery fixed noncell hardware, Li-ion, NMC622, baseline-kWh reference</t>
+        </is>
       </c>
       <c r="B51" s="3">
-        <f>-5.621123761917986</f>
-        <v>-5.621123761917986</v>
-      </c>
-      <c r="C51" t="s">
-        <v>7</v>
-      </c>
-      <c r="D51" t="s">
-        <v>3</v>
-      </c>
-      <c r="E51" t="s">
-        <v>14</v>
-      </c>
-      <c r="F51" t="s">
-        <v>54</v>
+        <f>1</f>
+        <v>1</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>battery fixed noncell hardware, Li-ion, NMC622, baseline-kWh reference</t>
+        </is>
       </c>
       <c r="G51">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H51" s="7">
-        <f>-5.621123761917986</f>
-        <v>-5.621123761917986</v>
+        <f>1</f>
+        <v>1</v>
       </c>
       <c r="I51" s="3">
-        <f>-6.745348514301584</f>
-        <v>-6.745348514301584</v>
+        <f>1</f>
+        <v>1</v>
       </c>
       <c r="J51" s="3">
-        <f>-4.818106081643988</f>
-        <v>-4.818106081643988</v>
-      </c>
-      <c r="K51" t="b">
-        <v>1</v>
+        <f>1</f>
+        <v>1</v>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="M51" s="3"/>
       <c r="N51" s="3"/>
@@ -8926,7 +9006,9 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. Chemistry=NMC811; geometry proxy=NMC811; cellmass=112.37kg, scalablehardware=151.63000000000002kg, assumed cellbaseline=0.28kWh/kg, grossreference=31.463600000000003kWh, fixedcontrolmass=6.568kg. Retained listed hardware material coefficients sum1kg/kg; upstream cell/processing yields are not overwritten. Raw source rounding and cell-specific gaps remain in those providers. Cell-share metadata now refers only to scalable hardware; total installed pack also includes fixed unit-valued control hardware.
+          <t>APPROVED STATIONARY CELL-ONLY DENSITY LEARNING, issue64,2026-10-18. Carry the issue63 fixed-noncell boundary through to six stationary lithium-ion capacity references. Preserve original stationary chemistry,baseline complete-pack materials,controls and capacity. Copy the corresponding mobile capacity references at the same chemistry-specific kgcell/kWh and fixed-noncell unit/kWh; these suppliers use the identical existing source pack architecture already used by stationary inventories. This does not transfer vehicle operation,chargers or roads into stationary storage. Only cell manufacture and its pairedcell disposal follow the existing cell-density curve. Noncellcase,busbar,coolant,packaging and associated disposal remain fixed inside the existing unit provider; central/module controls are already supplied once and treated by their own helper. Keep the stationary capacity activity identities so existing stationary scenario markets and dispatch/efficiency assumptions remain. There is no additional outer purchase of mobile capacity, no repeated density scaling and no second waste treatment. LFP,NMC111,NMC532,NMC622,NMC811,NMC955 baseline material/service vectors must match their pre-change stationary references,not only totalkg. The existing mobile geometry is an explicit shared engineering design; stationary-specific container/cooling/inverter topology and replacement lives are not validated by this change. No runtime,YAML or native edits; uncertainty on scalablecell quantity retained, fixedhardware deterministic as inissue63. Sodium-ion stationary already forwards1kWh to its corrected common capacity and needs no second change. Home-storage,leadacid and flowbattery designs remain separate.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. Chemistry=NMC811; geometry proxy=NMC811; cellmass=112.37kg, scalablehardware=151.63000000000002kg, assumed cellbaseline=0.28kWh/kg, grossreference=31.463600000000003kWh, fixedcontrolmass=6.568kg. Retained listed hardware material coefficients sum1kg/kg; upstream cell/processing yields are not overwritten. Raw source rounding and cell-specific gaps remain in those providers. Cell-share metadata now refers only to scalable hardware; total installed pack also includes fixed unit-valued control hardware.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 This dataset provides 1 kWh of battery gross capacity (not NET), using a Li-ion NMC811 battery. Specific energy density in 2020: (min, mean, max) 0.240, 0.280, 0.340 kWh/kg cell. Battery management (BoP) mass share: 29%. Battery energy density in 2020: 0.20 kWh/kg battery. Battery mass per kWh: 5.03 kg. Lifetime: 1'000-1'200 cycles. Source for parameters: Hasselwander, S.; Meyer, M.; Österle, I. Techno-Economic Analysis of Different Battery Cell Chemistries for the Passenger Vehicle Market. Batteries 2023, 9, 379. https://doi.org/10.3390/batteries9070379.</t>
         </is>
@@ -9043,80 +9125,98 @@
     <row r="63" spans="1:14" ns3:dyDescent="0.2">
       <c r="A63" t="inlineStr">
         <is>
-          <t>market for battery hardware, Li-ion, NMC811, engineering reference</t>
+          <t>market for battery cells, Li-ion, NMC811, density-scaled reference</t>
         </is>
       </c>
       <c r="B63" s="3">
-        <f>4.819219669713574</f>
-        <v>4.819219669713574</v>
-      </c>
-      <c r="C63" t="s">
-        <v>7</v>
-      </c>
-      <c r="D63" t="s">
-        <v>3</v>
-      </c>
-      <c r="E63" t="s">
-        <v>14</v>
+        <f>3.571428571428571</f>
+        <v>3.571428571428571</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>battery hardware, Li-ion, NMC811, engineering reference</t>
+          <t>market for battery cells, Li-ion, NMC811, density-scaled reference</t>
         </is>
       </c>
       <c r="G63">
         <v>5</v>
       </c>
       <c r="H63" s="7">
-        <f>4.819219669713574</f>
-        <v>4.819219669713574</v>
+        <f>3.571428571428571</f>
+        <v>3.571428571428571</v>
       </c>
       <c r="I63" s="3">
-        <f>3.96876913976412</f>
-        <v>3.96876913976412</v>
+        <f>2.9411764705882355</f>
+        <v>2.9411764705882355</v>
       </c>
       <c r="J63" s="3">
-        <f>5.622422947999169</f>
-        <v>5.622422947999169</v>
+        <f>4.166666666666666</f>
+        <v>4.166666666666666</v>
       </c>
     </row>
     <row r="64" spans="1:14" ns3:dyDescent="0.2">
-      <c r="A64" t="s">
-        <v>53</v>
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>battery fixed noncell hardware, Li-ion, NMC811, baseline-kWh reference</t>
+        </is>
       </c>
       <c r="B64" s="3">
-        <f>-4.819219669713574</f>
-        <v>-4.819219669713574</v>
-      </c>
-      <c r="C64" t="s">
-        <v>7</v>
-      </c>
-      <c r="D64" t="s">
-        <v>3</v>
-      </c>
-      <c r="E64" t="s">
-        <v>14</v>
-      </c>
-      <c r="F64" t="s">
-        <v>54</v>
+        <f>1</f>
+        <v>1</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>battery fixed noncell hardware, Li-ion, NMC811, baseline-kWh reference</t>
+        </is>
       </c>
       <c r="G64">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H64" s="7">
-        <f>-4.819219669713574</f>
-        <v>-4.819219669713574</v>
+        <f>1</f>
+        <v>1</v>
       </c>
       <c r="I64" s="3">
-        <f>-5.622422947999169</f>
-        <v>-5.622422947999169</v>
+        <f>1</f>
+        <v>1</v>
       </c>
       <c r="J64" s="3">
-        <f>-3.96876913976412</f>
-        <v>-3.96876913976412</v>
-      </c>
-      <c r="K64" t="b">
-        <v>1</v>
+        <f>1</f>
+        <v>1</v>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="M64" s="3"/>
       <c r="N64" s="3"/>
@@ -9165,7 +9265,9 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. Chemistry=NMC955; geometry proxy=NMC622; cellmass=108.03kg, scalablehardware=145.74kg, assumed cellbaseline=0.34kWh/kg, grossreference=36.7302kWh, fixedcontrolmass=6.538kg. Retained listed hardware material coefficients sum1kg/kg; upstream cell/processing yields are not overwritten. Raw source rounding and cell-specific gaps remain in those providers. Cell-share metadata now refers only to scalable hardware; total installed pack also includes fixed unit-valued control hardware.
+          <t>APPROVED STATIONARY CELL-ONLY DENSITY LEARNING, issue64,2026-10-18. Carry the issue63 fixed-noncell boundary through to six stationary lithium-ion capacity references. Preserve original stationary chemistry,baseline complete-pack materials,controls and capacity. Copy the corresponding mobile capacity references at the same chemistry-specific kgcell/kWh and fixed-noncell unit/kWh; these suppliers use the identical existing source pack architecture already used by stationary inventories. This does not transfer vehicle operation,chargers or roads into stationary storage. Only cell manufacture and its pairedcell disposal follow the existing cell-density curve. Noncellcase,busbar,coolant,packaging and associated disposal remain fixed inside the existing unit provider; central/module controls are already supplied once and treated by their own helper. Keep the stationary capacity activity identities so existing stationary scenario markets and dispatch/efficiency assumptions remain. There is no additional outer purchase of mobile capacity, no repeated density scaling and no second waste treatment. LFP,NMC111,NMC532,NMC622,NMC811,NMC955 baseline material/service vectors must match their pre-change stationary references,not only totalkg. The existing mobile geometry is an explicit shared engineering design; stationary-specific container/cooling/inverter topology and replacement lives are not validated by this change. No runtime,YAML or native edits; uncertainty on scalablecell quantity retained, fixedhardware deterministic as inissue63. Sodium-ion stationary already forwards1kWh to its corrected common capacity and needs no second change. Home-storage,leadacid and flowbattery designs remain separate.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. Chemistry=NMC955; geometry proxy=NMC622; cellmass=108.03kg, scalablehardware=145.74kg, assumed cellbaseline=0.34kWh/kg, grossreference=36.7302kWh, fixedcontrolmass=6.538kg. Retained listed hardware material coefficients sum1kg/kg; upstream cell/processing yields are not overwritten. Raw source rounding and cell-specific gaps remain in those providers. Cell-share metadata now refers only to scalable hardware; total installed pack also includes fixed unit-valued control hardware.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 Provides 1 kWh gross battery capacity using a Li-ion NMC955 pack. The complete-pack manufacturing recipe in lci-batteries-NMC955-LTO.xlsx contains 0.72591 kg cells per kg pack (72.591% cells, 27.409% other pack components). Use this manufactured cell fraction instead of the former generic 71% assumption. At the retained 2020 cell energy densities (minimum/mean/maximum) of 0.300/0.340/0.380 kWh per kg cell, pack mass is 1/(cell density * cell mass share): mean 4.051709537805285 kg/kWh, range 3.625213796983677 to 4.591937476179324 kg/kWh. Manufacturing and end of life use equal pack mass; signed disposal bounds mirror the manufacturing bounds. Source density/lifetime parameters: Hasselwander et al. (2023), https://doi.org/10.3390/batteries9070379. The source lifetime of 1000-1500 cycles and the existing future density trajectory remain modelling assumptions. Matching cell fraction is an allocation correction, not validation of practical cell performance. Rebuild scenario databases to apply.</t>
         </is>
@@ -9279,80 +9381,98 @@
     <row r="76" spans="1:14" ns3:dyDescent="0.2">
       <c r="A76" t="inlineStr">
         <is>
-          <t>market for battery hardware, Li-ion, NMC955, engineering reference</t>
+          <t>market for battery cells, Li-ion, NMC955, density-scaled reference</t>
         </is>
       </c>
       <c r="B76" s="3">
-        <f>3.967852067236225</f>
-        <v>3.967852067236225</v>
-      </c>
-      <c r="C76" t="s">
-        <v>7</v>
-      </c>
-      <c r="D76" t="s">
-        <v>3</v>
-      </c>
-      <c r="E76" t="s">
-        <v>14</v>
+        <f>2.941176470588235</f>
+        <v>2.941176470588235</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>battery hardware, Li-ion, NMC955, engineering reference</t>
+          <t>market for battery cells, Li-ion, NMC955, density-scaled reference</t>
         </is>
       </c>
       <c r="G76">
         <v>5</v>
       </c>
       <c r="H76" s="7">
-        <f>3.967852067236225</f>
-        <v>3.967852067236225</v>
+        <f>2.941176470588235</f>
+        <v>2.941176470588235</v>
       </c>
       <c r="I76" s="3">
-        <f>3.550183428579781</f>
-        <v>3.550183428579781</v>
+        <f>2.6315789473684212</f>
+        <v>2.6315789473684212</v>
       </c>
       <c r="J76" s="3">
-        <f>4.496899009534389</f>
-        <v>4.496899009534389</v>
+        <f>3.333333333333334</f>
+        <v>3.333333333333334</v>
       </c>
     </row>
     <row r="77" spans="1:14" ns3:dyDescent="0.2">
-      <c r="A77" t="s">
-        <v>53</v>
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>battery fixed noncell hardware, Li-ion, NMC955, baseline-kWh reference</t>
+        </is>
       </c>
       <c r="B77" s="3">
-        <f>-3.967852067236225</f>
-        <v>-3.967852067236225</v>
-      </c>
-      <c r="C77" t="s">
-        <v>7</v>
-      </c>
-      <c r="D77" t="s">
-        <v>3</v>
-      </c>
-      <c r="E77" t="s">
-        <v>14</v>
-      </c>
-      <c r="F77" t="s">
-        <v>54</v>
+        <f>1</f>
+        <v>1</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>battery fixed noncell hardware, Li-ion, NMC955, baseline-kWh reference</t>
+        </is>
       </c>
       <c r="G77">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H77" s="7">
-        <f>-3.967852067236225</f>
-        <v>-3.967852067236225</v>
+        <f>1</f>
+        <v>1</v>
       </c>
       <c r="I77" s="3">
-        <f>-4.496899009534389</f>
-        <v>-4.496899009534389</v>
+        <f>1</f>
+        <v>1</v>
       </c>
       <c r="J77" s="3">
-        <f>-3.550183428579781</f>
-        <v>-3.550183428579781</v>
-      </c>
-      <c r="K77" t="b">
-        <v>1</v>
+        <f>1</f>
+        <v>1</v>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="M77" s="3"/>
       <c r="N77" s="3"/>

--- a/premise/data/additional_inventories/lci-battery-capacity.xlsx
+++ b/premise/data/additional_inventories/lci-battery-capacity.xlsx
@@ -918,7 +918,7 @@
     <row r="13" spans="1:14" ns3:dyDescent="0.2">
       <c r="A13" t="inlineStr">
         <is>
-          <t>market for battery cells, Li-ion, LFP, density-scaled reference</t>
+          <t xml:space="preserve">market for battery cell, Li-ion, LFP, including end-of-life treatment</t>
         </is>
       </c>
       <c r="B13" s="7">
@@ -938,7 +938,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>market for battery cells, Li-ion, LFP, density-scaled reference</t>
+          <t xml:space="preserve">battery cell, Li-ion, LFP, including end-of-life treatment</t>
         </is>
       </c>
       <c r="G13">
@@ -960,7 +960,7 @@
     <row r="14" spans="1:14" ns3:dyDescent="0.2">
       <c r="A14" t="inlineStr">
         <is>
-          <t>battery fixed noncell hardware, Li-ion, LFP, baseline-kWh reference</t>
+          <t xml:space="preserve">battery pack component production and end-of-life treatment, Li-ion, LFP, without cells and controls</t>
         </is>
       </c>
       <c r="B14" s="7">
@@ -982,7 +982,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>battery fixed noncell hardware, Li-ion, LFP, baseline-kWh reference</t>
+          <t xml:space="preserve">battery pack components, Li-ion, LFP, without cells and controls</t>
         </is>
       </c>
       <c r="G14">
@@ -1011,7 +1011,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>battery monitoring and central controls, LFP, engineering reference</t>
+          <t xml:space="preserve">battery monitoring and central control system production, Li-ion, LFP</t>
         </is>
       </c>
       <c r="B15">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>battery monitoring and central controls, LFP, engineering reference</t>
+          <t xml:space="preserve">battery monitoring and central control system, Li-ion, LFP</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
     <row r="26" spans="1:14" ns3:dyDescent="0.2">
       <c r="A26" t="inlineStr">
         <is>
-          <t>market for battery cells, Li-ion, NMC111, density-scaled reference</t>
+          <t xml:space="preserve">market for battery cell, Li-ion, NMC111, including end-of-life treatment</t>
         </is>
       </c>
       <c r="B26" s="3">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>market for battery cells, Li-ion, NMC111, density-scaled reference</t>
+          <t xml:space="preserve">battery cell, Li-ion, NMC111, including end-of-life treatment</t>
         </is>
       </c>
       <c r="G26">
@@ -1210,7 +1210,7 @@
     <row r="27" spans="1:14" ns3:dyDescent="0.2">
       <c r="A27" t="inlineStr">
         <is>
-          <t>battery fixed noncell hardware, Li-ion, NMC111, baseline-kWh reference</t>
+          <t xml:space="preserve">battery pack component production and end-of-life treatment, Li-ion, NMC111, without cells and controls</t>
         </is>
       </c>
       <c r="B27" s="3">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>battery fixed noncell hardware, Li-ion, NMC111, baseline-kWh reference</t>
+          <t xml:space="preserve">battery pack components, Li-ion, NMC111, without cells and controls</t>
         </is>
       </c>
       <c r="G27">
@@ -1261,7 +1261,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>battery monitoring and central controls, NMC111, engineering reference</t>
+          <t xml:space="preserve">battery monitoring and central control system production, Li-ion, NMC111</t>
         </is>
       </c>
       <c r="B28">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>battery monitoring and central controls, NMC111, engineering reference</t>
+          <t xml:space="preserve">battery monitoring and central control system, Li-ion, NMC111</t>
         </is>
       </c>
     </row>
@@ -1418,7 +1418,7 @@
     <row r="39" spans="1:14" ns3:dyDescent="0.2">
       <c r="A39" t="inlineStr">
         <is>
-          <t>market for battery cells, Li-ion, NMC532, density-scaled reference</t>
+          <t xml:space="preserve">market for battery cell, Li-ion, NMC532, including end-of-life treatment</t>
         </is>
       </c>
       <c r="B39" s="3">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>market for battery cells, Li-ion, NMC532, density-scaled reference</t>
+          <t xml:space="preserve">battery cell, Li-ion, NMC532, including end-of-life treatment</t>
         </is>
       </c>
       <c r="G39">
@@ -1460,7 +1460,7 @@
     <row r="40" spans="1:14" ns3:dyDescent="0.2">
       <c r="A40" t="inlineStr">
         <is>
-          <t>battery fixed noncell hardware, Li-ion, NMC532, baseline-kWh reference</t>
+          <t xml:space="preserve">battery pack component production and end-of-life treatment, Li-ion, NMC532, without cells and controls</t>
         </is>
       </c>
       <c r="B40" s="3">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>battery fixed noncell hardware, Li-ion, NMC532, baseline-kWh reference</t>
+          <t xml:space="preserve">battery pack components, Li-ion, NMC532, without cells and controls</t>
         </is>
       </c>
       <c r="G40">
@@ -1511,7 +1511,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>battery monitoring and central controls, NMC532, engineering reference</t>
+          <t xml:space="preserve">battery monitoring and central control system production, Li-ion, NMC532</t>
         </is>
       </c>
       <c r="B41">
@@ -1534,7 +1534,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>battery monitoring and central controls, NMC532, engineering reference</t>
+          <t xml:space="preserve">battery monitoring and central control system, Li-ion, NMC532</t>
         </is>
       </c>
     </row>
@@ -1670,7 +1670,7 @@
     <row r="52" spans="1:14" ns3:dyDescent="0.2">
       <c r="A52" t="inlineStr">
         <is>
-          <t>market for battery cells, Li-ion, NMC622, density-scaled reference</t>
+          <t xml:space="preserve">market for battery cell, Li-ion, NMC622, including end-of-life treatment</t>
         </is>
       </c>
       <c r="B52" s="3">
@@ -1690,7 +1690,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>market for battery cells, Li-ion, NMC622, density-scaled reference</t>
+          <t xml:space="preserve">battery cell, Li-ion, NMC622, including end-of-life treatment</t>
         </is>
       </c>
       <c r="G52">
@@ -1712,7 +1712,7 @@
     <row r="53" spans="1:14" ns3:dyDescent="0.2">
       <c r="A53" t="inlineStr">
         <is>
-          <t>battery fixed noncell hardware, Li-ion, NMC622, baseline-kWh reference</t>
+          <t xml:space="preserve">battery pack component production and end-of-life treatment, Li-ion, NMC622, without cells and controls</t>
         </is>
       </c>
       <c r="B53" s="3">
@@ -1734,7 +1734,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>battery fixed noncell hardware, Li-ion, NMC622, baseline-kWh reference</t>
+          <t xml:space="preserve">battery pack components, Li-ion, NMC622, without cells and controls</t>
         </is>
       </c>
       <c r="G53">
@@ -1763,7 +1763,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>battery monitoring and central controls, NMC622, engineering reference</t>
+          <t xml:space="preserve">battery monitoring and central control system production, Li-ion, NMC622</t>
         </is>
       </c>
       <c r="B54">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>battery monitoring and central controls, NMC622, engineering reference</t>
+          <t xml:space="preserve">battery monitoring and central control system, Li-ion, NMC622</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
     <row r="65" spans="1:14" ns3:dyDescent="0.2">
       <c r="A65" t="inlineStr">
         <is>
-          <t>market for battery cells, Li-ion, NMC811, density-scaled reference</t>
+          <t xml:space="preserve">market for battery cell, Li-ion, NMC811, including end-of-life treatment</t>
         </is>
       </c>
       <c r="B65" s="3">
@@ -1943,7 +1943,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>market for battery cells, Li-ion, NMC811, density-scaled reference</t>
+          <t xml:space="preserve">battery cell, Li-ion, NMC811, including end-of-life treatment</t>
         </is>
       </c>
       <c r="G65">
@@ -1965,7 +1965,7 @@
     <row r="66" spans="1:14" ns3:dyDescent="0.2">
       <c r="A66" t="inlineStr">
         <is>
-          <t>battery fixed noncell hardware, Li-ion, NMC811, baseline-kWh reference</t>
+          <t xml:space="preserve">battery pack component production and end-of-life treatment, Li-ion, NMC811, without cells and controls</t>
         </is>
       </c>
       <c r="B66" s="3">
@@ -1987,7 +1987,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>battery fixed noncell hardware, Li-ion, NMC811, baseline-kWh reference</t>
+          <t xml:space="preserve">battery pack components, Li-ion, NMC811, without cells and controls</t>
         </is>
       </c>
       <c r="G66">
@@ -2016,7 +2016,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>battery monitoring and central controls, NMC811, engineering reference</t>
+          <t xml:space="preserve">battery monitoring and central control system production, Li-ion, NMC811</t>
         </is>
       </c>
       <c r="B67">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>battery monitoring and central controls, NMC811, engineering reference</t>
+          <t xml:space="preserve">battery monitoring and central control system, Li-ion, NMC811</t>
         </is>
       </c>
     </row>
@@ -2173,7 +2173,7 @@
     <row r="78" spans="1:14" ns3:dyDescent="0.2">
       <c r="A78" t="inlineStr">
         <is>
-          <t>market for battery cells, Li-ion, NMC955, density-scaled reference</t>
+          <t xml:space="preserve">market for battery cell, Li-ion, NMC955, including end-of-life treatment</t>
         </is>
       </c>
       <c r="B78" s="3">
@@ -2193,7 +2193,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>market for battery cells, Li-ion, NMC955, density-scaled reference</t>
+          <t xml:space="preserve">battery cell, Li-ion, NMC955, including end-of-life treatment</t>
         </is>
       </c>
       <c r="G78">
@@ -2215,7 +2215,7 @@
     <row r="79" spans="1:14" ns3:dyDescent="0.2">
       <c r="A79" t="inlineStr">
         <is>
-          <t>battery fixed noncell hardware, Li-ion, NMC955, baseline-kWh reference</t>
+          <t xml:space="preserve">battery pack component production and end-of-life treatment, Li-ion, NMC955, without cells and controls</t>
         </is>
       </c>
       <c r="B79" s="3">
@@ -2237,7 +2237,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>battery fixed noncell hardware, Li-ion, NMC955, baseline-kWh reference</t>
+          <t xml:space="preserve">battery pack components, Li-ion, NMC955, without cells and controls</t>
         </is>
       </c>
       <c r="G79">
@@ -2266,7 +2266,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>battery monitoring and central controls, NMC955, engineering reference</t>
+          <t xml:space="preserve">battery monitoring and central control system production, Li-ion, NMC955</t>
         </is>
       </c>
       <c r="B80">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>battery monitoring and central controls, NMC955, engineering reference</t>
+          <t xml:space="preserve">battery monitoring and central control system, Li-ion, NMC955</t>
         </is>
       </c>
     </row>
@@ -2423,7 +2423,7 @@
     <row r="91" spans="1:14" ns3:dyDescent="0.2">
       <c r="A91" t="inlineStr">
         <is>
-          <t>market for battery cells, Li-ion, NCA, density-scaled reference</t>
+          <t xml:space="preserve">market for battery cell, Li-ion, NCA, including end-of-life treatment</t>
         </is>
       </c>
       <c r="B91" s="3">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>market for battery cells, Li-ion, NCA, density-scaled reference</t>
+          <t xml:space="preserve">battery cell, Li-ion, NCA, including end-of-life treatment</t>
         </is>
       </c>
       <c r="G91">
@@ -2465,7 +2465,7 @@
     <row r="92" spans="1:14" ns3:dyDescent="0.2">
       <c r="A92" t="inlineStr">
         <is>
-          <t>battery fixed noncell hardware, Li-ion, NCA, baseline-kWh reference</t>
+          <t xml:space="preserve">battery pack component production and end-of-life treatment, Li-ion, NCA, without cells and controls</t>
         </is>
       </c>
       <c r="B92" s="3">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>battery fixed noncell hardware, Li-ion, NCA, baseline-kWh reference</t>
+          <t xml:space="preserve">battery pack components, Li-ion, NCA, without cells and controls</t>
         </is>
       </c>
       <c r="G92">
@@ -2516,7 +2516,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>battery monitoring and central controls, NCA, engineering reference</t>
+          <t xml:space="preserve">battery monitoring and central control system production, Li-ion, NCA</t>
         </is>
       </c>
       <c r="B93">
@@ -2539,7 +2539,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>battery monitoring and central controls, NCA, engineering reference</t>
+          <t xml:space="preserve">battery monitoring and central control system, Li-ion, NCA</t>
         </is>
       </c>
     </row>
@@ -2675,7 +2675,7 @@
     <row r="104" spans="1:14" ns3:dyDescent="0.2">
       <c r="A104" t="inlineStr">
         <is>
-          <t>market for battery cells, Li-ion, LTO, density-scaled reference</t>
+          <t xml:space="preserve">market for battery cell, Li-ion, LTO, including end-of-life treatment</t>
         </is>
       </c>
       <c r="B104" s="3">
@@ -2695,7 +2695,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>market for battery cells, Li-ion, LTO, density-scaled reference</t>
+          <t xml:space="preserve">battery cell, Li-ion, LTO, including end-of-life treatment</t>
         </is>
       </c>
       <c r="G104">
@@ -2717,7 +2717,7 @@
     <row r="105" spans="1:14" ns3:dyDescent="0.2">
       <c r="A105" t="inlineStr">
         <is>
-          <t>battery fixed noncell hardware, Li-ion, LTO, baseline-kWh reference</t>
+          <t xml:space="preserve">battery pack component production and end-of-life treatment, Li-ion, LTO, without cells and controls</t>
         </is>
       </c>
       <c r="B105" s="3">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>battery fixed noncell hardware, Li-ion, LTO, baseline-kWh reference</t>
+          <t xml:space="preserve">battery pack components, Li-ion, LTO, without cells and controls</t>
         </is>
       </c>
       <c r="G105">
@@ -2768,7 +2768,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>battery monitoring and central controls, LTO, engineering reference</t>
+          <t xml:space="preserve">battery monitoring and central control system production, Li-ion, LTO</t>
         </is>
       </c>
       <c r="B106">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>battery monitoring and central controls, LTO, engineering reference</t>
+          <t xml:space="preserve">battery monitoring and central control system, Li-ion, LTO</t>
         </is>
       </c>
     </row>
@@ -2925,7 +2925,7 @@
     <row r="117" spans="1:14" ns3:dyDescent="0.2">
       <c r="A117" t="inlineStr">
         <is>
-          <t>market for battery cells, Li-ion, LiMn2O4, density-scaled reference</t>
+          <t xml:space="preserve">market for battery cell, Li-ion, LiMn2O4, including end-of-life treatment</t>
         </is>
       </c>
       <c r="B117" s="3">
@@ -2945,7 +2945,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>market for battery cells, Li-ion, LiMn2O4, density-scaled reference</t>
+          <t xml:space="preserve">battery cell, Li-ion, LiMn2O4, including end-of-life treatment</t>
         </is>
       </c>
       <c r="G117">
@@ -2967,7 +2967,7 @@
     <row r="118" spans="1:14" ns3:dyDescent="0.2">
       <c r="A118" t="inlineStr">
         <is>
-          <t>battery fixed noncell hardware, Li-ion, LiMn2O4, baseline-kWh reference</t>
+          <t xml:space="preserve">battery pack component production and end-of-life treatment, Li-ion, LiMn2O4, without cells and controls</t>
         </is>
       </c>
       <c r="B118" s="3">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>battery fixed noncell hardware, Li-ion, LiMn2O4, baseline-kWh reference</t>
+          <t xml:space="preserve">battery pack components, Li-ion, LiMn2O4, without cells and controls</t>
         </is>
       </c>
       <c r="G118">
@@ -3018,7 +3018,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>battery monitoring and central controls, LiMn2O4, engineering reference</t>
+          <t xml:space="preserve">battery monitoring and central control system production, Li-ion, LiMn2O4</t>
         </is>
       </c>
       <c r="B119">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>battery monitoring and central controls, LiMn2O4, engineering reference</t>
+          <t xml:space="preserve">battery monitoring and central control system, Li-ion, LiMn2O4</t>
         </is>
       </c>
     </row>
@@ -3177,7 +3177,7 @@
     <row r="130" spans="1:14" ns3:dyDescent="0.2">
       <c r="A130" t="inlineStr">
         <is>
-          <t>market for battery cells, Li-sulfur, Li-S, density-scaled reference</t>
+          <t xml:space="preserve">market for battery cell, Li-sulfur, Li-S, including end-of-life treatment</t>
         </is>
       </c>
       <c r="B130" s="3">
@@ -3197,7 +3197,7 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>market for battery cells, Li-sulfur, Li-S, density-scaled reference</t>
+          <t xml:space="preserve">battery cell, Li-sulfur, Li-S, including end-of-life treatment</t>
         </is>
       </c>
       <c r="G130">
@@ -3219,7 +3219,7 @@
     <row r="131" spans="1:14" ns3:dyDescent="0.2">
       <c r="A131" t="inlineStr">
         <is>
-          <t>battery fixed noncell hardware, Li-sulfur, Li-S, baseline-kWh reference</t>
+          <t xml:space="preserve">battery pack component production and end-of-life treatment, Li-sulfur, Li-S, without cells and controls</t>
         </is>
       </c>
       <c r="B131" s="3">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>battery fixed noncell hardware, Li-sulfur, Li-S, baseline-kWh reference</t>
+          <t xml:space="preserve">battery pack components, Li-sulfur, Li-S, without cells and controls</t>
         </is>
       </c>
       <c r="G131">
@@ -3270,7 +3270,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>battery controls and cooling, 16-module engineering reference</t>
+          <t xml:space="preserve">battery control and cooling system production, 16 modules</t>
         </is>
       </c>
       <c r="B132">
@@ -3293,7 +3293,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>battery controls and cooling, 16-module engineering reference</t>
+          <t xml:space="preserve">battery control and cooling system, 16 modules</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -3433,7 +3433,7 @@
     <row r="143" spans="1:14" ns3:dyDescent="0.2">
       <c r="A143" t="inlineStr">
         <is>
-          <t>market for battery cells, Li-ion, Li-O2, density-scaled reference</t>
+          <t xml:space="preserve">market for battery cell, Li-ion, Li-O2, including end-of-life treatment</t>
         </is>
       </c>
       <c r="B143" s="3">
@@ -3453,7 +3453,7 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>market for battery cells, Li-ion, Li-O2, density-scaled reference</t>
+          <t xml:space="preserve">battery cell, Li-ion, Li-O2, including end-of-life treatment</t>
         </is>
       </c>
       <c r="G143">
@@ -3475,7 +3475,7 @@
     <row r="144" spans="1:14" ns3:dyDescent="0.2">
       <c r="A144" t="inlineStr">
         <is>
-          <t>battery fixed noncell hardware, Li-ion, Li-O2, baseline-kWh reference</t>
+          <t xml:space="preserve">battery pack component production and end-of-life treatment, Li-ion, Li-O2, without cells and controls</t>
         </is>
       </c>
       <c r="B144" s="3">
@@ -3497,7 +3497,7 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>battery fixed noncell hardware, Li-ion, Li-O2, baseline-kWh reference</t>
+          <t xml:space="preserve">battery pack components, Li-ion, Li-O2, without cells and controls</t>
         </is>
       </c>
       <c r="G144">
@@ -3526,7 +3526,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>battery auxiliary lifecycle, Li-O2 engineering reference</t>
+          <t xml:space="preserve">battery auxiliaries supply and end-of-life treatment, lithium-oxygen</t>
         </is>
       </c>
       <c r="B145">
@@ -3549,7 +3549,7 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>battery auxiliary lifecycle, Li-O2 engineering reference</t>
+          <t xml:space="preserve">battery auxiliaries supply and end-of-life treatment, lithium-oxygen</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
@@ -3690,7 +3690,7 @@
     <row r="156" spans="1:14" ns3:dyDescent="0.2">
       <c r="A156" t="inlineStr">
         <is>
-          <t>market for battery cells, Sodium-ion, SiB, density-scaled reference</t>
+          <t xml:space="preserve">market for battery cell, Sodium-ion, SiB, including end-of-life treatment</t>
         </is>
       </c>
       <c r="B156" s="3">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>market for battery cells, Sodium-ion, SiB, density-scaled reference</t>
+          <t xml:space="preserve">battery cell, Sodium-ion, SiB, including end-of-life treatment</t>
         </is>
       </c>
       <c r="G156">
@@ -3732,7 +3732,7 @@
     <row r="157" spans="1:14" ns3:dyDescent="0.2">
       <c r="A157" t="inlineStr">
         <is>
-          <t>battery fixed noncell hardware, Sodium-ion, SiB, baseline-kWh reference</t>
+          <t xml:space="preserve">battery pack component production and end-of-life treatment, Sodium-ion, SiB, without cells and controls</t>
         </is>
       </c>
       <c r="B157" s="3">
@@ -3754,7 +3754,7 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>battery fixed noncell hardware, Sodium-ion, SiB, baseline-kWh reference</t>
+          <t xml:space="preserve">battery pack components, Sodium-ion, SiB, without cells and controls</t>
         </is>
       </c>
       <c r="G157">
@@ -3783,7 +3783,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>battery controls and cooling, 16-module engineering reference</t>
+          <t xml:space="preserve">battery control and cooling system production, 16 modules</t>
         </is>
       </c>
       <c r="B158">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>battery controls and cooling, 16-module engineering reference</t>
+          <t xml:space="preserve">battery control and cooling system, 16 modules</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>high-power battery capacity, FCEV car, engineering reference</t>
+          <t xml:space="preserve">market for electricity storage capacity, battery, high power, fuel cell passenger car</t>
         </is>
       </c>
     </row>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>high-power battery capacity, FCEV car, engineering reference</t>
+          <t xml:space="preserve">electricity storage capacity, high power, fuel cell passenger car</t>
         </is>
       </c>
     </row>
@@ -5631,7 +5631,8 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>APPROVED FCEV HIGH-POWER PACK ENGINEERING REFERENCES, item24, 2026-10-18. Toyota Mirai2 manufacturer https://newsroom.toyota.eu/introducing-the-all-new-toyota-mirai/; AKASOL AKASYSTEM15OEM37PRC May2021 https://www.act-news.com/wp-content/uploads/2020/11/210525_LowRes_AK_Datenblatt_AKASystem_15-OEM-37-PRC_2021_2159x2794mm_EN.pdf; Dai2018 Table8 https://publications.anl.gov/anlpubs/2018/10/146906.pdf. Match complete physical pack mass and nominal energy, not the changing BEV MIX. Car reference44.6kg/1.2432kWh (=310.8V*4Ah/1000),31.5kW for10seconds; truck reference238kg/25kWh,36kW continuous charge,50kW continuous RMS discharge,150kW10second discharge. Retain existing vehicle capacities/power sizing and lifetime replacement counts. These manufacturer ratings are NOT inferred from chemistry or treated as continuous pulse ratings. Material split remains an engineering proxy:70percent cells, as in the truck sizing source; assume the same70percent for cars. NMC622 cell manufacturing is a bulk-composition proxy, NOT a measured Mirai/AKASOL cell design or a validated high-power electrode/capacity recipe. Thus mass-equivalence is corrected while chemistry-specific metal intensities remain uncertain. Sensitivity cell share50-80percent and alternative documented high-power chemistries. One4.518kg central-control/protection assembly per reference pack; remaining mass is allocated using public Dai non-electronic hardware proportions. Car air-cooled reference excludes liquid coolant; unknown fan/duct design is embedded in the residual housing proxy, not independently validated. Truck liquid cooling retains Dai50/50 glycol/water proportions; pump/thermal ratings remain gaps. No module electronics are added on top of the central package; missing distributed monitoring is a coverage gap. All retained material inputs use100percent assembly retention reference; generic working services additional. Equal negative used-battery treatment equals complete manufactured reference mass, including controls, once; no duplicated control waste. These dedicated capacity providers are deliberately outside generic chemistry-density and MIX updates, preserving the already-declared fixed2020 FCEV hardware assumption through2050. Do not interpret corrected mass as a validated manufacturer BOM, annual procurement or primary/secondary content.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: high-power battery capacity, FCEV car, engineering reference. Former reference product: high-power battery capacity, FCEV car, engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED FCEV HIGH-POWER PACK ENGINEERING REFERENCES, item24, 2026-10-18. Toyota Mirai2 manufacturer https://newsroom.toyota.eu/introducing-the-all-new-toyota-mirai/; AKASOL AKASYSTEM15OEM37PRC May2021 https://www.act-news.com/wp-content/uploads/2020/11/210525_LowRes_AK_Datenblatt_AKASystem_15-OEM-37-PRC_2021_2159x2794mm_EN.pdf; Dai2018 Table8 https://publications.anl.gov/anlpubs/2018/10/146906.pdf. Match complete physical pack mass and nominal energy, not the changing BEV MIX. Car reference44.6kg/1.2432kWh (=310.8V*4Ah/1000),31.5kW for10seconds; truck reference238kg/25kWh,36kW continuous charge,50kW continuous RMS discharge,150kW10second discharge. Retain existing vehicle capacities/power sizing and lifetime replacement counts. These manufacturer ratings are NOT inferred from chemistry or treated as continuous pulse ratings. Material split remains an engineering proxy:70percent cells, as in the truck sizing source; assume the same70percent for cars. NMC622 cell manufacturing is a bulk-composition proxy, NOT a measured Mirai/AKASOL cell design or a validated high-power electrode/capacity recipe. Thus mass-equivalence is corrected while chemistry-specific metal intensities remain uncertain. Sensitivity cell share50-80percent and alternative documented high-power chemistries. One4.518kg central-control/protection assembly per reference pack; remaining mass is allocated using public Dai non-electronic hardware proportions. Car air-cooled reference excludes liquid coolant; unknown fan/duct design is embedded in the residual housing proxy, not independently validated. Truck liquid cooling retains Dai50/50 glycol/water proportions; pump/thermal ratings remain gaps. No module electronics are added on top of the central package; missing distributed monitoring is a coverage gap. All retained material inputs use100percent assembly retention reference; generic working services additional. Equal negative used-battery treatment equals complete manufactured reference mass, including controls, once; no duplicated control waste. These dedicated capacity providers are deliberately outside generic chemistry-density and MIX updates, preserving the already-declared fixed2020 FCEV hardware assumption through2050. Do not interpret corrected mass as a validated manufacturer BOM, annual procurement or primary/secondary content.</t>
         </is>
       </c>
     </row>
@@ -5687,7 +5688,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>high-power battery capacity, FCEV car, engineering reference</t>
+          <t xml:space="preserve">market for electricity storage capacity, battery, high power, fuel cell passenger car</t>
         </is>
       </c>
       <c r="B278">
@@ -5710,7 +5711,7 @@
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>high-power battery capacity, FCEV car, engineering reference</t>
+          <t xml:space="preserve">electricity storage capacity, high power, fuel cell passenger car</t>
         </is>
       </c>
     </row>
@@ -5747,7 +5748,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>battery central controls and protection, engineering reference</t>
+          <t xml:space="preserve">battery central control and protection unit production</t>
         </is>
       </c>
       <c r="B280">
@@ -5770,7 +5771,7 @@
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>battery central controls and protection, engineering reference</t>
+          <t xml:space="preserve">battery central control and protection unit</t>
         </is>
       </c>
     </row>
@@ -6052,7 +6053,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>high-power battery capacity, FCEV truck, engineering reference</t>
+          <t xml:space="preserve">market for electricity storage capacity, battery, high power, fuel cell truck</t>
         </is>
       </c>
     </row>
@@ -6086,7 +6087,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>high-power battery capacity, FCEV truck, engineering reference</t>
+          <t xml:space="preserve">electricity storage capacity, high power, fuel cell truck</t>
         </is>
       </c>
     </row>
@@ -6122,7 +6123,8 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>APPROVED FCEV HIGH-POWER PACK ENGINEERING REFERENCES, item24, 2026-10-18. Toyota Mirai2 manufacturer https://newsroom.toyota.eu/introducing-the-all-new-toyota-mirai/; AKASOL AKASYSTEM15OEM37PRC May2021 https://www.act-news.com/wp-content/uploads/2020/11/210525_LowRes_AK_Datenblatt_AKASystem_15-OEM-37-PRC_2021_2159x2794mm_EN.pdf; Dai2018 Table8 https://publications.anl.gov/anlpubs/2018/10/146906.pdf. Match complete physical pack mass and nominal energy, not the changing BEV MIX. Car reference44.6kg/1.2432kWh (=310.8V*4Ah/1000),31.5kW for10seconds; truck reference238kg/25kWh,36kW continuous charge,50kW continuous RMS discharge,150kW10second discharge. Retain existing vehicle capacities/power sizing and lifetime replacement counts. These manufacturer ratings are NOT inferred from chemistry or treated as continuous pulse ratings. Material split remains an engineering proxy:70percent cells, as in the truck sizing source; assume the same70percent for cars. NMC622 cell manufacturing is a bulk-composition proxy, NOT a measured Mirai/AKASOL cell design or a validated high-power electrode/capacity recipe. Thus mass-equivalence is corrected while chemistry-specific metal intensities remain uncertain. Sensitivity cell share50-80percent and alternative documented high-power chemistries. One4.518kg central-control/protection assembly per reference pack; remaining mass is allocated using public Dai non-electronic hardware proportions. Car air-cooled reference excludes liquid coolant; unknown fan/duct design is embedded in the residual housing proxy, not independently validated. Truck liquid cooling retains Dai50/50 glycol/water proportions; pump/thermal ratings remain gaps. No module electronics are added on top of the central package; missing distributed monitoring is a coverage gap. All retained material inputs use100percent assembly retention reference; generic working services additional. Equal negative used-battery treatment equals complete manufactured reference mass, including controls, once; no duplicated control waste. These dedicated capacity providers are deliberately outside generic chemistry-density and MIX updates, preserving the already-declared fixed2020 FCEV hardware assumption through2050. Do not interpret corrected mass as a validated manufacturer BOM, annual procurement or primary/secondary content.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: high-power battery capacity, FCEV truck, engineering reference. Former reference product: high-power battery capacity, FCEV truck, engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED FCEV HIGH-POWER PACK ENGINEERING REFERENCES, item24, 2026-10-18. Toyota Mirai2 manufacturer https://newsroom.toyota.eu/introducing-the-all-new-toyota-mirai/; AKASOL AKASYSTEM15OEM37PRC May2021 https://www.act-news.com/wp-content/uploads/2020/11/210525_LowRes_AK_Datenblatt_AKASystem_15-OEM-37-PRC_2021_2159x2794mm_EN.pdf; Dai2018 Table8 https://publications.anl.gov/anlpubs/2018/10/146906.pdf. Match complete physical pack mass and nominal energy, not the changing BEV MIX. Car reference44.6kg/1.2432kWh (=310.8V*4Ah/1000),31.5kW for10seconds; truck reference238kg/25kWh,36kW continuous charge,50kW continuous RMS discharge,150kW10second discharge. Retain existing vehicle capacities/power sizing and lifetime replacement counts. These manufacturer ratings are NOT inferred from chemistry or treated as continuous pulse ratings. Material split remains an engineering proxy:70percent cells, as in the truck sizing source; assume the same70percent for cars. NMC622 cell manufacturing is a bulk-composition proxy, NOT a measured Mirai/AKASOL cell design or a validated high-power electrode/capacity recipe. Thus mass-equivalence is corrected while chemistry-specific metal intensities remain uncertain. Sensitivity cell share50-80percent and alternative documented high-power chemistries. One4.518kg central-control/protection assembly per reference pack; remaining mass is allocated using public Dai non-electronic hardware proportions. Car air-cooled reference excludes liquid coolant; unknown fan/duct design is embedded in the residual housing proxy, not independently validated. Truck liquid cooling retains Dai50/50 glycol/water proportions; pump/thermal ratings remain gaps. No module electronics are added on top of the central package; missing distributed monitoring is a coverage gap. All retained material inputs use100percent assembly retention reference; generic working services additional. Equal negative used-battery treatment equals complete manufactured reference mass, including controls, once; no duplicated control waste. These dedicated capacity providers are deliberately outside generic chemistry-density and MIX updates, preserving the already-declared fixed2020 FCEV hardware assumption through2050. Do not interpret corrected mass as a validated manufacturer BOM, annual procurement or primary/secondary content.</t>
         </is>
       </c>
     </row>
@@ -6178,7 +6180,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>high-power battery capacity, FCEV truck, engineering reference</t>
+          <t xml:space="preserve">market for electricity storage capacity, battery, high power, fuel cell truck</t>
         </is>
       </c>
       <c r="B301">
@@ -6201,7 +6203,7 @@
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>high-power battery capacity, FCEV truck, engineering reference</t>
+          <t xml:space="preserve">electricity storage capacity, high power, fuel cell truck</t>
         </is>
       </c>
     </row>
@@ -6238,7 +6240,7 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>battery central controls and protection, engineering reference</t>
+          <t xml:space="preserve">battery central control and protection unit production</t>
         </is>
       </c>
       <c r="B303">
@@ -6261,7 +6263,7 @@
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>battery central controls and protection, engineering reference</t>
+          <t xml:space="preserve">battery central control and protection unit</t>
         </is>
       </c>
     </row>
@@ -6603,7 +6605,7 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>battery capacity, hydrogen rail, LFP engineering reference</t>
+          <t xml:space="preserve">market for electricity storage capacity, battery, Li-ion, LFP, hydrogen train</t>
         </is>
       </c>
     </row>
@@ -6637,7 +6639,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>battery capacity, hydrogen rail, LFP engineering reference</t>
+          <t xml:space="preserve">electricity storage capacity, Li-ion, LFP, hydrogen train</t>
         </is>
       </c>
     </row>
@@ -6673,7 +6675,8 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>APPROVED HYDROGEN-RAIL COMPLETE LFP CAPACITY REFERENCE, issue33, 2026-10-18. Knibbe2023 DOI10.1016/j.est.2023.108090,3.6MWhLFP/860kWreference and133Wh/kgpack; Dai2018 public LFP non-cell material proportions https://publications.anl.gov/anlpubs/2018/10/146906.pdf Table8. Replace old whole-pack23.5kWh/165kg conversion purchased as bareNMC622cells with a complete3.6MWhLFP reference. Referencepack133Wh/kg =&gt;27067.66917293233kg installed; existing40year/15year lifetime convention gives9600kWh manufactured and treated, not annual procurement.15years remains an engineering calendar assumption, not demonstrated rail LFP cycle life; sensitivity10-20years and source-specific duty/aging remains required. At860kW total stored energy/power=4.186h; battery peakpower and simultaneous fuel-cell duty are not proven by this ratio. Per1kWh:6.25kg cells at existing160Wh/kgcell reference. Assume modular100kWh subsystems, each112series-equivalent3.2V LFPcells at279.017857Ah; series/parallel arrangement and thermal ratings are a design reference, not measured locomotive architecture. One existing6.668kg LFP monitoring/central-controls package per100kWh; other retained mass uses Dai non-electronic module/pack material proportions including50/50glycol/water. This hardware geometry/control allocation is an explicit engineering transfer. Complete pack mass/cellcapacity/control+waste close together. Controls package already treats its6.668kg, so local battery waste excludes that mass; no duplicate EOL. Source cell manufacturing chemistry, electronics-specific materials and thermal duty remain proxies; source133Wh/kg is not certification of this constructed BOM. Existing rail inventory had fixed barecell mass over time; this dedicated fixed-reference provider retains that temporal boundary and is outside generic road density-learning markets. No future LFP electrode evolution is claimed. No locomotive body, tender or track added. Rail source and explicit passenger-energy link are both changed.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: battery capacity, hydrogen rail, LFP engineering reference. Former reference product: battery capacity, hydrogen rail, LFP engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED HYDROGEN-RAIL COMPLETE LFP CAPACITY REFERENCE, issue33, 2026-10-18. Knibbe2023 DOI10.1016/j.est.2023.108090,3.6MWhLFP/860kWreference and133Wh/kgpack; Dai2018 public LFP non-cell material proportions https://publications.anl.gov/anlpubs/2018/10/146906.pdf Table8. Replace old whole-pack23.5kWh/165kg conversion purchased as bareNMC622cells with a complete3.6MWhLFP reference. Referencepack133Wh/kg =&gt;27067.66917293233kg installed; existing40year/15year lifetime convention gives9600kWh manufactured and treated, not annual procurement.15years remains an engineering calendar assumption, not demonstrated rail LFP cycle life; sensitivity10-20years and source-specific duty/aging remains required. At860kW total stored energy/power=4.186h; battery peakpower and simultaneous fuel-cell duty are not proven by this ratio. Per1kWh:6.25kg cells at existing160Wh/kgcell reference. Assume modular100kWh subsystems, each112series-equivalent3.2V LFPcells at279.017857Ah; series/parallel arrangement and thermal ratings are a design reference, not measured locomotive architecture. One existing6.668kg LFP monitoring/central-controls package per100kWh; other retained mass uses Dai non-electronic module/pack material proportions including50/50glycol/water. This hardware geometry/control allocation is an explicit engineering transfer. Complete pack mass/cellcapacity/control+waste close together. Controls package already treats its6.668kg, so local battery waste excludes that mass; no duplicate EOL. Source cell manufacturing chemistry, electronics-specific materials and thermal duty remain proxies; source133Wh/kg is not certification of this constructed BOM. Existing rail inventory had fixed barecell mass over time; this dedicated fixed-reference provider retains that temporal boundary and is outside generic road density-learning markets. No future LFP electrode evolution is claimed. No locomotive body, tender or track added. Rail source and explicit passenger-energy link are both changed.</t>
         </is>
       </c>
     </row>
@@ -6734,7 +6737,7 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>battery capacity, hydrogen rail, LFP engineering reference</t>
+          <t xml:space="preserve">market for electricity storage capacity, battery, Li-ion, LFP, hydrogen train</t>
         </is>
       </c>
       <c r="B326">
@@ -6757,12 +6760,12 @@
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>battery capacity, hydrogen rail, LFP engineering reference</t>
+          <t xml:space="preserve">electricity storage capacity, Li-ion, LFP, hydrogen train</t>
         </is>
       </c>
       <c r="I326" t="inlineStr">
         <is>
-          <t>battery capacity, hydrogen rail, LFP engineering reference</t>
+          <t xml:space="preserve">electricity storage capacity, Li-ion, LFP, hydrogen train</t>
         </is>
       </c>
     </row>
@@ -6804,7 +6807,7 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>battery monitoring and central controls, LFP, engineering reference</t>
+          <t xml:space="preserve">battery monitoring and central control system production, Li-ion, LFP</t>
         </is>
       </c>
       <c r="B328">
@@ -6827,12 +6830,12 @@
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>battery monitoring and central controls, LFP, engineering reference</t>
+          <t xml:space="preserve">battery monitoring and central control system, Li-ion, LFP</t>
         </is>
       </c>
       <c r="I328" t="inlineStr">
         <is>
-          <t>battery monitoring and central controls, LFP, engineering reference</t>
+          <t xml:space="preserve">battery monitoring and central control system, Li-ion, LFP</t>
         </is>
       </c>
     </row>
@@ -7229,7 +7232,7 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>battery hardware, fuel-cell bus LTO, engineering reference</t>
+          <t xml:space="preserve">battery pack production, Li-ion, LTO, fuel cell bus, without controls</t>
         </is>
       </c>
     </row>
@@ -7263,7 +7266,7 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>battery hardware, fuel-cell bus LTO, engineering reference</t>
+          <t xml:space="preserve">battery pack, Li-ion, LTO, fuel cell bus, without controls</t>
         </is>
       </c>
     </row>
@@ -7299,7 +7302,8 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>APPROVED FUEL-CELL BUS BUFFER REFERENCE, issue59, 2026-10-18. Forsee Power PULSE15 manufacturer https://www.forseepower.com/lithium-ion-battery/high-power-batteries/pulse-15/ :14.6kWh,260kg,635V,LTO,63kWcontinuous,127kW10seconds,liquidcooling,15years/15000cycles.2020CaetanoH2 application https://www.forseepower.com/wp-content/uploads/2023/07/2020-01-27-Forsee-Power_CP-Caetano-h2_EN.pdf . Internal BOM not published. Replace six genericMIX highenergy batteries with a bus-specific fixed highpower LTO reference. Select smallest integer parallelpack count meeting both original nominalkWh and entire motorcontinuouspower/63kW; this deliberately conservative power check does not credit fuelcell contribution. Eachpack14.6kWh/260kg; preserve635V inparallel,do not addseriesvoltage. Nominalenergy is not advertised usableenergy; assume80%usable only as explicit sensitivity,not manufacturerDoD. Lifetime packcount=installedcount*ceil(vehicleyears/15); cyclethroughput unknown despite15000cycle claim. Sourcebatteryreplacement assumptions superseded explicitly, not appliedtwice. Internal cell reference:existing LTO cell chemistry/production recipe transferred at assumed80Wh/kgcell (sensitivity60-100),182.5kgcells/pack. Existing60Wh/kgrecipe coefficient is a different engineeringdesign;80Wh/kg is NOT measured PULSEcellperformance. Actual cathode,cellformat,cellcount,energy/power capability remain unresolved.6.538kg controls perpack from16module NMC955reference,architecture transfer not measured PULSEBMS. Other70.962kg casing/cooling/busbars assigned explicit engineering proportions50%Al,15%Cu,10%steel,10%PA,15%50/50glycolwater. Source260kg ensures physicalmassclosure; no assertion this unpublished BOM matches actualmanufacturer. Fixeddesign has no highenergy density trajectory or genericMIXchemistry switching; actualfuturepower/cellredesign requires evidence. Packdisposal covers253.462kg noncontrols,controlshelper disposes6.538kg,onceeach. Update vehicle specification notes and productionassembly mass by installedmassdelta; common glider unchanged, lifetimeenergy/service demand unchanged pending a new driving/thermal simulation. This changed mass/reference is therefore a manufacturing audit correction,not a validated roadperformance prediction. No extra wholevehicle procurement, primarysecondaryshares or recyclingcredit. Refresh affected storedperMJ equipment from actualsource inventories.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: battery hardware, fuel-cell bus LTO, engineering reference. Former reference product: battery hardware, fuel-cell bus LTO, engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED FUEL-CELL BUS BUFFER REFERENCE, issue59, 2026-10-18. Forsee Power PULSE15 manufacturer https://www.forseepower.com/lithium-ion-battery/high-power-batteries/pulse-15/ :14.6kWh,260kg,635V,LTO,63kWcontinuous,127kW10seconds,liquidcooling,15years/15000cycles.2020CaetanoH2 application https://www.forseepower.com/wp-content/uploads/2023/07/2020-01-27-Forsee-Power_CP-Caetano-h2_EN.pdf . Internal BOM not published. Replace six genericMIX highenergy batteries with a bus-specific fixed highpower LTO reference. Select smallest integer parallelpack count meeting both original nominalkWh and entire motorcontinuouspower/63kW; this deliberately conservative power check does not credit fuelcell contribution. Eachpack14.6kWh/260kg; preserve635V inparallel,do not addseriesvoltage. Nominalenergy is not advertised usableenergy; assume80%usable only as explicit sensitivity,not manufacturerDoD. Lifetime packcount=installedcount*ceil(vehicleyears/15); cyclethroughput unknown despite15000cycle claim. Sourcebatteryreplacement assumptions superseded explicitly, not appliedtwice. Internal cell reference:existing LTO cell chemistry/production recipe transferred at assumed80Wh/kgcell (sensitivity60-100),182.5kgcells/pack. Existing60Wh/kgrecipe coefficient is a different engineeringdesign;80Wh/kg is NOT measured PULSEcellperformance. Actual cathode,cellformat,cellcount,energy/power capability remain unresolved.6.538kg controls perpack from16module NMC955reference,architecture transfer not measured PULSEBMS. Other70.962kg casing/cooling/busbars assigned explicit engineering proportions50%Al,15%Cu,10%steel,10%PA,15%50/50glycolwater. Source260kg ensures physicalmassclosure; no assertion this unpublished BOM matches actualmanufacturer. Fixeddesign has no highenergy density trajectory or genericMIXchemistry switching; actualfuturepower/cellredesign requires evidence. Packdisposal covers253.462kg noncontrols,controlshelper disposes6.538kg,onceeach. Update vehicle specification notes and productionassembly mass by installedmassdelta; common glider unchanged, lifetimeenergy/service demand unchanged pending a new driving/thermal simulation. This changed mass/reference is therefore a manufacturing audit correction,not a validated roadperformance prediction. No extra wholevehicle procurement, primarysecondaryshares or recyclingcredit. Refresh affected storedperMJ equipment from actualsource inventories.</t>
         </is>
       </c>
     </row>
@@ -7360,7 +7364,7 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>battery hardware, fuel-cell bus LTO, engineering reference</t>
+          <t xml:space="preserve">battery pack production, Li-ion, LTO, fuel cell bus, without controls</t>
         </is>
       </c>
       <c r="B351">
@@ -7383,12 +7387,12 @@
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>battery hardware, fuel-cell bus LTO, engineering reference</t>
+          <t xml:space="preserve">battery pack, Li-ion, LTO, fuel cell bus, without controls</t>
         </is>
       </c>
       <c r="I351" t="inlineStr">
         <is>
-          <t>battery hardware, fuel-cell bus LTO, engineering reference</t>
+          <t xml:space="preserve">battery pack, Li-ion, LTO, fuel cell bus, without controls</t>
         </is>
       </c>
     </row>
@@ -7680,7 +7684,7 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>high-power battery capacity, fuel-cell bus LTO, engineering reference</t>
+          <t xml:space="preserve">market for electricity storage capacity, battery, Li-ion, LTO, high power, fuel cell bus</t>
         </is>
       </c>
     </row>
@@ -7714,7 +7718,7 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>high-power battery capacity, fuel-cell bus LTO, engineering reference</t>
+          <t xml:space="preserve">electricity storage capacity, Li-ion, LTO, high power, fuel cell bus</t>
         </is>
       </c>
     </row>
@@ -7750,7 +7754,8 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>APPROVED FUEL-CELL BUS BUFFER REFERENCE, issue59, 2026-10-18. Forsee Power PULSE15 manufacturer https://www.forseepower.com/lithium-ion-battery/high-power-batteries/pulse-15/ :14.6kWh,260kg,635V,LTO,63kWcontinuous,127kW10seconds,liquidcooling,15years/15000cycles.2020CaetanoH2 application https://www.forseepower.com/wp-content/uploads/2023/07/2020-01-27-Forsee-Power_CP-Caetano-h2_EN.pdf . Internal BOM not published. Replace six genericMIX highenergy batteries with a bus-specific fixed highpower LTO reference. Select smallest integer parallelpack count meeting both original nominalkWh and entire motorcontinuouspower/63kW; this deliberately conservative power check does not credit fuelcell contribution. Eachpack14.6kWh/260kg; preserve635V inparallel,do not addseriesvoltage. Nominalenergy is not advertised usableenergy; assume80%usable only as explicit sensitivity,not manufacturerDoD. Lifetime packcount=installedcount*ceil(vehicleyears/15); cyclethroughput unknown despite15000cycle claim. Sourcebatteryreplacement assumptions superseded explicitly, not appliedtwice. Internal cell reference:existing LTO cell chemistry/production recipe transferred at assumed80Wh/kgcell (sensitivity60-100),182.5kgcells/pack. Existing60Wh/kgrecipe coefficient is a different engineeringdesign;80Wh/kg is NOT measured PULSEcellperformance. Actual cathode,cellformat,cellcount,energy/power capability remain unresolved.6.538kg controls perpack from16module NMC955reference,architecture transfer not measured PULSEBMS. Other70.962kg casing/cooling/busbars assigned explicit engineering proportions50%Al,15%Cu,10%steel,10%PA,15%50/50glycolwater. Source260kg ensures physicalmassclosure; no assertion this unpublished BOM matches actualmanufacturer. Fixeddesign has no highenergy density trajectory or genericMIXchemistry switching; actualfuturepower/cellredesign requires evidence. Packdisposal covers253.462kg noncontrols,controlshelper disposes6.538kg,onceeach. Update vehicle specification notes and productionassembly mass by installedmassdelta; common glider unchanged, lifetimeenergy/service demand unchanged pending a new driving/thermal simulation. This changed mass/reference is therefore a manufacturing audit correction,not a validated roadperformance prediction. No extra wholevehicle procurement, primarysecondaryshares or recyclingcredit. Refresh affected storedperMJ equipment from actualsource inventories.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: high-power battery capacity, fuel-cell bus LTO, engineering reference. Former reference product: high-power battery capacity, fuel-cell bus LTO, engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED FUEL-CELL BUS BUFFER REFERENCE, issue59, 2026-10-18. Forsee Power PULSE15 manufacturer https://www.forseepower.com/lithium-ion-battery/high-power-batteries/pulse-15/ :14.6kWh,260kg,635V,LTO,63kWcontinuous,127kW10seconds,liquidcooling,15years/15000cycles.2020CaetanoH2 application https://www.forseepower.com/wp-content/uploads/2023/07/2020-01-27-Forsee-Power_CP-Caetano-h2_EN.pdf . Internal BOM not published. Replace six genericMIX highenergy batteries with a bus-specific fixed highpower LTO reference. Select smallest integer parallelpack count meeting both original nominalkWh and entire motorcontinuouspower/63kW; this deliberately conservative power check does not credit fuelcell contribution. Eachpack14.6kWh/260kg; preserve635V inparallel,do not addseriesvoltage. Nominalenergy is not advertised usableenergy; assume80%usable only as explicit sensitivity,not manufacturerDoD. Lifetime packcount=installedcount*ceil(vehicleyears/15); cyclethroughput unknown despite15000cycle claim. Sourcebatteryreplacement assumptions superseded explicitly, not appliedtwice. Internal cell reference:existing LTO cell chemistry/production recipe transferred at assumed80Wh/kgcell (sensitivity60-100),182.5kgcells/pack. Existing60Wh/kgrecipe coefficient is a different engineeringdesign;80Wh/kg is NOT measured PULSEcellperformance. Actual cathode,cellformat,cellcount,energy/power capability remain unresolved.6.538kg controls perpack from16module NMC955reference,architecture transfer not measured PULSEBMS. Other70.962kg casing/cooling/busbars assigned explicit engineering proportions50%Al,15%Cu,10%steel,10%PA,15%50/50glycolwater. Source260kg ensures physicalmassclosure; no assertion this unpublished BOM matches actualmanufacturer. Fixeddesign has no highenergy density trajectory or genericMIXchemistry switching; actualfuturepower/cellredesign requires evidence. Packdisposal covers253.462kg noncontrols,controlshelper disposes6.538kg,onceeach. Update vehicle specification notes and productionassembly mass by installedmassdelta; common glider unchanged, lifetimeenergy/service demand unchanged pending a new driving/thermal simulation. This changed mass/reference is therefore a manufacturing audit correction,not a validated roadperformance prediction. No extra wholevehicle procurement, primarysecondaryshares or recyclingcredit. Refresh affected storedperMJ equipment from actualsource inventories.</t>
         </is>
       </c>
     </row>
@@ -7811,7 +7816,7 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>high-power battery capacity, fuel-cell bus LTO, engineering reference</t>
+          <t xml:space="preserve">market for electricity storage capacity, battery, Li-ion, LTO, high power, fuel cell bus</t>
         </is>
       </c>
       <c r="B371">
@@ -7834,19 +7839,19 @@
       </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t>high-power battery capacity, fuel-cell bus LTO, engineering reference</t>
+          <t xml:space="preserve">electricity storage capacity, Li-ion, LTO, high power, fuel cell bus</t>
         </is>
       </c>
       <c r="I371" t="inlineStr">
         <is>
-          <t>high-power battery capacity, fuel-cell bus LTO, engineering reference</t>
+          <t xml:space="preserve">electricity storage capacity, Li-ion, LTO, high power, fuel cell bus</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>battery hardware, fuel-cell bus LTO, engineering reference</t>
+          <t xml:space="preserve">battery pack production, Li-ion, LTO, fuel cell bus, without controls</t>
         </is>
       </c>
       <c r="B372">
@@ -7869,19 +7874,19 @@
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>battery hardware, fuel-cell bus LTO, engineering reference</t>
+          <t xml:space="preserve">battery pack, Li-ion, LTO, fuel cell bus, without controls</t>
         </is>
       </c>
       <c r="I372" t="inlineStr">
         <is>
-          <t>battery hardware, fuel-cell bus LTO, engineering reference</t>
+          <t xml:space="preserve">battery pack, Li-ion, LTO, fuel cell bus, without controls</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>battery monitoring and central controls, NMC955, engineering reference</t>
+          <t xml:space="preserve">battery monitoring and central control system production, Li-ion, NMC955</t>
         </is>
       </c>
       <c r="B373">
@@ -7904,12 +7909,12 @@
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>battery monitoring and central controls, NMC955, engineering reference</t>
+          <t xml:space="preserve">battery monitoring and central control system, Li-ion, NMC955</t>
         </is>
       </c>
       <c r="I373" t="inlineStr">
         <is>
-          <t>battery monitoring and central controls, NMC955, engineering reference</t>
+          <t xml:space="preserve">battery monitoring and central control system, Li-ion, NMC955</t>
         </is>
       </c>
     </row>
@@ -8096,7 +8101,7 @@
     <row r="11" spans="1:14" ns3:dyDescent="0.2">
       <c r="A11" t="inlineStr">
         <is>
-          <t>market for battery cells, Li-ion, LFP, density-scaled reference</t>
+          <t xml:space="preserve">market for battery cell, Li-ion, LFP, including end-of-life treatment</t>
         </is>
       </c>
       <c r="B11" s="7">
@@ -8120,7 +8125,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>market for battery cells, Li-ion, LFP, density-scaled reference</t>
+          <t xml:space="preserve">battery cell, Li-ion, LFP, including end-of-life treatment</t>
         </is>
       </c>
       <c r="G11">
@@ -8142,7 +8147,7 @@
     <row r="12" spans="1:14" ns3:dyDescent="0.2">
       <c r="A12" t="inlineStr">
         <is>
-          <t>battery fixed noncell hardware, Li-ion, LFP, baseline-kWh reference</t>
+          <t xml:space="preserve">battery pack component production and end-of-life treatment, Li-ion, LFP, without cells and controls</t>
         </is>
       </c>
       <c r="B12" s="7">
@@ -8166,7 +8171,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>battery fixed noncell hardware, Li-ion, LFP, baseline-kWh reference</t>
+          <t xml:space="preserve">battery pack components, Li-ion, LFP, without cells and controls</t>
         </is>
       </c>
       <c r="G12">
@@ -8195,7 +8200,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>battery monitoring and central controls, LFP, engineering reference</t>
+          <t xml:space="preserve">battery monitoring and central control system production, Li-ion, LFP</t>
         </is>
       </c>
       <c r="B13">
@@ -8218,7 +8223,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>battery monitoring and central controls, LFP, engineering reference</t>
+          <t xml:space="preserve">battery monitoring and central control system, Li-ion, LFP</t>
         </is>
       </c>
     </row>
@@ -8352,7 +8357,7 @@
     <row r="24" spans="1:14" ns3:dyDescent="0.2">
       <c r="A24" t="inlineStr">
         <is>
-          <t>market for battery cells, Li-ion, NMC111, density-scaled reference</t>
+          <t xml:space="preserve">market for battery cell, Li-ion, NMC111, including end-of-life treatment</t>
         </is>
       </c>
       <c r="B24" s="3">
@@ -8376,7 +8381,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>market for battery cells, Li-ion, NMC111, density-scaled reference</t>
+          <t xml:space="preserve">battery cell, Li-ion, NMC111, including end-of-life treatment</t>
         </is>
       </c>
       <c r="G24">
@@ -8398,7 +8403,7 @@
     <row r="25" spans="1:14" ns3:dyDescent="0.2">
       <c r="A25" t="inlineStr">
         <is>
-          <t>battery fixed noncell hardware, Li-ion, NMC111, baseline-kWh reference</t>
+          <t xml:space="preserve">battery pack component production and end-of-life treatment, Li-ion, NMC111, without cells and controls</t>
         </is>
       </c>
       <c r="B25" s="3">
@@ -8422,7 +8427,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>battery fixed noncell hardware, Li-ion, NMC111, baseline-kWh reference</t>
+          <t xml:space="preserve">battery pack components, Li-ion, NMC111, without cells and controls</t>
         </is>
       </c>
       <c r="G25">
@@ -8451,7 +8456,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>battery monitoring and central controls, NMC111, engineering reference</t>
+          <t xml:space="preserve">battery monitoring and central control system production, Li-ion, NMC111</t>
         </is>
       </c>
       <c r="B26">
@@ -8474,7 +8479,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>battery monitoring and central controls, NMC111, engineering reference</t>
+          <t xml:space="preserve">battery monitoring and central control system, Li-ion, NMC111</t>
         </is>
       </c>
     </row>
@@ -8608,7 +8613,7 @@
     <row r="37" spans="1:14" ns3:dyDescent="0.2">
       <c r="A37" t="inlineStr">
         <is>
-          <t>market for battery cells, Li-ion, NMC532, density-scaled reference</t>
+          <t xml:space="preserve">market for battery cell, Li-ion, NMC532, including end-of-life treatment</t>
         </is>
       </c>
       <c r="B37" s="3">
@@ -8632,7 +8637,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>market for battery cells, Li-ion, NMC532, density-scaled reference</t>
+          <t xml:space="preserve">battery cell, Li-ion, NMC532, including end-of-life treatment</t>
         </is>
       </c>
       <c r="G37">
@@ -8654,7 +8659,7 @@
     <row r="38" spans="1:14" ns3:dyDescent="0.2">
       <c r="A38" t="inlineStr">
         <is>
-          <t>battery fixed noncell hardware, Li-ion, NMC532, baseline-kWh reference</t>
+          <t xml:space="preserve">battery pack component production and end-of-life treatment, Li-ion, NMC532, without cells and controls</t>
         </is>
       </c>
       <c r="B38" s="3">
@@ -8678,7 +8683,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>battery fixed noncell hardware, Li-ion, NMC532, baseline-kWh reference</t>
+          <t xml:space="preserve">battery pack components, Li-ion, NMC532, without cells and controls</t>
         </is>
       </c>
       <c r="G38">
@@ -8707,7 +8712,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>battery monitoring and central controls, NMC532, engineering reference</t>
+          <t xml:space="preserve">battery monitoring and central control system production, Li-ion, NMC532</t>
         </is>
       </c>
       <c r="B39">
@@ -8730,7 +8735,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>battery monitoring and central controls, NMC532, engineering reference</t>
+          <t xml:space="preserve">battery monitoring and central control system, Li-ion, NMC532</t>
         </is>
       </c>
     </row>
@@ -8866,7 +8871,7 @@
     <row r="50" spans="1:14" ns3:dyDescent="0.2">
       <c r="A50" t="inlineStr">
         <is>
-          <t>market for battery cells, Li-ion, NMC622, density-scaled reference</t>
+          <t xml:space="preserve">market for battery cell, Li-ion, NMC622, including end-of-life treatment</t>
         </is>
       </c>
       <c r="B50" s="3">
@@ -8890,7 +8895,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>market for battery cells, Li-ion, NMC622, density-scaled reference</t>
+          <t xml:space="preserve">battery cell, Li-ion, NMC622, including end-of-life treatment</t>
         </is>
       </c>
       <c r="G50">
@@ -8912,7 +8917,7 @@
     <row r="51" spans="1:14" ns3:dyDescent="0.2">
       <c r="A51" t="inlineStr">
         <is>
-          <t>battery fixed noncell hardware, Li-ion, NMC622, baseline-kWh reference</t>
+          <t xml:space="preserve">battery pack component production and end-of-life treatment, Li-ion, NMC622, without cells and controls</t>
         </is>
       </c>
       <c r="B51" s="3">
@@ -8936,7 +8941,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>battery fixed noncell hardware, Li-ion, NMC622, baseline-kWh reference</t>
+          <t xml:space="preserve">battery pack components, Li-ion, NMC622, without cells and controls</t>
         </is>
       </c>
       <c r="G51">
@@ -8965,7 +8970,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>battery monitoring and central controls, NMC622, engineering reference</t>
+          <t xml:space="preserve">battery monitoring and central control system production, Li-ion, NMC622</t>
         </is>
       </c>
       <c r="B52">
@@ -8988,7 +8993,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>battery monitoring and central controls, NMC622, engineering reference</t>
+          <t xml:space="preserve">battery monitoring and central control system, Li-ion, NMC622</t>
         </is>
       </c>
     </row>
@@ -9125,7 +9130,7 @@
     <row r="63" spans="1:14" ns3:dyDescent="0.2">
       <c r="A63" t="inlineStr">
         <is>
-          <t>market for battery cells, Li-ion, NMC811, density-scaled reference</t>
+          <t xml:space="preserve">market for battery cell, Li-ion, NMC811, including end-of-life treatment</t>
         </is>
       </c>
       <c r="B63" s="3">
@@ -9149,7 +9154,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>market for battery cells, Li-ion, NMC811, density-scaled reference</t>
+          <t xml:space="preserve">battery cell, Li-ion, NMC811, including end-of-life treatment</t>
         </is>
       </c>
       <c r="G63">
@@ -9171,7 +9176,7 @@
     <row r="64" spans="1:14" ns3:dyDescent="0.2">
       <c r="A64" t="inlineStr">
         <is>
-          <t>battery fixed noncell hardware, Li-ion, NMC811, baseline-kWh reference</t>
+          <t xml:space="preserve">battery pack component production and end-of-life treatment, Li-ion, NMC811, without cells and controls</t>
         </is>
       </c>
       <c r="B64" s="3">
@@ -9195,7 +9200,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>battery fixed noncell hardware, Li-ion, NMC811, baseline-kWh reference</t>
+          <t xml:space="preserve">battery pack components, Li-ion, NMC811, without cells and controls</t>
         </is>
       </c>
       <c r="G64">
@@ -9224,7 +9229,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>battery monitoring and central controls, NMC811, engineering reference</t>
+          <t xml:space="preserve">battery monitoring and central control system production, Li-ion, NMC811</t>
         </is>
       </c>
       <c r="B65">
@@ -9247,7 +9252,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>battery monitoring and central controls, NMC811, engineering reference</t>
+          <t xml:space="preserve">battery monitoring and central control system, Li-ion, NMC811</t>
         </is>
       </c>
     </row>
@@ -9381,7 +9386,7 @@
     <row r="76" spans="1:14" ns3:dyDescent="0.2">
       <c r="A76" t="inlineStr">
         <is>
-          <t>market for battery cells, Li-ion, NMC955, density-scaled reference</t>
+          <t xml:space="preserve">market for battery cell, Li-ion, NMC955, including end-of-life treatment</t>
         </is>
       </c>
       <c r="B76" s="3">
@@ -9405,7 +9410,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>market for battery cells, Li-ion, NMC955, density-scaled reference</t>
+          <t xml:space="preserve">battery cell, Li-ion, NMC955, including end-of-life treatment</t>
         </is>
       </c>
       <c r="G76">
@@ -9427,7 +9432,7 @@
     <row r="77" spans="1:14" ns3:dyDescent="0.2">
       <c r="A77" t="inlineStr">
         <is>
-          <t>battery fixed noncell hardware, Li-ion, NMC955, baseline-kWh reference</t>
+          <t xml:space="preserve">battery pack component production and end-of-life treatment, Li-ion, NMC955, without cells and controls</t>
         </is>
       </c>
       <c r="B77" s="3">
@@ -9451,7 +9456,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>battery fixed noncell hardware, Li-ion, NMC955, baseline-kWh reference</t>
+          <t xml:space="preserve">battery pack components, Li-ion, NMC955, without cells and controls</t>
         </is>
       </c>
       <c r="G77">
@@ -9480,7 +9485,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>battery monitoring and central controls, NMC955, engineering reference</t>
+          <t xml:space="preserve">battery monitoring and central control system production, Li-ion, NMC955</t>
         </is>
       </c>
       <c r="B79">
@@ -9503,7 +9508,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>battery monitoring and central controls, NMC955, engineering reference</t>
+          <t xml:space="preserve">battery monitoring and central control system, Li-ion, NMC955</t>
         </is>
       </c>
     </row>
@@ -9660,7 +9665,7 @@
     <row r="91" spans="1:11" ns3:dyDescent="0.2">
       <c r="A91" t="inlineStr">
         <is>
-          <t>market for used redox-flow battery, Vanadium, reference design</t>
+          <t xml:space="preserve">market for used redox-flow battery, vanadium</t>
         </is>
       </c>
       <c r="B91" s="3">
@@ -9677,7 +9682,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>used redox-flow battery, Vanadium, reference design</t>
+          <t xml:space="preserve">used redox-flow battery, vanadium</t>
         </is>
       </c>
       <c r="G91">

--- a/premise/data/additional_inventories/lci-battery-capacity.xlsx
+++ b/premise/data/additional_inventories/lci-battery-capacity.xlsx
@@ -969,7 +969,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t xml:space="preserve">kilowatt hour</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery pack components, Li-ion, LFP, without cells and controls</t>
+          <t xml:space="preserve">battery pack component provision, Li-ion, LFP, without cells and controls</t>
         </is>
       </c>
       <c r="G14">
@@ -1219,7 +1219,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t xml:space="preserve">kilowatt hour</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery pack components, Li-ion, NMC111, without cells and controls</t>
+          <t xml:space="preserve">battery pack component provision, Li-ion, NMC111, without cells and controls</t>
         </is>
       </c>
       <c r="G27">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t xml:space="preserve">kilowatt hour</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery pack components, Li-ion, NMC532, without cells and controls</t>
+          <t xml:space="preserve">battery pack component provision, Li-ion, NMC532, without cells and controls</t>
         </is>
       </c>
       <c r="G40">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t xml:space="preserve">kilowatt hour</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -1734,7 +1734,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery pack components, Li-ion, NMC622, without cells and controls</t>
+          <t xml:space="preserve">battery pack component provision, Li-ion, NMC622, without cells and controls</t>
         </is>
       </c>
       <c r="G53">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t xml:space="preserve">kilowatt hour</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -1987,7 +1987,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery pack components, Li-ion, NMC811, without cells and controls</t>
+          <t xml:space="preserve">battery pack component provision, Li-ion, NMC811, without cells and controls</t>
         </is>
       </c>
       <c r="G66">
@@ -2224,7 +2224,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t xml:space="preserve">kilowatt hour</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -2237,7 +2237,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery pack components, Li-ion, NMC955, without cells and controls</t>
+          <t xml:space="preserve">battery pack component provision, Li-ion, NMC955, without cells and controls</t>
         </is>
       </c>
       <c r="G79">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t xml:space="preserve">kilowatt hour</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery pack components, Li-ion, NCA, without cells and controls</t>
+          <t xml:space="preserve">battery pack component provision, Li-ion, NCA, without cells and controls</t>
         </is>
       </c>
       <c r="G92">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t xml:space="preserve">kilowatt hour</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery pack components, Li-ion, LTO, without cells and controls</t>
+          <t xml:space="preserve">battery pack component provision, Li-ion, LTO, without cells and controls</t>
         </is>
       </c>
       <c r="G105">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t xml:space="preserve">kilowatt hour</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery pack components, Li-ion, LiMn2O4, without cells and controls</t>
+          <t xml:space="preserve">battery pack component provision, Li-ion, LiMn2O4, without cells and controls</t>
         </is>
       </c>
       <c r="G118">
@@ -3228,7 +3228,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t xml:space="preserve">kilowatt hour</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery pack components, Li-sulfur, Li-S, without cells and controls</t>
+          <t xml:space="preserve">battery pack component provision, Li-sulfur, Li-S, without cells and controls</t>
         </is>
       </c>
       <c r="G131">
@@ -3484,7 +3484,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t xml:space="preserve">kilowatt hour</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -3497,7 +3497,7 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery pack components, Li-ion, Li-O2, without cells and controls</t>
+          <t xml:space="preserve">battery pack component provision, Li-ion, Li-O2, without cells and controls</t>
         </is>
       </c>
       <c r="G144">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t xml:space="preserve">kilowatt hour</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -3754,7 +3754,7 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery pack components, Sodium-ion, SiB, without cells and controls</t>
+          <t xml:space="preserve">battery pack component provision, Sodium-ion, SiB, without cells and controls</t>
         </is>
       </c>
       <c r="G157">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t xml:space="preserve">kilowatt hour</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -8171,7 +8171,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery pack components, Li-ion, LFP, without cells and controls</t>
+          <t xml:space="preserve">battery pack component provision, Li-ion, LFP, without cells and controls</t>
         </is>
       </c>
       <c r="G12">
@@ -8412,7 +8412,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t xml:space="preserve">kilowatt hour</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -8427,7 +8427,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery pack components, Li-ion, NMC111, without cells and controls</t>
+          <t xml:space="preserve">battery pack component provision, Li-ion, NMC111, without cells and controls</t>
         </is>
       </c>
       <c r="G25">
@@ -8668,7 +8668,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t xml:space="preserve">kilowatt hour</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -8683,7 +8683,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery pack components, Li-ion, NMC532, without cells and controls</t>
+          <t xml:space="preserve">battery pack component provision, Li-ion, NMC532, without cells and controls</t>
         </is>
       </c>
       <c r="G38">
@@ -8926,7 +8926,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t xml:space="preserve">kilowatt hour</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery pack components, Li-ion, NMC622, without cells and controls</t>
+          <t xml:space="preserve">battery pack component provision, Li-ion, NMC622, without cells and controls</t>
         </is>
       </c>
       <c r="G51">
@@ -9185,7 +9185,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t xml:space="preserve">kilowatt hour</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -9200,7 +9200,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery pack components, Li-ion, NMC811, without cells and controls</t>
+          <t xml:space="preserve">battery pack component provision, Li-ion, NMC811, without cells and controls</t>
         </is>
       </c>
       <c r="G64">
@@ -9441,7 +9441,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t xml:space="preserve">kilowatt hour</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9456,7 +9456,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery pack components, Li-ion, NMC955, without cells and controls</t>
+          <t xml:space="preserve">battery pack component provision, Li-ion, NMC955, without cells and controls</t>
         </is>
       </c>
       <c r="G77">

--- a/premise/data/additional_inventories/lci-battery-capacity.xlsx
+++ b/premise/data/additional_inventories/lci-battery-capacity.xlsx
@@ -771,7 +771,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:ns4="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N374"/>
+  <dimension ref="A1:N379"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" ns3:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="46.5" customWidth="1"/>
@@ -918,7 +918,7 @@
     <row r="13" spans="1:14" ns3:dyDescent="0.2">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">market for battery cell, Li-ion, LFP, including end-of-life treatment</t>
+          <t xml:space="preserve">market for battery cell, lithium-ion, lfp, including end-of-life treatment</t>
         </is>
       </c>
       <c r="B13" s="7">
@@ -960,7 +960,7 @@
     <row r="14" spans="1:14" ns3:dyDescent="0.2">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery pack component production and end-of-life treatment, Li-ion, LFP, without cells and controls</t>
+          <t xml:space="preserve">battery pack component production and end-of-life treatment, lithium-ion, lfp, without cells and controls</t>
         </is>
       </c>
       <c r="B14" s="7">
@@ -1011,7 +1011,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery monitoring and central control system production, Li-ion, LFP</t>
+          <t xml:space="preserve">battery monitoring and central control system production, lithium-ion, lfp</t>
         </is>
       </c>
       <c r="B15">
@@ -1168,7 +1168,7 @@
     <row r="26" spans="1:14" ns3:dyDescent="0.2">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">market for battery cell, Li-ion, NMC111, including end-of-life treatment</t>
+          <t xml:space="preserve">market for battery cell, lithium-ion, nmc111, including end-of-life treatment</t>
         </is>
       </c>
       <c r="B26" s="3">
@@ -1210,7 +1210,7 @@
     <row r="27" spans="1:14" ns3:dyDescent="0.2">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery pack component production and end-of-life treatment, Li-ion, NMC111, without cells and controls</t>
+          <t xml:space="preserve">battery pack component production and end-of-life treatment, lithium-ion, nmc111, without cells and controls</t>
         </is>
       </c>
       <c r="B27" s="3">
@@ -1261,7 +1261,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery monitoring and central control system production, Li-ion, NMC111</t>
+          <t xml:space="preserve">battery monitoring and central control system production, lithium-ion, nmc111</t>
         </is>
       </c>
       <c r="B28">
@@ -1418,7 +1418,7 @@
     <row r="39" spans="1:14" ns3:dyDescent="0.2">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">market for battery cell, Li-ion, NMC532, including end-of-life treatment</t>
+          <t xml:space="preserve">market for battery cell, lithium-ion, nmc532, including end-of-life treatment</t>
         </is>
       </c>
       <c r="B39" s="3">
@@ -1460,7 +1460,7 @@
     <row r="40" spans="1:14" ns3:dyDescent="0.2">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery pack component production and end-of-life treatment, Li-ion, NMC532, without cells and controls</t>
+          <t xml:space="preserve">battery pack component production and end-of-life treatment, lithium-ion, nmc532, without cells and controls</t>
         </is>
       </c>
       <c r="B40" s="3">
@@ -1511,7 +1511,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery monitoring and central control system production, Li-ion, NMC532</t>
+          <t xml:space="preserve">battery monitoring and central control system production, lithium-ion, nmc532</t>
         </is>
       </c>
       <c r="B41">
@@ -1670,7 +1670,7 @@
     <row r="52" spans="1:14" ns3:dyDescent="0.2">
       <c r="A52" t="inlineStr">
         <is>
-          <t xml:space="preserve">market for battery cell, Li-ion, NMC622, including end-of-life treatment</t>
+          <t xml:space="preserve">market for battery cell, lithium-ion, nmc622, including end-of-life treatment</t>
         </is>
       </c>
       <c r="B52" s="3">
@@ -1712,7 +1712,7 @@
     <row r="53" spans="1:14" ns3:dyDescent="0.2">
       <c r="A53" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery pack component production and end-of-life treatment, Li-ion, NMC622, without cells and controls</t>
+          <t xml:space="preserve">battery pack component production and end-of-life treatment, lithium-ion, nmc622, without cells and controls</t>
         </is>
       </c>
       <c r="B53" s="3">
@@ -1763,7 +1763,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery monitoring and central control system production, Li-ion, NMC622</t>
+          <t xml:space="preserve">battery monitoring and central control system production, lithium-ion, nmc622</t>
         </is>
       </c>
       <c r="B54">
@@ -1923,7 +1923,7 @@
     <row r="65" spans="1:14" ns3:dyDescent="0.2">
       <c r="A65" t="inlineStr">
         <is>
-          <t xml:space="preserve">market for battery cell, Li-ion, NMC811, including end-of-life treatment</t>
+          <t xml:space="preserve">market for battery cell, lithium-ion, nmc811, including end-of-life treatment</t>
         </is>
       </c>
       <c r="B65" s="3">
@@ -1965,7 +1965,7 @@
     <row r="66" spans="1:14" ns3:dyDescent="0.2">
       <c r="A66" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery pack component production and end-of-life treatment, Li-ion, NMC811, without cells and controls</t>
+          <t xml:space="preserve">battery pack component production and end-of-life treatment, lithium-ion, nmc811, without cells and controls</t>
         </is>
       </c>
       <c r="B66" s="3">
@@ -2016,7 +2016,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery monitoring and central control system production, Li-ion, NMC811</t>
+          <t xml:space="preserve">battery monitoring and central control system production, lithium-ion, nmc811</t>
         </is>
       </c>
       <c r="B67">
@@ -2173,7 +2173,7 @@
     <row r="78" spans="1:14" ns3:dyDescent="0.2">
       <c r="A78" t="inlineStr">
         <is>
-          <t xml:space="preserve">market for battery cell, Li-ion, NMC955, including end-of-life treatment</t>
+          <t xml:space="preserve">market for battery cell, lithium-ion, nmc955, including end-of-life treatment</t>
         </is>
       </c>
       <c r="B78" s="3">
@@ -2215,7 +2215,7 @@
     <row r="79" spans="1:14" ns3:dyDescent="0.2">
       <c r="A79" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery pack component production and end-of-life treatment, Li-ion, NMC955, without cells and controls</t>
+          <t xml:space="preserve">battery pack component production and end-of-life treatment, lithium-ion, nmc955, without cells and controls</t>
         </is>
       </c>
       <c r="B79" s="3">
@@ -2266,7 +2266,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery monitoring and central control system production, Li-ion, NMC955</t>
+          <t xml:space="preserve">battery monitoring and central control system production, lithium-ion, nmc955</t>
         </is>
       </c>
       <c r="B80">
@@ -2423,7 +2423,7 @@
     <row r="91" spans="1:14" ns3:dyDescent="0.2">
       <c r="A91" t="inlineStr">
         <is>
-          <t xml:space="preserve">market for battery cell, Li-ion, NCA, including end-of-life treatment</t>
+          <t xml:space="preserve">market for battery cell, lithium-ion, nca, including end-of-life treatment</t>
         </is>
       </c>
       <c r="B91" s="3">
@@ -2465,7 +2465,7 @@
     <row r="92" spans="1:14" ns3:dyDescent="0.2">
       <c r="A92" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery pack component production and end-of-life treatment, Li-ion, NCA, without cells and controls</t>
+          <t xml:space="preserve">battery pack component production and end-of-life treatment, lithium-ion, nca, without cells and controls</t>
         </is>
       </c>
       <c r="B92" s="3">
@@ -2516,7 +2516,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery monitoring and central control system production, Li-ion, NCA</t>
+          <t xml:space="preserve">battery monitoring and central control system production, lithium-ion, nca</t>
         </is>
       </c>
       <c r="B93">
@@ -2675,7 +2675,7 @@
     <row r="104" spans="1:14" ns3:dyDescent="0.2">
       <c r="A104" t="inlineStr">
         <is>
-          <t xml:space="preserve">market for battery cell, Li-ion, LTO, including end-of-life treatment</t>
+          <t xml:space="preserve">market for battery cell, lithium-ion, lto, including end-of-life treatment</t>
         </is>
       </c>
       <c r="B104" s="3">
@@ -2717,7 +2717,7 @@
     <row r="105" spans="1:14" ns3:dyDescent="0.2">
       <c r="A105" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery pack component production and end-of-life treatment, Li-ion, LTO, without cells and controls</t>
+          <t xml:space="preserve">battery pack component production and end-of-life treatment, lithium-ion, lto, without cells and controls</t>
         </is>
       </c>
       <c r="B105" s="3">
@@ -2768,7 +2768,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery monitoring and central control system production, Li-ion, LTO</t>
+          <t xml:space="preserve">battery monitoring and central control system production, lithium-ion, lto</t>
         </is>
       </c>
       <c r="B106">
@@ -2925,7 +2925,7 @@
     <row r="117" spans="1:14" ns3:dyDescent="0.2">
       <c r="A117" t="inlineStr">
         <is>
-          <t xml:space="preserve">market for battery cell, Li-ion, LiMn2O4, including end-of-life treatment</t>
+          <t xml:space="preserve">market for battery cell, lithium-ion, limn2o4, including end-of-life treatment</t>
         </is>
       </c>
       <c r="B117" s="3">
@@ -2967,7 +2967,7 @@
     <row r="118" spans="1:14" ns3:dyDescent="0.2">
       <c r="A118" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery pack component production and end-of-life treatment, Li-ion, LiMn2O4, without cells and controls</t>
+          <t xml:space="preserve">battery pack component production and end-of-life treatment, lithium-ion, limn2o4, without cells and controls</t>
         </is>
       </c>
       <c r="B118" s="3">
@@ -3018,7 +3018,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery monitoring and central control system production, Li-ion, LiMn2O4</t>
+          <t xml:space="preserve">battery monitoring and central control system production, lithium-ion, limn2o4</t>
         </is>
       </c>
       <c r="B119">
@@ -3177,7 +3177,7 @@
     <row r="130" spans="1:14" ns3:dyDescent="0.2">
       <c r="A130" t="inlineStr">
         <is>
-          <t xml:space="preserve">market for battery cell, Li-sulfur, Li-S, including end-of-life treatment</t>
+          <t xml:space="preserve">market for battery cell, lithium-sulfur, including end-of-life treatment</t>
         </is>
       </c>
       <c r="B130" s="3">
@@ -3219,7 +3219,7 @@
     <row r="131" spans="1:14" ns3:dyDescent="0.2">
       <c r="A131" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery pack component production and end-of-life treatment, Li-sulfur, Li-S, without cells and controls</t>
+          <t xml:space="preserve">battery pack component production and end-of-life treatment, lithium-sulfur, without cells and controls</t>
         </is>
       </c>
       <c r="B131" s="3">
@@ -3433,7 +3433,7 @@
     <row r="143" spans="1:14" ns3:dyDescent="0.2">
       <c r="A143" t="inlineStr">
         <is>
-          <t xml:space="preserve">market for battery cell, Li-ion, Li-O2, including end-of-life treatment</t>
+          <t xml:space="preserve">market for battery cell, lithium-oxygen, including end-of-life treatment</t>
         </is>
       </c>
       <c r="B143" s="3">
@@ -3475,7 +3475,7 @@
     <row r="144" spans="1:14" ns3:dyDescent="0.2">
       <c r="A144" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery pack component production and end-of-life treatment, Li-ion, Li-O2, without cells and controls</t>
+          <t xml:space="preserve">battery pack component production and end-of-life treatment, lithium-oxygen, without cells and controls</t>
         </is>
       </c>
       <c r="B144" s="3">
@@ -3690,7 +3690,7 @@
     <row r="156" spans="1:14" ns3:dyDescent="0.2">
       <c r="A156" t="inlineStr">
         <is>
-          <t xml:space="preserve">market for battery cell, Sodium-ion, SiB, including end-of-life treatment</t>
+          <t xml:space="preserve">market for battery cell, sodium-ion, including end-of-life treatment</t>
         </is>
       </c>
       <c r="B156" s="3">
@@ -3732,7 +3732,7 @@
     <row r="157" spans="1:14" ns3:dyDescent="0.2">
       <c r="A157" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery pack component production and end-of-life treatment, Sodium-ion, SiB, without cells and controls</t>
+          <t xml:space="preserve">battery pack component production and end-of-life treatment, sodium-ion, without cells and controls</t>
         </is>
       </c>
       <c r="B157" s="3">
@@ -5639,90 +5639,72 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Exchanges</t>
+          <t xml:space="preserve">type</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t xml:space="preserve">processwithreferenceproduct</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B277" t="inlineStr">
-        <is>
-          <t>amount</t>
-        </is>
-      </c>
-      <c r="C277" t="inlineStr">
-        <is>
-          <t>location</t>
-        </is>
-      </c>
-      <c r="D277" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="E277" t="inlineStr">
-        <is>
-          <t>categories</t>
-        </is>
-      </c>
-      <c r="F277" t="inlineStr">
-        <is>
-          <t>type</t>
-        </is>
-      </c>
-      <c r="G277" t="inlineStr">
-        <is>
-          <t>reference product</t>
-        </is>
-      </c>
-      <c r="H277" t="inlineStr">
-        <is>
-          <t>comment</t>
+          <t>Exchanges</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t xml:space="preserve">market for electricity storage capacity, battery, high power, fuel cell passenger car</t>
-        </is>
-      </c>
-      <c r="B278">
-        <v>1</v>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t>location</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>kilowatt hour</t>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>categories</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>production</t>
+          <t>type</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t xml:space="preserve">electricity storage capacity, high power, fuel cell passenger car</t>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>comment</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>market for battery cell, Li-ion, NMC622</t>
+          <t xml:space="preserve">market for electricity storage capacity, battery, high power, fuel cell passenger car</t>
         </is>
       </c>
       <c r="B279">
-        <v>25.11261261261261</v>
+        <v>1</v>
       </c>
       <c r="C279" t="inlineStr">
         <is>
@@ -5731,28 +5713,28 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t>kilowatt hour</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t>production</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>battery cell, Li-ion, NMC622</t>
+          <t xml:space="preserve">electricity storage capacity, high power, fuel cell passenger car</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery central control and protection unit production</t>
+          <t>market for battery cell, Li-ion, NMC622</t>
         </is>
       </c>
       <c r="B280">
-        <v>0.8043758043758044</v>
+        <v>25.11261261261261</v>
       </c>
       <c r="C280" t="inlineStr">
         <is>
@@ -5761,7 +5743,7 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>kilogram</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
@@ -5771,18 +5753,18 @@
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery central control and protection unit</t>
+          <t>battery cell, Li-ion, NMC622</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>market for copper, cathode</t>
+          <t xml:space="preserve">battery central control and protection unit production</t>
         </is>
       </c>
       <c r="B281">
-        <v>0.12078060465157239</v>
+        <v>0.8043758043758044</v>
       </c>
       <c r="C281" t="inlineStr">
         <is>
@@ -5791,7 +5773,7 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
@@ -5801,14 +5783,14 @@
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>copper, cathode</t>
+          <t xml:space="preserve">battery central control and protection unit</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>metal working, average for copper product manufacturing</t>
+          <t>market for copper, cathode</t>
         </is>
       </c>
       <c r="B282">
@@ -5816,7 +5798,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>RER</t>
+          <t>GLO</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -5831,22 +5813,22 @@
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>metal working, average for copper product manufacturing</t>
+          <t>copper, cathode</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>market for aluminium, wrought alloy</t>
+          <t>metal working, average for copper product manufacturing</t>
         </is>
       </c>
       <c r="B283">
-        <v>6.566284025961444</v>
+        <v>0.12078060465157239</v>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t>RER</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -5861,14 +5843,14 @@
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>aluminium, wrought alloy</t>
+          <t>metal working, average for copper product manufacturing</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>metal working, average for aluminium product manufacturing</t>
+          <t>market for aluminium, wrought alloy</t>
         </is>
       </c>
       <c r="B284">
@@ -5876,7 +5858,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>RER</t>
+          <t>GLO</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -5891,22 +5873,22 @@
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>metal working, average for aluminium product manufacturing</t>
+          <t>aluminium, wrought alloy</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>market for polyethylene, high density, granulate</t>
+          <t>metal working, average for aluminium product manufacturing</t>
         </is>
       </c>
       <c r="B285">
-        <v>0.19742983452660873</v>
+        <v>6.566284025961444</v>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t>RER</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -5921,18 +5903,18 @@
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>polyethylene, high density, granulate</t>
+          <t>metal working, average for aluminium product manufacturing</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>market for glass fibre reinforced plastic, polyester resin, hand lay-up</t>
+          <t>market for polyethylene, high density, granulate</t>
         </is>
       </c>
       <c r="B286">
-        <v>0.025549743291678775</v>
+        <v>0.19742983452660873</v>
       </c>
       <c r="C286" t="inlineStr">
         <is>
@@ -5951,18 +5933,18 @@
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>glass fibre reinforced plastic, polyester resin, hand lay-up</t>
+          <t>polyethylene, high density, granulate</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>market for steel, low-alloyed</t>
+          <t>market for glass fibre reinforced plastic, polyester resin, hand lay-up</t>
         </is>
       </c>
       <c r="B287">
-        <v>0.21833416994707314</v>
+        <v>0.025549743291678775</v>
       </c>
       <c r="C287" t="inlineStr">
         <is>
@@ -5981,14 +5963,14 @@
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>steel, low-alloyed</t>
+          <t>glass fibre reinforced plastic, polyester resin, hand lay-up</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>metal working, average for steel product manufacturing</t>
+          <t>market for steel, low-alloyed</t>
         </is>
       </c>
       <c r="B288">
@@ -5996,7 +5978,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>RER</t>
+          <t>GLO</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -6011,240 +5993,222 @@
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>metal working, average for steel product manufacturing</t>
+          <t>steel, low-alloyed</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
+          <t>metal working, average for steel product manufacturing</t>
+        </is>
+      </c>
+      <c r="B289">
+        <v>0.21833416994707314</v>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>metal working, average for steel product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
           <t>market for used Li-ion battery</t>
         </is>
       </c>
-      <c r="B289">
+      <c r="B290">
         <v>-35.87516087516087</v>
       </c>
-      <c r="C289" t="inlineStr">
+      <c r="C290" t="inlineStr">
         <is>
           <t>GLO</t>
         </is>
       </c>
-      <c r="D289" t="inlineStr">
+      <c r="D290" t="inlineStr">
         <is>
           <t>kilogram</t>
         </is>
       </c>
-      <c r="F289" t="inlineStr">
+      <c r="F290" t="inlineStr">
         <is>
           <t>technosphere</t>
         </is>
       </c>
-      <c r="G289" t="inlineStr">
+      <c r="G290" t="inlineStr">
         <is>
           <t>used Li-ion battery</t>
-        </is>
-      </c>
-    </row>
-    <row r="292">
-      <c r="A292" t="inlineStr">
-        <is>
-          <t>Activity</t>
-        </is>
-      </c>
-      <c r="B292" t="inlineStr">
-        <is>
-          <t xml:space="preserve">market for electricity storage capacity, battery, high power, fuel cell truck</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>location</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t xml:space="preserve">market for electricity storage capacity, battery, high power, fuel cell truck</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>production amount</t>
-        </is>
-      </c>
-      <c r="B294">
-        <v>1</v>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>reference product</t>
-        </is>
-      </c>
-      <c r="B295" t="inlineStr">
-        <is>
-          <t xml:space="preserve">electricity storage capacity, high power, fuel cell truck</t>
-        </is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B295">
+        <v>1</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>reference product</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>kilowatt hour</t>
+          <t xml:space="preserve">electricity storage capacity, high power, fuel cell truck</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>source</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Toyota Mirai2 manufacturer https://newsroom.toyota.eu/introducing-the-all-new-toyota-mirai/; AKASOL AKASYSTEM15OEM37PRC May2021 https://www.act-news.com/wp-content/uploads/2020/11/210525_LowRes_AK_Datenblatt_AKASystem_15-OEM-37-PRC_2021_2159x2794mm_EN.pdf; Dai2018 Table8 https://publications.anl.gov/anlpubs/2018/10/146906.pdf.</t>
+          <t>kilowatt hour</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>Toyota Mirai2 manufacturer https://newsroom.toyota.eu/introducing-the-all-new-toyota-mirai/; AKASOL AKASYSTEM15OEM37PRC May2021 https://www.act-news.com/wp-content/uploads/2020/11/210525_LowRes_AK_Datenblatt_AKASystem_15-OEM-37-PRC_2021_2159x2794mm_EN.pdf; Dai2018 Table8 https://publications.anl.gov/anlpubs/2018/10/146906.pdf.</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
           <t>comment</t>
         </is>
       </c>
-      <c r="B298" t="inlineStr">
+      <c r="B299" t="inlineStr">
         <is>
           <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: high-power battery capacity, FCEV truck, engineering reference. Former reference product: high-power battery capacity, FCEV truck, engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
 APPROVED FCEV HIGH-POWER PACK ENGINEERING REFERENCES, item24, 2026-10-18. Toyota Mirai2 manufacturer https://newsroom.toyota.eu/introducing-the-all-new-toyota-mirai/; AKASOL AKASYSTEM15OEM37PRC May2021 https://www.act-news.com/wp-content/uploads/2020/11/210525_LowRes_AK_Datenblatt_AKASystem_15-OEM-37-PRC_2021_2159x2794mm_EN.pdf; Dai2018 Table8 https://publications.anl.gov/anlpubs/2018/10/146906.pdf. Match complete physical pack mass and nominal energy, not the changing BEV MIX. Car reference44.6kg/1.2432kWh (=310.8V*4Ah/1000),31.5kW for10seconds; truck reference238kg/25kWh,36kW continuous charge,50kW continuous RMS discharge,150kW10second discharge. Retain existing vehicle capacities/power sizing and lifetime replacement counts. These manufacturer ratings are NOT inferred from chemistry or treated as continuous pulse ratings. Material split remains an engineering proxy:70percent cells, as in the truck sizing source; assume the same70percent for cars. NMC622 cell manufacturing is a bulk-composition proxy, NOT a measured Mirai/AKASOL cell design or a validated high-power electrode/capacity recipe. Thus mass-equivalence is corrected while chemistry-specific metal intensities remain uncertain. Sensitivity cell share50-80percent and alternative documented high-power chemistries. One4.518kg central-control/protection assembly per reference pack; remaining mass is allocated using public Dai non-electronic hardware proportions. Car air-cooled reference excludes liquid coolant; unknown fan/duct design is embedded in the residual housing proxy, not independently validated. Truck liquid cooling retains Dai50/50 glycol/water proportions; pump/thermal ratings remain gaps. No module electronics are added on top of the central package; missing distributed monitoring is a coverage gap. All retained material inputs use100percent assembly retention reference; generic working services additional. Equal negative used-battery treatment equals complete manufactured reference mass, including controls, once; no duplicated control waste. These dedicated capacity providers are deliberately outside generic chemistry-density and MIX updates, preserving the already-declared fixed2020 FCEV hardware assumption through2050. Do not interpret corrected mass as a validated manufacturer BOM, annual procurement or primary/secondary content.</t>
         </is>
       </c>
     </row>
-    <row r="299">
-      <c r="A299" t="inlineStr">
-        <is>
-          <t>Exchanges</t>
-        </is>
-      </c>
-    </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>name</t>
+          <t xml:space="preserve">type</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>amount</t>
-        </is>
-      </c>
-      <c r="C300" t="inlineStr">
-        <is>
-          <t>location</t>
-        </is>
-      </c>
-      <c r="D300" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="E300" t="inlineStr">
-        <is>
-          <t>categories</t>
-        </is>
-      </c>
-      <c r="F300" t="inlineStr">
-        <is>
-          <t>type</t>
-        </is>
-      </c>
-      <c r="G300" t="inlineStr">
-        <is>
-          <t>reference product</t>
-        </is>
-      </c>
-      <c r="H300" t="inlineStr">
-        <is>
-          <t>comment</t>
+          <t xml:space="preserve">processwithreferenceproduct</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t xml:space="preserve">market for electricity storage capacity, battery, high power, fuel cell truck</t>
-        </is>
-      </c>
-      <c r="B301">
-        <v>1</v>
-      </c>
-      <c r="C301" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-      <c r="D301" t="inlineStr">
-        <is>
-          <t>kilowatt hour</t>
-        </is>
-      </c>
-      <c r="F301" t="inlineStr">
-        <is>
-          <t>production</t>
-        </is>
-      </c>
-      <c r="G301" t="inlineStr">
-        <is>
-          <t xml:space="preserve">electricity storage capacity, high power, fuel cell truck</t>
+          <t>Exchanges</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>market for battery cell, Li-ion, NMC622</t>
-        </is>
-      </c>
-      <c r="B302">
-        <v>6.664</v>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t>location</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>categories</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t>type</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>battery cell, Li-ion, NMC622</t>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>comment</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery central control and protection unit production</t>
+          <t xml:space="preserve">market for electricity storage capacity, battery, high power, fuel cell truck</t>
         </is>
       </c>
       <c r="B303">
-        <v>0.04</v>
+        <v>1</v>
       </c>
       <c r="C303" t="inlineStr">
         <is>
@@ -6253,28 +6217,28 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>kilowatt hour</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t>production</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery central control and protection unit</t>
+          <t xml:space="preserve">electricity storage capacity, high power, fuel cell truck</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>market for copper, cathode</t>
+          <t>market for battery cell, Li-ion, NMC622</t>
         </is>
       </c>
       <c r="B304">
-        <v>0.03689062848050915</v>
+        <v>6.664</v>
       </c>
       <c r="C304" t="inlineStr">
         <is>
@@ -6293,27 +6257,27 @@
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>copper, cathode</t>
+          <t>battery cell, Li-ion, NMC622</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>metal working, average for copper product manufacturing</t>
+          <t xml:space="preserve">battery central control and protection unit production</t>
         </is>
       </c>
       <c r="B305">
-        <v>0.03689062848050915</v>
+        <v>0.04</v>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>RER</t>
+          <t>GLO</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
@@ -6323,18 +6287,18 @@
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>metal working, average for copper product manufacturing</t>
+          <t xml:space="preserve">battery central control and protection unit</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>market for aluminium, wrought alloy</t>
+          <t>market for copper, cathode</t>
         </is>
       </c>
       <c r="B306">
-        <v>2.005573206046141</v>
+        <v>0.03689062848050915</v>
       </c>
       <c r="C306" t="inlineStr">
         <is>
@@ -6353,18 +6317,18 @@
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>aluminium, wrought alloy</t>
+          <t>copper, cathode</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>metal working, average for aluminium product manufacturing</t>
+          <t>metal working, average for copper product manufacturing</t>
         </is>
       </c>
       <c r="B307">
-        <v>2.005573206046141</v>
+        <v>0.03689062848050915</v>
       </c>
       <c r="C307" t="inlineStr">
         <is>
@@ -6383,18 +6347,18 @@
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>metal working, average for aluminium product manufacturing</t>
+          <t>metal working, average for copper product manufacturing</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>market for polyethylene, high density, granulate</t>
+          <t>market for aluminium, wrought alloy</t>
         </is>
       </c>
       <c r="B308">
-        <v>0.06030198886237072</v>
+        <v>2.005573206046141</v>
       </c>
       <c r="C308" t="inlineStr">
         <is>
@@ -6413,22 +6377,22 @@
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>polyethylene, high density, granulate</t>
+          <t>aluminium, wrought alloy</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>market for glass fibre reinforced plastic, polyester resin, hand lay-up</t>
+          <t>metal working, average for aluminium product manufacturing</t>
         </is>
       </c>
       <c r="B309">
-        <v>0.007803786793953858</v>
+        <v>2.005573206046141</v>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t>RER</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -6443,18 +6407,18 @@
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>glass fibre reinforced plastic, polyester resin, hand lay-up</t>
+          <t>metal working, average for aluminium product manufacturing</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>market for steel, low-alloyed</t>
+          <t>market for polyethylene, high density, granulate</t>
         </is>
       </c>
       <c r="B310">
-        <v>0.06668690533015115</v>
+        <v>0.06030198886237072</v>
       </c>
       <c r="C310" t="inlineStr">
         <is>
@@ -6473,22 +6437,22 @@
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>steel, low-alloyed</t>
+          <t>polyethylene, high density, granulate</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>metal working, average for steel product manufacturing</t>
+          <t>market for glass fibre reinforced plastic, polyester resin, hand lay-up</t>
         </is>
       </c>
       <c r="B311">
-        <v>0.06668690533015115</v>
+        <v>0.007803786793953858</v>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>RER</t>
+          <t>GLO</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -6503,22 +6467,22 @@
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>metal working, average for steel product manufacturing</t>
+          <t>glass fibre reinforced plastic, polyester resin, hand lay-up</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>ethylene glycols production, thermal hydrolysis of ethylene oxide</t>
+          <t>market for steel, low-alloyed</t>
         </is>
       </c>
       <c r="B312">
-        <v>0.2490117422434367</v>
+        <v>0.06668690533015115</v>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>RER</t>
+          <t>GLO</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -6533,22 +6497,22 @@
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>ethylene glycol</t>
+          <t>steel, low-alloyed</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>market for water, deionised</t>
+          <t>metal working, average for steel product manufacturing</t>
         </is>
       </c>
       <c r="B313">
-        <v>0.2490117422434367</v>
+        <v>0.06668690533015115</v>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>RoW</t>
+          <t>RER</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -6563,259 +6527,216 @@
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>water, deionised</t>
+          <t>metal working, average for steel product manufacturing</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
+          <t>ethylene glycols production, thermal hydrolysis of ethylene oxide</t>
+        </is>
+      </c>
+      <c r="B314">
+        <v>0.2490117422434367</v>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>ethylene glycol</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>market for water, deionised</t>
+        </is>
+      </c>
+      <c r="B315">
+        <v>0.2490117422434367</v>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>water, deionised</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
           <t>market for used Li-ion battery</t>
         </is>
       </c>
-      <c r="B314">
+      <c r="B316">
         <v>-9.52</v>
       </c>
-      <c r="C314" t="inlineStr">
+      <c r="C316" t="inlineStr">
         <is>
           <t>GLO</t>
         </is>
       </c>
-      <c r="D314" t="inlineStr">
+      <c r="D316" t="inlineStr">
         <is>
           <t>kilogram</t>
         </is>
       </c>
-      <c r="F314" t="inlineStr">
+      <c r="F316" t="inlineStr">
         <is>
           <t>technosphere</t>
         </is>
       </c>
-      <c r="G314" t="inlineStr">
+      <c r="G316" t="inlineStr">
         <is>
           <t>used Li-ion battery</t>
-        </is>
-      </c>
-    </row>
-    <row r="317">
-      <c r="A317" t="inlineStr">
-        <is>
-          <t>Activity</t>
-        </is>
-      </c>
-      <c r="B317" t="inlineStr">
-        <is>
-          <t xml:space="preserve">market for electricity storage capacity, battery, Li-ion, LFP, hydrogen train</t>
-        </is>
-      </c>
-    </row>
-    <row r="318">
-      <c r="A318" t="inlineStr">
-        <is>
-          <t>location</t>
-        </is>
-      </c>
-      <c r="B318" t="inlineStr">
-        <is>
-          <t>GLO</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>production amount</t>
-        </is>
-      </c>
-      <c r="B319">
-        <v>1</v>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t xml:space="preserve">market for electricity storage capacity, battery, lithium-ion, lfp, hydrogen train</t>
+        </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>reference product</t>
+          <t>location</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t xml:space="preserve">electricity storage capacity, Li-ion, LFP, hydrogen train</t>
+          <t>GLO</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="B321" t="inlineStr">
-        <is>
-          <t>kilowatt hour</t>
-        </is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B321">
+        <v>1</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>source</t>
+          <t>reference product</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Knibbe2023 DOI10.1016/j.est.2023.108090,3.6MWhLFP/860kWreference and133Wh/kgpack; Dai2018 public LFP non-cell material proportions https://publications.anl.gov/anlpubs/2018/10/146906.pdf Table8.</t>
+          <t xml:space="preserve">electricity storage capacity, Li-ion, LFP, hydrogen train</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>Knibbe2023 DOI10.1016/j.est.2023.108090,3.6MWhLFP/860kWreference and133Wh/kgpack; Dai2018 public LFP non-cell material proportions https://publications.anl.gov/anlpubs/2018/10/146906.pdf Table8.</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
           <t>comment</t>
         </is>
       </c>
-      <c r="B323" t="inlineStr">
+      <c r="B325" t="inlineStr">
         <is>
           <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: battery capacity, hydrogen rail, LFP engineering reference. Former reference product: battery capacity, hydrogen rail, LFP engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
 APPROVED HYDROGEN-RAIL COMPLETE LFP CAPACITY REFERENCE, issue33, 2026-10-18. Knibbe2023 DOI10.1016/j.est.2023.108090,3.6MWhLFP/860kWreference and133Wh/kgpack; Dai2018 public LFP non-cell material proportions https://publications.anl.gov/anlpubs/2018/10/146906.pdf Table8. Replace old whole-pack23.5kWh/165kg conversion purchased as bareNMC622cells with a complete3.6MWhLFP reference. Referencepack133Wh/kg =&gt;27067.66917293233kg installed; existing40year/15year lifetime convention gives9600kWh manufactured and treated, not annual procurement.15years remains an engineering calendar assumption, not demonstrated rail LFP cycle life; sensitivity10-20years and source-specific duty/aging remains required. At860kW total stored energy/power=4.186h; battery peakpower and simultaneous fuel-cell duty are not proven by this ratio. Per1kWh:6.25kg cells at existing160Wh/kgcell reference. Assume modular100kWh subsystems, each112series-equivalent3.2V LFPcells at279.017857Ah; series/parallel arrangement and thermal ratings are a design reference, not measured locomotive architecture. One existing6.668kg LFP monitoring/central-controls package per100kWh; other retained mass uses Dai non-electronic module/pack material proportions including50/50glycol/water. This hardware geometry/control allocation is an explicit engineering transfer. Complete pack mass/cellcapacity/control+waste close together. Controls package already treats its6.668kg, so local battery waste excludes that mass; no duplicate EOL. Source cell manufacturing chemistry, electronics-specific materials and thermal duty remain proxies; source133Wh/kg is not certification of this constructed BOM. Existing rail inventory had fixed barecell mass over time; this dedicated fixed-reference provider retains that temporal boundary and is outside generic road density-learning markets. No future LFP electrode evolution is claimed. No locomotive body, tender or track added. Rail source and explicit passenger-energy link are both changed.</t>
         </is>
       </c>
     </row>
-    <row r="324">
-      <c r="A324" t="inlineStr">
-        <is>
-          <t>Exchanges</t>
-        </is>
-      </c>
-    </row>
-    <row r="325">
-      <c r="A325" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B325" t="inlineStr">
-        <is>
-          <t>amount</t>
-        </is>
-      </c>
-      <c r="C325" t="inlineStr">
-        <is>
-          <t>location</t>
-        </is>
-      </c>
-      <c r="D325" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="E325" t="inlineStr">
-        <is>
-          <t>categories</t>
-        </is>
-      </c>
-      <c r="F325" t="inlineStr">
-        <is>
-          <t>type</t>
-        </is>
-      </c>
-      <c r="G325" t="inlineStr">
-        <is>
-          <t>reference product</t>
-        </is>
-      </c>
-      <c r="H325" t="inlineStr">
-        <is>
-          <t>comment</t>
-        </is>
-      </c>
-      <c r="I325" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-    </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t xml:space="preserve">market for electricity storage capacity, battery, Li-ion, LFP, hydrogen train</t>
-        </is>
-      </c>
-      <c r="B326">
-        <v>1</v>
-      </c>
-      <c r="C326" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-      <c r="D326" t="inlineStr">
-        <is>
-          <t>kilowatt hour</t>
-        </is>
-      </c>
-      <c r="F326" t="inlineStr">
-        <is>
-          <t>production</t>
-        </is>
-      </c>
-      <c r="G326" t="inlineStr">
-        <is>
-          <t xml:space="preserve">electricity storage capacity, Li-ion, LFP, hydrogen train</t>
-        </is>
-      </c>
-      <c r="I326" t="inlineStr">
-        <is>
-          <t xml:space="preserve">electricity storage capacity, Li-ion, LFP, hydrogen train</t>
+          <t xml:space="preserve">type</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t xml:space="preserve">processwithreferenceproduct</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>market for battery cell, Li-ion, LFP</t>
-        </is>
-      </c>
-      <c r="B327">
-        <v>6.25</v>
-      </c>
-      <c r="C327" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-      <c r="D327" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="F327" t="inlineStr">
-        <is>
-          <t>technosphere</t>
-        </is>
-      </c>
-      <c r="G327" t="inlineStr">
-        <is>
-          <t>battery cell, Li-ion, LFP</t>
-        </is>
-      </c>
-      <c r="I327" t="inlineStr">
-        <is>
-          <t>battery cell, Li-ion, LFP</t>
+          <t>Exchanges</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery monitoring and central control system production, Li-ion, LFP</t>
-        </is>
-      </c>
-      <c r="B328">
-        <v>0.01</v>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t>location</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
@@ -6823,30 +6744,40 @@
           <t>unit</t>
         </is>
       </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t>type</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery monitoring and central control system, Li-ion, LFP</t>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>comment</t>
         </is>
       </c>
       <c r="I328" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery monitoring and central control system, Li-ion, LFP</t>
+          <t>product</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>market for copper, cathode</t>
+          <t xml:space="preserve">market for electricity storage capacity, battery, lithium-ion, lfp, hydrogen train</t>
         </is>
       </c>
       <c r="B329">
-        <v>0.01512710646109896</v>
+        <v>1</v>
       </c>
       <c r="C329" t="inlineStr">
         <is>
@@ -6855,37 +6786,37 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t>kilowatt hour</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t>production</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>copper, cathode</t>
+          <t xml:space="preserve">electricity storage capacity, Li-ion, LFP, hydrogen train</t>
         </is>
       </c>
       <c r="I329" t="inlineStr">
         <is>
-          <t>copper, cathode</t>
+          <t xml:space="preserve">electricity storage capacity, Li-ion, LFP, hydrogen train</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>metal working, average for copper product manufacturing</t>
+          <t>market for battery cell, Li-ion, LFP</t>
         </is>
       </c>
       <c r="B330">
-        <v>0.01512710646109896</v>
+        <v>6.25</v>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>RER</t>
+          <t>GLO</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
@@ -6900,23 +6831,23 @@
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>metal working, average for copper product manufacturing</t>
+          <t>battery cell, Li-ion, LFP</t>
         </is>
       </c>
       <c r="I330" t="inlineStr">
         <is>
-          <t>metal working, average for copper product manufacturing</t>
+          <t>battery cell, Li-ion, LFP</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>market for aluminium, wrought alloy</t>
+          <t xml:space="preserve">battery monitoring and central control system production, lithium-ion, lfp</t>
         </is>
       </c>
       <c r="B331">
-        <v>0.8717605062178482</v>
+        <v>0.01</v>
       </c>
       <c r="C331" t="inlineStr">
         <is>
@@ -6925,7 +6856,7 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
@@ -6935,27 +6866,27 @@
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>aluminium, wrought alloy</t>
+          <t xml:space="preserve">battery monitoring and central control system, Li-ion, LFP</t>
         </is>
       </c>
       <c r="I331" t="inlineStr">
         <is>
-          <t>aluminium, wrought alloy</t>
+          <t xml:space="preserve">battery monitoring and central control system, Li-ion, LFP</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>metal working, average for aluminium product manufacturing</t>
+          <t>market for copper, cathode</t>
         </is>
       </c>
       <c r="B332">
-        <v>0.8717605062178482</v>
+        <v>0.01512710646109896</v>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>RER</t>
+          <t>GLO</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
@@ -6970,27 +6901,27 @@
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>metal working, average for aluminium product manufacturing</t>
+          <t>copper, cathode</t>
         </is>
       </c>
       <c r="I332" t="inlineStr">
         <is>
-          <t>metal working, average for aluminium product manufacturing</t>
+          <t>copper, cathode</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>market for polyethylene, high density, granulate</t>
+          <t>metal working, average for copper product manufacturing</t>
         </is>
       </c>
       <c r="B333">
-        <v>0.02439855880822413</v>
+        <v>0.01512710646109896</v>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t>RER</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
@@ -7005,23 +6936,23 @@
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>polyethylene, high density, granulate</t>
+          <t>metal working, average for copper product manufacturing</t>
         </is>
       </c>
       <c r="I333" t="inlineStr">
         <is>
-          <t>polyethylene, high density, granulate</t>
+          <t>metal working, average for copper product manufacturing</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>market for glass fibre reinforced plastic, polyester resin, hand lay-up</t>
+          <t>market for aluminium, wrought alloy</t>
         </is>
       </c>
       <c r="B334">
-        <v>0.003171812645069137</v>
+        <v>0.8717605062178482</v>
       </c>
       <c r="C334" t="inlineStr">
         <is>
@@ -7040,27 +6971,27 @@
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>glass fibre reinforced plastic, polyester resin, hand lay-up</t>
+          <t>aluminium, wrought alloy</t>
         </is>
       </c>
       <c r="I334" t="inlineStr">
         <is>
-          <t>glass fibre reinforced plastic, polyester resin, hand lay-up</t>
+          <t>aluminium, wrought alloy</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>market for steel, low-alloyed</t>
+          <t>metal working, average for aluminium product manufacturing</t>
         </is>
       </c>
       <c r="B335">
-        <v>0.03513392468384275</v>
+        <v>0.8717605062178482</v>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t>RER</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
@@ -7075,27 +7006,27 @@
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>steel, low-alloyed</t>
+          <t>metal working, average for aluminium product manufacturing</t>
         </is>
       </c>
       <c r="I335" t="inlineStr">
         <is>
-          <t>steel, low-alloyed</t>
+          <t>metal working, average for aluminium product manufacturing</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>metal working, average for steel product manufacturing</t>
+          <t>market for polyethylene, high density, granulate</t>
         </is>
       </c>
       <c r="B336">
-        <v>0.03513392468384275</v>
+        <v>0.02439855880822413</v>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>RER</t>
+          <t>GLO</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
@@ -7110,27 +7041,27 @@
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>metal working, average for steel product manufacturing</t>
+          <t>polyethylene, high density, granulate</t>
         </is>
       </c>
       <c r="I336" t="inlineStr">
         <is>
-          <t>metal working, average for steel product manufacturing</t>
+          <t>polyethylene, high density, granulate</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>ethylene glycols production, thermal hydrolysis of ethylene oxide</t>
+          <t>market for glass fibre reinforced plastic, polyester resin, hand lay-up</t>
         </is>
       </c>
       <c r="B337">
-        <v>0.12626254183255986</v>
+        <v>0.003171812645069137</v>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>RER</t>
+          <t>GLO</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
@@ -7145,27 +7076,27 @@
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>ethylene glycol</t>
+          <t>glass fibre reinforced plastic, polyester resin, hand lay-up</t>
         </is>
       </c>
       <c r="I337" t="inlineStr">
         <is>
-          <t>ethylene glycol</t>
+          <t>glass fibre reinforced plastic, polyester resin, hand lay-up</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>market for water, deionised</t>
+          <t>market for steel, low-alloyed</t>
         </is>
       </c>
       <c r="B338">
-        <v>0.12626254183255986</v>
+        <v>0.03513392468384275</v>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>RoW</t>
+          <t>GLO</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
@@ -7180,27 +7111,27 @@
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>water, deionised</t>
+          <t>steel, low-alloyed</t>
         </is>
       </c>
       <c r="I338" t="inlineStr">
         <is>
-          <t>water, deionised</t>
+          <t>steel, low-alloyed</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>market for used Li-ion battery</t>
+          <t>metal working, average for steel product manufacturing</t>
         </is>
       </c>
       <c r="B339">
-        <v>-7.452116992481203</v>
+        <v>0.03513392468384275</v>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t>RER</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
@@ -7215,300 +7146,277 @@
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>used Li-ion battery</t>
+          <t>metal working, average for steel product manufacturing</t>
         </is>
       </c>
       <c r="I339" t="inlineStr">
         <is>
-          <t>used Li-ion battery</t>
+          <t>metal working, average for steel product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>ethylene glycols production, thermal hydrolysis of ethylene oxide</t>
+        </is>
+      </c>
+      <c r="B340">
+        <v>0.12626254183255986</v>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>ethylene glycol</t>
+        </is>
+      </c>
+      <c r="I340" t="inlineStr">
+        <is>
+          <t>ethylene glycol</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>market for water, deionised</t>
+        </is>
+      </c>
+      <c r="B341">
+        <v>0.12626254183255986</v>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>water, deionised</t>
+        </is>
+      </c>
+      <c r="I341" t="inlineStr">
+        <is>
+          <t>water, deionised</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>Activity</t>
-        </is>
-      </c>
-      <c r="B342" t="inlineStr">
-        <is>
-          <t xml:space="preserve">battery pack production, Li-ion, LTO, fuel cell bus, without controls</t>
-        </is>
-      </c>
-    </row>
-    <row r="343">
-      <c r="A343" t="inlineStr">
-        <is>
-          <t>location</t>
-        </is>
-      </c>
-      <c r="B343" t="inlineStr">
+          <t>market for used Li-ion battery</t>
+        </is>
+      </c>
+      <c r="B342">
+        <v>-7.452116992481203</v>
+      </c>
+      <c r="C342" t="inlineStr">
         <is>
           <t>GLO</t>
         </is>
       </c>
-    </row>
-    <row r="344">
-      <c r="A344" t="inlineStr">
-        <is>
-          <t>production amount</t>
-        </is>
-      </c>
-      <c r="B344">
-        <v>1</v>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>used Li-ion battery</t>
+        </is>
+      </c>
+      <c r="I342" t="inlineStr">
+        <is>
+          <t>used Li-ion battery</t>
+        </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>reference product</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery pack, Li-ion, LTO, fuel cell bus, without controls</t>
+          <t xml:space="preserve">battery pack production, lithium-ion, lto, fuel cell bus, without controls</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>location</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>GLO</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>source</t>
-        </is>
-      </c>
-      <c r="B347" t="inlineStr">
-        <is>
-          <t>Forsee Power PULSE15 manufacturer https://www.forseepower.com/lithium-ion-battery/high-power-batteries/pulse-15/ :14.6kWh,260kg,635V,LTO,63kWcontinuous,127kW10seconds,liquidcooling,15years/15000cycles.2020CaetanoH2 application https://www.forseepower.com/wp-content/uploads/2023/07/2020-01-27-Forsee-Power_CP-Caetano-h2_EN.pdf . Internal BOM not published.</t>
-        </is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B347">
+        <v>1</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t xml:space="preserve">battery pack, Li-ion, LTO, fuel cell bus, without controls</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>Forsee Power PULSE15 manufacturer https://www.forseepower.com/lithium-ion-battery/high-power-batteries/pulse-15/ :14.6kWh,260kg,635V,LTO,63kWcontinuous,127kW10seconds,liquidcooling,15years/15000cycles.2020CaetanoH2 application https://www.forseepower.com/wp-content/uploads/2023/07/2020-01-27-Forsee-Power_CP-Caetano-h2_EN.pdf . Internal BOM not published.</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
           <t>comment</t>
         </is>
       </c>
-      <c r="B348" t="inlineStr">
+      <c r="B351" t="inlineStr">
         <is>
           <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: battery hardware, fuel-cell bus LTO, engineering reference. Former reference product: battery hardware, fuel-cell bus LTO, engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
 APPROVED FUEL-CELL BUS BUFFER REFERENCE, issue59, 2026-10-18. Forsee Power PULSE15 manufacturer https://www.forseepower.com/lithium-ion-battery/high-power-batteries/pulse-15/ :14.6kWh,260kg,635V,LTO,63kWcontinuous,127kW10seconds,liquidcooling,15years/15000cycles.2020CaetanoH2 application https://www.forseepower.com/wp-content/uploads/2023/07/2020-01-27-Forsee-Power_CP-Caetano-h2_EN.pdf . Internal BOM not published. Replace six genericMIX highenergy batteries with a bus-specific fixed highpower LTO reference. Select smallest integer parallelpack count meeting both original nominalkWh and entire motorcontinuouspower/63kW; this deliberately conservative power check does not credit fuelcell contribution. Eachpack14.6kWh/260kg; preserve635V inparallel,do not addseriesvoltage. Nominalenergy is not advertised usableenergy; assume80%usable only as explicit sensitivity,not manufacturerDoD. Lifetime packcount=installedcount*ceil(vehicleyears/15); cyclethroughput unknown despite15000cycle claim. Sourcebatteryreplacement assumptions superseded explicitly, not appliedtwice. Internal cell reference:existing LTO cell chemistry/production recipe transferred at assumed80Wh/kgcell (sensitivity60-100),182.5kgcells/pack. Existing60Wh/kgrecipe coefficient is a different engineeringdesign;80Wh/kg is NOT measured PULSEcellperformance. Actual cathode,cellformat,cellcount,energy/power capability remain unresolved.6.538kg controls perpack from16module NMC955reference,architecture transfer not measured PULSEBMS. Other70.962kg casing/cooling/busbars assigned explicit engineering proportions50%Al,15%Cu,10%steel,10%PA,15%50/50glycolwater. Source260kg ensures physicalmassclosure; no assertion this unpublished BOM matches actualmanufacturer. Fixeddesign has no highenergy density trajectory or genericMIXchemistry switching; actualfuturepower/cellredesign requires evidence. Packdisposal covers253.462kg noncontrols,controlshelper disposes6.538kg,onceeach. Update vehicle specification notes and productionassembly mass by installedmassdelta; common glider unchanged, lifetimeenergy/service demand unchanged pending a new driving/thermal simulation. This changed mass/reference is therefore a manufacturing audit correction,not a validated roadperformance prediction. No extra wholevehicle procurement, primarysecondaryshares or recyclingcredit. Refresh affected storedperMJ equipment from actualsource inventories.</t>
         </is>
       </c>
     </row>
-    <row r="349">
-      <c r="A349" t="inlineStr">
-        <is>
-          <t>Exchanges</t>
-        </is>
-      </c>
-    </row>
-    <row r="350">
-      <c r="A350" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B350" t="inlineStr">
-        <is>
-          <t>amount</t>
-        </is>
-      </c>
-      <c r="C350" t="inlineStr">
-        <is>
-          <t>location</t>
-        </is>
-      </c>
-      <c r="D350" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="E350" t="inlineStr">
-        <is>
-          <t>categories</t>
-        </is>
-      </c>
-      <c r="F350" t="inlineStr">
-        <is>
-          <t>type</t>
-        </is>
-      </c>
-      <c r="G350" t="inlineStr">
-        <is>
-          <t>reference product</t>
-        </is>
-      </c>
-      <c r="H350" t="inlineStr">
-        <is>
-          <t>comment</t>
-        </is>
-      </c>
-      <c r="I350" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-    </row>
-    <row r="351">
-      <c r="A351" t="inlineStr">
-        <is>
-          <t xml:space="preserve">battery pack production, Li-ion, LTO, fuel cell bus, without controls</t>
-        </is>
-      </c>
-      <c r="B351">
-        <v>1</v>
-      </c>
-      <c r="C351" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-      <c r="D351" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="F351" t="inlineStr">
-        <is>
-          <t>production</t>
-        </is>
-      </c>
-      <c r="G351" t="inlineStr">
-        <is>
-          <t xml:space="preserve">battery pack, Li-ion, LTO, fuel cell bus, without controls</t>
-        </is>
-      </c>
-      <c r="I351" t="inlineStr">
-        <is>
-          <t xml:space="preserve">battery pack, Li-ion, LTO, fuel cell bus, without controls</t>
-        </is>
-      </c>
-    </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>battery cell production, Li-ion, LTO</t>
-        </is>
-      </c>
-      <c r="B352">
-        <v>182.5</v>
-      </c>
-      <c r="C352" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-      <c r="D352" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="F352" t="inlineStr">
-        <is>
-          <t>technosphere</t>
-        </is>
-      </c>
-      <c r="G352" t="inlineStr">
-        <is>
-          <t>battery cell, Li-ion, LTO</t>
-        </is>
-      </c>
-      <c r="I352" t="inlineStr">
-        <is>
-          <t>battery cell, Li-ion, LTO</t>
+          <t xml:space="preserve">type</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t xml:space="preserve">processwithreferenceproduct</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>market for aluminium, wrought alloy</t>
-        </is>
-      </c>
-      <c r="B353">
-        <v>35.481</v>
-      </c>
-      <c r="C353" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-      <c r="D353" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="F353" t="inlineStr">
-        <is>
-          <t>technosphere</t>
-        </is>
-      </c>
-      <c r="G353" t="inlineStr">
-        <is>
-          <t>aluminium, wrought alloy</t>
-        </is>
-      </c>
-      <c r="I353" t="inlineStr">
-        <is>
-          <t>aluminium, wrought alloy</t>
+          <t>Exchanges</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>market for copper, cathode</t>
-        </is>
-      </c>
-      <c r="B354">
-        <v>10.6443</v>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t>location</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>categories</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t>type</t>
         </is>
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>copper, cathode</t>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>comment</t>
         </is>
       </c>
       <c r="I354" t="inlineStr">
         <is>
-          <t>copper, cathode</t>
+          <t>product</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>market for steel, low-alloyed</t>
+          <t xml:space="preserve">battery pack production, lithium-ion, lto, fuel cell bus, without controls</t>
         </is>
       </c>
       <c r="B355">
-        <v>7.0962000000000005</v>
+        <v>1</v>
       </c>
       <c r="C355" t="inlineStr">
         <is>
@@ -7517,37 +7425,37 @@
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t>production</t>
         </is>
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>steel, low-alloyed</t>
+          <t xml:space="preserve">battery pack, Li-ion, LTO, fuel cell bus, without controls</t>
         </is>
       </c>
       <c r="I355" t="inlineStr">
         <is>
-          <t>steel, low-alloyed</t>
+          <t xml:space="preserve">battery pack, Li-ion, LTO, fuel cell bus, without controls</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>market for nylon 6</t>
+          <t>battery cell production, Li-ion, LTO</t>
         </is>
       </c>
       <c r="B356">
-        <v>7.0962000000000005</v>
+        <v>182.5</v>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>RER</t>
+          <t>GLO</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
@@ -7562,27 +7470,27 @@
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>nylon 6</t>
+          <t>battery cell, Li-ion, LTO</t>
         </is>
       </c>
       <c r="I356" t="inlineStr">
         <is>
-          <t>nylon 6</t>
+          <t>battery cell, Li-ion, LTO</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>ethylene glycols production, thermal hydrolysis of ethylene oxide</t>
+          <t>market for aluminium, wrought alloy</t>
         </is>
       </c>
       <c r="B357">
-        <v>5.32215</v>
+        <v>35.481</v>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>RER</t>
+          <t>GLO</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
@@ -7597,27 +7505,27 @@
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>ethylene glycol</t>
+          <t>aluminium, wrought alloy</t>
         </is>
       </c>
       <c r="I357" t="inlineStr">
         <is>
-          <t>ethylene glycol</t>
+          <t>aluminium, wrought alloy</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>market for water, deionised</t>
+          <t>market for copper, cathode</t>
         </is>
       </c>
       <c r="B358">
-        <v>5.32215</v>
+        <v>10.6443</v>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>RoW</t>
+          <t>GLO</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
@@ -7632,23 +7540,23 @@
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>water, deionised</t>
+          <t>copper, cathode</t>
         </is>
       </c>
       <c r="I358" t="inlineStr">
         <is>
-          <t>water, deionised</t>
+          <t>copper, cathode</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>market group for electricity, medium voltage</t>
+          <t>market for steel, low-alloyed</t>
         </is>
       </c>
       <c r="B359">
-        <v>260</v>
+        <v>7.0962000000000005</v>
       </c>
       <c r="C359" t="inlineStr">
         <is>
@@ -7657,7 +7565,7 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>kilowatt hour</t>
+          <t>kilogram</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
@@ -7667,287 +7575,439 @@
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>electricity, medium voltage</t>
+          <t>steel, low-alloyed</t>
         </is>
       </c>
       <c r="I359" t="inlineStr">
         <is>
-          <t>electricity, medium voltage</t>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>market for nylon 6</t>
+        </is>
+      </c>
+      <c r="B360">
+        <v>7.0962000000000005</v>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>nylon 6</t>
+        </is>
+      </c>
+      <c r="I360" t="inlineStr">
+        <is>
+          <t>nylon 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>ethylene glycols production, thermal hydrolysis of ethylene oxide</t>
+        </is>
+      </c>
+      <c r="B361">
+        <v>5.32215</v>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>ethylene glycol</t>
+        </is>
+      </c>
+      <c r="I361" t="inlineStr">
+        <is>
+          <t>ethylene glycol</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>Activity</t>
-        </is>
-      </c>
-      <c r="B362" t="inlineStr">
-        <is>
-          <t xml:space="preserve">market for electricity storage capacity, battery, Li-ion, LTO, high power, fuel cell bus</t>
+          <t>market for water, deionised</t>
+        </is>
+      </c>
+      <c r="B362">
+        <v>5.32215</v>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>water, deionised</t>
+        </is>
+      </c>
+      <c r="I362" t="inlineStr">
+        <is>
+          <t>water, deionised</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>location</t>
-        </is>
-      </c>
-      <c r="B363" t="inlineStr">
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B363">
+        <v>260</v>
+      </c>
+      <c r="C363" t="inlineStr">
         <is>
           <t>GLO</t>
         </is>
       </c>
-    </row>
-    <row r="364">
-      <c r="A364" t="inlineStr">
-        <is>
-          <t>production amount</t>
-        </is>
-      </c>
-      <c r="B364">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="365">
-      <c r="A365" t="inlineStr">
-        <is>
-          <t>reference product</t>
-        </is>
-      </c>
-      <c r="B365" t="inlineStr">
-        <is>
-          <t xml:space="preserve">electricity storage capacity, Li-ion, LTO, high power, fuel cell bus</t>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="I363" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>kilowatt hour</t>
+          <t xml:space="preserve">market for electricity storage capacity, battery, lithium-ion, lto, high power, fuel cell bus</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>source</t>
+          <t>location</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Forsee Power PULSE15 manufacturer https://www.forseepower.com/lithium-ion-battery/high-power-batteries/pulse-15/ :14.6kWh,260kg,635V,LTO,63kWcontinuous,127kW10seconds,liquidcooling,15years/15000cycles.2020CaetanoH2 application https://www.forseepower.com/wp-content/uploads/2023/07/2020-01-27-Forsee-Power_CP-Caetano-h2_EN.pdf . Internal BOM not published.</t>
+          <t>GLO</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B368">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t xml:space="preserve">electricity storage capacity, Li-ion, LTO, high power, fuel cell bus</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>Forsee Power PULSE15 manufacturer https://www.forseepower.com/lithium-ion-battery/high-power-batteries/pulse-15/ :14.6kWh,260kg,635V,LTO,63kWcontinuous,127kW10seconds,liquidcooling,15years/15000cycles.2020CaetanoH2 application https://www.forseepower.com/wp-content/uploads/2023/07/2020-01-27-Forsee-Power_CP-Caetano-h2_EN.pdf . Internal BOM not published.</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
           <t>comment</t>
         </is>
       </c>
-      <c r="B368" t="inlineStr">
+      <c r="B372" t="inlineStr">
         <is>
           <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: high-power battery capacity, fuel-cell bus LTO, engineering reference. Former reference product: high-power battery capacity, fuel-cell bus LTO, engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
 APPROVED FUEL-CELL BUS BUFFER REFERENCE, issue59, 2026-10-18. Forsee Power PULSE15 manufacturer https://www.forseepower.com/lithium-ion-battery/high-power-batteries/pulse-15/ :14.6kWh,260kg,635V,LTO,63kWcontinuous,127kW10seconds,liquidcooling,15years/15000cycles.2020CaetanoH2 application https://www.forseepower.com/wp-content/uploads/2023/07/2020-01-27-Forsee-Power_CP-Caetano-h2_EN.pdf . Internal BOM not published. Replace six genericMIX highenergy batteries with a bus-specific fixed highpower LTO reference. Select smallest integer parallelpack count meeting both original nominalkWh and entire motorcontinuouspower/63kW; this deliberately conservative power check does not credit fuelcell contribution. Eachpack14.6kWh/260kg; preserve635V inparallel,do not addseriesvoltage. Nominalenergy is not advertised usableenergy; assume80%usable only as explicit sensitivity,not manufacturerDoD. Lifetime packcount=installedcount*ceil(vehicleyears/15); cyclethroughput unknown despite15000cycle claim. Sourcebatteryreplacement assumptions superseded explicitly, not appliedtwice. Internal cell reference:existing LTO cell chemistry/production recipe transferred at assumed80Wh/kgcell (sensitivity60-100),182.5kgcells/pack. Existing60Wh/kgrecipe coefficient is a different engineeringdesign;80Wh/kg is NOT measured PULSEcellperformance. Actual cathode,cellformat,cellcount,energy/power capability remain unresolved.6.538kg controls perpack from16module NMC955reference,architecture transfer not measured PULSEBMS. Other70.962kg casing/cooling/busbars assigned explicit engineering proportions50%Al,15%Cu,10%steel,10%PA,15%50/50glycolwater. Source260kg ensures physicalmassclosure; no assertion this unpublished BOM matches actualmanufacturer. Fixeddesign has no highenergy density trajectory or genericMIXchemistry switching; actualfuturepower/cellredesign requires evidence. Packdisposal covers253.462kg noncontrols,controlshelper disposes6.538kg,onceeach. Update vehicle specification notes and productionassembly mass by installedmassdelta; common glider unchanged, lifetimeenergy/service demand unchanged pending a new driving/thermal simulation. This changed mass/reference is therefore a manufacturing audit correction,not a validated roadperformance prediction. No extra wholevehicle procurement, primarysecondaryshares or recyclingcredit. Refresh affected storedperMJ equipment from actualsource inventories.</t>
         </is>
       </c>
     </row>
-    <row r="369">
-      <c r="A369" t="inlineStr">
-        <is>
-          <t>Exchanges</t>
-        </is>
-      </c>
-    </row>
-    <row r="370">
-      <c r="A370" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B370" t="inlineStr">
-        <is>
-          <t>amount</t>
-        </is>
-      </c>
-      <c r="C370" t="inlineStr">
-        <is>
-          <t>location</t>
-        </is>
-      </c>
-      <c r="D370" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="E370" t="inlineStr">
-        <is>
-          <t>categories</t>
-        </is>
-      </c>
-      <c r="F370" t="inlineStr">
-        <is>
-          <t>type</t>
-        </is>
-      </c>
-      <c r="G370" t="inlineStr">
-        <is>
-          <t>reference product</t>
-        </is>
-      </c>
-      <c r="H370" t="inlineStr">
-        <is>
-          <t>comment</t>
-        </is>
-      </c>
-      <c r="I370" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-    </row>
-    <row r="371">
-      <c r="A371" t="inlineStr">
-        <is>
-          <t xml:space="preserve">market for electricity storage capacity, battery, Li-ion, LTO, high power, fuel cell bus</t>
-        </is>
-      </c>
-      <c r="B371">
-        <v>1</v>
-      </c>
-      <c r="C371" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-      <c r="D371" t="inlineStr">
-        <is>
-          <t>kilowatt hour</t>
-        </is>
-      </c>
-      <c r="F371" t="inlineStr">
-        <is>
-          <t>production</t>
-        </is>
-      </c>
-      <c r="G371" t="inlineStr">
-        <is>
-          <t xml:space="preserve">electricity storage capacity, Li-ion, LTO, high power, fuel cell bus</t>
-        </is>
-      </c>
-      <c r="I371" t="inlineStr">
-        <is>
-          <t xml:space="preserve">electricity storage capacity, Li-ion, LTO, high power, fuel cell bus</t>
-        </is>
-      </c>
-    </row>
-    <row r="372">
-      <c r="A372" t="inlineStr">
-        <is>
-          <t xml:space="preserve">battery pack production, Li-ion, LTO, fuel cell bus, without controls</t>
-        </is>
-      </c>
-      <c r="B372">
-        <v>0.0684931506849315</v>
-      </c>
-      <c r="C372" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-      <c r="D372" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="F372" t="inlineStr">
-        <is>
-          <t>technosphere</t>
-        </is>
-      </c>
-      <c r="G372" t="inlineStr">
-        <is>
-          <t xml:space="preserve">battery pack, Li-ion, LTO, fuel cell bus, without controls</t>
-        </is>
-      </c>
-      <c r="I372" t="inlineStr">
-        <is>
-          <t xml:space="preserve">battery pack, Li-ion, LTO, fuel cell bus, without controls</t>
-        </is>
-      </c>
-    </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery monitoring and central control system production, Li-ion, NMC955</t>
-        </is>
-      </c>
-      <c r="B373">
-        <v>0.0684931506849315</v>
-      </c>
-      <c r="C373" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-      <c r="D373" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="F373" t="inlineStr">
-        <is>
-          <t>technosphere</t>
-        </is>
-      </c>
-      <c r="G373" t="inlineStr">
-        <is>
-          <t xml:space="preserve">battery monitoring and central control system, Li-ion, NMC955</t>
-        </is>
-      </c>
-      <c r="I373" t="inlineStr">
-        <is>
-          <t xml:space="preserve">battery monitoring and central control system, Li-ion, NMC955</t>
+          <t xml:space="preserve">type</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t xml:space="preserve">processwithreferenceproduct</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H375" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I375" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t xml:space="preserve">market for electricity storage capacity, battery, lithium-ion, lto, high power, fuel cell bus</t>
+        </is>
+      </c>
+      <c r="B376">
+        <v>1</v>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t xml:space="preserve">electricity storage capacity, Li-ion, LTO, high power, fuel cell bus</t>
+        </is>
+      </c>
+      <c r="I376" t="inlineStr">
+        <is>
+          <t xml:space="preserve">electricity storage capacity, Li-ion, LTO, high power, fuel cell bus</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t xml:space="preserve">battery pack production, lithium-ion, lto, fuel cell bus, without controls</t>
+        </is>
+      </c>
+      <c r="B377">
+        <v>0.0684931506849315</v>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t xml:space="preserve">battery pack, Li-ion, LTO, fuel cell bus, without controls</t>
+        </is>
+      </c>
+      <c r="I377" t="inlineStr">
+        <is>
+          <t xml:space="preserve">battery pack, Li-ion, LTO, fuel cell bus, without controls</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t xml:space="preserve">battery monitoring and central control system production, lithium-ion, nmc955</t>
+        </is>
+      </c>
+      <c r="B378">
+        <v>0.0684931506849315</v>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G378" t="inlineStr">
+        <is>
+          <t xml:space="preserve">battery monitoring and central control system, Li-ion, NMC955</t>
+        </is>
+      </c>
+      <c r="I378" t="inlineStr">
+        <is>
+          <t xml:space="preserve">battery monitoring and central control system, Li-ion, NMC955</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
           <t>market for used Li-ion battery</t>
         </is>
       </c>
-      <c r="B374">
+      <c r="B379">
         <v>-17.360410958904108</v>
       </c>
-      <c r="C374" t="inlineStr">
+      <c r="C379" t="inlineStr">
         <is>
           <t>GLO</t>
         </is>
       </c>
-      <c r="D374" t="inlineStr">
+      <c r="D379" t="inlineStr">
         <is>
           <t>kilogram</t>
         </is>
       </c>
-      <c r="F374" t="inlineStr">
+      <c r="F379" t="inlineStr">
         <is>
           <t>technosphere</t>
         </is>
       </c>
-      <c r="G374" t="inlineStr">
+      <c r="G379" t="inlineStr">
         <is>
           <t>used Li-ion battery</t>
         </is>
       </c>
-      <c r="I374" t="inlineStr">
+      <c r="I379" t="inlineStr">
         <is>
           <t>used Li-ion battery</t>
         </is>
@@ -8101,7 +8161,7 @@
     <row r="11" spans="1:14" ns3:dyDescent="0.2">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">market for battery cell, Li-ion, LFP, including end-of-life treatment</t>
+          <t xml:space="preserve">market for battery cell, lithium-ion, lfp, including end-of-life treatment</t>
         </is>
       </c>
       <c r="B11" s="7">
@@ -8147,7 +8207,7 @@
     <row r="12" spans="1:14" ns3:dyDescent="0.2">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery pack component production and end-of-life treatment, Li-ion, LFP, without cells and controls</t>
+          <t xml:space="preserve">battery pack component production and end-of-life treatment, lithium-ion, lfp, without cells and controls</t>
         </is>
       </c>
       <c r="B12" s="7">
@@ -8200,7 +8260,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery monitoring and central control system production, Li-ion, LFP</t>
+          <t xml:space="preserve">battery monitoring and central control system production, lithium-ion, lfp</t>
         </is>
       </c>
       <c r="B13">
@@ -8357,7 +8417,7 @@
     <row r="24" spans="1:14" ns3:dyDescent="0.2">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">market for battery cell, Li-ion, NMC111, including end-of-life treatment</t>
+          <t xml:space="preserve">market for battery cell, lithium-ion, nmc111, including end-of-life treatment</t>
         </is>
       </c>
       <c r="B24" s="3">
@@ -8403,7 +8463,7 @@
     <row r="25" spans="1:14" ns3:dyDescent="0.2">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery pack component production and end-of-life treatment, Li-ion, NMC111, without cells and controls</t>
+          <t xml:space="preserve">battery pack component production and end-of-life treatment, lithium-ion, nmc111, without cells and controls</t>
         </is>
       </c>
       <c r="B25" s="3">
@@ -8456,7 +8516,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery monitoring and central control system production, Li-ion, NMC111</t>
+          <t xml:space="preserve">battery monitoring and central control system production, lithium-ion, nmc111</t>
         </is>
       </c>
       <c r="B26">
@@ -8613,7 +8673,7 @@
     <row r="37" spans="1:14" ns3:dyDescent="0.2">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">market for battery cell, Li-ion, NMC532, including end-of-life treatment</t>
+          <t xml:space="preserve">market for battery cell, lithium-ion, nmc532, including end-of-life treatment</t>
         </is>
       </c>
       <c r="B37" s="3">
@@ -8659,7 +8719,7 @@
     <row r="38" spans="1:14" ns3:dyDescent="0.2">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery pack component production and end-of-life treatment, Li-ion, NMC532, without cells and controls</t>
+          <t xml:space="preserve">battery pack component production and end-of-life treatment, lithium-ion, nmc532, without cells and controls</t>
         </is>
       </c>
       <c r="B38" s="3">
@@ -8712,7 +8772,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery monitoring and central control system production, Li-ion, NMC532</t>
+          <t xml:space="preserve">battery monitoring and central control system production, lithium-ion, nmc532</t>
         </is>
       </c>
       <c r="B39">
@@ -8871,7 +8931,7 @@
     <row r="50" spans="1:14" ns3:dyDescent="0.2">
       <c r="A50" t="inlineStr">
         <is>
-          <t xml:space="preserve">market for battery cell, Li-ion, NMC622, including end-of-life treatment</t>
+          <t xml:space="preserve">market for battery cell, lithium-ion, nmc622, including end-of-life treatment</t>
         </is>
       </c>
       <c r="B50" s="3">
@@ -8917,7 +8977,7 @@
     <row r="51" spans="1:14" ns3:dyDescent="0.2">
       <c r="A51" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery pack component production and end-of-life treatment, Li-ion, NMC622, without cells and controls</t>
+          <t xml:space="preserve">battery pack component production and end-of-life treatment, lithium-ion, nmc622, without cells and controls</t>
         </is>
       </c>
       <c r="B51" s="3">
@@ -8970,7 +9030,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery monitoring and central control system production, Li-ion, NMC622</t>
+          <t xml:space="preserve">battery monitoring and central control system production, lithium-ion, nmc622</t>
         </is>
       </c>
       <c r="B52">
@@ -9130,7 +9190,7 @@
     <row r="63" spans="1:14" ns3:dyDescent="0.2">
       <c r="A63" t="inlineStr">
         <is>
-          <t xml:space="preserve">market for battery cell, Li-ion, NMC811, including end-of-life treatment</t>
+          <t xml:space="preserve">market for battery cell, lithium-ion, nmc811, including end-of-life treatment</t>
         </is>
       </c>
       <c r="B63" s="3">
@@ -9176,7 +9236,7 @@
     <row r="64" spans="1:14" ns3:dyDescent="0.2">
       <c r="A64" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery pack component production and end-of-life treatment, Li-ion, NMC811, without cells and controls</t>
+          <t xml:space="preserve">battery pack component production and end-of-life treatment, lithium-ion, nmc811, without cells and controls</t>
         </is>
       </c>
       <c r="B64" s="3">
@@ -9229,7 +9289,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery monitoring and central control system production, Li-ion, NMC811</t>
+          <t xml:space="preserve">battery monitoring and central control system production, lithium-ion, nmc811</t>
         </is>
       </c>
       <c r="B65">
@@ -9386,7 +9446,7 @@
     <row r="76" spans="1:14" ns3:dyDescent="0.2">
       <c r="A76" t="inlineStr">
         <is>
-          <t xml:space="preserve">market for battery cell, Li-ion, NMC955, including end-of-life treatment</t>
+          <t xml:space="preserve">market for battery cell, lithium-ion, nmc955, including end-of-life treatment</t>
         </is>
       </c>
       <c r="B76" s="3">
@@ -9432,7 +9492,7 @@
     <row r="77" spans="1:14" ns3:dyDescent="0.2">
       <c r="A77" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery pack component production and end-of-life treatment, Li-ion, NMC955, without cells and controls</t>
+          <t xml:space="preserve">battery pack component production and end-of-life treatment, lithium-ion, nmc955, without cells and controls</t>
         </is>
       </c>
       <c r="B77" s="3">
@@ -9485,7 +9545,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery monitoring and central control system production, Li-ion, NMC955</t>
+          <t xml:space="preserve">battery monitoring and central control system production, lithium-ion, nmc955</t>
         </is>
       </c>
       <c r="B79">

--- a/premise/data/additional_inventories/lci-battery-capacity.xlsx
+++ b/premise/data/additional_inventories/lci-battery-capacity.xlsx
@@ -4276,9 +4276,9 @@
       </c>
     </row>
     <row r="189" spans="1:11" ht="16" ns3:dyDescent="0.2">
-      <c r="A189" s="6" t="inlineStr">
-        <is>
-          <t>market for battery capacity, ASSB, polymer</t>
+      <c r="A189" t="inlineStr" s="6">
+        <is>
+          <t xml:space="preserve">market for battery capacity, all-solid-state battery, polymer</t>
         </is>
       </c>
       <c r="B189">
@@ -4298,9 +4298,9 @@
       </c>
     </row>
     <row r="190" spans="1:11" ht="16" ns3:dyDescent="0.2">
-      <c r="A190" s="6" t="inlineStr">
-        <is>
-          <t>market for battery capacity, ASSB, oxidic</t>
+      <c r="A190" t="inlineStr" s="6">
+        <is>
+          <t xml:space="preserve">market for battery capacity, all-solid-state battery, oxidic</t>
         </is>
       </c>
       <c r="B190">
@@ -4380,9 +4380,9 @@
       </c>
     </row>
     <row r="194" spans="1:11" ht="16" ns3:dyDescent="0.2">
-      <c r="A194" s="5" t="inlineStr">
-        <is>
-          <t>market for battery capacity, ASSB, sulfidic</t>
+      <c r="A194" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">market for battery capacity, all-solid-state battery, sulfidic</t>
         </is>
       </c>
       <c r="B194">
@@ -4660,9 +4660,9 @@
       </c>
     </row>
     <row r="213" spans="1:6" ht="16" ns3:dyDescent="0.2">
-      <c r="A213" s="6" t="inlineStr">
-        <is>
-          <t>market for battery capacity, ASSB, polymer</t>
+      <c r="A213" t="inlineStr" s="6">
+        <is>
+          <t xml:space="preserve">market for battery capacity, all-solid-state battery, polymer</t>
         </is>
       </c>
       <c r="B213">
@@ -4682,9 +4682,9 @@
       </c>
     </row>
     <row r="214" spans="1:6" ht="16" ns3:dyDescent="0.2">
-      <c r="A214" s="6" t="inlineStr">
-        <is>
-          <t>market for battery capacity, ASSB, oxidic</t>
+      <c r="A214" t="inlineStr" s="6">
+        <is>
+          <t xml:space="preserve">market for battery capacity, all-solid-state battery, oxidic</t>
         </is>
       </c>
       <c r="B214">
@@ -4764,9 +4764,9 @@
       </c>
     </row>
     <row r="218" spans="1:6" ht="16" ns3:dyDescent="0.2">
-      <c r="A218" s="5" t="inlineStr">
-        <is>
-          <t>market for battery capacity, ASSB, sulfidic</t>
+      <c r="A218" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">market for battery capacity, all-solid-state battery, sulfidic</t>
         </is>
       </c>
       <c r="B218">
@@ -5044,9 +5044,9 @@
       </c>
     </row>
     <row r="237" spans="1:11" ht="16" ns3:dyDescent="0.2">
-      <c r="A237" s="6" t="inlineStr">
-        <is>
-          <t>market for battery capacity, ASSB, polymer</t>
+      <c r="A237" t="inlineStr" s="6">
+        <is>
+          <t xml:space="preserve">market for battery capacity, all-solid-state battery, polymer</t>
         </is>
       </c>
       <c r="B237">
@@ -5066,9 +5066,9 @@
       </c>
     </row>
     <row r="238" spans="1:11" ht="16" ns3:dyDescent="0.2">
-      <c r="A238" s="6" t="inlineStr">
-        <is>
-          <t>market for battery capacity, ASSB, oxidic</t>
+      <c r="A238" t="inlineStr" s="6">
+        <is>
+          <t xml:space="preserve">market for battery capacity, all-solid-state battery, oxidic</t>
         </is>
       </c>
       <c r="B238">
@@ -5148,9 +5148,9 @@
       </c>
     </row>
     <row r="242" spans="1:11" ht="16" ns3:dyDescent="0.2">
-      <c r="A242" s="5" t="inlineStr">
-        <is>
-          <t>market for battery capacity, ASSB, sulfidic</t>
+      <c r="A242" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">market for battery capacity, all-solid-state battery, sulfidic</t>
         </is>
       </c>
       <c r="B242">
@@ -5428,9 +5428,9 @@
       </c>
     </row>
     <row r="261" spans="1:6" ht="16" ns3:dyDescent="0.2">
-      <c r="A261" s="6" t="inlineStr">
-        <is>
-          <t>market for battery capacity, ASSB, polymer</t>
+      <c r="A261" t="inlineStr" s="6">
+        <is>
+          <t xml:space="preserve">market for battery capacity, all-solid-state battery, polymer</t>
         </is>
       </c>
       <c r="B261">
@@ -5450,9 +5450,9 @@
       </c>
     </row>
     <row r="262" spans="1:6" ht="16" ns3:dyDescent="0.2">
-      <c r="A262" s="6" t="inlineStr">
-        <is>
-          <t>market for battery capacity, ASSB, oxidic</t>
+      <c r="A262" t="inlineStr" s="6">
+        <is>
+          <t xml:space="preserve">market for battery capacity, all-solid-state battery, oxidic</t>
         </is>
       </c>
       <c r="B262">
@@ -5532,9 +5532,9 @@
       </c>
     </row>
     <row r="266" spans="1:6" ht="16" ns3:dyDescent="0.2">
-      <c r="A266" s="5" t="inlineStr">
-        <is>
-          <t>market for battery capacity, ASSB, sulfidic</t>
+      <c r="A266" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">market for battery capacity, all-solid-state battery, sulfidic</t>
         </is>
       </c>
       <c r="B266">
